--- a/Data/Piura/noticias_piura_20260904_20260911.xlsx
+++ b/Data/Piura/noticias_piura_20260904_20260911.xlsx
@@ -466,21 +466,21 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Ministro de Defensa promete mayor velocidad en la descolmatación del río Piura</t>
+          <t>Contraloría: Obra recién culminada presenta signos de deterioro prematuro en Universidad Nacional de Frontera</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>El ministro de Defensa, Rafael Belaunde , aseguró que el Ejército incrementará la velocidad de los trabajos de descolmatación del río Piura , como parte de las acciones preventivas frente al eventual impacto del fenómeno El Niño en la región. El titular del sector supervisó el despliegue de personal y maquinaria pesada en dos de los puntos considerados críticos. Durante su visita al puente Bolognesi, en Piura, Belaunde verificó las labores destinadas a retirar los sedimentos acumulados en el cauce. Según explicó, existe confianza en que los trabajos avanzarán al ritmo requerido para cumplir con las metas establecidas. “Estoy confiado en que el Ejército avanzará en la velocidad que se le ha requerido”, afirmó el ministro durante la inspección. ¿Dónde se realizan los trabajos en el río Piura? Las labores de limpieza y recuperación del cauce se ejecutan en siete puntos críticos del río Piura , en un tramo de aproximadamente 15.5 kilómetros comprendido entre los puentes Independencia y Bolognesi. Para esta operación se ha desplegado personal especializado del Ejército y maquinaria pesada destinada principalmente a retirar el material acumulado en diferentes sectores del afluente. La intervención busca mejorar las condiciones del cauce ante la posibilidad de lluvias intensas y un incremento del caudal. En el sector del puente Bolognesi trabaja el Batallón de Ingeniería de Construcción N.° 1 “Jazán”, unidad trasladada desde la región Amazonas. Para cumplir con su misión, cuenta con 13 camiones volquetes, dos excavadoras, dos tractores oruga y un cargador frontal . La meta establecida para este punto es intervenir aproximadamente dos kilómetros del cauce del río Piura . El retiro de los sedimentos permitirá recuperar parte de la capacidad hidráulica del río en una zona considerada estratégica para la prevención de inundaciones. Ejército trabaja en el puente Independencia El ministro de Defensa también llegó hasta el puente Independencia para inspeccionar los trabajos que se desarrollan en este sector. Las acciones están a cargo del Batallón de Ingeniería de Combate N.° 211, proveniente de Tumbes. Esta unidad dispone de dos tractores oruga, una excavadora, un cargador frontal y un volquete . De acuerdo con la planificación presentada durante la supervisión, sus trabajos tienen como objetivo intervenir aproximadamente 1.8 kilómetros del cauce. La presencia de maquinaria en ambos sectores forma parte de una operación de ingeniería de mayor escala. Para el Gobierno, la recuperación del cauce constituye una de las medidas preventivas frente a un eventual escenario de lluvias asociadas al fenómeno El Niño. Piura recibirá 600 toneladas de ayuda no alimentaria Durante su visita, el ministro de Defensa también informó sobre las acciones de preparación ante una eventual emergencia por lluvias. Según indicó, alrededor de 200 toneladas de ayuda no alimentaria ya han llegado a Piura como parte de un envío mayor. La ayuda es gestionada mediante el Instituto Nacional de Defensa Civil (Indeci) y forma parte de un total de 600 toneladas que serán trasladadas y almacenadas en un hangar ubicado en territorio piurano. Según declaraciones brindadas a TVPerú, el objetivo es contar con recursos suficientes para atender a unas 100,000 familias , lo que representa cerca de medio millón de personas ante un escenario de emergencia. “La idea es tener capacidad para atender a 100,000 familias. Eso es algo cercano al medio millón de personas”, explicó Belaunde, quien añadió que progresivamente también se incorporará ayuda alimentaria. ¿Por qué es importante la descolmatación del río Piura? La descolmatación consiste en retirar sedimentos, tierra y otros materiales acumulados en el cauce de un río. En el caso del río Piura , estas labores tienen especial importancia durante la temporada de lluvias, debido al riesgo de incremento del caudal y posibles desbordes. La recuperación de la capacidad del cauce forma parte de las medidas de prevención frente a inundaciones. En Piura, una región que históricamente ha enfrentado episodios de lluvias intensas, mantener libres los sectores críticos permite mejorar las condiciones para el desplazamiento del agua. De acuerdo con el Instituto Nacional de Defensa Civil (Indeci) , las acciones de preparación y prevención son fundamentales para reducir los riesgos y mejorar la capacidad de respuesta ante emergencias. Una operación que abarca 15.5 kilómetros La intervención del Ejército contempla un tramo total de 15.5 kilómetros del río Piura , distribuido en siete puntos críticos ubicados entre los puentes Independencia y Bolognesi. La operación requiere el desplazamiento de unidades de ingeniería, operadores y maquinaria especializada. Para las autoridades, el avance de estos trabajos será especialmente importante conforme se acerquen los periodos de mayor riesgo de lluvias. La incorporación de nuevos equipos, anunciada por el Ministerio de Defensa, busca acelerar el retiro de los sedimentos y cumplir con las metas establecidas para cada sector. La información sobre las acciones de prevención y respuesta ante emergencias puede consultarse en los canales oficiales del Ministerio de Defensa y del Indeci .</t>
+          <t>La Contraloría General de la República (CGR) evidenció que la obra de ampliación del servicio de aulas de la facultad de Ingeniería Económica de la Universidad Nacional de Frontera, en la provincia de Sullana, presenta signos de deterioro prematuro pese a que los trabajos fueron recibidos en enero de este año. Esta situación genera el riesgo de afectar la calidad, operatividad y vida útil de este proyecto que tiene una inversión superior a los S/ 14 millones. En el Informe de Hito de Control n.° 11384-2026-CG/GRPI-SCC (periodo de evaluación del 12 al 18 de agosto de 2026), se identificaron diversas deficiencias en la infraestructura de los bloques I-A, I-B y II, entre ellas, puertas de madera desniveladas, falta de agua en inodoros y lavatorios, y tapajuntas de acero inoxidable con fijación deficiente en juntas de dilatación. En los servicios higiénicos del cuarto piso se constató que algunos inodoros permanecen inoperativos por falla en el sistema de abastecimiento de agua, mientras que el lavamanos destinado a personas con discapacidad presenta insuficiente presión. Además, se observaron aberturas en los tapajuntas que podrían facilitar el ingreso de humedad, residuos y agentes contaminantes. También se detectaron problemas en ambientes administrativos y académicos: una de las cuatro unidades evaporadoras del sistema de aire acondicionado de la sala de cómputo se encuentra inoperativa y varios lavatorios no cuentan con flujo de agua. En la sala de impresiones se verificó el desprendimiento de una baldosa del techo que dejó un sensor de humo suspendido por sus cables, además de evidencias de humedad y moho. En la actual área de grados y títulos y responsabilidad social se constató la ausencia de una puerta de vidrio, situación que deja expuestos equipos, mobiliario y documentación. A ello se suman el desprendimiento y agrietamiento del sellador de una escalera de madera, deformaciones en elementos de la pérgola en una plazoleta y tapas de concreto de canaletas pluviales deterioradas y desalineadas, generando riesgos para los usuarios. Asimismo, se constató que el ascensor del pabellón permanece fuera de servicio, pese a que la Unidad Ejecutora de Inversiones había requerido al contratista la subsanación de la falla en el marco de la garantía de obra y posteriormente realizó gestiones para evaluar técnicamente el problema. La inoperatividad del equipo obliga a estudiantes, docentes y personal a utilizar exclusivamente las escaleras y constituye una barrera crítica para las personas con movilidad reducida o discapacidad. Durante la inspección se verificó una diferencia entre los equipos adquiridos para el proyecto y los encontrados físicamente en el pabellón de la Facultad de Ingeniería Económica. De los 26 monitores con procesador integrado previstos para el proyecto, solo 12 fueron ubicados, uno en cada una de las aulas. Del mismo modo, se constató que únicamente ocho equipos cuentan con actas de entrega al área usuaria, pese a que la documentación de la entidad acredita la adquisición de los 26 monitores. Esta situación genera el riesgo de que 14 equipos no estén siendo utilizados para el fin para el cual fueron adquiridos, se encuentren en desuso o incluso se haya producido su pérdida. La obra se inició en noviembre de 2023 y debió culminar al siguiente año. Recién en enero de este año se suscribió el acta de recepción. El informe fue notificado al titular de la entidad para que adopte las acciones que correspondan, en el marco de sus competencias y obligaciones en la gestión institucional.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>https://eltiempo.pe/local/ministro-de-defensa-promete-mayor-velocidad-en-la-descolmatacion-del-rio-piura/</t>
+          <t>https://eltiempo.pe/local/contraloria-obra-recien-culminada-presenta-signos-de-deterioro-prematuro-en-universidad-nacional-de-frontera/</t>
         </is>
       </c>
     </row>
@@ -491,55 +491,46 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>¿Quién responde por los 106 muertos en la región Piura? Nuevo asesinato se consuma en Castilla</t>
+          <t>Más de 4 mil casos de violencia contra mujeres y familiares genera preocupación en Piura</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>La racha criminal sigue en aumento en la región, luego que un joven técnico de celulares fuera asesinado de tres balazos en la cabeza y rostro por un gatillero, que disparó con una pasmosa frialdad, delante de dos amigos, para luego huir en un auto blanco. El asesinato de José Fernando Castillo Quevedo, de 24 años, ocurrió cerca de las nueve de la noche del pasado martes frente al bar “Pikaflor”, ubicado en la Asociación Villa Universitaria, sector norteste de Castilla. Hasta ese lugar llegó la Policía para iniciar las investigaciones. ESCALOFRIANTE DATA Con este episodio escaló a 106 los asesinatos ocurridos en lo que va del año en la región, siendo la mayoría de casos por la modalidad de sicariato (o crimenes por encargo). Cabe resaltar que en 2025 se registraron 107 homicidios en el lapso de enero a setiembre. Cabe precisar que en menos de 72 horas han ocurrido siete homicidios: dos mujeres, un varón y un menor de 13 años en Sullana, otro caso en Talara. De igual manera uno en Paita Alta y el último registrado en Castilla, contra José Fernando Castillo. IMÁGENES CLAVES El asesinato del joven técnico de equipos móviles muestra el alto grado de peligrosidad que existe en las calles. Precisamente una cámara de seguridad muestra que ya no se puede confian en nadie, luego que en escena se observa a José Fernando Castillo platicando con dos personas, que serían amigos. Según las imágenes de las cámaras de seguridad, Castillo Quevedo y dos sujetos, en la vía públlica, observan un celular. De pronto, se aprecia la salida de un individuo desconocido para subir apuradamente a un automóvil blanco y dar arranque. TODOS SE CONOCÍAN En ese momento, se oberva la llegada de un gatillero que vestía polo verde y bermuda blu jeans, quien se acerca a los tres amigos y dispara tres veces contra José Fernando Castillo, luego con pistola en mano camina y sube al mencionado vehículo blanco. Del mismo modo se distingue que uno de los dos individuos, que estaba conversando con la víctima mortal abordó el mismo vehículo en el que huyó el atacante. La Policía continúa con las investigaciones para esclarecer el crimen, identificar a los involucrados y determinar las circunstancias del asesinato.</t>
+          <t>La violencia contra las mujeres y los integrantes del grupo familiar mantiene cifras preocupantes en Piura . Entre enero y julio de 2026, los Centros Emergencia Mujer (CEM) de la región atendieron 4,578 casos de violencia , de acuerdo con el último reporte del Programa Nacional Warmi Ñan del Ministerio de la Mujer y Poblaciones Vulnerables (MIMP). La cifra representa un incremento considerable respecto al reporte acumulado hasta junio, cuando se registraban 3,272 casos. En solo un mes se sumaron 1,306 nuevas atenciones, lo que evidencia la magnitud del problema que enfrentan mujeres, niñas, niños, adolescentes y otros integrantes de las familias en diferentes provincias de la región. Según el Programa Nacional Warmi Ñan , los CEM son servicios públicos especializados y gratuitos que brindan atención psicológica, social y legal a personas afectadas por hechos de violencia. Consulta aquí la información oficial de Warmi Ñan sobre los Centros Emergencia Mujer . Piura concentra la mayor cantidad de casos de violencia La provincia de Piura concentra la mayor cantidad de atenciones reportadas en la región, con 2,580 casos entre enero y julio. La distribución muestra que las situaciones de violencia llegan a diferentes puntos de atención y no se concentran únicamente en una institución. La comisaría de Piura atendió 735 víctimas, mientras que el centro de salud Santa Julia registró 547 casos. A estos se suman 435 atenciones en la comisaría de familia, 236 en la comisaría rural de Tambogrande, 231 en Catacaos, 208 en La Unión y 188 correspondientes al distrito de Piura. Después de la provincia de Piura aparecen Sullana, con 436 casos; Paita, con 420; Ayabaca, con 359; Talara, con 256; Morropón, con 252; Sechura, con 163; y Huancabamba, con 112 casos . ¿Quiénes son los principales afectados por la violencia en Piura? Del total de 4,578 casos atendidos en los primeros siete meses del año, 4,015 corresponden a mujeres , equivalente al 87.7 %. Los hombres representan 563 casos, es decir, el 12.3 % del total. El grupo de edad con mayor número de atenciones corresponde a personas de entre 18 y 59 años, con 3,067 casos , que representan el 67 % del registro regional. También preocupa la cantidad de menores afectados. Entre niñas, niños y adolescentes de 0 a 17 años se contabilizaron 1,294 casos , equivalentes al 28.3 %. En tanto, las personas adultas mayores de 60 años registraron 217 atenciones, que representan el 4.7 %. Estos datos muestran que la violencia no afecta únicamente a las parejas o a mujeres adultas. También alcanza a menores de edad y adultos mayores dentro del entorno familiar, lo que amplía el impacto social de este problema. Violencia psicológica encabeza los casos registrados La violencia psicológica es la modalidad que concentra la mayor cantidad de atenciones en la región Piura. De acuerdo con el reporte, se registraron 2,091 casos, equivalentes al 45.7 % del total. En segundo lugar aparece la violencia física , con 1,833 casos y una participación del 40 %. Le sigue la violencia sexual, que alcanzó 650 casos, equivalente al 14.2 %. Finalmente, se reportaron cuatro casos de violencia económica, que representan el 0.1 %. La distribución permite observar que las agresiones no siempre dejan lesiones visibles. La violencia psicológica representa casi la mitad de las atenciones registradas y puede manifestarse mediante amenazas, humillaciones, control, intimidación u otras conductas que afectan a la víctima. Piura registra un feminicidio y dos tentativas El reporte del Programa Nacional Warmi Ñan también registra hechos de mayor gravedad. Durante el periodo analizado se confirmó un caso de feminicidio en la provincia de Huancabamba . Asimismo, fueron reportadas dos tentativas de feminicidio , ocurridas en las provincias de Piura y Morropón. Estos casos reflejan situaciones de violencia extrema que requieren una intervención rápida de las instituciones responsables de proteger a las víctimas. De acuerdo con el MIMP, el Programa Nacional Warmi Ñan desarrolla servicios de atención, protección y prevención frente a la violencia contra las mujeres y los integrantes del grupo familiar en todo el país. Conoce los servicios oficiales del Programa Nacional Warmi Ñan . Adolescentes y embarazo también forman parte del panorama El informe incorpora además un indicador relacionado con las adolescentes de la región. El 10.6 % de las mujeres de 15 a 19 años en Piura ha tenido un hijo o ha estado embarazada por primera vez . Del total, el 9.9 % ya son madres, mientras que el 0.7 % estuvo embarazada por primera vez. Este indicador forma parte del contexto social que acompaña las cifras de violencia y permite observar la situación de adolescentes y jóvenes en la región. Warmi Ñan cuenta con 20 Centros Emergencia Mujer en Piura Para atender esta problemática, la región cuenta con 20 Centros Emergencia Mujer . De ellos, 10 funcionan en comisarías y brindan atención durante las 24 horas del día. El despliegue también incluye el Servicio de Atención Rural (SAR) , que atendió 117 casos en comunidades de Sechura y Huancabamba. Este servicio busca acercar la atención especializada a poblaciones ubicadas en zonas rurales y con mayores dificultades para acceder a los servicios institucionales. Asimismo, el Hogar de Refugio Temporal recibió a 61 personas en situación de riesgo severo: 32 mujeres y 29 hijos o acompañantes. Estos espacios permiten brindar protección y atención integral a personas que necesitan salir de un entorno considerado peligroso. Línea 100 recibió más de 3 mil consultas en Piura La atención frente a la violencia también se realiza mediante servicios remotos. Entre enero y julio de 2026, la Línea 100 registró 3,375 consultas telefónicas en la región. Del total de consultas, el 36.4 % estuvo relacionado con violencia física, el 32.8 % con violencia psicológica y el 7.3 % con violencia sexual. El servicio permite orientar a las personas afectadas o a quienes conocen un caso de violencia. Por su parte, el Chat 100 atendió 153 consultas relacionadas principalmente con la identificación de situaciones de riesgo en relaciones de pareja o noviazgo. Según el Ministerio de la Mujer y Poblaciones Vulnerables, la Línea 100 brinda orientación y consejería de manera gratuita las 24 horas del día. Revisa la información oficial del MIMP sobre la Línea 100 y los servicios de atención . ¿Dónde buscar ayuda ante un caso de violencia? Las personas que atraviesen una situación de violencia o conozcan un caso pueden acudir a un Centro Emergencia Mujer para recibir orientación especializada. También pueden comunicarse con la Línea 100 para solicitar información y apoyo. Los CEM brindan atención integral y gratuita, incluyendo orientación legal, atención psicológica y acompañamiento social, de acuerdo con las características de cada caso. Consulta los servicios y datos oficiales de Warmi Ñan .</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>https://eltiempo.pe/local/quien-responde-por-los-106-muertos-en-la-region-piura-nuevo-asesinato-se-consuma-en-castilla/</t>
+          <t>https://eltiempo.pe/local/mas-de-4-mil-casos-de-violencia-contra-mujeres-y-familiares-genera-preocupacion-en-piura/</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Andina</t>
+          <t>El Tiempo</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Productores de Piura mejorarán producción de forraje caprino con ayuda tecnológica de INIA</t>
+          <t>Sí habrá mango, pero en menor cantidad: La anomalía en las temperaturas no permitieron una adecuada floración de las plantaciones</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>La actividad, desarrollada a través de la Estación Experimental Agraria El Chira (EEA Chira), como parte de las acciones del Proyecto Caprinos Procap, está dirigida a productores de la Asociación Agraria Alfa y Omega, con el propósito de fortalecer el manejo integral del sistema productivo, promoviendo una adecuada relación entre la conservación de la fertilidad del suelo, el establecimiento de especies forrajeras y la disponibilidad de alimento de calidad para los animales.
-Durante el desarrollo de las jornadas técnicas, especialistas del INIA capacitaron a los productores en la selección y el uso de semillas de alta calidad, evaluación de la fertilidad del suelo, preparación del terreno, elaboración de planes de fertilización, establecimiento y manejo de pastos mejorados, producción y aplicación de abonos orgánicos, así como en prácticas orientadas a conservar la capacidad productiva del suelo.
-La región Piura es considerada una de las principales zonas de producción caprina del país.
-Cuenta con más de 317 mil cabezas de ganado caprino, entre animales criollos y razas especializadas como Saanen y Anglo Nubian.
-Asimismo, alberga más de 2,25 millones de hectáreas de bosque seco que constituyen un ecosistema estratégico para el desarrollo de esta actividad pecuaria.
-A través de la aplicación adecuada de la tecnología transferida por el INIA, los productores mejorarán la eficiencia en el uso de los recursos productivos, incrementarán la disponibilidad de biomasa forrajera, favorecerán la calidad nutricional de la alimentación de los animales y reducirán riesgos asociados al deterioro del suelo, manejo inadecuado de cultivos y uso excesivo de insumos químicos.
-De esta manera, se busca contribuir progresivamente a mejores condiciones de producción de carne y leche caprina .
-Mediante el proyecto caprinos Procap, la EEA Chira del INIA ha realizado en la región Piura 305 inseminaciones artificiales en 21 cabras de productores beneficiarios, logrando hasta la fecha el nacimiento de 56 crías de la raza Anglo Nubian con alto valor genético, lo cual le permite desarrollar carne y leche de calidad para los diferentes procesos industriales.
-Más en Andina: ?? Lambayeque registra 3,998 casos confirmados de dengue, 1,440 probables y 13 defunciones asociadas a la enfermedad.
-La Geresa reforzó las acciones de prevención y control, especialmente en Chiclayo, La Victoria y Motupe.?? https://t.co/MjncOyjiFL pic.twitter.com/l13jzOYyy5 — Agencia Andina (@Agencia_Andina) September 10, 2026</t>
+          <t>El invierno cálido que se vivió en Piura dejó secuelas importantes en la agricultura piurana. Las altas temperaturas afectaron el proceso de floración de algunos cultivos como es el caso del mango, lo cual traerá consecuencias en la producción nacional que tiene destino Estados Unidos o Europa. De acuerdo a los especialistas, en la variedad de exportación del mango Kent la floración alcanzó un 30% en promedio entre las más de 33 mil hectáreas del valle de San Lorenzo en Tambogrande. De esta manera se podría tener un disminución de la producción con fines de exportación de más del 60%. Sin embargo, otras variedades como el mango criollo, Ataulfo o Edwards han tenido mejores resultados en la floración. “El año pasado la producción se contrajo un 20%. Ahora la situación se ha agudizado porque las anomalías de 4 y 5 grados en la temperatura impiden la producción de fitohormonas en el nivel adecuado para la floración. No hay una respuesta floral adecuada”, informó la doctora en agrometeorología, Ninell Dediós. De continuar las condiciones térmicas, lo siguiente serían problemas con el cuajado de la fruta que ha logrado generar. Asimismo, una lluvia en plena etapa de cosecha dañaría este proceso final antes de la exportación. Un similar impacto se tiene en cultivos como el limón (floración del 30%), arroz (plantas débiles por acelerado crecimiento ante el calor) y algodón (menor calidad de la fibra). En el campo Desde el lado de los productores aún existe una ligera esperanza de que este panorama pueda mejorar en las siguientes semanas. “Algunos productores dicen que la floración está en 20% y otros en 30%. Todavía no está todo culminado, ni vencido; hay una pequeña ventana de oportunidad. En un año relativamente bueno en el norte se producen 500 mil toneladas de mango, pero ahora que está en 30% [de la floración], nos quedarían unas 120 mil toneladas aproximadamente. Se estima una disminución del 70% de la producción en todas las variedades”, manifestó el expresidente de la Junta de Usuarios del valle de San Lorenzo, Darío Castillo. Seguro Para los agricultores, la expectativa es que se pueda aplicar el seguro agrario catastrófico frente a las pérdidas que sufrirán por efecto del impacto del clima. “El ministro ha sido claro, habló de que existe un seguro agrario catastrófico por cambio climático o un bono, pero es relativamente poco que no soluciona el problema. por una hectárea te dan 800 soles. Por una hectárea de mango se invierte arriba de 10 mil soles”, informó Castillo. Producción para mercado local ayudaría En declaraciones a un medio nacional, Milton Calle, productor de mango en Piura y Casma y propietario de la exportadora Boom Fruit, informó que la baja floración de las plantas de mango no significa necesariamente una caída significativa. “Pienso que vamos a tener una caída de alrededor de 60% en la producción, básicamente por El Niño”, señaló. En ese contexto, el país cerraría la campaña con entre 80.000 y 100.000 toneladas exportables, frente a las 240.000 toneladas registradas en la temporada anterior. Agregó que es posible que parte de la fruta que se destina al mercado local o a la industria de congelados podría irse hacia a la exportación para compensar parcialmente el menor volumen que se obtenga de los campos. De otro lado, Calle también mencionó que Brasil se vería beneficiado con mayores ventas en el mercado europeo por la caída de la producción en Ecuador y Perú.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>https://andina.pe/agencia/noticia-productores-piura-mejoraran-produccion-forraje-caprino-ayuda-tecnologica-inia-1091279.aspx</t>
+          <t>https://eltiempo.pe/local/si-habra-mango-pero-en-menor-cantidad-la-anomalia-en-las-temperaturas-no-permitieron-una-adecuada-floracion-de-las-plantaciones/</t>
         </is>
       </c>
     </row>
@@ -550,34 +541,29 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Quintal de café podría cotizarse en US$ 5,000 en tercera Subasta Internacional</t>
+          <t>Lluvias ligeras a moderadas prevista en la selva ponen en riesgo a 160 distritos</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>“Estas subastas han tenido resultados muy importantes para los caficultores.
-El año pasado, cuando la Bolsa de Valores cotizada a 140 dólares el quintal de café, durante la subasta se ha alcanzado precios de hasta 2,350 dólares el quintal, lo que nos da una idea de la importancia de este producto para el desarrollo de muchas familias caficultoras”, manifestó.
-Jorge detalló que se espera la participación de empresarios de Estados Unidos, Francia, Alemania, Ucrania, entre otros países.
-“Esta tercera subasta contará con un promedio de 27 contenedores , aproximadamente; lo que equivale a 17 millones de dólares en negociaciones”, precisó.
-En ese sentido, el empresario cafetalero exhortó a las autoridades del sector agrario que consideren un presupuesto especial en sus calendarios de actividades para el 2027 para esta subasta internacional.
-Beneficios El coordinador de la tercera Subasta Internacional de Finos Cafés y Chocolates Grano de Oro 2026 afirmó que uno de los beneficios de la subasta es que los productores tendrán la oportunidad de mostrar la calidad de sus cafés que, dependiendo de su fineza, podrán participar del evento con un precio base.
-“Ese pequeño agricultor que cultiva y cosecha en las zonas más profundas y altas de la selva, siendo precisamente él quien produce finos cafés, tienen la opción de que su producto sea subastado a los mejores precios internacionales”, precisó Jorge.
-Agregó que la subasta mostrará la calidad del café que se produce en el Perú.
-“El café que generalmente se exporta tiene un puntaje de 82.
-Un café de mayor puntaje (86 puntos) es considerado café fino y si ese puntaje supera los 90 puntos es considerando un café extremadamente fino”, detalló.
-Jorge aseguró que estos productos son cosechados por agricultores que se encuentran en las partes altas.
-“Esas buenas altitudes, microclimas, suelos, variedades y un buen proceso juegan un papel importante en la calidad del café”, puntualizó.
-Más en Andina: ???? Productores caprinos de Piura fortalecen sus capacidades para mejorar la producción de forraje de alto valor nutricional con tecnologías transferidas por el INIA.
-La capacitación incluyó manejo de semillas, fertilización, pastos mejorados, abonos orgánicos y conservación del… pic.twitter.com/nSfOYK5Q83 — Agencia Andina (@Agencia_Andina) September 10, 2026</t>
+          <t>Según dicho documento, San Martín es el departamento que presenta la mayor cantidad de distritos en riesgo muy alto, con 16 jurisdicciones, seguido de Amazonas (5), Ayacucho (5), Pasco (3), Cajamarca (2), Junín (2), Puno (2) y Loreto (1).
+En tanto , 124 distritos de estas mismas regiones, además de Cusco, Huánuco y Ucayali se encuentran en riesgo alto.
+Para conocer cuáles son los distritos involucrados, ingrese aquí: https://docs.google.com/spreadsheets/d/1QznLMU9e11ZMkB7Z7jWsK8nwiUkMw9UT/edit?gid=1755029279#gid=1755029279 El Senamhi añade en su aviso, que la lluvia estará acompañada de descargas eléctricas y ráfagas de viento con velocidades cercanas a los 45 km/h.
+Para el domingo 13 de setiembre se prevén acumulados pluviales cercanos a los 36 mm/día en la selva norte, próximos a 35 mm/día en la selva centro y alrededor de los 50 mm/día en la selva sur.
+Ante esta situación, el Instituto Nacional de Defensa Civil (Indeci) exhorta a las autoridades de los gobiernos locales y/o regionales revisar que las rutas de evacuación estén despejadas y debidamente señalizadas, para dirigir a la población hacia una zona segura y alejada del cauce de ríos o quebradas.
+También verificar la disponibilidad de los centros de salud, compañías de bomberos y comisarías en la jurisdicción en caso de presentarse una emergencia.
+Del mismo modo, recomienda a la población proteger y reforzar el techo de sus viviendas, así como establecer un sistema de alerta temprana usando silbatos, campanas, alarmas, sirenas o altoparlantes, en coordinación con las autoridades locales.
+Más en Andina: ?? Intensifican trabajos preventivos en el río Piura ante riesgo de desbordes.
+La ANA interviene 2 km de la margen derecha en Malingas para proteger a 30 familias y unas 80 hectáreas de cultivos.?? https://t.co/pHt1feyULt pic.twitter.com/dNAQiiBqHZ — Agencia Andina (@Agencia_Andina) September 10, 2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>https://andina.pe/agencia/noticia-quintal-cafe-podria-cotizarse-5000-tercera-subasta-internacional-1091285.aspx</t>
+          <t>https://andina.pe/agencia/noticia-lluvias-ligeras-a-moderadas-prevista-la-selva-ponen-riesgo-a-160-distritos-1091335.aspx</t>
         </is>
       </c>
     </row>
@@ -592,87 +578,10 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>PIAS Terrestres llevarán servicios médicos a comunidades altoandinas de Arequipa</t>
+          <t>Piura: Gobierno se anticipa a El Niño y fortalece la capacidad de respuesta de EsSalud</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
-        <is>
-          <t>Del 10 al 11 de setiembre, esta intervención coordinada con el Ejército del Perú, llegará a los distritos de San Antonio de Chuca y Yanque, respectivamente, para brindar atenciones médicas en diversas especialidades, priorizando el cuidado de la salud de niños, gestantes y adultos mayores.
-A través del Minsa Móvil, las personas accederán a servicios de pediatría, dermatología, medicina física y rehabilitación, ginecología, oftalmología y otorrinolaringología, entre otros; mientras que la Gerencia de Salud también atenderá en medicina general, enfermería, obstetricia, psicología, odontología y el tamizaje para descarte de anemia, especialidades que fortalecerán el derecho a la salud en las alturas de la región arequipeña.
-El director ejecutivo del Programa PAIS, Javier Carmelo, llegó hasta San Antonio de Chuca para supervisar la jornada de atenciones que más de 80 profesionales realizarán durante ambos días.
-“Llegar a estas comunidades significa acercar el Estado a quienes más lo necesitan.
-La población no tendrá que recorrer grandes distancias ni asumir gastos que afecten la economía de sus hogares para acceder no solo a estos servicios médicos, sino también a otros que fortalezcan su desarrollo social, económico y productivo”, destacó.
-Además de los servicios de salud, la población realizará de manera gratuita diversos trámites de identidad, accederán a los servicios del Banco de la Nación, recibirán orientación de la Defensoría del Pueblo, servicios registrales y asistencia legal, así como información sobre los programas sociales del Midis .
-También se brindará asistencia técnica productiva , atención en casos de orfandad, la actualización socioeconómica de hogares y servicios dirigidos a personas con discapacidad, entre otras importantes atenciones.
-Lea también: PIAS Aérea acerca servicios médicos y sociales a comunidades de Ucayali Esta es la novena campaña de las PIAS Terrestres que el Programa PAIS del Midis gestiona en el presente año.
-Durante ambos días se desplegarán entidades públicas y privadas para brindar de manera conjunta más de 2000 atenciones que contribuyan a mejorar la calidad de vida de la población.
-Esta campaña forma parte de un recorrido que ya ha acercado servicios públicos a comunidades rurales de La Libertad, Lima, Puno, Amazonas, Cajamarca, Tacna y Cusco.
-La décima y última intervención se desarrollará en octubre en centros poblados de Piura.
-En conjunto, las diez intervenciones prevén superar las 24 000 atenciones y beneficiar a más de 6000 personas en distintas regiones del país.</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>https://andina.pe/agencia/noticia-pias-terrestres-llevaran-servicios-medicos-a-comunidades-altoandinas-arequipa-1091290.aspx</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Andina</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="n">
-        <v>46275</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Midis fortalece su presencia en el territorio para enfrentar los efectos de El Niño</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>En esta ocasión, los viceministros de Políticas y Evaluación Social, Carlos Salazar, y de Prestaciones Sociales, Alejandro Afuso, lideraron acciones de supervisión en Piura y Áncash.
-En ambas regiones, los funcionarios constataron las medidas preventivas que vienen implementando los gobiernos regionales y los programas sociales “para proteger a la población más vulnerable y garantizar la continuidad de los servicios esenciales ante posibles emergencias”.
-El viceministro Salazar supervisó las condiciones de almacenamiento de los productos entregados por el Programa de Alimentación Escolar (PAE) y el servicio que se brinda en la I.E.
-N°14011 Nuestra Señora del Pilar, ubicada en el distrito de Veintiséis de Octubre, en Piura.
-Esta institución cuenta con un almacén y una cocina implementados por Foncodes, a través del Programa de Mejoramiento y Acondicionamiento de Cocina y Almacén (MACA).
-Por su parte, el viceministro Afuso visitó el Tambo Cordillera Blanca, en Áncash, donde supervisó el funcionamiento de esta plataforma del programa PAIS y las acciones de articulación que desarrolla para acercar los servicios del Estado a las poblaciones rurales y dispersas.
-El tambo atiende a 49 centros poblados y beneficia a 3047 personas; además, registró 9065 atenciones entre enero y julio de 2026.
-[Lea también: Midis y Banco Mundial cooperan en acciones de protección social ante El Niño y la anemia ] Reuniones de trabajo Posteriormente, Salazar sostuvo una reunión de trabajo con el gerente general del Gobierno Regional de Piura, Arturo Córdova; su equipo técnico; y representantes del Instituto Nacional de Defensa Civil (Indeci), para revisar las intervenciones que viene desarrollando el Midis en la región.
-Asimismo, para coordinar acciones orientadas a fortalecer la preparación institucional frente al FEN.
-Las autoridades regionales también expusieron sus inquietudes.
-En tanto, Afuso visitó el Centro Infantil de Atención Integral (CIAI) Semillitas Mágicas, en el distrito de Independencia, provincia de Huaraz, Áncash, donde verificó las condiciones de atención y cuidado que reciben 61 niñas y niños menores de 36 meses a través del programa Cuna Más.
-“Asimismo, constató el trabajo que realizan las madres cuidadoras y los actores comunales para promover el desarrollo infantil temprano”, detalló el Midis en una nota de prensa.
-La jornada concluyó con reuniones de trabajo junto con los equipos territoriales del Midis en Áncash y Piura.
-En Áncash, el viceministro Afuso sostuvo un encuentro con el gerente general regional, Marco Antonio La Rosa, con el propósito de coordinar acciones de prevención y lucha contra la anemia, además de la continuidad de los servicios sociales frente a los riesgos asociados al FEN.
-[Lea también: Midis coordina acciones preventivas en Amazonas, Cajamarca y Ucayali ante El Niño ] Garantizar los servicios sociales Estas acciones permitieron a ambos funcionarios verificar en territorio el nivel de preparación de los programas sociales y de las autoridades regionales frente a los posibles impactos de El Niño, así como fortalecer las intervenciones orientadas a prevenir y reducir la anemia.
-En la jornada se constató la implementación de medidas para proteger los alimentos para la población vulnerable, garantizar la continuidad de los servicios sociales y reforzar el acceso a servicios de salud, nutrición y desarrollo infantil, especialmente en zonas rurales y de mayor vulnerabilidad.
-[Lea también: El Niño: Midis impulsa articulación estratégica con lideresas de comedores populares ] Más en Andina: La nueva campaña de las PIAS Terrestres, gestionada por el Programa PAIS del Ministerio de Desarrollo e Inclusión Social (Midis), llevará servicios médicos a centros poblados de la provincia arequipeña de Caylloma, ubicados a más de 4500 metros de altura.… pic.twitter.com/NG2pIzaGq1 — Agencia Andina (@Agencia_Andina) September 10, 2026</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>https://andina.pe/agencia/noticia-midis-fortalece-su-presencia-el-territorio-para-enfrentar-los-efectos-de-nino-1091297.aspx</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Andina</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="n">
-        <v>46275</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Piura: Gobierno se anticipa a El Niño y fortalece la capacidad de respuesta de EsSalud</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
         <is>
           <t>En ese marco, el ministro de Trabajo y Promoción del Empleo, Juan Sheput, acompañado por la presidenta ejecutiva encargada de EsSalud, Hilda Sandoval, realizó visitas inopinadas a los hospitales de Talara y Sullana.
 Durante las supervisiones, verificaron las condiciones reales de los servicios, identificaron brechas en equipamiento, atención y personal especializado, y dispusieron medidas para fortalecer la capacidad de respuesta de los establecimientos y asegurar la continuidad de la atención a los asegurados.
@@ -702,16 +611,83 @@
 ?? https://t.co/apWpg6Rfab pic.twitter.com/1rxtBZSOiX — Agencia Andina (@Agencia_Andina) September 11, 2026</t>
         </is>
       </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>https://andina.pe/agencia/noticia-piura-gobierno-se-anticipa-a-nino-y-fortalece-capacidad-respuesta-essalud-1091317.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Andina</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>46275</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Piura: Vivienda inspecciona infraestructura estratégica ante posibles impactos de El Niño</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Como parte de estas acciones, el equipo del OTASS efectuó una jornada de inspección técnica en diversas instalaciones de la EPS Grau, entre ellas la planta de tratamiento de agua potable (PTAP) Curumuy, que representa aproximadamente el 44% del abastecimiento de agua potable de la provincia de Piura.
+También se inspeccionaron la PTAR San Martín y la estación de bombeo de aguas residuales (EBAR) Cortijo, en el distrito de Castilla, donde se verificó la operatividad de tres electrobombas recientemente instaladas, de 250 litros por segundo cada una, financiadas mediante una IOARR de emergencia, y las condiciones de sus demás componentes.
+La EBAR Cortijo concentra cerca del 60% de las aguas residuales de Castilla.
+Medidas anticipadas “Estamos tomando medidas con anticipación para proteger a las familias piuranas, verificando la infraestructura, identificando los puntos críticos y coordinando las acciones necesarias para garantizar que los servicios de agua potable y saneamiento continúen funcionando durante eventuales lluvias intensas” , señaló el ministro de Vivienda, Mauricio Arnillas.
+Durante la jornada, el titular del OTASS, Carlos Yáñez, sostuvo una reunión de trabajo con el nuevo gerente general de la EPS Grau y funcionarios de la empresa, en la cual se evaluó la situación operativa de la prestadora, las intervenciones en ejecución y las principales necesidades de sus sistemas de agua potable y saneamiento.
+Estas acciones forman parte del trabajo articulado que impulsa el MVCS para fortalecer la gestión de las empresas prestadoras y proteger la continuidad de los servicios de agua y saneamiento que requiere la población de Piura.
+Más en Andina: Gobierno se anticipa a El Niño y fortalece la capacidad de respuesta de EsSalud.
+El ministro Juan Sheput y la presidenta ejecutiva encargada de EsSalud supervisaron hospitales de Talara y Sullana.
+?? https://t.co/Rk9ilfkyym pic.twitter.com/nFvVi2wW2B — Agencia Andina (@Agencia_Andina) September 11, 2026</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>https://andina.pe/agencia/noticia-piura-vivienda-inspecciona-infraestructura-estrategica-ante-posibles-impactos-de-nino-1091321.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Andina</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>46275</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>El Niño: aprueban patrullaje integrado y respuesta logística con OxI ante emergencias</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>La Resolución Ministerial 1334-2026-IN, que lleva la firma del ministro del Interior, César Astudillo Salcedo, y publicada en la edición extraordinaria del boletín de Normas Legales del Diario Oficial El Peruano , tiene por finalidad acelerar y financiar de manera prioritaria el despliegue logístico y de seguridad ciudadana frente a situaciones críticas en el país como el FEN.
+De esta forma se reducirá la exposición de la población y la infraestructura pública, además de asegurar la continuidad de los servicios públicos esenciales y evitar que los daños que pudieran producirse deriven en perjuicios de difícil o imposible reparación y en mayores costos fiscales de rehabilitación y reconstrucción.
+Todo ello al amparo del Decreto de Urgencia 010-2026, que dicta medidas extraordinarias y temporales, en materia económica y financiera, para habilitar la ejecución de Servicios e Inversiones de Optimización, de Ampliación Marginal, de Rehabilitación y de Reposición (IOARR) de emergencia, mediante el mecanismo de OxI regulado por la Ley 29230.
+La Ley 29230, además, simplifica los plazos y procedimientos aplicables a esas intervenciones para la atención de acciones de prevención, preparación, respuesta y rehabilitación en el marco del FEN 2026-2027.
+A ProInversión Se dispone la remisión de una copia de la R.
+M.
+1334-2026-IN y su anexo a la Agencia de Promoción de la Inversión Privada (ProInversión), para los fines consiguientes, en el contexto del seguimiento y difusión del mecanismo de Obras por Impuestos.
+Asimismo, se dispone la notificación de la resolución a la Policía Nacional del Perú (PNP) y a los pliegos adscritos al Mininter, a la Oficina General de Planeamiento y Presupuesto, a la Oficina General de Administración y a las unidades de organización, que en el marco de sus competencias intervendrán en la implementación y ejecución de las medidas extraordinarias mediante el mecanismo de OxI ante El Niño.
+Más en Andina: El Ministerio de Vivienda, Construcción y Saneamiento refuerza las acciones de preparación y prevención frente a los posibles impactos del fenómeno El Niño (FEN) en Piura, mediante la inspección de la infraestructura estratégica de la EPS Grau.
+?? https://t.co/ypNmV34u4N pic.twitter.com/kvK3SeA6Qh — Agencia Andina (@Agencia_Andina) September 11, 2026</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>https://andina.pe/agencia/noticia-piura-gobierno-se-anticipa-a-nino-y-fortalece-capacidad-respuesta-essalud-1091317.aspx</t>
+          <t>https://andina.pe/agencia/noticia-el-nino-aprueban-patrullaje-integrado-y-respuesta-logistica-oxi-ante-emergencias-1091329.aspx</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>El Comercio</t>
+          <t>Andina</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
@@ -719,24 +695,42 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>¿Masificación de gas en el norte? Gasoducto entre Piura y Chiclayo es posible, señala Gas Energy</t>
+          <t>Conoce las 125 agencias donde el Reniec brindará atención especial este fin de semana</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>El norte del Perú tiene la oportunidad de abastecerse de gas natural y lograr una verdadera masificación sin la obligatoriedad de recurrir a Camisea. Esto, a través de la construcción de gasoductos que aprovechen el potencial de los lotes de hidrocarburos piuranos. Y es que la única manera de lograr un proceso de masificación económico y eficiente es “construyendo tubos”, alternativa que elimina la necesidad de transportar el gas en camiones, apunta Luis Fernández, socio director de Gas Energy Perú. En esa línea, la consultora lanzó en la XV Conferencia Gas Natural Perú 2026 una propuesta para crear un corredor energético de gas natural entre Piura y Chimbote utilizando las reservas y recursos de los campos piuranos, hoy desaprovechados. “El norte del Perú tiene suficientes reservas y recursos para crear un polo de desarrollo energético e industrial descentralizado e independiente del gas de Camisea”, manifiesta el especialista. Así, la consultora propone construir un gasoducto de 250 kilómetros de longitud que conecte Piura con la localidad lambayecana de Eten, en una primera etapa, sacando partido de la existencia de dos plantas térmicas en esa jurisdicción, las cuales servirán de ‘ancla’ para el proyecto. Es el caso de las centrales duales Eten (180 MW) y Recka (190 MW) las cuales están en capacidad de producir electricidad tanto con gas como con diésel. Se trata, explica Fernández, de dos infraestructuras que hoy en día no pueden ser abastecidas con gas pues el transporte en camiones cisternas no permite el abastecimiento de grandes volúmenes. De allí la solución de un gasoducto capaz de proveer los 80 millones de pies cúbicos diarios (mmpcd) de gas que necesitarían continuamente. “Si tenemos 80 mmpcd de demanda en Éten ya existiría un ancla para incentivar la producción de los lotes piuranos. Y a ello se agregaría la demanda de GNV en Chiclayo y las azucareras que tienen un alto consumo de energía”, precisa el especialista. Piura produce y consume alrededor de 60 mmpcd de gas natural. La apertura de nuevos mercados en Lambayeque incentivaría la búsqueda y producción de mayores volúmenes, lo cual no representaría un problema pues la región tiene un potencial de 5,5 trillones de pies cúbicos (TFC) de gas, es decir, 91.666 veces su producción diaria hoy. “Conceptualmente, el proyecto es posible porque existe el gas y existen las centrales térmicas que servirían de ancla. Por lo tanto, se puede construir la infraestructura”, manifiesta Fernández. Dicho ducto recorrería Paita, Sechura y Bayóvar hasta llegar a Éten, siguiendo un recorrido paralelo al que Gasnorp opera en Piura. Así, se conectaría la ciudad de Chiclayo, en primer lugar, y luego las de Trujillo, Paramonga y Chimbote, andando el tiempo. Lo único que faltaría para concretar el proyecto es plasmar las condiciones para que sea comercial y regulatoriamente posible, anota Fernández. Y es que la regulación no contempla una tarifa especial para el sector de generación eléctrica en el norte del país, a diferencia de lo que ocurre en las concesiones de Lima (Cálidda) e Ica (Contugas). “Para que el proyecto tenga éxito hace falta armar una nueva regulación que permita que esas centrales entren en base y para ello se necesita políticas adecuadas que partan desde el Minem”, anota Fernández.</t>
+          <t>La atención del sábado se realizará en agencias de Piura, La Libertad, Lambayeque, Tumbes, Cajamarca, San Martín, Loreto, Áncash, Junín, Ayacucho, Arequipa, Cusco, Lima, Puno, Ica, Ucayali, Huancavelica, Madre de Dios y Amazonas.
+En tanto, el domingo, el Reniec continuará atendiendo en Piura, Lambayeque, Tumbes, Lima y Puno, de 8:15 a.
+m.
+a 12:45 p.
+m.
+Conoce aquí las agencias, centros de atención y horarios habilitados para este fin de semana: Enlace: https://docs.google.com/spreadsheets/d/1TnRZB_IOqx5TS8fzKlCfA2gmvg2oovzQ/edit?gid=154156413#gid=154156413 Lima Metropolitana y Callao: atención este sábado En Lima Metropolitana y Callao, el Reniec atenderá este sábado 12 de setiembre en seis centros, donde los ciudadanos podrán realizar trámites y recoger sus documentos de identidad.
+La atención será de 8:15 a.
+m.
+a 12:45 p.
+m.
+en MAC Callao, MAC Lima Este, MAC Lima Norte, MAC Lima Sur, MAC Ventanilla y la agencia de Miraflores.
+Esta atención especial busca ampliar las opciones para quienes, por sus actividades durante la semana, requieren realizar sus trámites o recoger su DNI durante el fin de semana, especialmente ante la proximidad de las Elecciones Regionales y Municipales (ERM) 2026.
+Atención el domingo 13 en cinco regiones El domingo 13 de setiembre, el Reniec continuará atendiendo en 13 centros ubicados en Piura, Lambayeque, Tumbes, Lima y Puno, de 8:15 a.
+m.
+a 12:45 p.
+m.
+En Lima, funcionarán los centros de atención de Independencia y Cercado de Lima, en el mismo horario.
+Conoce aquí las agencias, centros de atención y horarios habilitados para este fin de semana: Enlace: https://docs.google.com/spreadsheets/d/1TnRZB_IOqx5TS8fzKlCfA2gmvg2oovzQ/edit?gid=154156413#gid=154156413 Lea también: Reniec tomará gratis la foto para DNI de niños: conoce en qué sedes y cómo hacerlo ¿Dónde consultar si mi DNI se encuentra listo para recogerlo? Los ciudadanos deben acceder a la página oficial de Reniec a través de este Enlace: https://serviciosportal.reniec.gob.pe/cetdnipi/inicio.htm ingresar su número de DNI o de solicitud, hacer clic en ‘Consultar’ y, de inmediato, les aparecerá sus datos completos, la sede que eligieron para el recojo de su DNI y si el estado de su trámite se encuentra al 100%, listo para recoger su documento.
+Más en Andina: La Autoridad Nacional de Infraestructura (ANIN) amplió su cartera de intervención integral para el control de riesgos por movimientos de masa e inundaciones en la cuenca del río Rímac con la incorporación de las quebradas Vizcachera, Ñaña y La Laguna ?? https://t.co/T25qFB3xn7 pic.twitter.com/vrqvZ2YCgN — Agencia Andina (@Agencia_Andina) September 10, 2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>https://elcomercio.pe/economia/peru/masificacion-de-gas-en-el-norte-gasoducto-entre-piura-y-chiclayo-es-posible-senala-gas-energy-noticia/</t>
+          <t>https://andina.pe/agencia/noticia-conoce-las-125-agencias-donde-reniec-brindara-atencion-especial-este-fin-semana-1091330.aspx</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>El Tiempo</t>
+          <t>El Comercio</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -744,17 +738,17 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Comerciantes del Complejo de Mercados de Piura solicitan administración de parqueos</t>
+          <t>¿Masificación de gas en el norte? Gasoducto entre Piura y Chiclayo es posible, señala Gas Energy</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>A través de Resolución de Alcaldía N° 0592-2026, la Municipalidad Provincial de Piura ha dispuesto la conformación de una Comisión técnica multidisciplinaria para que evalué la viabilidad jurídica, técnica, económica, financiera, patrimonial y administrativa sobre la propuesta presentada por la Asociación regional de mercados de Piura (AREMEPI) referente a la administración de los estacionamientos del Complejo de Mercados. La asociación, que representa a los mercados formales, plantea implementar un modelo de gestión conjunta con la comuna piurana orientado a mejorar la administración del servicio, reducir los costos operativos y generar recursos económicos destinados a financiar proyectos estratégicos para el ordenamiento urbano del propio centro de abastos de la ciudad. La gerente de Desarrollo Económico, Ruth Oliva, señaló que hay voluntad política para evaluar el pedido de los comerciantes, por lo que se tendrá que esperar los informes técnicos para la toma de decisiones. REVERSIÓN La funcionaria también dio a conocer que realizaron una inspección en el Mercado San Miguel y constataron una vez más que varios puestos se encuentran cerrados. Indicó que este tipo de acciones que vienen realizando permitirán identificar los puestos que no cumplen con las disposiciones establecidas y, posteriormente, iniciar el proceso de reversión de aquellos espacios que correspondan, con el objetivo de brindar la oportunidad a otros comerciantes que sí tengan la voluntad de trabajar en dicho local comercial.</t>
+          <t>El norte del Perú tiene la oportunidad de abastecerse de gas natural y lograr una verdadera masificación sin la obligatoriedad de recurrir a Camisea. Esto, a través de la construcción de gasoductos que aprovechen el potencial de los lotes de hidrocarburos piuranos. Y es que la única manera de lograr un proceso de masificación económico y eficiente es “construyendo tubos”, alternativa que elimina la necesidad de transportar el gas en camiones, apunta Luis Fernández, socio director de Gas Energy Perú. En esa línea, la consultora lanzó en la XV Conferencia Gas Natural Perú 2026 una propuesta para crear un corredor energético de gas natural entre Piura y Chimbote utilizando las reservas y recursos de los campos piuranos, hoy desaprovechados. “El norte del Perú tiene suficientes reservas y recursos para crear un polo de desarrollo energético e industrial descentralizado e independiente del gas de Camisea”, manifiesta el especialista. Así, la consultora propone construir un gasoducto de 250 kilómetros de longitud que conecte Piura con la localidad lambayecana de Eten, en una primera etapa, sacando partido de la existencia de dos plantas térmicas en esa jurisdicción, las cuales servirán de ‘ancla’ para el proyecto. Es el caso de las centrales duales Eten (180 MW) y Recka (190 MW) las cuales están en capacidad de producir electricidad tanto con gas como con diésel. Se trata, explica Fernández, de dos infraestructuras que hoy en día no pueden ser abastecidas con gas pues el transporte en camiones cisternas no permite el abastecimiento de grandes volúmenes. De allí la solución de un gasoducto capaz de proveer los 80 millones de pies cúbicos diarios (mmpcd) de gas que necesitarían continuamente. “Si tenemos 80 mmpcd de demanda en Éten ya existiría un ancla para incentivar la producción de los lotes piuranos. Y a ello se agregaría la demanda de GNV en Chiclayo y las azucareras que tienen un alto consumo de energía”, precisa el especialista. Piura produce y consume alrededor de 60 mmpcd de gas natural. La apertura de nuevos mercados en Lambayeque incentivaría la búsqueda y producción de mayores volúmenes, lo cual no representaría un problema pues la región tiene un potencial de 5,5 trillones de pies cúbicos (TFC) de gas, es decir, 91.666 veces su producción diaria hoy. “Conceptualmente, el proyecto es posible porque existe el gas y existen las centrales térmicas que servirían de ancla. Por lo tanto, se puede construir la infraestructura”, manifiesta Fernández. Dicho ducto recorrería Paita, Sechura y Bayóvar hasta llegar a Éten, siguiendo un recorrido paralelo al que Gasnorp opera en Piura. Así, se conectaría la ciudad de Chiclayo, en primer lugar, y luego las de Trujillo, Paramonga y Chimbote, andando el tiempo. Lo único que faltaría para concretar el proyecto es plasmar las condiciones para que sea comercial y regulatoriamente posible, anota Fernández. Y es que la regulación no contempla una tarifa especial para el sector de generación eléctrica en el norte del país, a diferencia de lo que ocurre en las concesiones de Lima (Cálidda) e Ica (Contugas). “Para que el proyecto tenga éxito hace falta armar una nueva regulación que permita que esas centrales entren en base y para ello se necesita políticas adecuadas que partan desde el Minem”, anota Fernández.</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>https://eltiempo.pe/local/comerciantes-del-complejo-de-mercados-de-piura-solicitan-administracion-de-parqueos/</t>
+          <t>https://elcomercio.pe/economia/peru/masificacion-de-gas-en-el-norte-gasoducto-entre-piura-y-chiclayo-es-posible-senala-gas-energy-noticia/</t>
         </is>
       </c>
     </row>
@@ -769,17 +763,17 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Burocracia retrasa obras de emergencia por el Fenómeno El Niño</t>
+          <t>Ministro de Defensa promete mayor velocidad en la descolmatación del río Piura</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Mientras que entidades oficiales como Enfen y Senamhi advierten de un Fenómeno El Niño de “magnitud fuerte” o “extraordinario”; el empresariado piurano aún sigue a la espera que Proinversión defina los proyectos que se van ejecutar a través de la modalidad de “servicios por impuestos”. Se trata de 18 propuestas que han hecho llegar a Proinversión, según lo informó la gerente general de la Cámara de Comercio y Producción de Piura, Susana Seminario, quien ayer aprovechó la presencia de los ministros de Desarrollo Agrario y Riego, Marco Vinelli; del ministro de Defensa, Rafael Belaúnde Llosa y de otras autoridades que participaron de la reunión de trabajo de la Plataforma de Defensa Civil para pedir celeridad en los trámites y los proyectos se pueden iniciar cuanto antes en aras de mitigar el impacto del FEN. S/ 130 millones La empresaria también dio a conocer que disponen de 130 millones de soles en impuestos para ser ejecutados en los proyectos de emergencia. Chutuque La ampliación del canal de Chutuque es una de las prioridades de los empresarios para evitar una posible inundación. Mientras días atrás el presidente de la Camco, Javier Bereche, señalaba que se trata de “un canal de 6.7 kilómetros de roca y eso hay que volarlo”, ayer el titular del Midagri remarcó que dentro de dos o tres días se iniciarán los trabajos, pero solo limpiarán 5 kilómetros que iniciarán en el distrito de Cristo Nos Valga y terminarán en Sechura. “Es lo que se puede garantizar y cumplir”, subrayó. Bajo Piura Sobre el reclamo del Bajo Piura que demanda más maquinaria para los trabajos de descolmatación, el ministro Vinelli aseguró que en los próximos días llegará más maquinaria aguas abajo del puente Grau. Para 3,900 m3/s Vinelli también dio a conocer que los trabajos de descolmatación tienen un avance del 42% en el tramo entre la represa Los Ejidos y el puente Bolognesi y el objetivo es ampliar la capacidad de la caja hidráulica a 3.900 metros cúbicos por segundo (m3/s); sin embargo, el supervisor de los trabajos indicó un día antes que la proyección es para 3.000 m3/s. Ayuda humanitaria Finalmente se dio a conocer que actualmente se cuenta con 725 toneladas de ayuda humanitaria en el almacén central y 113 toneladas distribuidas en 17 almacenes adelantados, además de 51 motobombas en mantenimiento y la planificación para incorporar otras 70. Solo priorizan 69 establecimientos de salud Durante la reunión realizada en el Gobierno Regional, también se dio a conocer sobre la intervención de establecimientos de salud para mitigar el impacto del FEN. Sin embargo, se informó que de los 438 establecimientos de salud existentes en la región, 269 requieren algún tipo de intervención y se han priorizado 69. Asimismo, se informó sobre la coordinación para implementar un hospital temporal de 104 camas en la Universidad de Piura, además del fortalecimiento de brigadas, equipos de fumigación, ambulancias y acciones de prevención frente al dengue. Sobre las vacunas, el titular del Midagri aseguró que llegará otro lote de 50 mil vacunas contra el dengue.</t>
+          <t>El ministro de Defensa, Rafael Belaunde , aseguró que el Ejército incrementará la velocidad de los trabajos de descolmatación del río Piura , como parte de las acciones preventivas frente al eventual impacto del fenómeno El Niño en la región. El titular del sector supervisó el despliegue de personal y maquinaria pesada en dos de los puntos considerados críticos. Durante su visita al puente Bolognesi, en Piura, Belaunde verificó las labores destinadas a retirar los sedimentos acumulados en el cauce. Según explicó, existe confianza en que los trabajos avanzarán al ritmo requerido para cumplir con las metas establecidas. “Estoy confiado en que el Ejército avanzará en la velocidad que se le ha requerido”, afirmó el ministro durante la inspección. ¿Dónde se realizan los trabajos en el río Piura? Las labores de limpieza y recuperación del cauce se ejecutan en siete puntos críticos del río Piura , en un tramo de aproximadamente 15.5 kilómetros comprendido entre los puentes Independencia y Bolognesi. Para esta operación se ha desplegado personal especializado del Ejército y maquinaria pesada destinada principalmente a retirar el material acumulado en diferentes sectores del afluente. La intervención busca mejorar las condiciones del cauce ante la posibilidad de lluvias intensas y un incremento del caudal. En el sector del puente Bolognesi trabaja el Batallón de Ingeniería de Construcción N.° 1 “Jazán”, unidad trasladada desde la región Amazonas. Para cumplir con su misión, cuenta con 13 camiones volquetes, dos excavadoras, dos tractores oruga y un cargador frontal . La meta establecida para este punto es intervenir aproximadamente dos kilómetros del cauce del río Piura . El retiro de los sedimentos permitirá recuperar parte de la capacidad hidráulica del río en una zona considerada estratégica para la prevención de inundaciones. Ejército trabaja en el puente Independencia El ministro de Defensa también llegó hasta el puente Independencia para inspeccionar los trabajos que se desarrollan en este sector. Las acciones están a cargo del Batallón de Ingeniería de Combate N.° 211, proveniente de Tumbes. Esta unidad dispone de dos tractores oruga, una excavadora, un cargador frontal y un volquete . De acuerdo con la planificación presentada durante la supervisión, sus trabajos tienen como objetivo intervenir aproximadamente 1.8 kilómetros del cauce. La presencia de maquinaria en ambos sectores forma parte de una operación de ingeniería de mayor escala. Para el Gobierno, la recuperación del cauce constituye una de las medidas preventivas frente a un eventual escenario de lluvias asociadas al fenómeno El Niño. Piura recibirá 600 toneladas de ayuda no alimentaria Durante su visita, el ministro de Defensa también informó sobre las acciones de preparación ante una eventual emergencia por lluvias. Según indicó, alrededor de 200 toneladas de ayuda no alimentaria ya han llegado a Piura como parte de un envío mayor. La ayuda es gestionada mediante el Instituto Nacional de Defensa Civil (Indeci) y forma parte de un total de 600 toneladas que serán trasladadas y almacenadas en un hangar ubicado en territorio piurano. Según declaraciones brindadas a TVPerú, el objetivo es contar con recursos suficientes para atender a unas 100,000 familias , lo que representa cerca de medio millón de personas ante un escenario de emergencia. “La idea es tener capacidad para atender a 100,000 familias. Eso es algo cercano al medio millón de personas”, explicó Belaunde, quien añadió que progresivamente también se incorporará ayuda alimentaria. ¿Por qué es importante la descolmatación del río Piura? La descolmatación consiste en retirar sedimentos, tierra y otros materiales acumulados en el cauce de un río. En el caso del río Piura , estas labores tienen especial importancia durante la temporada de lluvias, debido al riesgo de incremento del caudal y posibles desbordes. La recuperación de la capacidad del cauce forma parte de las medidas de prevención frente a inundaciones. En Piura, una región que históricamente ha enfrentado episodios de lluvias intensas, mantener libres los sectores críticos permite mejorar las condiciones para el desplazamiento del agua. De acuerdo con el Instituto Nacional de Defensa Civil (Indeci) , las acciones de preparación y prevención son fundamentales para reducir los riesgos y mejorar la capacidad de respuesta ante emergencias. Una operación que abarca 15.5 kilómetros La intervención del Ejército contempla un tramo total de 15.5 kilómetros del río Piura , distribuido en siete puntos críticos ubicados entre los puentes Independencia y Bolognesi. La operación requiere el desplazamiento de unidades de ingeniería, operadores y maquinaria especializada. Para las autoridades, el avance de estos trabajos será especialmente importante conforme se acerquen los periodos de mayor riesgo de lluvias. La incorporación de nuevos equipos, anunciada por el Ministerio de Defensa, busca acelerar el retiro de los sedimentos y cumplir con las metas establecidas para cada sector. La información sobre las acciones de prevención y respuesta ante emergencias puede consultarse en los canales oficiales del Ministerio de Defensa y del Indeci .</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>https://eltiempo.pe/local/burocracia-retrasa-obras-de-emergencia-por-el-fenomeno-el-nino/</t>
+          <t>https://eltiempo.pe/local/ministro-de-defensa-promete-mayor-velocidad-en-la-descolmatacion-del-rio-piura/</t>
         </is>
       </c>
     </row>
@@ -790,21 +784,21 @@
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Dos gatilleros matan a sujeto y hieren a otro en Paita, pero Policía los captura</t>
+          <t>¿Quién responde por los 106 muertos en la región Piura? Nuevo asesinato se consuma en Castilla</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>A cinco se incrementaron los asesinatos del pasado lunes en la región, luego que gatilleros motorizados asesinaran a tiros a joven en Paita alta y dejarán gravemente herido a su amigo. Esta vez, la Policía Nacional en rápida repuesta capturó a balazos dos sospechosos, incautando una motocicleta y un arma de fuego. Transcurría las 9:50 de la noche del lunes, cuando los amigos Giancarlo Jiménez Hernández, de 33 años, y William Daniel Aldana Prado, de 24 años, caminaban por la parte posterior de las empresas de transporte Andrea y Santangel, fueron interceptados por una motocicleta. Disparó a matar El sujeto que iba como pasajero sacó un arma de fuego y disparó a matar contra los dos amigos. Los ocupantes de la motocicleta al ver caer a sus blancos se dieron a la fuga por las calles de Paita Alta. Los dos amigos gravemenre heridos fueron socorridos y trasladados de emergencia al Hospital Nuestra Señora de las Mercedes.Lamentablemente, el médico de turno, Ricardo Pereira certificó la muerte de Giancarlo Jiménez por hemorragia intercraneal por disparo de arma de fuego. En tanto, dio el diagnóstico oara Willian Aldaba de traumatismo abdominal abierto por proyectil con arma de fuego. Su estado de salud es de pronostico reservado. Persecución y captura Un grupo de agentes de la Comisaría Ciudad del Pescador con las características de la moto y los sujetos a inmediaciones del colegio “Lunitas de Paita” localizó la motocicleta, modelo Triax, de placa de rodaje 1764-GP. Luego de una tenaz persecución capturó al conductor C. A. T. D. (20), el mismo que portaba un cartucho de dinamita. El pasajero de la moto huyó a pie realizando disparos contra la policía, bajo fuego cruzado se refugió en una vivienda donde finalmente fue detenido siendo identificado con las iniciales L. J. Ch. N. (25). Los custodios le hallaron un arma de fuego.</t>
+          <t>La racha criminal sigue en aumento en la región, luego que un joven técnico de celulares fuera asesinado de tres balazos en la cabeza y rostro por un gatillero, que disparó con una pasmosa frialdad, delante de dos amigos, para luego huir en un auto blanco. El asesinato de José Fernando Castillo Quevedo, de 24 años, ocurrió cerca de las nueve de la noche del pasado martes frente al bar “Pikaflor”, ubicado en la Asociación Villa Universitaria, sector norteste de Castilla. Hasta ese lugar llegó la Policía para iniciar las investigaciones. ESCALOFRIANTE DATA Con este episodio escaló a 106 los asesinatos ocurridos en lo que va del año en la región, siendo la mayoría de casos por la modalidad de sicariato (o crimenes por encargo). Cabe resaltar que en 2025 se registraron 107 homicidios en el lapso de enero a setiembre. Cabe precisar que en menos de 72 horas han ocurrido siete homicidios: dos mujeres, un varón y un menor de 13 años en Sullana, otro caso en Talara. De igual manera uno en Paita Alta y el último registrado en Castilla, contra José Fernando Castillo. IMÁGENES CLAVES El asesinato del joven técnico de equipos móviles muestra el alto grado de peligrosidad que existe en las calles. Precisamente una cámara de seguridad muestra que ya no se puede confian en nadie, luego que en escena se observa a José Fernando Castillo platicando con dos personas, que serían amigos. Según las imágenes de las cámaras de seguridad, Castillo Quevedo y dos sujetos, en la vía públlica, observan un celular. De pronto, se aprecia la salida de un individuo desconocido para subir apuradamente a un automóvil blanco y dar arranque. TODOS SE CONOCÍAN En ese momento, se oberva la llegada de un gatillero que vestía polo verde y bermuda blu jeans, quien se acerca a los tres amigos y dispara tres veces contra José Fernando Castillo, luego con pistola en mano camina y sube al mencionado vehículo blanco. Del mismo modo se distingue que uno de los dos individuos, que estaba conversando con la víctima mortal abordó el mismo vehículo en el que huyó el atacante. La Policía continúa con las investigaciones para esclarecer el crimen, identificar a los involucrados y determinar las circunstancias del asesinato.</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>https://eltiempo.pe/local/dos-gatilleros-matan-a-sujeto-y-hieren-a-otro-en-paita-pero-policia-los-captura/</t>
+          <t>https://eltiempo.pe/local/quien-responde-por-los-106-muertos-en-la-region-piura-nuevo-asesinato-se-consuma-en-castilla/</t>
         </is>
       </c>
     </row>
@@ -815,21 +809,21 @@
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Advierten que la sensación del calor podría llegar a los 39°C en la región Piura</t>
+          <t>Comerciantes del Complejo de Mercados de Piura solicitan administración de parqueos</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>El Senamhi Piura informó que durante el mes, se registraron temperaturas de hasta 37,2°C en Chulucanas, Piura. No descartan que la sensación de calor pueda alcanzar los 39 °C en Piura. Así lo señaló el especialista del Senamhi Piura, Héctor Yauri quien indicó que este panorama se podría dar por diversos factores, con lo cual la población deberá tomar sus precauciones. El Senamhi informó que durante las últimas semanas las temperaturas se han mantenido por encima de sus valores normales, especialmente las temperaturas máximas. MAGNITUD FUERTE Explican que esta situación estaría “asociada principalmente a la persistencia de anomalías positivas de la temperatura superficial del mar frente a la costa de Piura y en la región Niño 1+2”. “Se espera que las temperaturas del aire continúen registrando valores relativamente elevados durante las próximas semanas, debido a la persistencia de temperaturas superficiales del mar por encima de lo normal en la región Niño 1+2. Estas condiciones son consistentes con la evolución del evento Niño Costero, que actualmente presenta magnitud fuerte, favoreciendo la persistencia de temperaturas superiores a los valores climatológicos para la temporada”, indicó el especialista Fabricio Fabián Herrera. Asimismo, de acuerdo al aviso meteorológico 161 del Senamhi, no se descarta lluvias dispersas en la costa norte y la presencia de lluvias localizadas en la sierra norte.</t>
+          <t>A través de Resolución de Alcaldía N° 0592-2026, la Municipalidad Provincial de Piura ha dispuesto la conformación de una Comisión técnica multidisciplinaria para que evalué la viabilidad jurídica, técnica, económica, financiera, patrimonial y administrativa sobre la propuesta presentada por la Asociación regional de mercados de Piura (AREMEPI) referente a la administración de los estacionamientos del Complejo de Mercados. La asociación, que representa a los mercados formales, plantea implementar un modelo de gestión conjunta con la comuna piurana orientado a mejorar la administración del servicio, reducir los costos operativos y generar recursos económicos destinados a financiar proyectos estratégicos para el ordenamiento urbano del propio centro de abastos de la ciudad. La gerente de Desarrollo Económico, Ruth Oliva, señaló que hay voluntad política para evaluar el pedido de los comerciantes, por lo que se tendrá que esperar los informes técnicos para la toma de decisiones. REVERSIÓN La funcionaria también dio a conocer que realizaron una inspección en el Mercado San Miguel y constataron una vez más que varios puestos se encuentran cerrados. Indicó que este tipo de acciones que vienen realizando permitirán identificar los puestos que no cumplen con las disposiciones establecidas y, posteriormente, iniciar el proceso de reversión de aquellos espacios que correspondan, con el objetivo de brindar la oportunidad a otros comerciantes que sí tengan la voluntad de trabajar en dicho local comercial.</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>https://eltiempo.pe/local/advierten-que-la-sensacion-del-calor-podria-llegar-a-los-39c-en-la-region-piura/</t>
+          <t>https://eltiempo.pe/local/comerciantes-del-complejo-de-mercados-de-piura-solicitan-administracion-de-parqueos/</t>
         </is>
       </c>
     </row>
@@ -840,21 +834,21 @@
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Bajo Piura se levanta y exige obras para evitar inundación</t>
+          <t>Burocracia retrasa obras de emergencia por el Fenómeno El Niño</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>La población no quiere ser expectante de como apenas siete maquinarias pesadas trabajan en la descolmatación del río Piura, desde el puente Grau hasta el puente Independencia, sin haberse considerado obras adicionales como el reforzamiento de las defensas ribereñas, los diques de contención, entre otras obras que permitan mitigar el impacto del Fenómeno El Niño (FEN) que se avecina. Por ello ayer, y tras una asamblea, dirigentes de los distritos de Catacaos, Cura Mori y El Tallán acordaron realizar una marcha de protesta el 14 de setiembre a partir de las 8:00 a.m. bajo el lema “Inundación nunca más”. La población está dispuesta a bloquear las vías hasta ser escuchados por las autoridades. «Es una burla» Víctor Chunga, presidente del Frente de reconstrucción de pueblos afectados por el Niño Costero 2017, calificó como una “burla” que en su primera visita a Piura la presidenta Keiko Fujimori anunciara una inversión de 140 millones y un pull de maquinaria para los trabajos de descolmatación y no se está cumpliendo. “Anunció 140 millones, luego 129 millones, pero no está desglosado cuánto le toca a Piura y los trabajos no van ni al 30%. Ahora en la descolmatación (hacia el Bajo Piura) solo están retirando 90 centímetros de sedimento, eso es limpieza no descolmatación”, indicó. Para octubre prometen terminar descolmatación Tras la denuncia del diputado Félix Chang Apuy, sobre la paralización de los trabajos de descolmatación del río Piura, el supervisor de estos trabajos, Ítalo Cuba, señaló que ya solucionaron el tema administrativo de los contratos del personal y se ha retomado los trabajos en el tramo entre la represa Los Ejidos y el puente Bolognesi. Informó que 20 maquinarias pesadas del Gobierno Regional se sumarán a los trabajos, con lo cual esperan culminar los mismos antes de las lluvias pronosticadas para noviembre. “A mediados de octubre se quiere terminar todo esto”, indicó el supervisor quien agregó que buscan recuperar un encausamiento del río con capacidad para 3000 m3/s.</t>
+          <t>Mientras que entidades oficiales como Enfen y Senamhi advierten de un Fenómeno El Niño de “magnitud fuerte” o “extraordinario”; el empresariado piurano aún sigue a la espera que Proinversión defina los proyectos que se van ejecutar a través de la modalidad de “servicios por impuestos”. Se trata de 18 propuestas que han hecho llegar a Proinversión, según lo informó la gerente general de la Cámara de Comercio y Producción de Piura, Susana Seminario, quien ayer aprovechó la presencia de los ministros de Desarrollo Agrario y Riego, Marco Vinelli; del ministro de Defensa, Rafael Belaúnde Llosa y de otras autoridades que participaron de la reunión de trabajo de la Plataforma de Defensa Civil para pedir celeridad en los trámites y los proyectos se pueden iniciar cuanto antes en aras de mitigar el impacto del FEN. S/ 130 millones La empresaria también dio a conocer que disponen de 130 millones de soles en impuestos para ser ejecutados en los proyectos de emergencia. Chutuque La ampliación del canal de Chutuque es una de las prioridades de los empresarios para evitar una posible inundación. Mientras días atrás el presidente de la Camco, Javier Bereche, señalaba que se trata de “un canal de 6.7 kilómetros de roca y eso hay que volarlo”, ayer el titular del Midagri remarcó que dentro de dos o tres días se iniciarán los trabajos, pero solo limpiarán 5 kilómetros que iniciarán en el distrito de Cristo Nos Valga y terminarán en Sechura. “Es lo que se puede garantizar y cumplir”, subrayó. Bajo Piura Sobre el reclamo del Bajo Piura que demanda más maquinaria para los trabajos de descolmatación, el ministro Vinelli aseguró que en los próximos días llegará más maquinaria aguas abajo del puente Grau. Para 3,900 m3/s Vinelli también dio a conocer que los trabajos de descolmatación tienen un avance del 42% en el tramo entre la represa Los Ejidos y el puente Bolognesi y el objetivo es ampliar la capacidad de la caja hidráulica a 3.900 metros cúbicos por segundo (m3/s); sin embargo, el supervisor de los trabajos indicó un día antes que la proyección es para 3.000 m3/s. Ayuda humanitaria Finalmente se dio a conocer que actualmente se cuenta con 725 toneladas de ayuda humanitaria en el almacén central y 113 toneladas distribuidas en 17 almacenes adelantados, además de 51 motobombas en mantenimiento y la planificación para incorporar otras 70. Solo priorizan 69 establecimientos de salud Durante la reunión realizada en el Gobierno Regional, también se dio a conocer sobre la intervención de establecimientos de salud para mitigar el impacto del FEN. Sin embargo, se informó que de los 438 establecimientos de salud existentes en la región, 269 requieren algún tipo de intervención y se han priorizado 69. Asimismo, se informó sobre la coordinación para implementar un hospital temporal de 104 camas en la Universidad de Piura, además del fortalecimiento de brigadas, equipos de fumigación, ambulancias y acciones de prevención frente al dengue. Sobre las vacunas, el titular del Midagri aseguró que llegará otro lote de 50 mil vacunas contra el dengue.</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>https://eltiempo.pe/local/bajo-piura-se-levanta-y-exige-obras-para-evitar-inundacion/</t>
+          <t>https://eltiempo.pe/local/burocracia-retrasa-obras-de-emergencia-por-el-fenomeno-el-nino/</t>
         </is>
       </c>
     </row>
@@ -869,17 +863,17 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>UPAO Piura lleva el cine universitario a una nueva edición del Festival Ojo Errante</t>
+          <t>Piura: en menos de 72 horas, delincuentes asesinan a ocho personas en la región</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>La tercera edición del certamen convoca a jóvenes realizadores de todo el país, quienes presentarán sus cortometrajes de ficción, documental y animación hasta el 9 de octubre. El talento audiovisual universitario tiene un nuevo espacio de encuentro en Piura. El Programa de Estudio de Comunicación y Medios Digitales de la Universidad Privada Antenor Orrego (UPAO) filial Piura desarrollará la tercera edición del Festival de Cortometrajes Universitarios Ojo Errante, una iniciativa que promueve la producción audiovisual de jóvenes universitarios y su difusión desde las regiones. El certamen se desarrollará de manera presencial y tendrá ingreso gratuito. La convocatoria está dirigida a los estudiantes universitarios de comunicación y facultades afines de todo el país, quienes podrán postular cortometrajes realizados en el ámbito académico, entre agosto del 2024 y octubre del 2026. Ficción, documental y animación Los participantes podrán competir en tres categorías oficiales. En ficción, se recibirán obras basadas en personajes, situaciones y conflictos narrativos imaginarios, con una duración de 5 a 20 minutos. En documental, podrán participar obras de no ficción construidas a partir de hechos, realidades o espacios interpretados por el realizador, con una duración de 5 a 20 minutos. Por su parte, la categoría animación comprende creaciones realizadas mediante técnicas tradicionales, digitales o mixtas, con una duración de 30 segundos a 20 minutos. Inscripciones hasta el 9 de octubre Para la filial Piura, la convocatoria estará abierta hasta el 9 de octubre del 2026, hasta las 11:59 p. m. La exhibición oficial de los trabajos se realizará el 29 de octubre del presente. La inscripción es gratuita y se realizará exclusivamente de manera virtual. Los participantes deberán presentar el cortometraje en formato MP4 H.264 Full HD o 4K, además del póster, teaser y la evidencia del curso universitario y docente responsable. Un espacio para reconocer el talento emergente Los trabajos serán evaluados por un comité especializado, que considerará criterios como la originalidad, la coherencia narrativa y la resolución técnica. El festival otorgará un reconocimiento al mejor cortometraje y menciones honrosas al segundo mejor trabajo de cada categoría. Además, los equipos seleccionados recibirán constancias de participación. Acerca del Festival Ojo Errante El Festival de Cortometrajes Universitarios Ojo Errante es una plataforma cultural y académica impulsada por el Programa de Estudio de Comunicación y Medios Digitales de la UPAO. De este modo se promueve la visibilidad, circulación y experimentación de la producción audiovisual realizada por jóvenes universitarios. A través de proyecciones presenciales, circuitos itinerantes y espacios formativos en Piura, el festival fomenta el desarrollo de la industria cinematográfica emergente desde las regiones. Para más detalles o información, los interesados pueden comunicarse través del siguiente correo: [email protected]</t>
+          <t>La violencia criminal golpeó nuevamente a la región Piura . En menos de 72 horas, ocho personas fueron asesinadas en distintos hechos registrados en Sullana, Castilla, Paita y Talara. Entre las víctimas se encuentra un menor de 13 años y tres personas que murieron durante un ataque armado ocurrido en el asentamiento humano Manuel Seoane, en Sullana. Los homicidios se registraron entre la noche del domingo 6 y el lunes 7 de setiembre, en una seguidilla de hechos violentos que también dejó personas heridas y motivó operativos policiales en diferentes puntos de la región. Los casos presentan características similares, como el uso de armas de fuego y, en algunos ataques, la participación de sujetos que se movilizaban en motocicletas. Sin embargo, hasta el momento no existe información oficial que permita establecer que todos los crímenes estén relacionados. ¿Quiénes son las ocho víctimas asesinadas en Piura? El balance de los hechos registrados en este periodo incluye a Alexis Arellano Gómez , asesinado en el sector Salaverry de Sullana; Fernando Castillo , víctima de un ataque en Castilla; y Giancarlo Jiménez Hernández , asesinado en Paita Alta. A ellos se suma un adolescente de 13 años , asesinado la noche del domingo en Sullana. También figuran las tres víctimas mortales del ataque ocurrido la noche del lunes en Manuel Seoane: Sheyla Viera Elías, Lady Lore Valdiviezo Nole y Daniel Alfonso Páucar Manchay . El octavo caso corresponde a un hombre conocido como “Van Dan” , quien había trabajado como sereno y fue asesinado en el distrito de La Brea-Negritos, en la provincia de Talara. Sullana: asesinan a menor de 13 años en un mototaxi Uno de los casos que más conmoción provocó ocurrió la noche del domingo en Sullana. Un adolescente de 13 años fue asesinado cuando viajaba como pasajero en un mototaxi por la intersección de la calle Túpac Amaru con la avenida Par Vial, en el asentamiento humano 17 de Enero. El ataque ocurrió aproximadamente a las 10:40 de la noche. Según las primeras diligencias, el vehículo habría quedado detenido debido a un desperfecto mecánico. En ese momento, sujetos que se desplazaban en una motocicleta llegaron hasta el mototaxi y dispararon contra el menor. Uno de los proyectiles impactó en su cabeza y le provocó la muerte en el lugar. Sus acompañantes huyeron de la zona, mientras la víctima quedó junto al vehículo. Un tatuaje permitió identificar al adolescente La identificación del menor se realizó posteriormente en la morgue legal. Una familiar acudió ante las autoridades y logró reconocerlo por un tatuaje que llevaba en el brazo derecho con el nombre “Alexander”. La Policía continúa con las diligencias para establecer las circunstancias exactas del crimen. Entre las hipótesis preliminares figura un posible ajuste de cuentas, aunque esta versión todavía debe ser corroborada por los investigadores. Alexis Arellano Gómez fue asesinado en Sullana Otro de los homicidios registrados durante este periodo ocurrió en el sector Salaverry, en Sullana. La víctima fue identificada como Alexis Arellano Gómez . El asesinato forma parte de los hechos violentos registrados durante estas horas en la provincia. La Policía inició las diligencias correspondientes para recoger evidencias, identificar a los responsables y establecer el móvil del ataque. Fernando Castillo fue asesinado en Castilla La ola de violencia también alcanzó Castilla, en la provincia de Piura. Fernando Castillo fue asesinado en circunstancias que son investigadas por las autoridades. El caso se suma a los demás homicidios registrados en la región durante el mismo periodo. Los agentes buscan reconstruir los momentos previos al crimen y determinar quiénes participaron en el ataque. Paita: asesinan a Giancarlo Jiménez Hernández En Paita Alta, Giancarlo Jiménez Hernández, de 33 años , fue asesinado la noche del lunes durante un ataque perpetrado por sujetos que se movilizaban en una motocicleta. El joven caminaba junto a William Daniel Aldana Prado , de 24 años, por la parte posterior de las empresas de transporte Andrea y Santangel cuando fueron interceptados. Según la información preliminar, el pasajero de la motocicleta sacó un arma de fuego y disparó contra ambos. Los heridos fueron trasladados de emergencia al Hospital Nuestra Señora de las Mercedes. Sin embargo, el médico de turno certificó la muerte de Giancarlo Jiménez debido a una hemorragia intracraneal provocada por un proyectil de arma de fuego. William Aldana quedó gravemente herido y permanecía con pronóstico reservado. Dos sospechosos fueron capturados Tras el ataque, agentes de la Comisaría Ciudad del Pescador iniciaron la búsqueda de los responsables. La motocicleta fue ubicada en inmediaciones del colegio Lunitas de Paita y los policías iniciaron una persecución. El conductor, identificado con las iniciales C. A. T. D., de 20 años, fue intervenido. De acuerdo con la información proporcionada, durante el operativo se le encontró un cartucho de dinamita. El pasajero huyó a pie y, según la versión policial, realizó disparos contra los agentes antes de refugiarse en una vivienda. Finalmente fue detenido e identificado con las iniciales L. J. Ch. N., de 25 años. Los agentes le habrían encontrado un arma de fuego. Talara: exsereno es asesinado dentro de un restaurante Otro de los crímenes ocurrió en la provincia de Talara. Un hombre conocido como “Van Dan” , quien había trabajado como sereno y era propietario de un gimnasio en el distrito de La Brea-Negritos, fue asesinado dentro del restaurante La Caleta 10, ubicado en el asentamiento Mario Aguirre. Según la información preliminar, un sujeto irrumpió en el segundo piso del establecimiento y disparó varias veces contra la víctima. El hombre murió pocos segundos después del ataque. La Policía investiga las circunstancias del homicidio y busca establecer si existieron amenazas previas, conflictos personales u otros elementos que permitan determinar el móvil. Sullana: tres personas mueren en ataque armado en Manuel Seoane La noche del lunes 7 de setiembre, un ataque armado registrado en un puesto de venta de comida ubicado en el pasaje Municipal del asentamiento humano Manuel Seoane, en Sullana, dejó tres personas fallecidas y una herida de gravedad . De acuerdo con la información preliminar, varios sujetos armados llegaron hasta el establecimiento y dispararon contra un grupo de personas que se encontraba reunido alrededor de una mesa. Como consecuencia del atentado perdieron la vida Sheyla Viera Elías, Lady Lore Valdiviezo Nole y Daniel Alfonso Páucar Manchay . Asimismo, Carlos Daniel Cornejo Lupú resultó gravemente herido y fue trasladado a un establecimiento de salud para recibir atención médica. Criminalística recogió evidencias en la escena Tras el ataque, agentes de la División de Investigación Criminal (Divincri) y personal de Criminalística acudieron al lugar para realizar las diligencias correspondientes. Los especialistas recogieron evidencias e indicios balísticos que podrían ayudar a reconstruir el ataque e identificar a los responsables. Las autoridades también iniciaron las investigaciones para determinar el móvil del triple homicidio. Una de las víctimas estaba embarazada Entre las víctimas se encontraba Lady Lore Valdiviezo Nole, de 28 años , quien tenía aproximadamente seis meses de gestación. De acuerdo con la información proporcionada por sus familiares, la joven se dedicaba a la venta de parrilladas y hamburguesas durante fiestas, aniversarios y actividades patronales. Su hermana Greysi relató que ambas venían preparando actividades comerciales relacionadas con el aniversario del distrito de Ignacio Escudero. Según su versión, Loren había salido inicialmente de la vivienda donde ocurrió el ataque, pero decidió regresar. Poco después se escucharon los disparos. La familia pidió a las autoridades esclarecer el crimen y determinar quiénes estuvieron detrás del ataque. ¿Qué investiga la Policía tras los ocho asesinatos? Los ocho homicidios registrados en este periodo ocurrieron en diferentes puntos de Piura. Por ello, las autoridades deberán determinar si existe alguna relación entre los casos o si se trata de hechos independientes. El uso de armas de fuego y la participación de motocicletas en algunos de los ataques son elementos que forman parte de las diligencias. No obstante, establecer una conexión entre los crímenes requiere evidencias que todavía están siendo recopiladas. Piura permanece bajo medidas contra la criminalidad Los nuevos asesinatos se producen mientras diferentes sectores de la región permanecen bajo medidas especiales frente al incremento de la inseguridad. El Gobierno declaró el estado de emergencia en Piura, Castilla, Veintiséis de Octubre y Catacaos mediante el Decreto Supremo N.° 126-2026. Para el exjefe de la Región Policial de Piura, coronel en retiro Máximo Vargas Hugo, este tipo de medidas no ha generado los resultados que reclama la población. El exmando policial consideró necesario fortalecer la labor policial con recursos, logística e inteligencia. “La población quiere seguridad y están repitiendo lo mismo que han hecho gestiones anteriores”, señaló Vargas Hugo al referirse a las declaratorias de emergencia aplicadas en la región. Sobre el cambio en el comando de la Policía, sostuvo que una modificación en el alto mando no garantiza por sí sola mejores resultados y remarcó la necesidad de proporcionar herramientas adecuadas a los agentes para enfrentar a las organizaciones criminales. Por su parte, el general Daniel Jares, jefe de la Región Policial Piura, informó que durante los primeros días de setiembre se habían contabilizado 12 personas asesinadas . Esta cifra corresponde a un periodo más amplio y no debe confundirse con los ocho homicidios registrados en menos de 72 horas detallados en este reporte.</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>https://eltiempo.pe/local/upao-piura-lleva-el-cine-universitario-a-una-nueva-edicion-del-festival-ojo-errante/</t>
+          <t>https://eltiempo.pe/local/piura-en-menos-de-72-horas-delincuentes-asesinan-a-ocho-personas-en-la-region/</t>
         </is>
       </c>
     </row>
@@ -894,17 +888,17 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>¿Quiénes estuvieron detrás de asesinatos en Sullana?</t>
+          <t>ODPE Piura recibe material para capacitar a actores electorales</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>La violencia criminal continúa golpeando a la provincia de Sullana. Con los últimos hechos de sangre, ya son 46 las personas asesinadas por sicarios en lo que va del año, mientras que sólo en los primeros días de septiembre se han registrado cuatro homicidios, situación que mantiene preocupada a la población. Sin embargo, se abre la interrogante sobre el último episodio: ¿quienes estuvieron detrás del execrable baño de sangre? Alcohol, bala y tragedia El último ataque ocurrió en el sector Manuel Seoane, donde dos mujeres fueron asesinadas a balazos y otros dos sujetos quedaron heridos cuando se encontraban en una vivienda departiendo bebidas alcohólicas junto a otras personas. Una de las víctimas mortales fue identificada como Loren Valdiviezo Nole, de 28 años, quien se encontraba en estado de gestación. La joven deja en la orfandad a tres menores de edad. Retorno mortal Sus familiares exigieron a la Policía esclarecer el crimen y determinar quiénes estuvieron detrás del ataque. Aseguraron que Loren no tenía problemas con ninguna persona y que nunca había recibido amenazas. Se dedicaba a la venta de parrilladas y hamburguesas durante fiestas de aniversario y celebraciones patronales. Precisamente, junto a su hermana Greysi se encontraba preparando sus actividades comerciales para el aniversario del distrito de Ignacio Escudero. Según relató Greysi, la noche del crimen Loren ya había salido de la vivienda atacada, pero decidió regresar. Minutos después se escucharon los disparos. Estuvo en el lugar equivocado “Mi hermana estuvo en el lugar equivocado, es lo único que podemos decir, solo queremos que se esclarezca lo ocurrido”, manifestó Greysi Valdiviezo al diario La Hora. La segunda dama asesinada, Sheila Anabelen Viera Elías (30), quien también deja en la orfandad a tres niños, sus familiares, evitaron dar declaraciones y mayores detalles de lo ocurrido. La mañana de ayer su padre esperaba que culminara la necropsia en la morgue legal para retirar el cuerpo y trasladarlo a la calle Cusco, cuadra 8, en Bellavista, donde será velado. La Policía, desde la misma noche del lunes, puso en marcha un operativo que ayer dio resultados con la detención de un gatillero.</t>
+          <t>En el marco de las Elecciones Regionales y Municipales (ERM) 2026, la Oficina Descentralizada de Procesos Electorales (ODPE) Piura recibió el material de capacitación que será empleado en la preparación de los diversos actores electorales que participarán en los comicios del próximo 4 de octubre. Puedes Leer | Bajo Piura se levanta y exige obras para evitar inundación El cargamento, remitido desde el almacén central de la Gerencia de Gestión Electoral de la ONPE en Lurín, arribó a la sede de la ODPE Piura bajo protocolos de seguridad y resguardo para su inmediata verificación, almacenamiento y posterior distribución en los distritos y centros poblados bajo su jurisdicción. Entre los instrumentos recibidos se encuentran materiales pedagógicos que replican con exactitud las condiciones de una mesa de sufragio, los cuales serán utilizados en los talleres que se desarrollarán en las oficinas distritales de la circunscripción electoral, así como en las jornadas masivas de capacitación a miembros de mesa programadas para los días 20 y 27 de setiembre. Asimismo, arribó insumos didácticos dirigidos a los talleres de formación de capacitadores electorales, coordinadores distritales, coordinadores de local de votación y personal de campo que desplegará acciones informativas en los distritos. Mira También | Advierten incremento de casos de cáncer infantil en Piura El jefe de la ODPE Piura, Juan Roel Godofredo Valdivia, señaló que la preparación de los actores electorales constituye una etapa fundamental para garantizar el adecuado desarrollo de los comicios y destacó la importancia de que quienes participarán en la jornada conozcan oportunamente las tareas y responsabilidades que deberán cumplir. Para estos comicios, el organismo electoral instalará en los distritos Piura y Veintiséis de Octubre un total de 884 mesas de sufragio en 67 locales de votación, donde están llamados a sufragar aproximadamente 264 809 electores hábiles. Más información https://erm2026.onpe.gob.pe</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>https://eltiempo.pe/local/quienes-estuvieron-detras-de-asesinatos-en-sullana/</t>
+          <t>https://eltiempo.pe/local/odpe-piura-recibe-material-para-capacitar-a-actores-electorales/</t>
         </is>
       </c>
     </row>
@@ -919,17 +913,17 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Piura: en menos de 72 horas, delincuentes asesinan a ocho personas en la región</t>
+          <t>Dos gatilleros matan a sujeto y hieren a otro en Paita, pero Policía los captura</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>La violencia criminal golpeó nuevamente a la región Piura . En menos de 72 horas, ocho personas fueron asesinadas en distintos hechos registrados en Sullana, Castilla, Paita y Talara. Entre las víctimas se encuentra un menor de 13 años y tres personas que murieron durante un ataque armado ocurrido en el asentamiento humano Manuel Seoane, en Sullana. Los homicidios se registraron entre la noche del domingo 6 y el lunes 7 de setiembre, en una seguidilla de hechos violentos que también dejó personas heridas y motivó operativos policiales en diferentes puntos de la región. Los casos presentan características similares, como el uso de armas de fuego y, en algunos ataques, la participación de sujetos que se movilizaban en motocicletas. Sin embargo, hasta el momento no existe información oficial que permita establecer que todos los crímenes estén relacionados. ¿Quiénes son las ocho víctimas asesinadas en Piura? El balance de los hechos registrados en este periodo incluye a Alexis Arellano Gómez , asesinado en el sector Salaverry de Sullana; Fernando Castillo , víctima de un ataque en Castilla; y Giancarlo Jiménez Hernández , asesinado en Paita Alta. A ellos se suma un adolescente de 13 años , asesinado la noche del domingo en Sullana. También figuran las tres víctimas mortales del ataque ocurrido la noche del lunes en Manuel Seoane: Sheyla Viera Elías, Lady Lore Valdiviezo Nole y Daniel Alfonso Páucar Manchay . El octavo caso corresponde a un hombre conocido como “Van Dan” , quien había trabajado como sereno y fue asesinado en el distrito de La Brea-Negritos, en la provincia de Talara. Sullana: asesinan a menor de 13 años en un mototaxi Uno de los casos que más conmoción provocó ocurrió la noche del domingo en Sullana. Un adolescente de 13 años fue asesinado cuando viajaba como pasajero en un mototaxi por la intersección de la calle Túpac Amaru con la avenida Par Vial, en el asentamiento humano 17 de Enero. El ataque ocurrió aproximadamente a las 10:40 de la noche. Según las primeras diligencias, el vehículo habría quedado detenido debido a un desperfecto mecánico. En ese momento, sujetos que se desplazaban en una motocicleta llegaron hasta el mototaxi y dispararon contra el menor. Uno de los proyectiles impactó en su cabeza y le provocó la muerte en el lugar. Sus acompañantes huyeron de la zona, mientras la víctima quedó junto al vehículo. Un tatuaje permitió identificar al adolescente La identificación del menor se realizó posteriormente en la morgue legal. Una familiar acudió ante las autoridades y logró reconocerlo por un tatuaje que llevaba en el brazo derecho con el nombre “Alexander”. La Policía continúa con las diligencias para establecer las circunstancias exactas del crimen. Entre las hipótesis preliminares figura un posible ajuste de cuentas, aunque esta versión todavía debe ser corroborada por los investigadores. Alexis Arellano Gómez fue asesinado en Sullana Otro de los homicidios registrados durante este periodo ocurrió en el sector Salaverry, en Sullana. La víctima fue identificada como Alexis Arellano Gómez . El asesinato forma parte de los hechos violentos registrados durante estas horas en la provincia. La Policía inició las diligencias correspondientes para recoger evidencias, identificar a los responsables y establecer el móvil del ataque. Fernando Castillo fue asesinado en Castilla La ola de violencia también alcanzó Castilla, en la provincia de Piura. Fernando Castillo fue asesinado en circunstancias que son investigadas por las autoridades. El caso se suma a los demás homicidios registrados en la región durante el mismo periodo. Los agentes buscan reconstruir los momentos previos al crimen y determinar quiénes participaron en el ataque. Paita: asesinan a Giancarlo Jiménez Hernández En Paita Alta, Giancarlo Jiménez Hernández, de 33 años , fue asesinado la noche del lunes durante un ataque perpetrado por sujetos que se movilizaban en una motocicleta. El joven caminaba junto a William Daniel Aldana Prado , de 24 años, por la parte posterior de las empresas de transporte Andrea y Santangel cuando fueron interceptados. Según la información preliminar, el pasajero de la motocicleta sacó un arma de fuego y disparó contra ambos. Los heridos fueron trasladados de emergencia al Hospital Nuestra Señora de las Mercedes. Sin embargo, el médico de turno certificó la muerte de Giancarlo Jiménez debido a una hemorragia intracraneal provocada por un proyectil de arma de fuego. William Aldana quedó gravemente herido y permanecía con pronóstico reservado. Dos sospechosos fueron capturados Tras el ataque, agentes de la Comisaría Ciudad del Pescador iniciaron la búsqueda de los responsables. La motocicleta fue ubicada en inmediaciones del colegio Lunitas de Paita y los policías iniciaron una persecución. El conductor, identificado con las iniciales C. A. T. D., de 20 años, fue intervenido. De acuerdo con la información proporcionada, durante el operativo se le encontró un cartucho de dinamita. El pasajero huyó a pie y, según la versión policial, realizó disparos contra los agentes antes de refugiarse en una vivienda. Finalmente fue detenido e identificado con las iniciales L. J. Ch. N., de 25 años. Los agentes le habrían encontrado un arma de fuego. Talara: exsereno es asesinado dentro de un restaurante Otro de los crímenes ocurrió en la provincia de Talara. Un hombre conocido como “Van Dan” , quien había trabajado como sereno y era propietario de un gimnasio en el distrito de La Brea-Negritos, fue asesinado dentro del restaurante La Caleta 10, ubicado en el asentamiento Mario Aguirre. Según la información preliminar, un sujeto irrumpió en el segundo piso del establecimiento y disparó varias veces contra la víctima. El hombre murió pocos segundos después del ataque. La Policía investiga las circunstancias del homicidio y busca establecer si existieron amenazas previas, conflictos personales u otros elementos que permitan determinar el móvil. Sullana: tres personas mueren en ataque armado en Manuel Seoane La noche del lunes 7 de setiembre, un ataque armado registrado en un puesto de venta de comida ubicado en el pasaje Municipal del asentamiento humano Manuel Seoane, en Sullana, dejó tres personas fallecidas y una herida de gravedad . De acuerdo con la información preliminar, varios sujetos armados llegaron hasta el establecimiento y dispararon contra un grupo de personas que se encontraba reunido alrededor de una mesa. Como consecuencia del atentado perdieron la vida Sheyla Viera Elías, Lady Lore Valdiviezo Nole y Daniel Alfonso Páucar Manchay . Asimismo, Carlos Daniel Cornejo Lupú resultó gravemente herido y fue trasladado a un establecimiento de salud para recibir atención médica. Criminalística recogió evidencias en la escena Tras el ataque, agentes de la División de Investigación Criminal (Divincri) y personal de Criminalística acudieron al lugar para realizar las diligencias correspondientes. Los especialistas recogieron evidencias e indicios balísticos que podrían ayudar a reconstruir el ataque e identificar a los responsables. Las autoridades también iniciaron las investigaciones para determinar el móvil del triple homicidio. Una de las víctimas estaba embarazada Entre las víctimas se encontraba Lady Lore Valdiviezo Nole, de 28 años , quien tenía aproximadamente seis meses de gestación. De acuerdo con la información proporcionada por sus familiares, la joven se dedicaba a la venta de parrilladas y hamburguesas durante fiestas, aniversarios y actividades patronales. Su hermana Greysi relató que ambas venían preparando actividades comerciales relacionadas con el aniversario del distrito de Ignacio Escudero. Según su versión, Loren había salido inicialmente de la vivienda donde ocurrió el ataque, pero decidió regresar. Poco después se escucharon los disparos. La familia pidió a las autoridades esclarecer el crimen y determinar quiénes estuvieron detrás del ataque. ¿Qué investiga la Policía tras los ocho asesinatos? Los ocho homicidios registrados en este periodo ocurrieron en diferentes puntos de Piura. Por ello, las autoridades deberán determinar si existe alguna relación entre los casos o si se trata de hechos independientes. El uso de armas de fuego y la participación de motocicletas en algunos de los ataques son elementos que forman parte de las diligencias. No obstante, establecer una conexión entre los crímenes requiere evidencias que todavía están siendo recopiladas. Piura permanece bajo medidas contra la criminalidad Los nuevos asesinatos se producen mientras diferentes sectores de la región permanecen bajo medidas especiales frente al incremento de la inseguridad. El Gobierno declaró el estado de emergencia en Piura, Castilla, Veintiséis de Octubre y Catacaos mediante el Decreto Supremo N.° 126-2026. Para el exjefe de la Región Policial de Piura, coronel en retiro Máximo Vargas Hugo, este tipo de medidas no ha generado los resultados que reclama la población. El exmando policial consideró necesario fortalecer la labor policial con recursos, logística e inteligencia. “La población quiere seguridad y están repitiendo lo mismo que han hecho gestiones anteriores”, señaló Vargas Hugo al referirse a las declaratorias de emergencia aplicadas en la región. Sobre el cambio en el comando de la Policía, sostuvo que una modificación en el alto mando no garantiza por sí sola mejores resultados y remarcó la necesidad de proporcionar herramientas adecuadas a los agentes para enfrentar a las organizaciones criminales. Por su parte, el general Daniel Jares, jefe de la Región Policial Piura, informó que durante los primeros días de setiembre se habían contabilizado 12 personas asesinadas . Esta cifra corresponde a un periodo más amplio y no debe confundirse con los ocho homicidios registrados en menos de 72 horas detallados en este reporte.</t>
+          <t>A cinco se incrementaron los asesinatos del pasado lunes en la región, luego que gatilleros motorizados asesinaran a tiros a joven en Paita alta y dejarán gravemente herido a su amigo. Esta vez, la Policía Nacional en rápida repuesta capturó a balazos dos sospechosos, incautando una motocicleta y un arma de fuego. Transcurría las 9:50 de la noche del lunes, cuando los amigos Giancarlo Jiménez Hernández, de 33 años, y William Daniel Aldana Prado, de 24 años, caminaban por la parte posterior de las empresas de transporte Andrea y Santangel, fueron interceptados por una motocicleta. Disparó a matar El sujeto que iba como pasajero sacó un arma de fuego y disparó a matar contra los dos amigos. Los ocupantes de la motocicleta al ver caer a sus blancos se dieron a la fuga por las calles de Paita Alta. Los dos amigos gravemenre heridos fueron socorridos y trasladados de emergencia al Hospital Nuestra Señora de las Mercedes.Lamentablemente, el médico de turno, Ricardo Pereira certificó la muerte de Giancarlo Jiménez por hemorragia intercraneal por disparo de arma de fuego. En tanto, dio el diagnóstico oara Willian Aldaba de traumatismo abdominal abierto por proyectil con arma de fuego. Su estado de salud es de pronostico reservado. Persecución y captura Un grupo de agentes de la Comisaría Ciudad del Pescador con las características de la moto y los sujetos a inmediaciones del colegio “Lunitas de Paita” localizó la motocicleta, modelo Triax, de placa de rodaje 1764-GP. Luego de una tenaz persecución capturó al conductor C. A. T. D. (20), el mismo que portaba un cartucho de dinamita. El pasajero de la moto huyó a pie realizando disparos contra la policía, bajo fuego cruzado se refugió en una vivienda donde finalmente fue detenido siendo identificado con las iniciales L. J. Ch. N. (25). Los custodios le hallaron un arma de fuego.</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>https://eltiempo.pe/local/piura-en-menos-de-72-horas-delincuentes-asesinan-a-ocho-personas-en-la-region/</t>
+          <t>https://eltiempo.pe/local/dos-gatilleros-matan-a-sujeto-y-hieren-a-otro-en-paita-pero-policia-los-captura/</t>
         </is>
       </c>
     </row>
@@ -969,17 +963,17 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>ODPE Piura recibe material para capacitar a actores electorales</t>
+          <t>Advierten que la sensación del calor podría llegar a los 39°C en la región Piura</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>En el marco de las Elecciones Regionales y Municipales (ERM) 2026, la Oficina Descentralizada de Procesos Electorales (ODPE) Piura recibió el material de capacitación que será empleado en la preparación de los diversos actores electorales que participarán en los comicios del próximo 4 de octubre. Puedes Leer | Bajo Piura se levanta y exige obras para evitar inundación El cargamento, remitido desde el almacén central de la Gerencia de Gestión Electoral de la ONPE en Lurín, arribó a la sede de la ODPE Piura bajo protocolos de seguridad y resguardo para su inmediata verificación, almacenamiento y posterior distribución en los distritos y centros poblados bajo su jurisdicción. Entre los instrumentos recibidos se encuentran materiales pedagógicos que replican con exactitud las condiciones de una mesa de sufragio, los cuales serán utilizados en los talleres que se desarrollarán en las oficinas distritales de la circunscripción electoral, así como en las jornadas masivas de capacitación a miembros de mesa programadas para los días 20 y 27 de setiembre. Asimismo, arribó insumos didácticos dirigidos a los talleres de formación de capacitadores electorales, coordinadores distritales, coordinadores de local de votación y personal de campo que desplegará acciones informativas en los distritos. Mira También | Advierten incremento de casos de cáncer infantil en Piura El jefe de la ODPE Piura, Juan Roel Godofredo Valdivia, señaló que la preparación de los actores electorales constituye una etapa fundamental para garantizar el adecuado desarrollo de los comicios y destacó la importancia de que quienes participarán en la jornada conozcan oportunamente las tareas y responsabilidades que deberán cumplir. Para estos comicios, el organismo electoral instalará en los distritos Piura y Veintiséis de Octubre un total de 884 mesas de sufragio en 67 locales de votación, donde están llamados a sufragar aproximadamente 264 809 electores hábiles. Más información https://erm2026.onpe.gob.pe</t>
+          <t>El Senamhi Piura informó que durante el mes, se registraron temperaturas de hasta 37,2°C en Chulucanas, Piura. No descartan que la sensación de calor pueda alcanzar los 39 °C en Piura. Así lo señaló el especialista del Senamhi Piura, Héctor Yauri quien indicó que este panorama se podría dar por diversos factores, con lo cual la población deberá tomar sus precauciones. El Senamhi informó que durante las últimas semanas las temperaturas se han mantenido por encima de sus valores normales, especialmente las temperaturas máximas. MAGNITUD FUERTE Explican que esta situación estaría “asociada principalmente a la persistencia de anomalías positivas de la temperatura superficial del mar frente a la costa de Piura y en la región Niño 1+2”. “Se espera que las temperaturas del aire continúen registrando valores relativamente elevados durante las próximas semanas, debido a la persistencia de temperaturas superficiales del mar por encima de lo normal en la región Niño 1+2. Estas condiciones son consistentes con la evolución del evento Niño Costero, que actualmente presenta magnitud fuerte, favoreciendo la persistencia de temperaturas superiores a los valores climatológicos para la temporada”, indicó el especialista Fabricio Fabián Herrera. Asimismo, de acuerdo al aviso meteorológico 161 del Senamhi, no se descarta lluvias dispersas en la costa norte y la presencia de lluvias localizadas en la sierra norte.</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>https://eltiempo.pe/local/odpe-piura-recibe-material-para-capacitar-a-actores-electorales/</t>
+          <t>https://eltiempo.pe/local/advierten-que-la-sensacion-del-calor-podria-llegar-a-los-39c-en-la-region-piura/</t>
         </is>
       </c>
     </row>
@@ -990,21 +984,21 @@
         </is>
       </c>
       <c r="B20" s="2" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>El Niño superaría al de 1998 y traería impactos “insospechados” en la región Piura</t>
+          <t>Bajo Piura se levanta y exige obras para evitar inundación</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>El fenómeno “El Niño” (FEN) sigue acumulando energía en el mar frente a las costas de la región y los impactos de este calentamiento son hasta el momento insospechados, según informó el especialista en meteorología del Senamhi Piura, Héctor Yauli. PUEDES LEER ► Es hora de rescatar la cultura de Piura De lo que sí se tiene mayor certeza es que los indicadores de este fenómeno en desarrollo ya superaron los valores previos al Mega Niño que castigó la región entre los años 1997 y 1998. “Lo que ha dicho el Organismo Mundial de Meteorología es que los impactos que pueda generar este Niño en el contexto en el cual se presenta, porque el nivel de calentamiento es muy exacerbado y no se tiene comparación con los años 1997 y 1998. Es una gran cantidad de energía y calor no solamente en la zona tropical donde se desarrolla El Niño sino en todos los océanos el nivel de calentamiento es muy mayor. Se esperan impactos insospechados por la alta incertidumbre que hay. [...] Lo que sí tenemos mucha seguridad es en cuanto a que se van a presentar lluvias bastante fuertes e intensas en los meses de verano”, manifestó. Sobre la magnitud, Yauri indicó que existe una incertidumbre sobre los niveles que se alcanzarán las precipitaciones. Cabe indicar que durante el Mega Niño de 1998, se registró la máxima precipitación el 24 de enero con un valor de 173.6 milímetros de acumulado en una sola lluvia. Esto implica que ese día cayeron más de 173 litros de agua sobre un metro cuadrado. Peores En este punto, Yauli informó que el escenario es mucho más complicado porque no solo es un calentamiento del mar frente a la costa norte, sino en diferentes partes del mundo. “Es un nivel de calentamiento exacerbado que no tiene comparación. Si nos situamos en septiembre de 1997, solamente veíamos el calentamiento de El Niño, pero el océano Pacífico en el norte estaba en condiciones normales, en Chile estaba normal y en el Atlántico igual. Sin embargo, ahora está caliente el norte y sur del Pacífico, e incluso en el Atlántico también está caliente y eso trae otras implicancias y diferente tipo de impactos vinculados a que habrá mucha lluvia en la zona norte del Perú y bastante deficiencia de lluvias en la zona noroeste de Brasil”, destacó Yauli.</t>
+          <t>La población no quiere ser expectante de como apenas siete maquinarias pesadas trabajan en la descolmatación del río Piura, desde el puente Grau hasta el puente Independencia, sin haberse considerado obras adicionales como el reforzamiento de las defensas ribereñas, los diques de contención, entre otras obras que permitan mitigar el impacto del Fenómeno El Niño (FEN) que se avecina. Por ello ayer, y tras una asamblea, dirigentes de los distritos de Catacaos, Cura Mori y El Tallán acordaron realizar una marcha de protesta el 14 de setiembre a partir de las 8:00 a.m. bajo el lema “Inundación nunca más”. La población está dispuesta a bloquear las vías hasta ser escuchados por las autoridades. «Es una burla» Víctor Chunga, presidente del Frente de reconstrucción de pueblos afectados por el Niño Costero 2017, calificó como una “burla” que en su primera visita a Piura la presidenta Keiko Fujimori anunciara una inversión de 140 millones y un pull de maquinaria para los trabajos de descolmatación y no se está cumpliendo. “Anunció 140 millones, luego 129 millones, pero no está desglosado cuánto le toca a Piura y los trabajos no van ni al 30%. Ahora en la descolmatación (hacia el Bajo Piura) solo están retirando 90 centímetros de sedimento, eso es limpieza no descolmatación”, indicó. Para octubre prometen terminar descolmatación Tras la denuncia del diputado Félix Chang Apuy, sobre la paralización de los trabajos de descolmatación del río Piura, el supervisor de estos trabajos, Ítalo Cuba, señaló que ya solucionaron el tema administrativo de los contratos del personal y se ha retomado los trabajos en el tramo entre la represa Los Ejidos y el puente Bolognesi. Informó que 20 maquinarias pesadas del Gobierno Regional se sumarán a los trabajos, con lo cual esperan culminar los mismos antes de las lluvias pronosticadas para noviembre. “A mediados de octubre se quiere terminar todo esto”, indicó el supervisor quien agregó que buscan recuperar un encausamiento del río con capacidad para 3000 m3/s.</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>https://eltiempo.pe/local/el-nino-traera-unos-impactos-insospechados-en-la-region-piura/</t>
+          <t>https://eltiempo.pe/local/bajo-piura-se-levanta-y-exige-obras-para-evitar-inundacion/</t>
         </is>
       </c>
     </row>
@@ -1015,21 +1009,21 @@
         </is>
       </c>
       <c r="B21" s="2" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Los SARE siguen sin mantenimiento para funcionar durante las lluvias</t>
+          <t>¿Quiénes estuvieron detrás de asesinatos en Sullana?</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Diferentes informes de las oficinas de control institucional del Programa Nacional de Saneamiento Urbano (PNSU) dan cuenta del estado de abandono en su mantenimiento de los Sistemas Alternativos de Recolección y Evacuación de aguas de lluvia (SARE) que se habilitaron en Piura y que costaron millones de soles. Un ejemplo es lo que ocurre en el SARE Cinco Esquinas que costó más de 28 millones de soles, pero ni siquiera tiene un cerco perimétrico para proteger los costosos equipos instalados a pesar de los años pasados. “El grupo electrógeno y la electrobomba constituyen equipos necesarios para el funcionamiento del sistema de bombeo y la evacuación, por lo que su exposición en un área sin control físico permanente de acceso podría afectar su seguridad, conservación y disponibilidad cuando sean requeridos para la operación del SARE”, se lee en el informe de control. De otro lado, el SARE de Ignacio Merino, valorizado en 15 millones de soles, también tiene problemas de falta de mantenimiento. “La falta de culminación de la transferencia legal integral y la ausencia de un marco procedimental que regule las obligaciones de custodia operativa provisoria han provocado que un sistema pluvial de gran inversión (S/ 17.1 millones) no registre ningún tipo de mantenimiento preventivo sobre sus componentes críticos. Esto neutraliza la capacidad de respuesta instalada para salvaguardar a las urbanizaciones del distrito de Piura”, se indica en el documento de Contraloría. Entre las principales observaciones se tiene la acumulación de sedimentos en canaletas cunetas de las vías.</t>
+          <t>La violencia criminal continúa golpeando a la provincia de Sullana. Con los últimos hechos de sangre, ya son 46 las personas asesinadas por sicarios en lo que va del año, mientras que sólo en los primeros días de septiembre se han registrado cuatro homicidios, situación que mantiene preocupada a la población. Sin embargo, se abre la interrogante sobre el último episodio: ¿quienes estuvieron detrás del execrable baño de sangre? Alcohol, bala y tragedia El último ataque ocurrió en el sector Manuel Seoane, donde dos mujeres fueron asesinadas a balazos y otros dos sujetos quedaron heridos cuando se encontraban en una vivienda departiendo bebidas alcohólicas junto a otras personas. Una de las víctimas mortales fue identificada como Loren Valdiviezo Nole, de 28 años, quien se encontraba en estado de gestación. La joven deja en la orfandad a tres menores de edad. Retorno mortal Sus familiares exigieron a la Policía esclarecer el crimen y determinar quiénes estuvieron detrás del ataque. Aseguraron que Loren no tenía problemas con ninguna persona y que nunca había recibido amenazas. Se dedicaba a la venta de parrilladas y hamburguesas durante fiestas de aniversario y celebraciones patronales. Precisamente, junto a su hermana Greysi se encontraba preparando sus actividades comerciales para el aniversario del distrito de Ignacio Escudero. Según relató Greysi, la noche del crimen Loren ya había salido de la vivienda atacada, pero decidió regresar. Minutos después se escucharon los disparos. Estuvo en el lugar equivocado “Mi hermana estuvo en el lugar equivocado, es lo único que podemos decir, solo queremos que se esclarezca lo ocurrido”, manifestó Greysi Valdiviezo al diario La Hora. La segunda dama asesinada, Sheila Anabelen Viera Elías (30), quien también deja en la orfandad a tres niños, sus familiares, evitaron dar declaraciones y mayores detalles de lo ocurrido. La mañana de ayer su padre esperaba que culminara la necropsia en la morgue legal para retirar el cuerpo y trasladarlo a la calle Cusco, cuadra 8, en Bellavista, donde será velado. La Policía, desde la misma noche del lunes, puso en marcha un operativo que ayer dio resultados con la detención de un gatillero.</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>https://eltiempo.pe/local/los-sare-siguen-sin-mantenimiento-para-funcionar-durante-las-lluvias/</t>
+          <t>https://eltiempo.pe/local/quienes-estuvieron-detras-de-asesinatos-en-sullana/</t>
         </is>
       </c>
     </row>
@@ -1040,21 +1034,21 @@
         </is>
       </c>
       <c r="B22" s="2" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Refuerzan la vigilancia de flamencos en humedales de Sechura</t>
+          <t>UPAO Piura lleva el cine universitario a una nueva edición del Festival Ojo Errante</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Unos 4.800 flamencos chilenos ( Phoenicopterus chilensis ) habrían completado este año su etapa de reproducción y desplazamiento en el Estuario de Virrilá y la laguna La Niña , dos importantes humedales ubicados en la provincia de Sechura , en Piura. El registro fue recogido por el Servicio Nacional Forestal y de Fauna Silvestre (Serfor) , organismo adscrito al Ministerio de Desarrollo Agrario y Riego (Midagri), durante las labores de monitoreo de esta especie migratoria. Debido a la importancia de estos ecosistemas para la reproducción de los flamencos, especialistas del Serfor recorrieron los puntos de anidamiento identificados en los humedales de Sechura . Las acciones forman parte de las labores de vigilancia y seguimiento de la fauna silvestre en Piura. ¿Por qué se refuerza la vigilancia en Sechura? El seguimiento de los flamencos representa un desafío debido a la extensión del territorio y a las características de los humedales. A ello se suma que estas aves no necesariamente utilizan los mismos lugares para construir sus nidos cada año. Por esa razón, los especialistas deben realizar recorridos periódicos para localizar las zonas donde las aves se concentran durante su periodo reproductivo y verificar que no existan situaciones que puedan afectar a los ejemplares. El especialista en fauna silvestre del Serfor, Max Guerra, señaló que es necesario fortalecer las acciones de patrullaje y monitoreo en los espacios de anidamiento, tomando en cuenta tanto las condiciones del territorio como las amenazas que pueden afectar a estas aves. En las intervenciones realizadas en la provincia participaron representantes del Serfor sede Piura , la Fiscalía Especializada en Materia Ambiental de Piura y la Unidad Desconcentrada de Protección de Medio Ambiente de la Policía Nacional del Perú. El trabajo conjunto resulta especialmente importante en una zona donde ya se han registrado casos de afectación a estas aves. En julio de 2025, el Serfor constató la caza ilegal de crías de flamencos chilenos en la laguna del sector La Huaquilla, en Sechura, luego de recibir una alerta. Los especialistas encontraron patas y plumas de polluelos en el lugar. El ciclo reproductivo de los flamencos en Sechura La reproducción de los flamencos chilenos sigue un proceso que se desarrolla durante varios meses. En los humedales de Sechura , la temporada comienza aproximadamente a mediados de abril, cuando las aves empiezan a construir sus nidos. Entre mayo y junio ocurre la postura de los huevos, mientras que durante julio aparecen los primeros polluelos. A partir de la primera semana de agosto, las crías comienzan a desplazarse, una etapa que requiere especial atención por parte de quienes realizan el monitoreo. “Es un lugar alejado, hay mucho territorio que recorrer y se necesita prestar atención cuando están los polluelos; los puntos de anidamiento cambian todos los años”, explicó el guardaparque local Pablo Martínez, quien también destacó la coordinación con el Serfor para realizar los recorridos. ¿Dónde se reproducen los flamencos? El Estuario de Virrilá y la laguna La Niña forman parte de los espacios utilizados por estas aves en la costa norte del Perú. El Serfor ya ha documentado en años anteriores procesos reproductivos y trabajos de seguimiento en ambos lugares. En 2022, por ejemplo, la entidad informó sobre el nacimiento de alrededor de 700 pichones de flamenco chileno en el Estuario de Virrilá. El lugar fue reconocido además como Sitio Ramsar en 2021, debido a su importancia como humedal de relevancia internacional. Un año después, en agosto de 2023, el Serfor realizó el anillamiento de 183 polluelos nacidos en la laguna La Niña. Esta práctica permite identificar a los ejemplares y obtener información sobre sus desplazamientos y los lugares que utilizan durante su vida. El flamenco chileno es una especie migratoria El flamenco chileno utiliza diferentes cuerpos de agua a lo largo de su distribución. Según el Serfor, puede encontrarse en lagunas poco profundas de agua dulce y salada, desde la costa hasta zonas ubicadas a unos 4.800 metros de altitud. Su distribución comprende territorios desde Chile hasta Ecuador , por lo que los ejemplares que nacen en los humedales de Sechura pueden desplazarse posteriormente hacia otras zonas del país o incluso hacia territorios de países vecinos. El anillamiento se ha convertido en una herramienta para conocer mejor estos movimientos. Los registros realizados por especialistas y observadores de aves permiten identificar ejemplares en diferentes puntos y reconstruir parte de sus rutas de desplazamiento. De acuerdo con el Serfor, la especie está clasificada como “Casi Amenazada” . Entre las principales amenazas identificadas figuran la caza ilegal y la degradación de sus hábitats. ¿Qué amenazas enfrentan los flamencos de Sechura? La ubicación alejada de los humedales no elimina los riesgos para estas aves. La caza, la captura y el consumo de fauna silvestre son prácticas que pueden afectar directamente a las poblaciones de flamencos, especialmente durante la temporada en la que permanecen concentrados en las zonas de reproducción. La dificultad para acceder a determinados sectores también obliga a reforzar la vigilancia. Los recorridos permiten identificar nuevos puntos de anidamiento y detectar posibles casos de afectación antes de que el impacto sea mayor. El antecedente de 2025 en La Huaquilla muestra la necesidad de mantener una presencia constante en estos espacios. Para el Serfor, la protección de las áreas donde se reproducen y alimentan las aves requiere coordinación entre autoridades, especialistas y comunidades locales. ¿Cómo reportar un flamenco en situación de riesgo? La ciudadanía puede comunicar al Serfor cualquier caso relacionado con fauna silvestre que se encuentre herida, enferma, fuera de su hábitat o que requiera evaluación e intervención. Según el canal oficial Alerta SERFOR , los ciudadanos deben enviar un mensaje escrito al WhatsApp 947 588 269 , explicando qué ocurrió, dónde se produjo el hecho y cuándo fue observado. También se deben adjuntar fotografías, videos o información de ubicación que ayude a los especialistas a identificar el lugar y evaluar la situación. El Serfor precisa que este canal recibe mensajes escritos y no llamadas telefónicas . Los reportes son derivados a las Administraciones Técnicas Forestales y de Fauna Silvestre según el ámbito correspondiente.</t>
+          <t>La tercera edición del certamen convoca a jóvenes realizadores de todo el país, quienes presentarán sus cortometrajes de ficción, documental y animación hasta el 9 de octubre. El talento audiovisual universitario tiene un nuevo espacio de encuentro en Piura. El Programa de Estudio de Comunicación y Medios Digitales de la Universidad Privada Antenor Orrego (UPAO) filial Piura desarrollará la tercera edición del Festival de Cortometrajes Universitarios Ojo Errante, una iniciativa que promueve la producción audiovisual de jóvenes universitarios y su difusión desde las regiones. El certamen se desarrollará de manera presencial y tendrá ingreso gratuito. La convocatoria está dirigida a los estudiantes universitarios de comunicación y facultades afines de todo el país, quienes podrán postular cortometrajes realizados en el ámbito académico, entre agosto del 2024 y octubre del 2026. Ficción, documental y animación Los participantes podrán competir en tres categorías oficiales. En ficción, se recibirán obras basadas en personajes, situaciones y conflictos narrativos imaginarios, con una duración de 5 a 20 minutos. En documental, podrán participar obras de no ficción construidas a partir de hechos, realidades o espacios interpretados por el realizador, con una duración de 5 a 20 minutos. Por su parte, la categoría animación comprende creaciones realizadas mediante técnicas tradicionales, digitales o mixtas, con una duración de 30 segundos a 20 minutos. Inscripciones hasta el 9 de octubre Para la filial Piura, la convocatoria estará abierta hasta el 9 de octubre del 2026, hasta las 11:59 p. m. La exhibición oficial de los trabajos se realizará el 29 de octubre del presente. La inscripción es gratuita y se realizará exclusivamente de manera virtual. Los participantes deberán presentar el cortometraje en formato MP4 H.264 Full HD o 4K, además del póster, teaser y la evidencia del curso universitario y docente responsable. Un espacio para reconocer el talento emergente Los trabajos serán evaluados por un comité especializado, que considerará criterios como la originalidad, la coherencia narrativa y la resolución técnica. El festival otorgará un reconocimiento al mejor cortometraje y menciones honrosas al segundo mejor trabajo de cada categoría. Además, los equipos seleccionados recibirán constancias de participación. Acerca del Festival Ojo Errante El Festival de Cortometrajes Universitarios Ojo Errante es una plataforma cultural y académica impulsada por el Programa de Estudio de Comunicación y Medios Digitales de la UPAO. De este modo se promueve la visibilidad, circulación y experimentación de la producción audiovisual realizada por jóvenes universitarios. A través de proyecciones presenciales, circuitos itinerantes y espacios formativos en Piura, el festival fomenta el desarrollo de la industria cinematográfica emergente desde las regiones. Para más detalles o información, los interesados pueden comunicarse través del siguiente correo: [email protected]</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>https://eltiempo.pe/local/refuerzan-la-vigilancia-de-flamencos-en-humedales-de-sechura/</t>
+          <t>https://eltiempo.pe/local/upao-piura-lleva-el-cine-universitario-a-una-nueva-edicion-del-festival-ojo-errante/</t>
         </is>
       </c>
     </row>
@@ -1069,17 +1063,17 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Estado de emergencia en Piura es más de lo mismo</t>
+          <t>El Niño superaría al de 1998 y traería impactos “insospechados” en la región Piura</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>La emisión del decreto supremo N° 126-2026 con la declaratoria de emergencia en Piura, Castilla, Veintiséis de Octubre y Catacaos para luchar contra la criminalidad, no tuvo mayor impacto en la opinión pública agobiada por la ola criminal que castiga a la región. Según el exjefe de la Región Policial de Piura, Coronel (r) Máximo Vargas Hugo, esta medida es más de lo mismo y casi un calco de lo que hicieron los gobiernos anteriores, sin mayores resultados. “Es evidente que el actual gobierno viene utilizando las medidas de gobiernos anteriores para frenar la criminalidad e inseguridad que se vive [...] realmente no se tiene los resultados que la población requiere. Esto es algo repetitivo y creo que el gobierno actual puede entrar en un desgaste político toda vez que la población exige seguridad”, manifestó el exmando policial. Agregó que pese a estas declaratorias de emergencia, siguen creciendo la comisión de delitos como el asesinato, extorsiones y ahora los secuestros. “La población quiere seguridad y están repitiendo lo mismo que han hecho gestiones anteriores. Desde el año pasado, Piura viene en estados de emergencia y quizás tenemos el año en situación de emergencia. Esta es una medida que a todas luces no ha dado resultados. Cambios Sobre el cambio del comandante general de la Policía, Vargas Hugo señaló que los resultados se notarán cuando se fortalezca la labor policial con recursos, logística e inteligencia. “Ese cambio no garantiza una modificación en la lucha contra el crimen. Hay policías que tienen la mejor intención de tener éxito contra el crimen, pero si no le dan las herramientas necesarias, nada pueden hacer”, manifestó.</t>
+          <t>El fenómeno “El Niño” (FEN) sigue acumulando energía en el mar frente a las costas de la región y los impactos de este calentamiento son hasta el momento insospechados, según informó el especialista en meteorología del Senamhi Piura, Héctor Yauli. PUEDES LEER ► Es hora de rescatar la cultura de Piura De lo que sí se tiene mayor certeza es que los indicadores de este fenómeno en desarrollo ya superaron los valores previos al Mega Niño que castigó la región entre los años 1997 y 1998. “Lo que ha dicho el Organismo Mundial de Meteorología es que los impactos que pueda generar este Niño en el contexto en el cual se presenta, porque el nivel de calentamiento es muy exacerbado y no se tiene comparación con los años 1997 y 1998. Es una gran cantidad de energía y calor no solamente en la zona tropical donde se desarrolla El Niño sino en todos los océanos el nivel de calentamiento es muy mayor. Se esperan impactos insospechados por la alta incertidumbre que hay. [...] Lo que sí tenemos mucha seguridad es en cuanto a que se van a presentar lluvias bastante fuertes e intensas en los meses de verano”, manifestó. Sobre la magnitud, Yauri indicó que existe una incertidumbre sobre los niveles que se alcanzarán las precipitaciones. Cabe indicar que durante el Mega Niño de 1998, se registró la máxima precipitación el 24 de enero con un valor de 173.6 milímetros de acumulado en una sola lluvia. Esto implica que ese día cayeron más de 173 litros de agua sobre un metro cuadrado. Peores En este punto, Yauli informó que el escenario es mucho más complicado porque no solo es un calentamiento del mar frente a la costa norte, sino en diferentes partes del mundo. “Es un nivel de calentamiento exacerbado que no tiene comparación. Si nos situamos en septiembre de 1997, solamente veíamos el calentamiento de El Niño, pero el océano Pacífico en el norte estaba en condiciones normales, en Chile estaba normal y en el Atlántico igual. Sin embargo, ahora está caliente el norte y sur del Pacífico, e incluso en el Atlántico también está caliente y eso trae otras implicancias y diferente tipo de impactos vinculados a que habrá mucha lluvia en la zona norte del Perú y bastante deficiencia de lluvias en la zona noroeste de Brasil”, destacó Yauli.</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>https://eltiempo.pe/local/estado-de-emergencia-en-piura-es-mas-de-lo-mismo/</t>
+          <t>https://eltiempo.pe/local/el-nino-traera-unos-impactos-insospechados-en-la-region-piura/</t>
         </is>
       </c>
     </row>
@@ -1094,17 +1088,17 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Candidatos a gobernadores y alcaldes obligados a rendir sus gastos</t>
+          <t>Los SARE siguen sin mantenimiento para funcionar durante las lluvias</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Las organizaciones políticas que participarán en las Elecciones Regionales y Municipales (ERM) 2026 están obligadas a presentar ante la Oficina Nacional de Procesos Electorales (ONPE) dos informes donde registren los gastos, aportes e ingresos de sus campañas. La fecha límite para presentar el primero de dichos informes es el próximo viernes 11 de setiembre. La obligación y el plazo también alcanzan a todos los ciudadanos que hayan logrado inscribir sus candidaturas para una Gobernación, una Vicegobernación o una Alcaldía –provincial o distrital– y se mantienen aun cuando la candidatura no llegue al final del proceso por renuncia, tacha o exclusión. Debido a un cambio en la Ley de Organizaciones Políticas, ya no rinden cuentas quienes aspiran a ser consejeros regionales o regidores municipales. El informe financiero lo puede presentar él mismo o, si tiene, su responsable de campaña.</t>
+          <t>Diferentes informes de las oficinas de control institucional del Programa Nacional de Saneamiento Urbano (PNSU) dan cuenta del estado de abandono en su mantenimiento de los Sistemas Alternativos de Recolección y Evacuación de aguas de lluvia (SARE) que se habilitaron en Piura y que costaron millones de soles. Un ejemplo es lo que ocurre en el SARE Cinco Esquinas que costó más de 28 millones de soles, pero ni siquiera tiene un cerco perimétrico para proteger los costosos equipos instalados a pesar de los años pasados. “El grupo electrógeno y la electrobomba constituyen equipos necesarios para el funcionamiento del sistema de bombeo y la evacuación, por lo que su exposición en un área sin control físico permanente de acceso podría afectar su seguridad, conservación y disponibilidad cuando sean requeridos para la operación del SARE”, se lee en el informe de control. De otro lado, el SARE de Ignacio Merino, valorizado en 15 millones de soles, también tiene problemas de falta de mantenimiento. “La falta de culminación de la transferencia legal integral y la ausencia de un marco procedimental que regule las obligaciones de custodia operativa provisoria han provocado que un sistema pluvial de gran inversión (S/ 17.1 millones) no registre ningún tipo de mantenimiento preventivo sobre sus componentes críticos. Esto neutraliza la capacidad de respuesta instalada para salvaguardar a las urbanizaciones del distrito de Piura”, se indica en el documento de Contraloría. Entre las principales observaciones se tiene la acumulación de sedimentos en canaletas cunetas de las vías.</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>https://eltiempo.pe/local/candidatos-a-gobernadores-y-alcaldes-obligados-a-rendir-sus-gastos/</t>
+          <t>https://eltiempo.pe/local/los-sare-siguen-sin-mantenimiento-para-funcionar-durante-las-lluvias/</t>
         </is>
       </c>
     </row>
@@ -1119,17 +1113,17 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Piura: Sicarios asesinan a menor, dos mujeres y un exsereno</t>
+          <t>Refuerzan la vigilancia de flamencos en humedales de Sechura</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>La violencia volvió a golpear con fuerza a la provincia de Sullana y otros sectores de Piura. En distintos hechos registrados durante las últimas horas, sicarios habrían atacado a varias personas, dejando como saldo la muerte de un adolescente de 13 años, dos mujeres y un exsereno. Además, otras dos personas resultaron heridas por impactos de bala. Los casos son investigados por la Policía Nacional del Perú, que busca determinar quiénes participaron en los ataques y cuáles fueron los móviles. La institución mantiene abiertas distintas líneas de investigación y no descarta que algunos de estos crímenes estén relacionados con ajustes de cuentas. Sicarios asesinan a menor de 13 años en Sullana Uno de los casos que más ha conmocionado a Sullana corresponde a la muerte de un menor de apenas 13 años. El adolescente, identificado con las iniciales M. F. L. Ch., era natural de Trujillo, aunque residía en Piura, y se convirtió, según la información proporcionada, en la víctima número 44 de los asesinatos atribuidos al sicariato en la provincia. El crimen ocurrió la noche del domingo en la intersección de la calle Túpac Amaru con la avenida Par Vial, en el asentamiento 17 de Enero. Eran aproximadamente las 10:40 de la noche cuando el adolescente viajaba como pasajero en un mototaxi rojo de placa 3784-DP. De acuerdo con las primeras investigaciones, el vehículo habría quedado detenido en medio de la vía debido a un desperfecto mecánico. La tapa del tanque de combustible había sido retirada y esa situación habría sido aprovechada por los atacantes. Según los primeros testimonios recogidos en el lugar, sujetos que se desplazaban en una motocicleta llegaron hasta el mototaxi y dispararon directamente contra el menor. Uno de los proyectiles impactó en su cabeza y le ocasionó una herida de entrada y salida que provocó su muerte de manera instantánea. Un tatuaje permitió identificar al adolescente Tras el ataque, sus acompañantes habrían escapado corriendo en dirección al sector La Selva, mientras la víctima y el trimóvil quedaron abandonados en la zona. La identificación del adolescente se pudo realizar gracias a un tatuaje que llevaba en el brazo derecho con el nombre “Alexander”. Una tía acudió a la dependencia policial y posteriormente a la morgue legal, donde reconoció plenamente al menor. La Policía continúa con las diligencias para establecer las circunstancias exactas del asesinato. Entre las hipótesis que se manejan figura un posible ajuste de cuentas, aunque esta versión todavía debe ser corroborada por los investigadores. Para establecer si existían antecedentes que puedan ayudar a explicar el ataque, la Policía coordina con sus unidades de Piura para conocer si el adolescente había sido intervenido durante las últimas semanas. Asesinan a exsereno dentro de restaurante en Talara Otro hecho violento ocurrió en Talara. Un hombre conocido como “Van Dan”, quien había sido sereno y era propietario de un gimnasio en el distrito de La Brea-Negritos, fue asesinado a balazos dentro del restaurante “La Caleta 10”, ubicado en el asentamiento Mario Aguirre. Según la información preliminar, un sicario irrumpió en el segundo piso del establecimiento y disparó en cinco oportunidades contra la víctima. El hombre quedó sentado en una silla y murió pocos segundos después del ataque. La Policía deberá determinar si este crimen guarda relación con alguna amenaza previa, conflicto personal u otra actividad delictiva. Por ahora, el móvil permanece bajo investigación. Dos mujeres mueren tras una balacera en Sullana La noche del lunes, otro ataque armado dejó dos mujeres fallecidas y dos hombres heridos en el sector Manuel Seoane, en Sullana. El hecho ocurrió en la manzana B, lote 13, donde cuatro personas se encontraban dentro de una vivienda consumiendo bebidas alcohólicas y ceviche. Según los testimonios recogidos inicialmente, una motocicleta se estacionó frente al inmueble. Uno de los ocupantes descendió y habría ingresado rápidamente a la vivienda para abrir fuego contra las personas que se encontraban en el interior. Los testigos describieron el ataque como una ráfaga de disparos. Aunque las víctimas intentaron protegerse y lanzarse al suelo, varias de ellas fueron alcanzadas por los proyectiles. Las víctimas fueron identificadas Una de las víctimas fue identificada como Sheila Anabelen Viera Elias, de 30 años. De acuerdo con las primeras versiones, la mujer intentó escapar hacia el baño, pero el atacante la habría perseguido y disparado varias veces. También resultó gravemente herida Lady Loren Valdiviezo Nole, de 28 años. Los disparos le ocasionaron lesiones en el tórax y la cabeza. La mujer fue trasladada a un establecimiento de salud junto con los demás afectados. Además de las dos jóvenes, Daniel Paucar y Carlos Cornejo resultaron heridos por impactos de bala y fueron trasladados a los hospitales antiguo y nuevo de Sullana. Hasta el cierre de la información proporcionada, ambos permanecían con pronóstico reservado. Las dos mujeres fallecieron pese a los esfuerzos realizados por los médicos. En el caso de Loren Valdiviezo, se conoció que tenía seis meses de gestación, lo que añadió una nueva dimensión a la tragedia. ¿Qué investiga la Policía sobre los ataques? Los investigadores buscan establecer si los tres hechos tienen alguna conexión o si se trata de ataques independientes. La presencia de motocicletas, el uso de armas de fuego y la rapidez con la que actuaron los presuntos atacantes son algunos de los elementos que forman parte de las diligencias. De acuerdo con la Policía Nacional del Perú , la investigación criminal permite reunir evidencias para determinar responsabilidades y esclarecer los hechos. La institución mantiene información institucional y canales de atención a través de su portal oficial . Asimismo, el Ministerio Público participa en las investigaciones cuando corresponde y tiene entre sus funciones dirigir la investigación del delito. Para conocer información institucional, denuncias y servicios fiscales, se puede consultar el portal oficial del Ministerio Público . ¿Dónde se puede consultar información sobre el sicariato? Para conocer la incidencia de distintos delitos, el Ministerio del Interior cuenta con el Mapa del Delito Georreferenciado . Esta herramienta permite consultar registros relacionados con homicidios, extorsiones y sicariato , además de ubicar comisarías y otros puntos de interés. El servicio forma parte del Observatorio Nacional de Seguridad Ciudadana y puede ser consultado en el Mapa del Delito Georreferenciado del Ministerio del Interior . En Sullana, la violencia vinculada a ataques con armas de fuego y asesinatos por encargo no es un fenómeno nuevo. El propio Poder Judicial ha informado anteriormente sobre procesos por presunto sicariato en esta provincia, incluyendo investigaciones en las que se analizaron testimonios protegidos y registros audiovisuales como elementos de convicción. Mientras avanzan las diligencias, la Policía deberá determinar quiénes fueron los autores materiales de estos crímenes, quiénes pudieron ordenar los ataques y cuáles fueron las razones detrás de cada asesinato. Por el momento, las investigaciones continúan abiertas.</t>
+          <t>Unos 4.800 flamencos chilenos ( Phoenicopterus chilensis ) habrían completado este año su etapa de reproducción y desplazamiento en el Estuario de Virrilá y la laguna La Niña , dos importantes humedales ubicados en la provincia de Sechura , en Piura. El registro fue recogido por el Servicio Nacional Forestal y de Fauna Silvestre (Serfor) , organismo adscrito al Ministerio de Desarrollo Agrario y Riego (Midagri), durante las labores de monitoreo de esta especie migratoria. Debido a la importancia de estos ecosistemas para la reproducción de los flamencos, especialistas del Serfor recorrieron los puntos de anidamiento identificados en los humedales de Sechura . Las acciones forman parte de las labores de vigilancia y seguimiento de la fauna silvestre en Piura. ¿Por qué se refuerza la vigilancia en Sechura? El seguimiento de los flamencos representa un desafío debido a la extensión del territorio y a las características de los humedales. A ello se suma que estas aves no necesariamente utilizan los mismos lugares para construir sus nidos cada año. Por esa razón, los especialistas deben realizar recorridos periódicos para localizar las zonas donde las aves se concentran durante su periodo reproductivo y verificar que no existan situaciones que puedan afectar a los ejemplares. El especialista en fauna silvestre del Serfor, Max Guerra, señaló que es necesario fortalecer las acciones de patrullaje y monitoreo en los espacios de anidamiento, tomando en cuenta tanto las condiciones del territorio como las amenazas que pueden afectar a estas aves. En las intervenciones realizadas en la provincia participaron representantes del Serfor sede Piura , la Fiscalía Especializada en Materia Ambiental de Piura y la Unidad Desconcentrada de Protección de Medio Ambiente de la Policía Nacional del Perú. El trabajo conjunto resulta especialmente importante en una zona donde ya se han registrado casos de afectación a estas aves. En julio de 2025, el Serfor constató la caza ilegal de crías de flamencos chilenos en la laguna del sector La Huaquilla, en Sechura, luego de recibir una alerta. Los especialistas encontraron patas y plumas de polluelos en el lugar. El ciclo reproductivo de los flamencos en Sechura La reproducción de los flamencos chilenos sigue un proceso que se desarrolla durante varios meses. En los humedales de Sechura , la temporada comienza aproximadamente a mediados de abril, cuando las aves empiezan a construir sus nidos. Entre mayo y junio ocurre la postura de los huevos, mientras que durante julio aparecen los primeros polluelos. A partir de la primera semana de agosto, las crías comienzan a desplazarse, una etapa que requiere especial atención por parte de quienes realizan el monitoreo. “Es un lugar alejado, hay mucho territorio que recorrer y se necesita prestar atención cuando están los polluelos; los puntos de anidamiento cambian todos los años”, explicó el guardaparque local Pablo Martínez, quien también destacó la coordinación con el Serfor para realizar los recorridos. ¿Dónde se reproducen los flamencos? El Estuario de Virrilá y la laguna La Niña forman parte de los espacios utilizados por estas aves en la costa norte del Perú. El Serfor ya ha documentado en años anteriores procesos reproductivos y trabajos de seguimiento en ambos lugares. En 2022, por ejemplo, la entidad informó sobre el nacimiento de alrededor de 700 pichones de flamenco chileno en el Estuario de Virrilá. El lugar fue reconocido además como Sitio Ramsar en 2021, debido a su importancia como humedal de relevancia internacional. Un año después, en agosto de 2023, el Serfor realizó el anillamiento de 183 polluelos nacidos en la laguna La Niña. Esta práctica permite identificar a los ejemplares y obtener información sobre sus desplazamientos y los lugares que utilizan durante su vida. El flamenco chileno es una especie migratoria El flamenco chileno utiliza diferentes cuerpos de agua a lo largo de su distribución. Según el Serfor, puede encontrarse en lagunas poco profundas de agua dulce y salada, desde la costa hasta zonas ubicadas a unos 4.800 metros de altitud. Su distribución comprende territorios desde Chile hasta Ecuador , por lo que los ejemplares que nacen en los humedales de Sechura pueden desplazarse posteriormente hacia otras zonas del país o incluso hacia territorios de países vecinos. El anillamiento se ha convertido en una herramienta para conocer mejor estos movimientos. Los registros realizados por especialistas y observadores de aves permiten identificar ejemplares en diferentes puntos y reconstruir parte de sus rutas de desplazamiento. De acuerdo con el Serfor, la especie está clasificada como “Casi Amenazada” . Entre las principales amenazas identificadas figuran la caza ilegal y la degradación de sus hábitats. ¿Qué amenazas enfrentan los flamencos de Sechura? La ubicación alejada de los humedales no elimina los riesgos para estas aves. La caza, la captura y el consumo de fauna silvestre son prácticas que pueden afectar directamente a las poblaciones de flamencos, especialmente durante la temporada en la que permanecen concentrados en las zonas de reproducción. La dificultad para acceder a determinados sectores también obliga a reforzar la vigilancia. Los recorridos permiten identificar nuevos puntos de anidamiento y detectar posibles casos de afectación antes de que el impacto sea mayor. El antecedente de 2025 en La Huaquilla muestra la necesidad de mantener una presencia constante en estos espacios. Para el Serfor, la protección de las áreas donde se reproducen y alimentan las aves requiere coordinación entre autoridades, especialistas y comunidades locales. ¿Cómo reportar un flamenco en situación de riesgo? La ciudadanía puede comunicar al Serfor cualquier caso relacionado con fauna silvestre que se encuentre herida, enferma, fuera de su hábitat o que requiera evaluación e intervención. Según el canal oficial Alerta SERFOR , los ciudadanos deben enviar un mensaje escrito al WhatsApp 947 588 269 , explicando qué ocurrió, dónde se produjo el hecho y cuándo fue observado. También se deben adjuntar fotografías, videos o información de ubicación que ayude a los especialistas a identificar el lugar y evaluar la situación. El Serfor precisa que este canal recibe mensajes escritos y no llamadas telefónicas . Los reportes son derivados a las Administraciones Técnicas Forestales y de Fauna Silvestre según el ámbito correspondiente.</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>https://eltiempo.pe/local/piura-sicarios-asesinan-a-menor-dos-mujeres-y-un-exsereno/</t>
+          <t>https://eltiempo.pe/local/refuerzan-la-vigilancia-de-flamencos-en-humedales-de-sechura/</t>
         </is>
       </c>
     </row>
@@ -1144,17 +1138,17 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>¡Ni los niños se salvan del hampa! Delincuentes saquean colegio y se llevan hasta los juguetes en el Bajo Piura</t>
+          <t>Estado de emergencia en Piura es más de lo mismo</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>La inseguridad vuelve a causar indignación en el corazón del Bajo Piura. Esta vez, los delincuentes pusieron en la mira a la I. E. I. N.° 463 del caserío Santa Cruz, donde, durante la madrugada, ingresaron al plantel y sustrajeron diversos bienes utilizados por más de 40 estudiantes del nivel inicial. Según la información preliminar, los sujetos violentaron dos ambientes de la institución educativa para ingresar y apoderarse de dos parlantes, dos ventiladores y otros bienes. Pero lo que más ha indignado a los padres de familia es que los delincuentes también se llevaron los juguetes utilizados por los niños durante sus actividades de aprendizaje y desarrollo psicomotor. El robo fue descubierto en las primeras horas de la mañana y comunicado al personal de Serenazgo y a la Policía Nacional. La docente Gaby De La Cruz fue quien alertó a las autoridades, quienes llegaron hasta el colegio para constatar los daños y recoger información que permita esclarecer lo ocurrido. BLANCO DE LA DELINCUENCIA Sin embargo, este no sería un hecho aislado. Padres de familia señalaron que la institución educativa ya habría sido víctima anteriormente de la delincuencia. En una ocasión pasada, sujetos desconocidos se llevaron un tanque Rotoplas, dejando nuevamente al plantel expuesto y afectando el normal desarrollo de las actividades educativas. La presidenta Jackeline Silupú expresó su malestar y preocupación ante las autoridades por la situación que viene atravesando la institución. Los padres exigieron mayor seguridad y acciones concretas para evitar que los delincuentes continúen ingresando a los centros educativos. De acuerdo con las primeras versiones, serían dos sujetos los que habrían cometido el robo, para luego escapar rápidamente a bordo de un mototaxi. La Policía Nacional continúa con las diligencias e investigaciones para identificar a los responsables y recuperar los bienes sustraídos.</t>
+          <t>La emisión del decreto supremo N° 126-2026 con la declaratoria de emergencia en Piura, Castilla, Veintiséis de Octubre y Catacaos para luchar contra la criminalidad, no tuvo mayor impacto en la opinión pública agobiada por la ola criminal que castiga a la región. Según el exjefe de la Región Policial de Piura, Coronel (r) Máximo Vargas Hugo, esta medida es más de lo mismo y casi un calco de lo que hicieron los gobiernos anteriores, sin mayores resultados. “Es evidente que el actual gobierno viene utilizando las medidas de gobiernos anteriores para frenar la criminalidad e inseguridad que se vive [...] realmente no se tiene los resultados que la población requiere. Esto es algo repetitivo y creo que el gobierno actual puede entrar en un desgaste político toda vez que la población exige seguridad”, manifestó el exmando policial. Agregó que pese a estas declaratorias de emergencia, siguen creciendo la comisión de delitos como el asesinato, extorsiones y ahora los secuestros. “La población quiere seguridad y están repitiendo lo mismo que han hecho gestiones anteriores. Desde el año pasado, Piura viene en estados de emergencia y quizás tenemos el año en situación de emergencia. Esta es una medida que a todas luces no ha dado resultados. Cambios Sobre el cambio del comandante general de la Policía, Vargas Hugo señaló que los resultados se notarán cuando se fortalezca la labor policial con recursos, logística e inteligencia. “Ese cambio no garantiza una modificación en la lucha contra el crimen. Hay policías que tienen la mejor intención de tener éxito contra el crimen, pero si no le dan las herramientas necesarias, nada pueden hacer”, manifestó.</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>https://eltiempo.pe/local/ni-los-ninos-se-salvan-del-hampa-delincuentes-saquean-colegio-y-se-llevan-hasta-los-juguetes-en-el-bajo-piura/</t>
+          <t>https://eltiempo.pe/local/estado-de-emergencia-en-piura-es-mas-de-lo-mismo/</t>
         </is>
       </c>
     </row>
@@ -1169,17 +1163,17 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Dren Maldonado: MTC enviará puente a Piura tras alerta por riesgo de dejar incomunicadas a 60 mil personas</t>
+          <t>Piura: Sicarios asesinan a menor, dos mujeres y un exsereno</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>La senadora por Piura, Karla Schaefer, informó que el ministro de Transportes y Comunicaciones, Rafael Rey Rey, dispuso el envío de un puente que será utilizado para garantizar la conexión vial ante una eventual afectación del dren Maldonado. Puedes Leer | El Niño superaría al de 1998 y traería impactos “insospechados” en la región Piura La situación de riesgo en el dren Maldonado, en el distrito de Veintiséis de Octubre, habría encontrado una respuesta desde el Gobierno central. La senadora por Piura, Karla Schaefer , informó que el Ministerio de Transportes y Comunicaciones (MTC) dispuso el envío de un puente para atender una eventual interrupción de la vía en este sector. Según explicó Schaefer, el pedido fue trasladado al MTC debido a la preocupación por la seguridad de la red vial y el riesgo de que una eventual afectación del dren Maldonado pueda comprometer la comunicación de importantes sectores de Piura. “ El ministro de Transportes y Comunicaciones, Rafael Rey, afirmó que él va a poner el puente ”, señaló la senadora. Schaefer explicó que inicialmente se realizaron consultas tanto al MTC como al Ministerio de Defensa (Mindef), a través de la empresa estatal SIMA Perú , para evaluar una alternativa que permita responder ante una emergencia. Sin embargo, de acuerdo con la parlamentaria, el ministro Rey tomó la decisión de disponer directamente la estructura tras conocer la situación. “Se había hecho la consulta al Ministerio de Transportes y Comunicaciones y al Ministerio de Defensa a través de SIMA Perú. Pero el ministro Rafael Rey, gracias a la delegación de facultades, ni bien vio el tema, dijo: ‘ Yo voy a dar ese puente ’”, declaró. Puente será trasladado a Piura La senadora informó además que la estructura ya habría salido de Lima con destino a Piura y será almacenada temporalmente en Piura Futura , desde donde podrá ser trasladada hacia los puntos que requieran atención. “Hoy han salido de Lima y serán almacenados en Piura Futura para que desde ahí se vayan a varios puntos”, indicó Schaefer. La medida busca contar con una alternativa de conexión ante una eventual emergencia relacionada con el dren Maldonado, especialmente considerando el riesgo advertido para la población de Veintiséis de Octubre. En declaraciones difundidas previamente por El Tiempo , Schaefer había advertido que una eventual afectación del dren podría dejar incomunicadas a unas 60 mil personas y había cuestionado las dificultades generadas por la distribución de competencias entre distintas instituciones del Estado. Schaefer agradece respuesta del MTC La senadora destacó la rapidez con la que, según su versión, el ministro de Transportes habría atendido el pedido. “ Agradecerle al ministro esa eficiencia en solucionar ese problema en que se prioriza la vida ”, manifestó. Asimismo, reconoció el trabajo del director de Puentes, Julio Palacios , y de la Municipalidad Distrital de Veintiséis de Octubre , instituciones que, según indicó, tendrán participación en la gestión relacionada con la estructura. Mira También | ¡Ni los niños se salvan del hampa! Delincuentes saquean colegio y se llevan hasta los juguetes en el Bajo Piura El dren Maldonado es uno de los puntos críticos del sistema de drenaje de Veintiséis de Octubre. En febrero de 2026, el INDECI ya había identificado la necesidad de gestionar requerimientos para garantizar su operatividad, debido a su importancia para la evacuación de aguas pluviales durante lluvias intensas. La atención al dren Maldonado forma parte de una problemática mayor de infraestructura y prevención frente a lluvias en Piura, donde distintas autoridades han advertido sobre la necesidad de acelerar las intervenciones antes de que se presenten emergencias.</t>
+          <t>La violencia volvió a golpear con fuerza a la provincia de Sullana y otros sectores de Piura. En distintos hechos registrados durante las últimas horas, sicarios habrían atacado a varias personas, dejando como saldo la muerte de un adolescente de 13 años, dos mujeres y un exsereno. Además, otras dos personas resultaron heridas por impactos de bala. Los casos son investigados por la Policía Nacional del Perú, que busca determinar quiénes participaron en los ataques y cuáles fueron los móviles. La institución mantiene abiertas distintas líneas de investigación y no descarta que algunos de estos crímenes estén relacionados con ajustes de cuentas. Sicarios asesinan a menor de 13 años en Sullana Uno de los casos que más ha conmocionado a Sullana corresponde a la muerte de un menor de apenas 13 años. El adolescente, identificado con las iniciales M. F. L. Ch., era natural de Trujillo, aunque residía en Piura, y se convirtió, según la información proporcionada, en la víctima número 44 de los asesinatos atribuidos al sicariato en la provincia. El crimen ocurrió la noche del domingo en la intersección de la calle Túpac Amaru con la avenida Par Vial, en el asentamiento 17 de Enero. Eran aproximadamente las 10:40 de la noche cuando el adolescente viajaba como pasajero en un mototaxi rojo de placa 3784-DP. De acuerdo con las primeras investigaciones, el vehículo habría quedado detenido en medio de la vía debido a un desperfecto mecánico. La tapa del tanque de combustible había sido retirada y esa situación habría sido aprovechada por los atacantes. Según los primeros testimonios recogidos en el lugar, sujetos que se desplazaban en una motocicleta llegaron hasta el mototaxi y dispararon directamente contra el menor. Uno de los proyectiles impactó en su cabeza y le ocasionó una herida de entrada y salida que provocó su muerte de manera instantánea. Un tatuaje permitió identificar al adolescente Tras el ataque, sus acompañantes habrían escapado corriendo en dirección al sector La Selva, mientras la víctima y el trimóvil quedaron abandonados en la zona. La identificación del adolescente se pudo realizar gracias a un tatuaje que llevaba en el brazo derecho con el nombre “Alexander”. Una tía acudió a la dependencia policial y posteriormente a la morgue legal, donde reconoció plenamente al menor. La Policía continúa con las diligencias para establecer las circunstancias exactas del asesinato. Entre las hipótesis que se manejan figura un posible ajuste de cuentas, aunque esta versión todavía debe ser corroborada por los investigadores. Para establecer si existían antecedentes que puedan ayudar a explicar el ataque, la Policía coordina con sus unidades de Piura para conocer si el adolescente había sido intervenido durante las últimas semanas. Asesinan a exsereno dentro de restaurante en Talara Otro hecho violento ocurrió en Talara. Un hombre conocido como “Van Dan”, quien había sido sereno y era propietario de un gimnasio en el distrito de La Brea-Negritos, fue asesinado a balazos dentro del restaurante “La Caleta 10”, ubicado en el asentamiento Mario Aguirre. Según la información preliminar, un sicario irrumpió en el segundo piso del establecimiento y disparó en cinco oportunidades contra la víctima. El hombre quedó sentado en una silla y murió pocos segundos después del ataque. La Policía deberá determinar si este crimen guarda relación con alguna amenaza previa, conflicto personal u otra actividad delictiva. Por ahora, el móvil permanece bajo investigación. Dos mujeres mueren tras una balacera en Sullana La noche del lunes, otro ataque armado dejó dos mujeres fallecidas y dos hombres heridos en el sector Manuel Seoane, en Sullana. El hecho ocurrió en la manzana B, lote 13, donde cuatro personas se encontraban dentro de una vivienda consumiendo bebidas alcohólicas y ceviche. Según los testimonios recogidos inicialmente, una motocicleta se estacionó frente al inmueble. Uno de los ocupantes descendió y habría ingresado rápidamente a la vivienda para abrir fuego contra las personas que se encontraban en el interior. Los testigos describieron el ataque como una ráfaga de disparos. Aunque las víctimas intentaron protegerse y lanzarse al suelo, varias de ellas fueron alcanzadas por los proyectiles. Las víctimas fueron identificadas Una de las víctimas fue identificada como Sheila Anabelen Viera Elias, de 30 años. De acuerdo con las primeras versiones, la mujer intentó escapar hacia el baño, pero el atacante la habría perseguido y disparado varias veces. También resultó gravemente herida Lady Loren Valdiviezo Nole, de 28 años. Los disparos le ocasionaron lesiones en el tórax y la cabeza. La mujer fue trasladada a un establecimiento de salud junto con los demás afectados. Además de las dos jóvenes, Daniel Paucar y Carlos Cornejo resultaron heridos por impactos de bala y fueron trasladados a los hospitales antiguo y nuevo de Sullana. Hasta el cierre de la información proporcionada, ambos permanecían con pronóstico reservado. Las dos mujeres fallecieron pese a los esfuerzos realizados por los médicos. En el caso de Loren Valdiviezo, se conoció que tenía seis meses de gestación, lo que añadió una nueva dimensión a la tragedia. ¿Qué investiga la Policía sobre los ataques? Los investigadores buscan establecer si los tres hechos tienen alguna conexión o si se trata de ataques independientes. La presencia de motocicletas, el uso de armas de fuego y la rapidez con la que actuaron los presuntos atacantes son algunos de los elementos que forman parte de las diligencias. De acuerdo con la Policía Nacional del Perú , la investigación criminal permite reunir evidencias para determinar responsabilidades y esclarecer los hechos. La institución mantiene información institucional y canales de atención a través de su portal oficial . Asimismo, el Ministerio Público participa en las investigaciones cuando corresponde y tiene entre sus funciones dirigir la investigación del delito. Para conocer información institucional, denuncias y servicios fiscales, se puede consultar el portal oficial del Ministerio Público . ¿Dónde se puede consultar información sobre el sicariato? Para conocer la incidencia de distintos delitos, el Ministerio del Interior cuenta con el Mapa del Delito Georreferenciado . Esta herramienta permite consultar registros relacionados con homicidios, extorsiones y sicariato , además de ubicar comisarías y otros puntos de interés. El servicio forma parte del Observatorio Nacional de Seguridad Ciudadana y puede ser consultado en el Mapa del Delito Georreferenciado del Ministerio del Interior . En Sullana, la violencia vinculada a ataques con armas de fuego y asesinatos por encargo no es un fenómeno nuevo. El propio Poder Judicial ha informado anteriormente sobre procesos por presunto sicariato en esta provincia, incluyendo investigaciones en las que se analizaron testimonios protegidos y registros audiovisuales como elementos de convicción. Mientras avanzan las diligencias, la Policía deberá determinar quiénes fueron los autores materiales de estos crímenes, quiénes pudieron ordenar los ataques y cuáles fueron las razones detrás de cada asesinato. Por el momento, las investigaciones continúan abiertas.</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>https://eltiempo.pe/local/dren-maldonado-mtc-enviara-puente-a-piura-tras-alerta-por-riesgo-de-dejar-incomunicadas-a-60-mil-personas/</t>
+          <t>https://eltiempo.pe/local/piura-sicarios-asesinan-a-menor-dos-mujeres-y-un-exsereno/</t>
         </is>
       </c>
     </row>
@@ -1190,21 +1184,21 @@
         </is>
       </c>
       <c r="B28" s="2" t="n">
-        <v>46272</v>
+        <v>46273</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>I.E. San Ramón de Chulucanas se consagra campeona del Regional Singing Festival 2026</t>
+          <t>¡Ni los niños se salvan del hampa! Delincuentes saquean colegio y se llevan hasta los juguetes en el Bajo Piura</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>La Institución Educativa San Ramón de Chulucanas, representante de la UGEL Chulucanas , obtuvo el primer lugar en el Regional Singing Festival 2026 “Singing for a Better World”, organizado por la Dirección Regional de Educación de Piura. PUEDES LEER ► Sobrevive tras 10 días sepultada por el lodo y es rescatada cuando su familia ya la había dado por muerta La actividad se desarrolló en el parque Néstor Martos de Piura y reunió a estudiantes representantes de las 12 UGEL de la región, quienes demostraron sus habilidades en la interpretación de canciones en inglés. El festival tiene como finalidad fortalecer las competencias comunicativas en el idioma inglés, además de promover la creatividad, la expresión artística y la participación de los estudiantes. La iniciativa se desarrolla en concordancia con el Currículo Nacional de la Educación Básica. Durante sus presentaciones, los participantes también transmitieron mensajes relacionados con valores y actitudes que contribuyen a una convivencia democrática, respetuosa, inclusiva y solidaria. San Ramón conquistó el primer lugar La IE San Ramón logró imponerse en la competencia con la interpretación de la canción “Hand for Chulucanas”, presentación que le permitió quedarse con el primer puesto del festival regional. El segundo lugar fue para la IE Libertadores de América, representante de la UGEL La Unión, que participó con la canción “The Song of Tomorrow”. Mientras que el tercer puesto correspondió a la IE César Vallejo, de la UGEL Morropón, con la interpretación de “Brighter Than Before”. La competencia comenzó en cada institución educativa y posteriormente continuó en las diferentes etapas de las 12 UGEL de Piura: Ayabaca, Chulucanas, Huancabamba, Huarmaca, La Unión, Morropón, Paita, Piura, Sechura, Sullana, Talara y Tambogrande. Además de impulsar el aprendizaje del inglés, el festival busca fortalecer la sana competencia, el trabajo en equipo y la integración entre estudiantes de diferentes provincias de la región.</t>
+          <t>La inseguridad vuelve a causar indignación en el corazón del Bajo Piura. Esta vez, los delincuentes pusieron en la mira a la I. E. I. N.° 463 del caserío Santa Cruz, donde, durante la madrugada, ingresaron al plantel y sustrajeron diversos bienes utilizados por más de 40 estudiantes del nivel inicial. Según la información preliminar, los sujetos violentaron dos ambientes de la institución educativa para ingresar y apoderarse de dos parlantes, dos ventiladores y otros bienes. Pero lo que más ha indignado a los padres de familia es que los delincuentes también se llevaron los juguetes utilizados por los niños durante sus actividades de aprendizaje y desarrollo psicomotor. El robo fue descubierto en las primeras horas de la mañana y comunicado al personal de Serenazgo y a la Policía Nacional. La docente Gaby De La Cruz fue quien alertó a las autoridades, quienes llegaron hasta el colegio para constatar los daños y recoger información que permita esclarecer lo ocurrido. BLANCO DE LA DELINCUENCIA Sin embargo, este no sería un hecho aislado. Padres de familia señalaron que la institución educativa ya habría sido víctima anteriormente de la delincuencia. En una ocasión pasada, sujetos desconocidos se llevaron un tanque Rotoplas, dejando nuevamente al plantel expuesto y afectando el normal desarrollo de las actividades educativas. La presidenta Jackeline Silupú expresó su malestar y preocupación ante las autoridades por la situación que viene atravesando la institución. Los padres exigieron mayor seguridad y acciones concretas para evitar que los delincuentes continúen ingresando a los centros educativos. De acuerdo con las primeras versiones, serían dos sujetos los que habrían cometido el robo, para luego escapar rápidamente a bordo de un mototaxi. La Policía Nacional continúa con las diligencias e investigaciones para identificar a los responsables y recuperar los bienes sustraídos.</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>https://eltiempo.pe/local/i-e-san-ramon-de-chulucanas-se-consagra-campeona-del-regional-singing-festival-2026/</t>
+          <t>https://eltiempo.pe/local/ni-los-ninos-se-salvan-del-hampa-delincuentes-saquean-colegio-y-se-llevan-hasta-los-juguetes-en-el-bajo-piura/</t>
         </is>
       </c>
     </row>
@@ -1215,21 +1209,21 @@
         </is>
       </c>
       <c r="B29" s="2" t="n">
-        <v>46272</v>
+        <v>46273</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Así van los candidatos a falta de un mes para elecciones</t>
+          <t>Dren Maldonado: MTC enviará puente a Piura tras alerta por riesgo de dejar incomunicadas a 60 mil personas</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>ICSI Perú hizo una encuesta y revela cómo van las preferencias de los piuranos sobre su próximo gobernador y alcaldes. PUEDES LEER ► Miniván queda al borde de un abismo en la carretera Canchaque -Huancabamba Las elecciones regionales y municipales están a la vuelta de la esquina y lo único seguro es que sí o sí habrá una segunda vuelta para el cargo de gobernador regional. De acuerdo a ley, si ninguna lista supera el 30% de votos válidos, se convoca a una segunda vuelta entre los dos primeros del escrutinio. De acuerdo a la última encuesta de la empresa ICSI Perú ninguno de los aspirantes a la máxima autoridad regional llega al 30% de las preferencias. Según el estudio de opinión pública, el primer lugar es para el exgobernador Reynaldo Hilbck (Alianza para el Progreso) con 22.5%; seguido por Santiago Paz (Somos Perú) con 13.7% ; Mártires Lizana (Fuerza Popular) con 11.1% y Guillermo La Torre (Podemos Perú) con 10.9%. En el caso de los candidatos provinciales, la disputa parece más reñida y la diferencia de porcentajes es más ajustada entre los aspirantes, con lo cual la campaña de aquí hasta el domingo 4 de octubre será una competencia voto a voto y de convencimiento de los indecisos. Gobierno Regional Sobre el tema, el gerente de ICSI Perú, Mauro Vegas Carmen , consideró que uno de los factores del respaldo a Hilbck son sus candidatos en las provincias con mayor caudal electoral de votos. “En los resultados de los 27 distritos a donde se ha ido, Hilbck alcanza la mayor votación en Piura, Veintiséis de Octubre, Catacaos, Sullana, Morropón, Chulucanas, Talara, Órganos y otros. Todo eso le da ese porcentaje que ahora ha sacado frente al segundo. Por ejemplo, en Piura tiene 19.66% y Somos Perú tiene 15.33%; en Castilla, Hilbck tiene 13.60% y Somos Perú unos 10.90% y en Veintiséis de Octubre, Hilbck tiene 20.35% y Somos Perú, 15.34%. En Sullana que es una plaza fuerte, se tiene 19.59% y Santiago Paz llega a 12.14%, asimismo, en Chulucanas, Hilbck logra 17.4% y Somos Perú 9.87%”, mencionó. Agrega que este respaldo de Hilbck en las provincias y distritos se refleja en sus candidatos para estas jurisdicciones. Un segundo factor, sostiene, es el respaldo de la maquinaria electoral de un partido como Alianza para el Progreso (APP). “Ese porcentaje es coherente porque sus candidatos provinciales y también distritales ganan, además que la maquinaria electoral que se percibe en la región”, agregó. Somos Perú Sobre Santiago Paz de Somos Perú que marcha en segundo lugar con 13.7%, el gerente de ICSI Perú sostuvo que no le va bien con sus candidatos en Piura, Castilla, Veintiséis de Octubre, Tambogrande o Sullana. “En el caso Chulucanas, como distrito capital, el candidato Nelson Mío que hace un mes era fuerte, ha tenido un descenso porque ahí han ingresado candidatos nuevos como Hernán Pasapera de Renovación y Manuel Cueva de Podemos. Eso le ha restado fuerza a Somos Perú”, aseveró. Sobre Mártires Lizana de Fuerza Popular que marcha tercero, Vegas destaca que esto ocurre por la aceptación del candidato a la provincia de Piura, Martín Olivares, que está segundo en la preferencial provincial. Nulos En el estudio también se revela que un 18% de los encuestados no votaría por ninguno de los postulantes o lo haría en blanco. “Esto puede variar producto de la campaña y contracampaña. Aquí quien tiene mejor equipo de contracampaña es el que tiene mayor ventaja de ganar. Es quien reacciona rápido, de forma contundente y demoledora. No siempre la percepción es la verdad, por eso una contracampaña tiene que responderse de manera rápida y contundente. No se trata del mejor indudablemente, sino de quien cometa menos errores y sepa responder a los ataques fundados o infundados”, destacó.n</t>
+          <t>La senadora por Piura, Karla Schaefer, informó que el ministro de Transportes y Comunicaciones, Rafael Rey Rey, dispuso el envío de un puente que será utilizado para garantizar la conexión vial ante una eventual afectación del dren Maldonado. Puedes Leer | El Niño superaría al de 1998 y traería impactos “insospechados” en la región Piura La situación de riesgo en el dren Maldonado, en el distrito de Veintiséis de Octubre, habría encontrado una respuesta desde el Gobierno central. La senadora por Piura, Karla Schaefer , informó que el Ministerio de Transportes y Comunicaciones (MTC) dispuso el envío de un puente para atender una eventual interrupción de la vía en este sector. Según explicó Schaefer, el pedido fue trasladado al MTC debido a la preocupación por la seguridad de la red vial y el riesgo de que una eventual afectación del dren Maldonado pueda comprometer la comunicación de importantes sectores de Piura. “ El ministro de Transportes y Comunicaciones, Rafael Rey, afirmó que él va a poner el puente ”, señaló la senadora. Schaefer explicó que inicialmente se realizaron consultas tanto al MTC como al Ministerio de Defensa (Mindef), a través de la empresa estatal SIMA Perú , para evaluar una alternativa que permita responder ante una emergencia. Sin embargo, de acuerdo con la parlamentaria, el ministro Rey tomó la decisión de disponer directamente la estructura tras conocer la situación. “Se había hecho la consulta al Ministerio de Transportes y Comunicaciones y al Ministerio de Defensa a través de SIMA Perú. Pero el ministro Rafael Rey, gracias a la delegación de facultades, ni bien vio el tema, dijo: ‘ Yo voy a dar ese puente ’”, declaró. Puente será trasladado a Piura La senadora informó además que la estructura ya habría salido de Lima con destino a Piura y será almacenada temporalmente en Piura Futura , desde donde podrá ser trasladada hacia los puntos que requieran atención. “Hoy han salido de Lima y serán almacenados en Piura Futura para que desde ahí se vayan a varios puntos”, indicó Schaefer. La medida busca contar con una alternativa de conexión ante una eventual emergencia relacionada con el dren Maldonado, especialmente considerando el riesgo advertido para la población de Veintiséis de Octubre. En declaraciones difundidas previamente por El Tiempo , Schaefer había advertido que una eventual afectación del dren podría dejar incomunicadas a unas 60 mil personas y había cuestionado las dificultades generadas por la distribución de competencias entre distintas instituciones del Estado. Schaefer agradece respuesta del MTC La senadora destacó la rapidez con la que, según su versión, el ministro de Transportes habría atendido el pedido. “ Agradecerle al ministro esa eficiencia en solucionar ese problema en que se prioriza la vida ”, manifestó. Asimismo, reconoció el trabajo del director de Puentes, Julio Palacios , y de la Municipalidad Distrital de Veintiséis de Octubre , instituciones que, según indicó, tendrán participación en la gestión relacionada con la estructura. Mira También | ¡Ni los niños se salvan del hampa! Delincuentes saquean colegio y se llevan hasta los juguetes en el Bajo Piura El dren Maldonado es uno de los puntos críticos del sistema de drenaje de Veintiséis de Octubre. En febrero de 2026, el INDECI ya había identificado la necesidad de gestionar requerimientos para garantizar su operatividad, debido a su importancia para la evacuación de aguas pluviales durante lluvias intensas. La atención al dren Maldonado forma parte de una problemática mayor de infraestructura y prevención frente a lluvias en Piura, donde distintas autoridades han advertido sobre la necesidad de acelerar las intervenciones antes de que se presenten emergencias.</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>https://eltiempo.pe/local/asi-van-los-candidatos-a-falta-de-un-mes-para-elecciones/</t>
+          <t>https://eltiempo.pe/local/dren-maldonado-mtc-enviara-puente-a-piura-tras-alerta-por-riesgo-de-dejar-incomunicadas-a-60-mil-personas/</t>
         </is>
       </c>
     </row>
@@ -1240,21 +1234,21 @@
         </is>
       </c>
       <c r="B30" s="2" t="n">
-        <v>46272</v>
+        <v>46273</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Fiesta termina con una mujer fallecida</t>
+          <t>Candidatos a gobernadores y alcaldes obligados a rendir sus gastos</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Una fiesta terminó en tragedia en la urbanización Las Casuarinas II Etapa, en el distrito Veintiséis de Octubre , luego de que una joven de nacionalidad colombiana perdiera la vida tras caer desde un tragaluz del tercer piso de un inmueble hacia el segundo nivel. La víctima fue identificada como Juliet Alisson Zambrano Fino, de 21 años de edad. PUEDES LEER ► FEN asusta a la banca privada El hecho ocurrió durante una reunión social y las circunstancias de la caída son materia de investigación por parte de la Policía. De acuerdo con información preliminar, una de las hipótesis que manejan las autoridades es que la joven habría sido presuntamente arrojada por un tragaluz, desde donde terminó cayendo hasta el segundo piso del inmueble. Sin embargo, esta versión todavía deberá ser corroborada mediante las diligencias policiales, pericias y demás elementos que permitan determinar qué ocurrió exactamente antes de la caída. SIN SIGNOS VITALES Tras conocerse el hecho, personal de Serenazgo del distrito Veintiséis de Octubre y una ambulancia del SAMU Piura llegaron hasta el lugar de la tragedia para brindar atención a la víctima. No obstante, los equipos de emergencia encontraron a la joven sin signos vitales. En el lugar también se encontraba un ciudadano extranjero, quien, visiblemente afectado y entre lágrimas, solicitaba ayuda para la mujer. RECOPILAN INFORMACIÓN Agentes de la Policía Nacional acudieron posteriormente a la escena para realizar las primeras diligencias, verificar las condiciones del inmueble y recopilar información que permita reconstruir los momentos previos y posteriores al fatal incidente. Las autoridades deberán determinar si la caída se produjo accidentalmente o si existió la intervención de otra persona. Para ello, se vienen recogiendo testimonios de quiénes participaron en la fiesta y de otros posibles testigos, además de realizarse las pericias correspondientes. El cuerpo de Juliet Alisson Zambrano Fino fue trasladado a la morgue de Piura, donde se realizarán los procedimientos establecidos por ley. INVESTIGACIONES Mientras avanzan las investigaciones, el caso ha generado preocupación entre los vecinos de Las Casuarinas. La Policía busca establecer las circunstancias exactas de la muerte y, de corresponder, identificar a los responsables y determinar las responsabilidades que establezca la investigación.</t>
+          <t>Las organizaciones políticas que participarán en las Elecciones Regionales y Municipales (ERM) 2026 están obligadas a presentar ante la Oficina Nacional de Procesos Electorales (ONPE) dos informes donde registren los gastos, aportes e ingresos de sus campañas. La fecha límite para presentar el primero de dichos informes es el próximo viernes 11 de setiembre. La obligación y el plazo también alcanzan a todos los ciudadanos que hayan logrado inscribir sus candidaturas para una Gobernación, una Vicegobernación o una Alcaldía –provincial o distrital– y se mantienen aun cuando la candidatura no llegue al final del proceso por renuncia, tacha o exclusión. Debido a un cambio en la Ley de Organizaciones Políticas, ya no rinden cuentas quienes aspiran a ser consejeros regionales o regidores municipales. El informe financiero lo puede presentar él mismo o, si tiene, su responsable de campaña.</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>https://eltiempo.pe/local/fiesta-termina-con-una-mujer-fallecida/</t>
+          <t>https://eltiempo.pe/local/candidatos-a-gobernadores-y-alcaldes-obligados-a-rendir-sus-gastos/</t>
         </is>
       </c>
     </row>
@@ -1269,17 +1263,17 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Choque de autos derriba poste</t>
+          <t>I.E. San Ramón de Chulucanas se consagra campeona del Regional Singing Festival 2026</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Un violento accidente de tránsito entre dos automóviles se registró ayer en horas de la mañana en la avenida Universitaria de Piura, a la altura del Fundo Vite. PUEDES LEER ► “Monstruo de las 10 cabezas” Según información preliminar, uno de los vehículos tras el choque habría también impactado contra un poste que no sería de tendido eléctrico, provocando que la estructura se desplomara y terminara cayendo sobre el otro automóvil. Los vehículos permanecieron en la zona del accidente, mientras efectivos de la Policía Nacional acudieron para realizar las diligencias correspondientes y determinar las circunstancias en que ocurrió el hecho. Hasta el cierre de edición, no se informó oficialmente sobre personas heridas como consecuencia del accidente. Cabe mencionar que el accidente generó preocupación entre los conductores que transitaban por este importante tramo de la avenida Universitaria.</t>
+          <t>La Institución Educativa San Ramón de Chulucanas, representante de la UGEL Chulucanas , obtuvo el primer lugar en el Regional Singing Festival 2026 “Singing for a Better World”, organizado por la Dirección Regional de Educación de Piura. PUEDES LEER ► Sobrevive tras 10 días sepultada por el lodo y es rescatada cuando su familia ya la había dado por muerta La actividad se desarrolló en el parque Néstor Martos de Piura y reunió a estudiantes representantes de las 12 UGEL de la región, quienes demostraron sus habilidades en la interpretación de canciones en inglés. El festival tiene como finalidad fortalecer las competencias comunicativas en el idioma inglés, además de promover la creatividad, la expresión artística y la participación de los estudiantes. La iniciativa se desarrolla en concordancia con el Currículo Nacional de la Educación Básica. Durante sus presentaciones, los participantes también transmitieron mensajes relacionados con valores y actitudes que contribuyen a una convivencia democrática, respetuosa, inclusiva y solidaria. San Ramón conquistó el primer lugar La IE San Ramón logró imponerse en la competencia con la interpretación de la canción “Hand for Chulucanas”, presentación que le permitió quedarse con el primer puesto del festival regional. El segundo lugar fue para la IE Libertadores de América, representante de la UGEL La Unión, que participó con la canción “The Song of Tomorrow”. Mientras que el tercer puesto correspondió a la IE César Vallejo, de la UGEL Morropón, con la interpretación de “Brighter Than Before”. La competencia comenzó en cada institución educativa y posteriormente continuó en las diferentes etapas de las 12 UGEL de Piura: Ayabaca, Chulucanas, Huancabamba, Huarmaca, La Unión, Morropón, Paita, Piura, Sechura, Sullana, Talara y Tambogrande. Además de impulsar el aprendizaje del inglés, el festival busca fortalecer la sana competencia, el trabajo en equipo y la integración entre estudiantes de diferentes provincias de la región.</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>https://eltiempo.pe/local/choque-de-autos-derriba-poste/</t>
+          <t>https://eltiempo.pe/local/i-e-san-ramon-de-chulucanas-se-consagra-campeona-del-regional-singing-festival-2026/</t>
         </is>
       </c>
     </row>
@@ -1294,17 +1288,17 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>FEN asusta a la banca privada</t>
+          <t>Así van los candidatos a falta de un mes para elecciones</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>El impacto del Fenómeno El Niño (FEN) en el terreno económico también se sentirá en los créditos a las pequeñas y medianas empresas relacionadas a los sectores primarios de la economía como son la pesca y agricultura. PUEDES LEER ► ProInversión y Marina de Guerra evaluarán proyectos de inversión privada sobre terrenos y bienes navales De acuerdo a los especialistas consultados, algunas empresas financieras podrían reforzar sus criterios para el otorgamiento de préstamos a los pequeños empresarios, con la finalidad de prevenir problemas de morosidad. “Los créditos asociados a personas que se desempeñan en esos sectores van a tener probablemente dificultades para afrontar sus deudas. Eso es algo que ya vimos en períodos pasados del FEN como en el 2023 y 2017” , comentó Stephani Maita, economista senior del Instituto Peruano de Economía (IPE). Explica que el impacto del FEN en el agro y pesca se relaciona en un primer momento con la pérdida del empleo. “Un tercio del empleo total en la región está vinculado al sector agrícola entonces las familias que tengan actividades vinculadas a este sector y tengan préstamos probablemente van a tener dificultades para afrontar sus deudas. Lo mismo con las empresas. A esto también se va el efecto por los precios al alza. Potencialmente podría terminar afectando la calidad de las carteras de créditos ”, enfatizó. Expectativas De otro lado, Maita señala que pese a la amenaza del fenómeno natural que se avecina, todavía hay expectativas positivas en la economía nacional. “El Banco Central de Reserva publicó una encuesta de perspectivas sobre el mercado de créditos tanto desde el lado de la oferta, es decir la perspectiva de los bancos y entidades financieras, como desde la demanda que es más desde los usuarios que solicitan los créditos. Por el lado de la demanda se encontraba que la perspectiva era favorable en la medida que la actividad económica en general, mas allá de los sectores primarios, goza de salud y está creciendo de forma importante”, aseveró Maita. Sin embargo, por el lado de las empresas existe un mayo grado de cautela sobre a quién le otorgan los préstamos con la finalidad de evitar el aumento de la morosidad. “Las empresas ya están previendo reforzar algunos criterios para otorgar créditos considerando los eventos climáticos que van a afectar, probablemente, en mayor medida los segmentos de las carteras más pequeñas, hablamos de microempresas, medianas y pequeñas empresas, las cuales son las que han registrado las mayores dificultades para afrontar sus créditos en el pasado”, manifestó Maita. Criterios Desde su punto de vista los nuevos requisitos implica un examen más exhaustivo del cliente que llega a solicitar el financiamiento. “Se refiere a otorgar créditos de menor tamaño, con plazos más extensos para que las cuotas sean un poco más pequeñas o quizás hacer una evaluación más minuciosa respecto de los ingresos de las empresas o que tanta exposición tienen a este tipo de fenómenos dependiendo de las actividades en las que se desempeñan. Por ejemplo, una empresa dedicada a la agroexportación probablemente será mucho más golpeada por el fenómeno climático frente a una empresa de transporte. Igual esta última va a sufrir algunos estragos por las lluvias, pero ese impacto es considerablemente menor frente a una empresa que se desempeña en agricultura. Agrega que en este punto los bancos tienden a elegir un poco mejor o cambiar un poco sus decisiones de dación de créditos para evitar exponerse a potenciales impagos.</t>
+          <t>ICSI Perú hizo una encuesta y revela cómo van las preferencias de los piuranos sobre su próximo gobernador y alcaldes. PUEDES LEER ► Miniván queda al borde de un abismo en la carretera Canchaque -Huancabamba Las elecciones regionales y municipales están a la vuelta de la esquina y lo único seguro es que sí o sí habrá una segunda vuelta para el cargo de gobernador regional. De acuerdo a ley, si ninguna lista supera el 30% de votos válidos, se convoca a una segunda vuelta entre los dos primeros del escrutinio. De acuerdo a la última encuesta de la empresa ICSI Perú ninguno de los aspirantes a la máxima autoridad regional llega al 30% de las preferencias. Según el estudio de opinión pública, el primer lugar es para el exgobernador Reynaldo Hilbck (Alianza para el Progreso) con 22.5%; seguido por Santiago Paz (Somos Perú) con 13.7% ; Mártires Lizana (Fuerza Popular) con 11.1% y Guillermo La Torre (Podemos Perú) con 10.9%. En el caso de los candidatos provinciales, la disputa parece más reñida y la diferencia de porcentajes es más ajustada entre los aspirantes, con lo cual la campaña de aquí hasta el domingo 4 de octubre será una competencia voto a voto y de convencimiento de los indecisos. Gobierno Regional Sobre el tema, el gerente de ICSI Perú, Mauro Vegas Carmen , consideró que uno de los factores del respaldo a Hilbck son sus candidatos en las provincias con mayor caudal electoral de votos. “En los resultados de los 27 distritos a donde se ha ido, Hilbck alcanza la mayor votación en Piura, Veintiséis de Octubre, Catacaos, Sullana, Morropón, Chulucanas, Talara, Órganos y otros. Todo eso le da ese porcentaje que ahora ha sacado frente al segundo. Por ejemplo, en Piura tiene 19.66% y Somos Perú tiene 15.33%; en Castilla, Hilbck tiene 13.60% y Somos Perú unos 10.90% y en Veintiséis de Octubre, Hilbck tiene 20.35% y Somos Perú, 15.34%. En Sullana que es una plaza fuerte, se tiene 19.59% y Santiago Paz llega a 12.14%, asimismo, en Chulucanas, Hilbck logra 17.4% y Somos Perú 9.87%”, mencionó. Agrega que este respaldo de Hilbck en las provincias y distritos se refleja en sus candidatos para estas jurisdicciones. Un segundo factor, sostiene, es el respaldo de la maquinaria electoral de un partido como Alianza para el Progreso (APP). “Ese porcentaje es coherente porque sus candidatos provinciales y también distritales ganan, además que la maquinaria electoral que se percibe en la región”, agregó. Somos Perú Sobre Santiago Paz de Somos Perú que marcha en segundo lugar con 13.7%, el gerente de ICSI Perú sostuvo que no le va bien con sus candidatos en Piura, Castilla, Veintiséis de Octubre, Tambogrande o Sullana. “En el caso Chulucanas, como distrito capital, el candidato Nelson Mío que hace un mes era fuerte, ha tenido un descenso porque ahí han ingresado candidatos nuevos como Hernán Pasapera de Renovación y Manuel Cueva de Podemos. Eso le ha restado fuerza a Somos Perú”, aseveró. Sobre Mártires Lizana de Fuerza Popular que marcha tercero, Vegas destaca que esto ocurre por la aceptación del candidato a la provincia de Piura, Martín Olivares, que está segundo en la preferencial provincial. Nulos En el estudio también se revela que un 18% de los encuestados no votaría por ninguno de los postulantes o lo haría en blanco. “Esto puede variar producto de la campaña y contracampaña. Aquí quien tiene mejor equipo de contracampaña es el que tiene mayor ventaja de ganar. Es quien reacciona rápido, de forma contundente y demoledora. No siempre la percepción es la verdad, por eso una contracampaña tiene que responderse de manera rápida y contundente. No se trata del mejor indudablemente, sino de quien cometa menos errores y sepa responder a los ataques fundados o infundados”, destacó.n</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>https://eltiempo.pe/local/fen-asusta-a-la-banca-privada/</t>
+          <t>https://eltiempo.pe/local/asi-van-los-candidatos-a-falta-de-un-mes-para-elecciones/</t>
         </is>
       </c>
     </row>
@@ -1319,17 +1313,17 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>“Monstruo de las 10 cabezas”</t>
+          <t>Miniván queda al borde de un abismo en la carretera Canchaque -Huancabamba</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>En la carrera contra el tiempo para ejecutar las actividades que aminoren el impacto del Fenómeno El Niño (FEN) , la región se enfrenta a otro enemigo. Se trata del propio Estado y la complejidad de sus instituciones, procesos y competencias que hacen mucho más lenta la respuesta a la emergencia. PUEDES LEER ► Callao: joven de 20 años es asesinado a balazos en el distrito de Mi Perú “La situación de desorden que tenemos en el Estado es como decir que tenemos un monstruo de 10 cabezas. Está lo que maneja Veintiséis de Octubre, lo que maneja la Municipalidad de Piura o el Ministerio de Vivienda, cuando debería haber una sola cabeza en el control de inundaciones y de nuestras cuencas [Luego] tenemos el proyecto Alto Piura y el proyecto Chira Piura que manejan la jurisdicción de estas dos cuencas con el ANA (Autoridad Nacional del Agua) como ente rector. [También] tuvimos la Autoridad para la Reconstrucción con Cambios (ARCC) que evaluaba un plan maestro”, aseveró la senadora de Piura, Karla Schaefer. Otra muestra del problema de esta gran burocracia, señala, es que luego se creó la Autoridad Nacional de Infraestructura (ANIN) que también tiene fichas de intervención de diferentes puntos críticos. “Y esas benditas competencias que no te dejan [trabajar] y todos se mueren de miedo de firmar un documento por la Contraloría [...] Por ejemplo, el alcalde de Veintiséis de Octubre tiene una situación compleja con el dren Maldonado y que podría dejar incomunicado a 60 mil personas de un lado a otro. Se pidió el apoyo a Transportes, como una de las alternativas, que tiene puentes Baileys, aún esperamos respuesta. [...] Este es un tema que el decreto de urgencia nos debería dejar actuar y que no permitan que los empresarios, que hace dos semanas están esperando este documento, luego se vean entrampados” , consideró. Reunión Schaefer brindó estas declaraciones este martes en la primera sesión descentralizada del Consejo Directivo Descentralizado Macro Región Norte que agrupa a las empresas asociadas a la Confiep (Confederación Nacional de Instituciones Empresariales Privadas), que desean apoyar a las actividades de mitigación contra El Niño. Parte de este problema también fue expuesto por el presidente de la Confiep, Jorge Zapata , quien destacó que las empresas privadas podrían invertir unos 4 mil millones de sus impuestos en Piura bajo una modalidad abreviada de obras por impuestos Se trata de servicios por impuestos que todavía no existe porque debe aprobarse el decreto supremo para que las empresas privadas tengan marco legal para intervenir en Chutuque, cuencas ciegas u otros puntos críticos. “Pi ura cuenta con 4 mil 352 millones de soles bajo la modalidad de obras o servicios por impuestos. Tenemos la plata y no somos capaces de solucionar los temas. No es un tema de dinero y hace mucho tiempo lo venimos diciendo. Los privados ya están haciendo el esfuerzo necesario; ya hemos visto donaciones de varias empresas; la Sociedad Nacional de Minería está evaluando la apertura del canal de Chutuque, pero hay un detalle mínimo y que parece absurdo, sobre a quién se va a contratar para la información de la ficha técnica [de Chutuque]. Tenemos que ponernos de acuerdo en un detalle mínimo cuando tenemos 18 mil millones de soles por ejecutar”, destacó. Zapata mencionó esto en relación a la ficha técnica que hace falta para intervenir en los 6 kilómetros del canal Chutuque mediante explosivos. La ANA señala que no hay información, mientras que desde la Cámara de Comercio se indica que esta información la posee el ingeniero César Alvarado. Alvarado es el especialista y autor de la primera versión del Plan Integral de Manejo del Río Piura que contrató la desaparecida Autoridad para la Reconstrucción con Cambios (ARCC), la cual nació luego de la inundación del 2017.</t>
+          <t>Unos 12 pasajeros se salvaron de caer a un abismo de aproximadamente 200 metros luego de que una miniván de una empresa de transporte sufriera un accidente en la carretera Canchaque-Huancabamba, en el sector Las Minas. Según información preliminar, la unidad terminó volcada y quedó peligrosamente cerca del precipicio, generando momentos de angustia entre los pasajeros, entre ellos algunos menores de edad, quienes temieron lo peor. Pese a la violencia del accidente, los ocupantes solo habrían sufrido algunos golpes, además del fuerte susto provocado por el incidente. Hasta el momento no se han reportado oficialmente personas con lesiones de consideración. EL EQUIPAJE El accidente también ocasionó la caída de algunos equipajes que eran transportados en la parte superior de la miniván, los cuales algunos habrían terminado en el fondo del abismo. De acuerdo con versiones preliminares, no se descarta que el vehículo haya sufrido algún desperfecto mecánico antes de producirse el accidente. Sin embargo, esta posibilidad deberá ser determinada mediante las investigaciones correspondientes. Asimismo, las autoridades realizan las diligencias para establecer las causas exactas del siniestro y determinar las condiciones en las que circulaba la unidad. Cabe mencionar que el hecho vuelve a poner en evidencia el peligro de transitar por esta vía, caracterizada por sus pronunciadas pendientes y zonas de profundo precipicio.</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>https://eltiempo.pe/local/monstruo-de-las-10-cabezas/</t>
+          <t>https://eltiempo.pe/local/minivan-queda-al-borde-de-un-abismo-en-la-carretera-canchaque-huancabamba/</t>
         </is>
       </c>
     </row>
@@ -1344,17 +1338,17 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Miniván queda al borde de un abismo en la carretera Canchaque -Huancabamba</t>
+          <t>Fiesta termina con una mujer fallecida</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Unos 12 pasajeros se salvaron de caer a un abismo de aproximadamente 200 metros luego de que una miniván de una empresa de transporte sufriera un accidente en la carretera Canchaque-Huancabamba, en el sector Las Minas. Según información preliminar, la unidad terminó volcada y quedó peligrosamente cerca del precipicio, generando momentos de angustia entre los pasajeros, entre ellos algunos menores de edad, quienes temieron lo peor. Pese a la violencia del accidente, los ocupantes solo habrían sufrido algunos golpes, además del fuerte susto provocado por el incidente. Hasta el momento no se han reportado oficialmente personas con lesiones de consideración. EL EQUIPAJE El accidente también ocasionó la caída de algunos equipajes que eran transportados en la parte superior de la miniván, los cuales algunos habrían terminado en el fondo del abismo. De acuerdo con versiones preliminares, no se descarta que el vehículo haya sufrido algún desperfecto mecánico antes de producirse el accidente. Sin embargo, esta posibilidad deberá ser determinada mediante las investigaciones correspondientes. Asimismo, las autoridades realizan las diligencias para establecer las causas exactas del siniestro y determinar las condiciones en las que circulaba la unidad. Cabe mencionar que el hecho vuelve a poner en evidencia el peligro de transitar por esta vía, caracterizada por sus pronunciadas pendientes y zonas de profundo precipicio.</t>
+          <t>Una fiesta terminó en tragedia en la urbanización Las Casuarinas II Etapa, en el distrito Veintiséis de Octubre , luego de que una joven de nacionalidad colombiana perdiera la vida tras caer desde un tragaluz del tercer piso de un inmueble hacia el segundo nivel. La víctima fue identificada como Juliet Alisson Zambrano Fino, de 21 años de edad. PUEDES LEER ► FEN asusta a la banca privada El hecho ocurrió durante una reunión social y las circunstancias de la caída son materia de investigación por parte de la Policía. De acuerdo con información preliminar, una de las hipótesis que manejan las autoridades es que la joven habría sido presuntamente arrojada por un tragaluz, desde donde terminó cayendo hasta el segundo piso del inmueble. Sin embargo, esta versión todavía deberá ser corroborada mediante las diligencias policiales, pericias y demás elementos que permitan determinar qué ocurrió exactamente antes de la caída. SIN SIGNOS VITALES Tras conocerse el hecho, personal de Serenazgo del distrito Veintiséis de Octubre y una ambulancia del SAMU Piura llegaron hasta el lugar de la tragedia para brindar atención a la víctima. No obstante, los equipos de emergencia encontraron a la joven sin signos vitales. En el lugar también se encontraba un ciudadano extranjero, quien, visiblemente afectado y entre lágrimas, solicitaba ayuda para la mujer. RECOPILAN INFORMACIÓN Agentes de la Policía Nacional acudieron posteriormente a la escena para realizar las primeras diligencias, verificar las condiciones del inmueble y recopilar información que permita reconstruir los momentos previos y posteriores al fatal incidente. Las autoridades deberán determinar si la caída se produjo accidentalmente o si existió la intervención de otra persona. Para ello, se vienen recogiendo testimonios de quiénes participaron en la fiesta y de otros posibles testigos, además de realizarse las pericias correspondientes. El cuerpo de Juliet Alisson Zambrano Fino fue trasladado a la morgue de Piura, donde se realizarán los procedimientos establecidos por ley. INVESTIGACIONES Mientras avanzan las investigaciones, el caso ha generado preocupación entre los vecinos de Las Casuarinas. La Policía busca establecer las circunstancias exactas de la muerte y, de corresponder, identificar a los responsables y determinar las responsabilidades que establezca la investigación.</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>https://eltiempo.pe/local/minivan-queda-al-borde-de-un-abismo-en-la-carretera-canchaque-huancabamba/</t>
+          <t>https://eltiempo.pe/local/fiesta-termina-con-una-mujer-fallecida/</t>
         </is>
       </c>
     </row>
@@ -1365,21 +1359,21 @@
         </is>
       </c>
       <c r="B35" s="2" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Piura: Dengue, una amenaza que sigue creciendo</t>
+          <t>Choque de autos derriba poste</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>El fenómeno El Niño aún no se manifiesta con fuertes lluvias en la región Piura, pero los casos de dengue ya superan las 8 mil personas infectadas . Un escenario peligroso de cara a lo que se viene en el verano que es cuando el zancudo transmisor de la enfermedad encuentra mejores condiciones para reproducirse. Asimismo, luego de vivir un año 2025 sin muertes por la enfermedad, en lo que va de este 2026 ya se han reportado cinco decesos por dengue. En tres casos, se confirmó la mortandad por dengue, mientras que los restantes siguen bajo investigación. Sobre el tema el médico epidemiólogo y exsubdirector de salud, César Guerrero, consideró que los casos actuales están fuera del promedio del canal endémico que se había previsto para esta época del año. “Hay más casos de lo que se esperaba en este año por lo cual se están tomando algunas acciones que podrían aumentar en el caso de finales de año, dependiendo de la intensidad de las lluvias y de los hábitos de las personas. Actualmente, se están reportando un promedio de 700 casos por semana. Además, hay otras subregiones que reportan curvas en ascenso” , sostuvo. Serotipo Asimismo, el especialista informó que también es posible un aumento de los casos graves tomando en cuenta que circulan los cuatro serotipos en la región. “Si yo he tenido una infección previa por un serotipo diferente al que me está dando actualmente, es más frecuente que el dengue actual sea más complicado. Si el año me dio dengue por el serotipo 1 y ahora te da dengue serotipo 3, puede hacer que la enfermedad sea más grave. [En el verano] podría ser que los casos que se presenten sean un poco más severos que los previos que tuvo”, afirmó. Agregó que en la actualidad están circulando dos tipos de serotipos del dengue completamente diferentes que están haciendo que se agrave la situación de salud de los piuranos. “Según las cifras de Diresa, el dengue con signos de alarma está en el orden del 15.9% de los enfermos de dengue y que ameritan hospitalización”, indicó. De otro lado, Guerrero agregó que con la proliferación del zancudo también aumenta el riesgo de propagación de otras enfermedades como el sika y chikungunya. A esto se sumarían las enfermedades digestivas por los problemas con el almacenamiento del agua potable durante las interrupciones del servicio. Leptospirosis, acecha y supera al 2025 Cabe indicar que de acuerdo a la sala situacional de la Dirección Regional de Salud (Diresa), los casos de leptospirosis ascienden a unss 1927 personas infectadas. La cifra genera preocupación porque dentro del mismo periodo del 2025, los reportes de los centros de salud solo habían contabilizado unos 341 casos de la bacteria. Cómo se sabe, las personas adquieren leptospirosis por el contacto con aguas empozadas y contaminadas con la bacteria que se encuentra en las deposiciones de los roedores. Este escenario podría complicarse con las lluvias de El Niño que generan acumulación de agua por falta sistema de drenaje. Del total de casos, la provincia de Sullana concentra el 33.7% de los casos, seguida por Morropón, Tambogrande y Chulucanas.</t>
+          <t>Un violento accidente de tránsito entre dos automóviles se registró ayer en horas de la mañana en la avenida Universitaria de Piura, a la altura del Fundo Vite. PUEDES LEER ► “Monstruo de las 10 cabezas” Según información preliminar, uno de los vehículos tras el choque habría también impactado contra un poste que no sería de tendido eléctrico, provocando que la estructura se desplomara y terminara cayendo sobre el otro automóvil. Los vehículos permanecieron en la zona del accidente, mientras efectivos de la Policía Nacional acudieron para realizar las diligencias correspondientes y determinar las circunstancias en que ocurrió el hecho. Hasta el cierre de edición, no se informó oficialmente sobre personas heridas como consecuencia del accidente. Cabe mencionar que el accidente generó preocupación entre los conductores que transitaban por este importante tramo de la avenida Universitaria.</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>https://eltiempo.pe/local/piura-dengue-una-amenaza-que-sigue-creciendo/</t>
+          <t>https://eltiempo.pe/local/choque-de-autos-derriba-poste/</t>
         </is>
       </c>
     </row>
@@ -1390,21 +1384,21 @@
         </is>
       </c>
       <c r="B36" s="2" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Sechura: Exigen control de flotas por caída de la pota</t>
+          <t>FEN asusta a la banca privada</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>La pesquería del calamar gigante o pota enfrenta una severa crisis logística y de mercado en el litoral norteño. Henry Juárez, presidente del gremio de pescadores artesanales de Parachique, alertó sobre las graves consecuencias del incremento descontrolado de la flota, la cual pasó de 5,000 embarcaciones el año pasado a 9,000 en la presente temporada, debido a la migración de botes provenientes de otras pesquerías. PUEDES LEER ► Declaran en emergencia 5 penales, pero olvidan a Piura Esta sobreoferta de naves ha saturado la cadena de suministro local. La salida simultánea de la flota ha provocado un agudo desabastecimiento de hielo, elevando su costo hasta rangos de entre S/200 y S/250 por la alta demanda . A este difícil panorama se suma el encarecimiento del petróleo y de los servicios asociados. En el aspecto comercial, el dirigente denunció una fuerte especulación por parte de intermediarios en playa y una preocupante disparidad de precios en las plantas procesadoras. Mientras que en el sur del país las fábricas pagan S/3.00 por kilogramo, en el norte el valor descendió de S/3.00 a S/2.50. Ante esta situación, el gremio exige un sinceramiento de los precios para conocer los márgenes reales de ganancia de las plantas al exportar al extranjero. Como solución, Juárez plantea implementar un modelo de ordenamiento inspirado en Chile, donde se distribuyan topes de pesca a las embarcaciones de acuerdo con la capacidad real de procesamiento de las fábricas. Si bien, en Parachique, la asamblea comunal fiscaliza de forma interna los límites de descarga colocando inspectores a bordo de cada nave, esta medida no se puede replicar en muelles privados ni en Paita.</t>
+          <t>El impacto del Fenómeno El Niño (FEN) en el terreno económico también se sentirá en los créditos a las pequeñas y medianas empresas relacionadas a los sectores primarios de la economía como son la pesca y agricultura. PUEDES LEER ► ProInversión y Marina de Guerra evaluarán proyectos de inversión privada sobre terrenos y bienes navales De acuerdo a los especialistas consultados, algunas empresas financieras podrían reforzar sus criterios para el otorgamiento de préstamos a los pequeños empresarios, con la finalidad de prevenir problemas de morosidad. “Los créditos asociados a personas que se desempeñan en esos sectores van a tener probablemente dificultades para afrontar sus deudas. Eso es algo que ya vimos en períodos pasados del FEN como en el 2023 y 2017” , comentó Stephani Maita, economista senior del Instituto Peruano de Economía (IPE). Explica que el impacto del FEN en el agro y pesca se relaciona en un primer momento con la pérdida del empleo. “Un tercio del empleo total en la región está vinculado al sector agrícola entonces las familias que tengan actividades vinculadas a este sector y tengan préstamos probablemente van a tener dificultades para afrontar sus deudas. Lo mismo con las empresas. A esto también se va el efecto por los precios al alza. Potencialmente podría terminar afectando la calidad de las carteras de créditos ”, enfatizó. Expectativas De otro lado, Maita señala que pese a la amenaza del fenómeno natural que se avecina, todavía hay expectativas positivas en la economía nacional. “El Banco Central de Reserva publicó una encuesta de perspectivas sobre el mercado de créditos tanto desde el lado de la oferta, es decir la perspectiva de los bancos y entidades financieras, como desde la demanda que es más desde los usuarios que solicitan los créditos. Por el lado de la demanda se encontraba que la perspectiva era favorable en la medida que la actividad económica en general, mas allá de los sectores primarios, goza de salud y está creciendo de forma importante”, aseveró Maita. Sin embargo, por el lado de las empresas existe un mayo grado de cautela sobre a quién le otorgan los préstamos con la finalidad de evitar el aumento de la morosidad. “Las empresas ya están previendo reforzar algunos criterios para otorgar créditos considerando los eventos climáticos que van a afectar, probablemente, en mayor medida los segmentos de las carteras más pequeñas, hablamos de microempresas, medianas y pequeñas empresas, las cuales son las que han registrado las mayores dificultades para afrontar sus créditos en el pasado”, manifestó Maita. Criterios Desde su punto de vista los nuevos requisitos implica un examen más exhaustivo del cliente que llega a solicitar el financiamiento. “Se refiere a otorgar créditos de menor tamaño, con plazos más extensos para que las cuotas sean un poco más pequeñas o quizás hacer una evaluación más minuciosa respecto de los ingresos de las empresas o que tanta exposición tienen a este tipo de fenómenos dependiendo de las actividades en las que se desempeñan. Por ejemplo, una empresa dedicada a la agroexportación probablemente será mucho más golpeada por el fenómeno climático frente a una empresa de transporte. Igual esta última va a sufrir algunos estragos por las lluvias, pero ese impacto es considerablemente menor frente a una empresa que se desempeña en agricultura. Agrega que en este punto los bancos tienden a elegir un poco mejor o cambiar un poco sus decisiones de dación de créditos para evitar exponerse a potenciales impagos.</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>https://eltiempo.pe/local/sechura-exigen-control-de-flotas-por-caida-de-la-pota/</t>
+          <t>https://eltiempo.pe/local/fen-asusta-a-la-banca-privada/</t>
         </is>
       </c>
     </row>
@@ -1415,21 +1409,21 @@
         </is>
       </c>
       <c r="B37" s="2" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Piura: Defensoría advierte riesgo crítico de colapso de casonas ante próximas lluvias</t>
+          <t>“Monstruo de las 10 cabezas”</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Para garantizar la seguridad de la ciudadanía y mitigar los impactos frente a la temporada de lluvias por el Fenómeno El Niño (FEN) 2026, personal de la Defensorial de Piura participó en la reunión de trabajo multisectorial para evaluar el estado situacional de las obras de infraestructura vial y los planes de contingencia vigentes en la provincia, convocada por la Segunda Fiscalía de Prevención del Delito del Ministerio Público. PUEDES LEER ► Tumbes: Detienen a adolescente y adulto luego de una persecución a balazos El encuentro contó con la participación de representantes de Corporación Diamantes Juvers SAC, Municipalidad de Castilla, equipo técnico de la EPS Grau, el supervisor de obras del centro de Piura y coordinadores de proyectos ejecutados en articulación con los gobiernos locales y el Gore. Durante la sesión, se solicitó los cronogramas y las condiciones de ejecución de las obras de pistas, veredas y drenaje pluvial que se desarrollan en la ciudad. Se enfatizó la necesidad de que las constructoras y entidades responsables adopten medidas correctivas inmediatas para evitar paralizaciones que dejen desprotegida a la infraestructura urbana ante las próximas precipitaciones.</t>
+          <t>En la carrera contra el tiempo para ejecutar las actividades que aminoren el impacto del Fenómeno El Niño (FEN) , la región se enfrenta a otro enemigo. Se trata del propio Estado y la complejidad de sus instituciones, procesos y competencias que hacen mucho más lenta la respuesta a la emergencia. PUEDES LEER ► Callao: joven de 20 años es asesinado a balazos en el distrito de Mi Perú “La situación de desorden que tenemos en el Estado es como decir que tenemos un monstruo de 10 cabezas. Está lo que maneja Veintiséis de Octubre, lo que maneja la Municipalidad de Piura o el Ministerio de Vivienda, cuando debería haber una sola cabeza en el control de inundaciones y de nuestras cuencas [Luego] tenemos el proyecto Alto Piura y el proyecto Chira Piura que manejan la jurisdicción de estas dos cuencas con el ANA (Autoridad Nacional del Agua) como ente rector. [También] tuvimos la Autoridad para la Reconstrucción con Cambios (ARCC) que evaluaba un plan maestro”, aseveró la senadora de Piura, Karla Schaefer. Otra muestra del problema de esta gran burocracia, señala, es que luego se creó la Autoridad Nacional de Infraestructura (ANIN) que también tiene fichas de intervención de diferentes puntos críticos. “Y esas benditas competencias que no te dejan [trabajar] y todos se mueren de miedo de firmar un documento por la Contraloría [...] Por ejemplo, el alcalde de Veintiséis de Octubre tiene una situación compleja con el dren Maldonado y que podría dejar incomunicado a 60 mil personas de un lado a otro. Se pidió el apoyo a Transportes, como una de las alternativas, que tiene puentes Baileys, aún esperamos respuesta. [...] Este es un tema que el decreto de urgencia nos debería dejar actuar y que no permitan que los empresarios, que hace dos semanas están esperando este documento, luego se vean entrampados” , consideró. Reunión Schaefer brindó estas declaraciones este martes en la primera sesión descentralizada del Consejo Directivo Descentralizado Macro Región Norte que agrupa a las empresas asociadas a la Confiep (Confederación Nacional de Instituciones Empresariales Privadas), que desean apoyar a las actividades de mitigación contra El Niño. Parte de este problema también fue expuesto por el presidente de la Confiep, Jorge Zapata , quien destacó que las empresas privadas podrían invertir unos 4 mil millones de sus impuestos en Piura bajo una modalidad abreviada de obras por impuestos Se trata de servicios por impuestos que todavía no existe porque debe aprobarse el decreto supremo para que las empresas privadas tengan marco legal para intervenir en Chutuque, cuencas ciegas u otros puntos críticos. “Pi ura cuenta con 4 mil 352 millones de soles bajo la modalidad de obras o servicios por impuestos. Tenemos la plata y no somos capaces de solucionar los temas. No es un tema de dinero y hace mucho tiempo lo venimos diciendo. Los privados ya están haciendo el esfuerzo necesario; ya hemos visto donaciones de varias empresas; la Sociedad Nacional de Minería está evaluando la apertura del canal de Chutuque, pero hay un detalle mínimo y que parece absurdo, sobre a quién se va a contratar para la información de la ficha técnica [de Chutuque]. Tenemos que ponernos de acuerdo en un detalle mínimo cuando tenemos 18 mil millones de soles por ejecutar”, destacó. Zapata mencionó esto en relación a la ficha técnica que hace falta para intervenir en los 6 kilómetros del canal Chutuque mediante explosivos. La ANA señala que no hay información, mientras que desde la Cámara de Comercio se indica que esta información la posee el ingeniero César Alvarado. Alvarado es el especialista y autor de la primera versión del Plan Integral de Manejo del Río Piura que contrató la desaparecida Autoridad para la Reconstrucción con Cambios (ARCC), la cual nació luego de la inundación del 2017.</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>https://eltiempo.pe/local/piura-defensoria-advierte-riesgo-critico-de-colapso-de-casonas-ante-proximas-lluvias/</t>
+          <t>https://eltiempo.pe/local/monstruo-de-las-10-cabezas/</t>
         </is>
       </c>
     </row>

--- a/Data/Piura/noticias_piura_20260904_20260911.xlsx
+++ b/Data/Piura/noticias_piura_20260904_20260911.xlsx
@@ -574,46 +574,35 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Piura: Gobierno se anticipa a El Niño y fortalece la capacidad de respuesta de EsSalud</t>
+          <t>Café: más de 46,000 familias cafetaleras se benefician de la Ruta Productiva Exportadora</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>En ese marco, el ministro de Trabajo y Promoción del Empleo, Juan Sheput, acompañado por la presidenta ejecutiva encargada de EsSalud, Hilda Sandoval, realizó visitas inopinadas a los hospitales de Talara y Sullana.
-Durante las supervisiones, verificaron las condiciones reales de los servicios, identificaron brechas en equipamiento, atención y personal especializado, y dispusieron medidas para fortalecer la capacidad de respuesta de los establecimientos y asegurar la continuidad de la atención a los asegurados.
-“Hemos venido a identificar los problemas y tomar decisiones para resolverlos –dijo el ministro–.
-Queremos conocer qué necesitan nuestros hospitales, qué requieren los profesionales de salud y, principalmente, qué están enfrentando los asegurados cuando buscan atención”.
-El titular del Ministerio de Trabajo y Promoción del Empleo (MTPE) remarcó que anticiparse al fenómeno El Niño “exige conocer directamente las condiciones de cada establecimiento” y convertir las necesidades identificadas en acciones concretas.
-“El asegurado necesita respuestas, atención oportuna y servicios que funcionen”, sostuvo.
-[Lea también: Simulacro nacional: EsSalud activa sus protocolos de emergencia en 400 establecimientos ] Talara: mayor capacidad quirúrgica y diagnóstica En el Hospital II Talara, Sheput y Sandoval verificaron la incorporación de equipos que permitirán poner en funcionamiento un segundo quirófano y aumentar aproximadamente en 30 % la capacidad del establecimiento para realizar intervenciones quirúrgicas.
-Asimismo, constataron la situación del tomógrafo destinado a fortalecer la atención en Talara, pero que actualmente se encuentra fuera de esta red asistencial, pese a que el hospital contaba con un espacio preparado para su instalación.
-Ante ello, el ministro dispuso revisar las decisiones adoptadas y evaluar las medidas necesarias para recuperar la capacidad diagnóstica que requieren los asegurados de la provincia.
-Durante la visita, ambas autoridades también supervisaron las acciones preventivas destinadas a garantizar la continuidad de los servicios, el abastecimiento y la capacidad operativa del hospital frente a posibles emergencias asociadas al fenómeno El Niño.
-“La prevención significa anticiparnos.
-Tenemos que garantizar que los establecimientos puedan seguir atendiendo y respondiendo cuando más los necesita la población”, señaló.
-[Lea también: Gobierno garantiza inmunoglobulina para pacientes de EsSalud y refuerza abastecimiento ] Sullana: más especialistas para atender a los asegurados En el Hospital I Sullana, identificaron como una de las principales prioridades fortalecer la disponibilidad de médicos especialistas y personal asistencial.
-Esta medida permitirá elevar la capacidad resolutiva del establecimiento y reducir la necesidad de trasladar pacientes a Piura para recibir atención.
-El ministro reconoció el compromiso de los profesionales del hospital y señaló que corresponde acompañar ese esfuerzo con mejores condiciones y con los equipos humanos necesarios para responder a la demanda de los asegurados.
-El ministro y la presidenta encargada también verificaron los avances alcanzados tras la recategorización del establecimiento.
-Su capacidad diaria de atención se ha duplicado, al pasar de aproximadamente 260 a cerca de 520 pacientes.
-Además, la implementación de una sala de emergencia con seis camas y oxígeno empotrado fortalece la respuesta frente a los casos que requieren atención inmediata.
-[Lea también: ProInversión: Torre Trecca da nuevo paso para iniciar su transformación ] Respuesta articulada frente al dengue Como parte de las medidas de preparación ante el incremento de las lluvias y las temperaturas, supervisaron un ambiente recientemente habilitado para la atención diferenciada de pacientes febriles y posibles casos de dengue.
-El ministro Sheput destacó la coordinación entre EsSalud y el Ministerio de Salud (Minsa) y planteó fortalecer los convenios de cooperación entre ambas instituciones para integrar capacidades, servicios y personal especializado frente a las necesidades sanitarias de la población.
-El ministro anunció que las supervisiones inopinadas continuarán en los establecimientos de EsSalud como parte de la estrategia del Gobierno para anticiparse a las emergencias, detectar oportunamente las brechas y acelerar las decisiones necesarias para mejorar los servicios.
-En coordinación con la presidenta ejecutiva encargada, se realizará el seguimiento de las medidas dispuestas para asegurar que los problemas identificados se conviertan en soluciones concretas para los asegurados.
-La jornada de trabajo en Piura continuará con nuevas acciones de supervisión y coordinación dentro de la red asistencial.
-[Lea también: Depresión afecta más a mujeres, según estadísticas del Hospital María Auxiliadora ] Más en Andina: EsSalud logra donación de órganos y piel que beneficiará a seis personas.
-Un hígado y dos riñones salvan vida a tres pacientes y dos córneas y piel mejoren la calidad de vida de otros tres.
-?? https://t.co/apWpg6Rfab pic.twitter.com/1rxtBZSOiX — Agencia Andina (@Agencia_Andina) September 11, 2026</t>
+          <t>La viceministra de Comercio Exterior, Sayuri Bayona , destacó este resultado durante su participación en el festival “Yo Tomo Café Peruano 2026”, que se desarrolla en el parque Kennedy, en Miraflores.
+Señaló que, a la fecha, 245 beneficiarios de la RPE forman parte de la cadena del café, con un impacto que alcanza a distintas regiones del país.
+Perú: ingreso por turismo receptivo sumará US$ 5,400 millones y superará nivel prepandemia “ Esta ruta brinda capacitaciones y asistencia técnica gratuita a organizaciones y mipymes, acompañándolos en el fortalecimiento de sus capacidades, desde la producción en campo hasta la comercialización en los mercados internacionales”, señaló la viceministra.
+El festival, organizado por la Comisión Nacional para el Desarrollo y Vida sin Drogas (Devida), reúne a productores y emprendimientos que presentan la diversidad y calidad de la oferta cafetalera nacional.
+En esta edición participan 20 beneficiarios de la Ruta Productiva Exportadora, quienes exhiben sus productos y acercan el café peruano a los consumidores.
+Como parte de este esfuerzo, Mincetur continuará impulsando herramientas que permitan a las organizaciones y mipymes de la cadena mejorar su productividad, fortalecer su oferta y aprovechar las oportunidades que brindan los mercados internacionales.
+La RPE es un instrumento multisectorial que articula los esfuerzos de distintas entidades, como Ministerio de la Producción (Produce), Ministerio de Desarrollo Agrario y Riego (Midagri), Ministerio del Ambiente (Minam), Ministerio de Ttrabajo y Promoción del Empleo (MTPE), Devida, entre otros, para promover el desarrollo productivo y la internacionalización de organizaciones y mipymes.
+“Desde el Mincetur impulsamos acciones para fortalecer las capacidades de nuestros productores, especialmente de las mipymes, y acompañarlos en su camino hacia la internacionalización”, puntualizó Bayona.
+Desempeño mundial del Perú El Perú se posiciona actualmente como el octavo exportador mundial de café y el cuarto en América Latina , gracias al trabajo de productores, cooperativas y micro, pequeñas y medianas empresas (mipymes) que vienen contribuyendo al fortalecimiento y crecimiento de la oferta cafetalera nacional.
+La producción cafetalera se desarrolla en diversas regiones del país, entre ellas Cajamarca, Junín, Amazonas, Piura, San Martín, Cusco, Puno, Pasco y Huánuco, que cuentan con un importante potencial para seguir incrementando su producción, mejorar la calidad de su oferta y conquistar nuevos mercados internacionales.
+En 2025, las exportaciones de café peruano alcanzaron los 1,800 millones de dólares, monto que representó un crecimiento de 63 % respecto de 2024 y que consolida a este producto como uno de los principales de la oferta agroexportadora peruana.
+Asimismo, el 59 % de las empresas que exportaron café en 2025 fueron mipymes, lo que evidencia el papel de estas empresas en la internacionalización del café peruano y en la generación de oportunidades económicas en las regiones productoras.
+Más en Andina: ??? El Gobierno aprobó nuevos servicios que podrán ejecutarse mediante Obras por Impuestos para atender el Fenómeno El Niño 2026-2027.
+Las nuevas relaciones corresponden a los sectores Ambiente y Producción.
+?? https://t.co/BDNcgRSUVA pic.twitter.com/rCZUAWWd6Z — Agencia Andina (@Agencia_Andina) September 11, 2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>https://andina.pe/agencia/noticia-piura-gobierno-se-anticipa-a-nino-y-fortalece-capacidad-respuesta-essalud-1091317.aspx</t>
+          <t>https://andina.pe/agencia/noticia-cafe-mas-46000-familias-cafetaleras-se-benefician-de-ruta-productiva-exportadora-1091362.aspx</t>
         </is>
       </c>
     </row>

--- a/Data/Piura/noticias_piura_20260904_20260911.xlsx
+++ b/Data/Piura/noticias_piura_20260904_20260911.xlsx
@@ -470,17 +470,17 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Contraloría: Obra recién culminada presenta signos de deterioro prematuro en Universidad Nacional de Frontera</t>
+          <t>Piura ya registra temperaturas máximas: Niño Costero entra en fase extraordinaria</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>La Contraloría General de la República (CGR) evidenció que la obra de ampliación del servicio de aulas de la facultad de Ingeniería Económica de la Universidad Nacional de Frontera, en la provincia de Sullana, presenta signos de deterioro prematuro pese a que los trabajos fueron recibidos en enero de este año. Esta situación genera el riesgo de afectar la calidad, operatividad y vida útil de este proyecto que tiene una inversión superior a los S/ 14 millones. En el Informe de Hito de Control n.° 11384-2026-CG/GRPI-SCC (periodo de evaluación del 12 al 18 de agosto de 2026), se identificaron diversas deficiencias en la infraestructura de los bloques I-A, I-B y II, entre ellas, puertas de madera desniveladas, falta de agua en inodoros y lavatorios, y tapajuntas de acero inoxidable con fijación deficiente en juntas de dilatación. En los servicios higiénicos del cuarto piso se constató que algunos inodoros permanecen inoperativos por falla en el sistema de abastecimiento de agua, mientras que el lavamanos destinado a personas con discapacidad presenta insuficiente presión. Además, se observaron aberturas en los tapajuntas que podrían facilitar el ingreso de humedad, residuos y agentes contaminantes. También se detectaron problemas en ambientes administrativos y académicos: una de las cuatro unidades evaporadoras del sistema de aire acondicionado de la sala de cómputo se encuentra inoperativa y varios lavatorios no cuentan con flujo de agua. En la sala de impresiones se verificó el desprendimiento de una baldosa del techo que dejó un sensor de humo suspendido por sus cables, además de evidencias de humedad y moho. En la actual área de grados y títulos y responsabilidad social se constató la ausencia de una puerta de vidrio, situación que deja expuestos equipos, mobiliario y documentación. A ello se suman el desprendimiento y agrietamiento del sellador de una escalera de madera, deformaciones en elementos de la pérgola en una plazoleta y tapas de concreto de canaletas pluviales deterioradas y desalineadas, generando riesgos para los usuarios. Asimismo, se constató que el ascensor del pabellón permanece fuera de servicio, pese a que la Unidad Ejecutora de Inversiones había requerido al contratista la subsanación de la falla en el marco de la garantía de obra y posteriormente realizó gestiones para evaluar técnicamente el problema. La inoperatividad del equipo obliga a estudiantes, docentes y personal a utilizar exclusivamente las escaleras y constituye una barrera crítica para las personas con movilidad reducida o discapacidad. Durante la inspección se verificó una diferencia entre los equipos adquiridos para el proyecto y los encontrados físicamente en el pabellón de la Facultad de Ingeniería Económica. De los 26 monitores con procesador integrado previstos para el proyecto, solo 12 fueron ubicados, uno en cada una de las aulas. Del mismo modo, se constató que únicamente ocho equipos cuentan con actas de entrega al área usuaria, pese a que la documentación de la entidad acredita la adquisición de los 26 monitores. Esta situación genera el riesgo de que 14 equipos no estén siendo utilizados para el fin para el cual fueron adquiridos, se encuentren en desuso o incluso se haya producido su pérdida. La obra se inició en noviembre de 2023 y debió culminar al siguiente año. Recién en enero de este año se suscribió el acta de recepción. El informe fue notificado al titular de la entidad para que adopte las acciones que correspondan, en el marco de sus competencias y obligaciones en la gestión institucional.</t>
+          <t>El Servicio Nacional de Meteorología e Hidrología del Perú (Senamhi) informó que El Niño Costero ingresó a una fase extraordinaria debido al incremento de la temperatura superficial del mar frente al litoral peruano y por la cual urge la ejecución de los proyectos para mitigar el impacto del fenómeno natural. El especialista del Senamhi, Nelson Quispe, informó que Tumbes, Piura, Lambayeque y La Libertad ya registran temperaturas máximas de hasta 37 °C, valores superiores a los habituales para esta época. El especialista explicó que el calentamiento del mar y la proximidad de la primavera, que comenzará el 22 de setiembre, serán otros de los factores que contribuirán al incremento del calor. Advierten que el escenario podría intensificarse durante los próximos meses. El Senamhi estima que las temperaturas en la costa norte continuarán aumentando y podrían bordear los 40 °C en febrero y marzo de 2027. LLUVIAS Y VIENTOS Respecto a las lluvias, el Senamhi precisó que todavía no se presentan precipitaciones intensas asociadas a esta fase del fenómeno. Asimismo informaron que entre el sábado y domingo se registrará un incremento de la velocidad del viento a lo largo de la costa, de moderada intensidad. “Este fenómeno podría generar levantamiento de polvo y arena, así como la reducción de la visibilidad horizontal”, refiere parte del aviso meteorológico regional N° 162, con lo cual se deberán tomar las precauciones del caso.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>https://eltiempo.pe/local/contraloria-obra-recien-culminada-presenta-signos-de-deterioro-prematuro-en-universidad-nacional-de-frontera/</t>
+          <t>https://eltiempo.pe/local/piura-ya-registra-temperaturas-maximas-nino-costero-entra-en-fase-extraordinaria/</t>
         </is>
       </c>
     </row>
@@ -495,17 +495,17 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Más de 4 mil casos de violencia contra mujeres y familiares genera preocupación en Piura</t>
+          <t>Contraloría: Obra recién culminada presenta signos de deterioro prematuro en Universidad Nacional de Frontera</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>La violencia contra las mujeres y los integrantes del grupo familiar mantiene cifras preocupantes en Piura . Entre enero y julio de 2026, los Centros Emergencia Mujer (CEM) de la región atendieron 4,578 casos de violencia , de acuerdo con el último reporte del Programa Nacional Warmi Ñan del Ministerio de la Mujer y Poblaciones Vulnerables (MIMP). La cifra representa un incremento considerable respecto al reporte acumulado hasta junio, cuando se registraban 3,272 casos. En solo un mes se sumaron 1,306 nuevas atenciones, lo que evidencia la magnitud del problema que enfrentan mujeres, niñas, niños, adolescentes y otros integrantes de las familias en diferentes provincias de la región. Según el Programa Nacional Warmi Ñan , los CEM son servicios públicos especializados y gratuitos que brindan atención psicológica, social y legal a personas afectadas por hechos de violencia. Consulta aquí la información oficial de Warmi Ñan sobre los Centros Emergencia Mujer . Piura concentra la mayor cantidad de casos de violencia La provincia de Piura concentra la mayor cantidad de atenciones reportadas en la región, con 2,580 casos entre enero y julio. La distribución muestra que las situaciones de violencia llegan a diferentes puntos de atención y no se concentran únicamente en una institución. La comisaría de Piura atendió 735 víctimas, mientras que el centro de salud Santa Julia registró 547 casos. A estos se suman 435 atenciones en la comisaría de familia, 236 en la comisaría rural de Tambogrande, 231 en Catacaos, 208 en La Unión y 188 correspondientes al distrito de Piura. Después de la provincia de Piura aparecen Sullana, con 436 casos; Paita, con 420; Ayabaca, con 359; Talara, con 256; Morropón, con 252; Sechura, con 163; y Huancabamba, con 112 casos . ¿Quiénes son los principales afectados por la violencia en Piura? Del total de 4,578 casos atendidos en los primeros siete meses del año, 4,015 corresponden a mujeres , equivalente al 87.7 %. Los hombres representan 563 casos, es decir, el 12.3 % del total. El grupo de edad con mayor número de atenciones corresponde a personas de entre 18 y 59 años, con 3,067 casos , que representan el 67 % del registro regional. También preocupa la cantidad de menores afectados. Entre niñas, niños y adolescentes de 0 a 17 años se contabilizaron 1,294 casos , equivalentes al 28.3 %. En tanto, las personas adultas mayores de 60 años registraron 217 atenciones, que representan el 4.7 %. Estos datos muestran que la violencia no afecta únicamente a las parejas o a mujeres adultas. También alcanza a menores de edad y adultos mayores dentro del entorno familiar, lo que amplía el impacto social de este problema. Violencia psicológica encabeza los casos registrados La violencia psicológica es la modalidad que concentra la mayor cantidad de atenciones en la región Piura. De acuerdo con el reporte, se registraron 2,091 casos, equivalentes al 45.7 % del total. En segundo lugar aparece la violencia física , con 1,833 casos y una participación del 40 %. Le sigue la violencia sexual, que alcanzó 650 casos, equivalente al 14.2 %. Finalmente, se reportaron cuatro casos de violencia económica, que representan el 0.1 %. La distribución permite observar que las agresiones no siempre dejan lesiones visibles. La violencia psicológica representa casi la mitad de las atenciones registradas y puede manifestarse mediante amenazas, humillaciones, control, intimidación u otras conductas que afectan a la víctima. Piura registra un feminicidio y dos tentativas El reporte del Programa Nacional Warmi Ñan también registra hechos de mayor gravedad. Durante el periodo analizado se confirmó un caso de feminicidio en la provincia de Huancabamba . Asimismo, fueron reportadas dos tentativas de feminicidio , ocurridas en las provincias de Piura y Morropón. Estos casos reflejan situaciones de violencia extrema que requieren una intervención rápida de las instituciones responsables de proteger a las víctimas. De acuerdo con el MIMP, el Programa Nacional Warmi Ñan desarrolla servicios de atención, protección y prevención frente a la violencia contra las mujeres y los integrantes del grupo familiar en todo el país. Conoce los servicios oficiales del Programa Nacional Warmi Ñan . Adolescentes y embarazo también forman parte del panorama El informe incorpora además un indicador relacionado con las adolescentes de la región. El 10.6 % de las mujeres de 15 a 19 años en Piura ha tenido un hijo o ha estado embarazada por primera vez . Del total, el 9.9 % ya son madres, mientras que el 0.7 % estuvo embarazada por primera vez. Este indicador forma parte del contexto social que acompaña las cifras de violencia y permite observar la situación de adolescentes y jóvenes en la región. Warmi Ñan cuenta con 20 Centros Emergencia Mujer en Piura Para atender esta problemática, la región cuenta con 20 Centros Emergencia Mujer . De ellos, 10 funcionan en comisarías y brindan atención durante las 24 horas del día. El despliegue también incluye el Servicio de Atención Rural (SAR) , que atendió 117 casos en comunidades de Sechura y Huancabamba. Este servicio busca acercar la atención especializada a poblaciones ubicadas en zonas rurales y con mayores dificultades para acceder a los servicios institucionales. Asimismo, el Hogar de Refugio Temporal recibió a 61 personas en situación de riesgo severo: 32 mujeres y 29 hijos o acompañantes. Estos espacios permiten brindar protección y atención integral a personas que necesitan salir de un entorno considerado peligroso. Línea 100 recibió más de 3 mil consultas en Piura La atención frente a la violencia también se realiza mediante servicios remotos. Entre enero y julio de 2026, la Línea 100 registró 3,375 consultas telefónicas en la región. Del total de consultas, el 36.4 % estuvo relacionado con violencia física, el 32.8 % con violencia psicológica y el 7.3 % con violencia sexual. El servicio permite orientar a las personas afectadas o a quienes conocen un caso de violencia. Por su parte, el Chat 100 atendió 153 consultas relacionadas principalmente con la identificación de situaciones de riesgo en relaciones de pareja o noviazgo. Según el Ministerio de la Mujer y Poblaciones Vulnerables, la Línea 100 brinda orientación y consejería de manera gratuita las 24 horas del día. Revisa la información oficial del MIMP sobre la Línea 100 y los servicios de atención . ¿Dónde buscar ayuda ante un caso de violencia? Las personas que atraviesen una situación de violencia o conozcan un caso pueden acudir a un Centro Emergencia Mujer para recibir orientación especializada. También pueden comunicarse con la Línea 100 para solicitar información y apoyo. Los CEM brindan atención integral y gratuita, incluyendo orientación legal, atención psicológica y acompañamiento social, de acuerdo con las características de cada caso. Consulta los servicios y datos oficiales de Warmi Ñan .</t>
+          <t>La Contraloría General de la República (CGR) evidenció que la obra de ampliación del servicio de aulas de la facultad de Ingeniería Económica de la Universidad Nacional de Frontera, en la provincia de Sullana, presenta signos de deterioro prematuro pese a que los trabajos fueron recibidos en enero de este año. Esta situación genera el riesgo de afectar la calidad, operatividad y vida útil de este proyecto que tiene una inversión superior a los S/ 14 millones. En el Informe de Hito de Control n.° 11384-2026-CG/GRPI-SCC (periodo de evaluación del 12 al 18 de agosto de 2026), se identificaron diversas deficiencias en la infraestructura de los bloques I-A, I-B y II, entre ellas, puertas de madera desniveladas, falta de agua en inodoros y lavatorios, y tapajuntas de acero inoxidable con fijación deficiente en juntas de dilatación. En los servicios higiénicos del cuarto piso se constató que algunos inodoros permanecen inoperativos por falla en el sistema de abastecimiento de agua, mientras que el lavamanos destinado a personas con discapacidad presenta insuficiente presión. Además, se observaron aberturas en los tapajuntas que podrían facilitar el ingreso de humedad, residuos y agentes contaminantes. También se detectaron problemas en ambientes administrativos y académicos: una de las cuatro unidades evaporadoras del sistema de aire acondicionado de la sala de cómputo se encuentra inoperativa y varios lavatorios no cuentan con flujo de agua. En la sala de impresiones se verificó el desprendimiento de una baldosa del techo que dejó un sensor de humo suspendido por sus cables, además de evidencias de humedad y moho. En la actual área de grados y títulos y responsabilidad social se constató la ausencia de una puerta de vidrio, situación que deja expuestos equipos, mobiliario y documentación. A ello se suman el desprendimiento y agrietamiento del sellador de una escalera de madera, deformaciones en elementos de la pérgola en una plazoleta y tapas de concreto de canaletas pluviales deterioradas y desalineadas, generando riesgos para los usuarios. Asimismo, se constató que el ascensor del pabellón permanece fuera de servicio, pese a que la Unidad Ejecutora de Inversiones había requerido al contratista la subsanación de la falla en el marco de la garantía de obra y posteriormente realizó gestiones para evaluar técnicamente el problema. La inoperatividad del equipo obliga a estudiantes, docentes y personal a utilizar exclusivamente las escaleras y constituye una barrera crítica para las personas con movilidad reducida o discapacidad. Durante la inspección se verificó una diferencia entre los equipos adquiridos para el proyecto y los encontrados físicamente en el pabellón de la Facultad de Ingeniería Económica. De los 26 monitores con procesador integrado previstos para el proyecto, solo 12 fueron ubicados, uno en cada una de las aulas. Del mismo modo, se constató que únicamente ocho equipos cuentan con actas de entrega al área usuaria, pese a que la documentación de la entidad acredita la adquisición de los 26 monitores. Esta situación genera el riesgo de que 14 equipos no estén siendo utilizados para el fin para el cual fueron adquiridos, se encuentren en desuso o incluso se haya producido su pérdida. La obra se inició en noviembre de 2023 y debió culminar al siguiente año. Recién en enero de este año se suscribió el acta de recepción. El informe fue notificado al titular de la entidad para que adopte las acciones que correspondan, en el marco de sus competencias y obligaciones en la gestión institucional.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>https://eltiempo.pe/local/mas-de-4-mil-casos-de-violencia-contra-mujeres-y-familiares-genera-preocupacion-en-piura/</t>
+          <t>https://eltiempo.pe/local/contraloria-obra-recien-culminada-presenta-signos-de-deterioro-prematuro-en-universidad-nacional-de-frontera/</t>
         </is>
       </c>
     </row>
@@ -520,24 +520,24 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Sí habrá mango, pero en menor cantidad: La anomalía en las temperaturas no permitieron una adecuada floración de las plantaciones</t>
+          <t>Más de 4 mil casos de violencia contra mujeres y familiares genera preocupación en Piura</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>El invierno cálido que se vivió en Piura dejó secuelas importantes en la agricultura piurana. Las altas temperaturas afectaron el proceso de floración de algunos cultivos como es el caso del mango, lo cual traerá consecuencias en la producción nacional que tiene destino Estados Unidos o Europa. De acuerdo a los especialistas, en la variedad de exportación del mango Kent la floración alcanzó un 30% en promedio entre las más de 33 mil hectáreas del valle de San Lorenzo en Tambogrande. De esta manera se podría tener un disminución de la producción con fines de exportación de más del 60%. Sin embargo, otras variedades como el mango criollo, Ataulfo o Edwards han tenido mejores resultados en la floración. “El año pasado la producción se contrajo un 20%. Ahora la situación se ha agudizado porque las anomalías de 4 y 5 grados en la temperatura impiden la producción de fitohormonas en el nivel adecuado para la floración. No hay una respuesta floral adecuada”, informó la doctora en agrometeorología, Ninell Dediós. De continuar las condiciones térmicas, lo siguiente serían problemas con el cuajado de la fruta que ha logrado generar. Asimismo, una lluvia en plena etapa de cosecha dañaría este proceso final antes de la exportación. Un similar impacto se tiene en cultivos como el limón (floración del 30%), arroz (plantas débiles por acelerado crecimiento ante el calor) y algodón (menor calidad de la fibra). En el campo Desde el lado de los productores aún existe una ligera esperanza de que este panorama pueda mejorar en las siguientes semanas. “Algunos productores dicen que la floración está en 20% y otros en 30%. Todavía no está todo culminado, ni vencido; hay una pequeña ventana de oportunidad. En un año relativamente bueno en el norte se producen 500 mil toneladas de mango, pero ahora que está en 30% [de la floración], nos quedarían unas 120 mil toneladas aproximadamente. Se estima una disminución del 70% de la producción en todas las variedades”, manifestó el expresidente de la Junta de Usuarios del valle de San Lorenzo, Darío Castillo. Seguro Para los agricultores, la expectativa es que se pueda aplicar el seguro agrario catastrófico frente a las pérdidas que sufrirán por efecto del impacto del clima. “El ministro ha sido claro, habló de que existe un seguro agrario catastrófico por cambio climático o un bono, pero es relativamente poco que no soluciona el problema. por una hectárea te dan 800 soles. Por una hectárea de mango se invierte arriba de 10 mil soles”, informó Castillo. Producción para mercado local ayudaría En declaraciones a un medio nacional, Milton Calle, productor de mango en Piura y Casma y propietario de la exportadora Boom Fruit, informó que la baja floración de las plantas de mango no significa necesariamente una caída significativa. “Pienso que vamos a tener una caída de alrededor de 60% en la producción, básicamente por El Niño”, señaló. En ese contexto, el país cerraría la campaña con entre 80.000 y 100.000 toneladas exportables, frente a las 240.000 toneladas registradas en la temporada anterior. Agregó que es posible que parte de la fruta que se destina al mercado local o a la industria de congelados podría irse hacia a la exportación para compensar parcialmente el menor volumen que se obtenga de los campos. De otro lado, Calle también mencionó que Brasil se vería beneficiado con mayores ventas en el mercado europeo por la caída de la producción en Ecuador y Perú.</t>
+          <t>La violencia contra las mujeres y los integrantes del grupo familiar mantiene cifras preocupantes en Piura . Entre enero y julio de 2026, los Centros Emergencia Mujer (CEM) de la región atendieron 4,578 casos de violencia , de acuerdo con el último reporte del Programa Nacional Warmi Ñan del Ministerio de la Mujer y Poblaciones Vulnerables (MIMP). La cifra representa un incremento considerable respecto al reporte acumulado hasta junio, cuando se registraban 3,272 casos. En solo un mes se sumaron 1,306 nuevas atenciones, lo que evidencia la magnitud del problema que enfrentan mujeres, niñas, niños, adolescentes y otros integrantes de las familias en diferentes provincias de la región. Según el Programa Nacional Warmi Ñan , los CEM son servicios públicos especializados y gratuitos que brindan atención psicológica, social y legal a personas afectadas por hechos de violencia. Consulta aquí la información oficial de Warmi Ñan sobre los Centros Emergencia Mujer . Piura concentra la mayor cantidad de casos de violencia La provincia de Piura concentra la mayor cantidad de atenciones reportadas en la región, con 2,580 casos entre enero y julio. La distribución muestra que las situaciones de violencia llegan a diferentes puntos de atención y no se concentran únicamente en una institución. La comisaría de Piura atendió 735 víctimas, mientras que el centro de salud Santa Julia registró 547 casos. A estos se suman 435 atenciones en la comisaría de familia, 236 en la comisaría rural de Tambogrande, 231 en Catacaos, 208 en La Unión y 188 correspondientes al distrito de Piura. Después de la provincia de Piura aparecen Sullana, con 436 casos; Paita, con 420; Ayabaca, con 359; Talara, con 256; Morropón, con 252; Sechura, con 163; y Huancabamba, con 112 casos . ¿Quiénes son los principales afectados por la violencia en Piura? Del total de 4,578 casos atendidos en los primeros siete meses del año, 4,015 corresponden a mujeres , equivalente al 87.7 %. Los hombres representan 563 casos, es decir, el 12.3 % del total. El grupo de edad con mayor número de atenciones corresponde a personas de entre 18 y 59 años, con 3,067 casos , que representan el 67 % del registro regional. También preocupa la cantidad de menores afectados. Entre niñas, niños y adolescentes de 0 a 17 años se contabilizaron 1,294 casos , equivalentes al 28.3 %. En tanto, las personas adultas mayores de 60 años registraron 217 atenciones, que representan el 4.7 %. Estos datos muestran que la violencia no afecta únicamente a las parejas o a mujeres adultas. También alcanza a menores de edad y adultos mayores dentro del entorno familiar, lo que amplía el impacto social de este problema. Violencia psicológica encabeza los casos registrados La violencia psicológica es la modalidad que concentra la mayor cantidad de atenciones en la región Piura. De acuerdo con el reporte, se registraron 2,091 casos, equivalentes al 45.7 % del total. En segundo lugar aparece la violencia física , con 1,833 casos y una participación del 40 %. Le sigue la violencia sexual, que alcanzó 650 casos, equivalente al 14.2 %. Finalmente, se reportaron cuatro casos de violencia económica, que representan el 0.1 %. La distribución permite observar que las agresiones no siempre dejan lesiones visibles. La violencia psicológica representa casi la mitad de las atenciones registradas y puede manifestarse mediante amenazas, humillaciones, control, intimidación u otras conductas que afectan a la víctima. Piura registra un feminicidio y dos tentativas El reporte del Programa Nacional Warmi Ñan también registra hechos de mayor gravedad. Durante el periodo analizado se confirmó un caso de feminicidio en la provincia de Huancabamba . Asimismo, fueron reportadas dos tentativas de feminicidio , ocurridas en las provincias de Piura y Morropón. Estos casos reflejan situaciones de violencia extrema que requieren una intervención rápida de las instituciones responsables de proteger a las víctimas. De acuerdo con el MIMP, el Programa Nacional Warmi Ñan desarrolla servicios de atención, protección y prevención frente a la violencia contra las mujeres y los integrantes del grupo familiar en todo el país. Conoce los servicios oficiales del Programa Nacional Warmi Ñan . Adolescentes y embarazo también forman parte del panorama El informe incorpora además un indicador relacionado con las adolescentes de la región. El 10.6 % de las mujeres de 15 a 19 años en Piura ha tenido un hijo o ha estado embarazada por primera vez . Del total, el 9.9 % ya son madres, mientras que el 0.7 % estuvo embarazada por primera vez. Este indicador forma parte del contexto social que acompaña las cifras de violencia y permite observar la situación de adolescentes y jóvenes en la región. Warmi Ñan cuenta con 20 Centros Emergencia Mujer en Piura Para atender esta problemática, la región cuenta con 20 Centros Emergencia Mujer . De ellos, 10 funcionan en comisarías y brindan atención durante las 24 horas del día. El despliegue también incluye el Servicio de Atención Rural (SAR) , que atendió 117 casos en comunidades de Sechura y Huancabamba. Este servicio busca acercar la atención especializada a poblaciones ubicadas en zonas rurales y con mayores dificultades para acceder a los servicios institucionales. Asimismo, el Hogar de Refugio Temporal recibió a 61 personas en situación de riesgo severo: 32 mujeres y 29 hijos o acompañantes. Estos espacios permiten brindar protección y atención integral a personas que necesitan salir de un entorno considerado peligroso. Línea 100 recibió más de 3 mil consultas en Piura La atención frente a la violencia también se realiza mediante servicios remotos. Entre enero y julio de 2026, la Línea 100 registró 3,375 consultas telefónicas en la región. Del total de consultas, el 36.4 % estuvo relacionado con violencia física, el 32.8 % con violencia psicológica y el 7.3 % con violencia sexual. El servicio permite orientar a las personas afectadas o a quienes conocen un caso de violencia. Por su parte, el Chat 100 atendió 153 consultas relacionadas principalmente con la identificación de situaciones de riesgo en relaciones de pareja o noviazgo. Según el Ministerio de la Mujer y Poblaciones Vulnerables, la Línea 100 brinda orientación y consejería de manera gratuita las 24 horas del día. Revisa la información oficial del MIMP sobre la Línea 100 y los servicios de atención . ¿Dónde buscar ayuda ante un caso de violencia? Las personas que atraviesen una situación de violencia o conozcan un caso pueden acudir a un Centro Emergencia Mujer para recibir orientación especializada. También pueden comunicarse con la Línea 100 para solicitar información y apoyo. Los CEM brindan atención integral y gratuita, incluyendo orientación legal, atención psicológica y acompañamiento social, de acuerdo con las características de cada caso. Consulta los servicios y datos oficiales de Warmi Ñan .</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>https://eltiempo.pe/local/si-habra-mango-pero-en-menor-cantidad-la-anomalia-en-las-temperaturas-no-permitieron-una-adecuada-floracion-de-las-plantaciones/</t>
+          <t>https://eltiempo.pe/local/mas-de-4-mil-casos-de-violencia-contra-mujeres-y-familiares-genera-preocupacion-en-piura/</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Andina</t>
+          <t>El Tiempo</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
@@ -545,10 +545,35 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
+          <t>Sí habrá mango, pero en menor cantidad: La anomalía en las temperaturas no permitieron una adecuada floración de las plantaciones</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>El invierno cálido que se vivió en Piura dejó secuelas importantes en la agricultura piurana. Las altas temperaturas afectaron el proceso de floración de algunos cultivos como es el caso del mango, lo cual traerá consecuencias en la producción nacional que tiene destino Estados Unidos o Europa. De acuerdo a los especialistas, en la variedad de exportación del mango Kent la floración alcanzó un 30% en promedio entre las más de 33 mil hectáreas del valle de San Lorenzo en Tambogrande. De esta manera se podría tener un disminución de la producción con fines de exportación de más del 60%. Sin embargo, otras variedades como el mango criollo, Ataulfo o Edwards han tenido mejores resultados en la floración. “El año pasado la producción se contrajo un 20%. Ahora la situación se ha agudizado porque las anomalías de 4 y 5 grados en la temperatura impiden la producción de fitohormonas en el nivel adecuado para la floración. No hay una respuesta floral adecuada”, informó la doctora en agrometeorología, Ninell Dediós. De continuar las condiciones térmicas, lo siguiente serían problemas con el cuajado de la fruta que ha logrado generar. Asimismo, una lluvia en plena etapa de cosecha dañaría este proceso final antes de la exportación. Un similar impacto se tiene en cultivos como el limón (floración del 30%), arroz (plantas débiles por acelerado crecimiento ante el calor) y algodón (menor calidad de la fibra). En el campo Desde el lado de los productores aún existe una ligera esperanza de que este panorama pueda mejorar en las siguientes semanas. “Algunos productores dicen que la floración está en 20% y otros en 30%. Todavía no está todo culminado, ni vencido; hay una pequeña ventana de oportunidad. En un año relativamente bueno en el norte se producen 500 mil toneladas de mango, pero ahora que está en 30% [de la floración], nos quedarían unas 120 mil toneladas aproximadamente. Se estima una disminución del 70% de la producción en todas las variedades”, manifestó el expresidente de la Junta de Usuarios del valle de San Lorenzo, Darío Castillo. Seguro Para los agricultores, la expectativa es que se pueda aplicar el seguro agrario catastrófico frente a las pérdidas que sufrirán por efecto del impacto del clima. “El ministro ha sido claro, habló de que existe un seguro agrario catastrófico por cambio climático o un bono, pero es relativamente poco que no soluciona el problema. por una hectárea te dan 800 soles. Por una hectárea de mango se invierte arriba de 10 mil soles”, informó Castillo. Producción para mercado local ayudaría En declaraciones a un medio nacional, Milton Calle, productor de mango en Piura y Casma y propietario de la exportadora Boom Fruit, informó que la baja floración de las plantas de mango no significa necesariamente una caída significativa. “Pienso que vamos a tener una caída de alrededor de 60% en la producción, básicamente por El Niño”, señaló. En ese contexto, el país cerraría la campaña con entre 80.000 y 100.000 toneladas exportables, frente a las 240.000 toneladas registradas en la temporada anterior. Agregó que es posible que parte de la fruta que se destina al mercado local o a la industria de congelados podría irse hacia a la exportación para compensar parcialmente el menor volumen que se obtenga de los campos. De otro lado, Calle también mencionó que Brasil se vería beneficiado con mayores ventas en el mercado europeo por la caída de la producción en Ecuador y Perú.</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>https://eltiempo.pe/local/si-habra-mango-pero-en-menor-cantidad-la-anomalia-en-las-temperaturas-no-permitieron-una-adecuada-floracion-de-las-plantaciones/</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Andina</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>46276</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
           <t>Lluvias ligeras a moderadas prevista en la selva ponen en riesgo a 160 distritos</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>Según dicho documento, San Martín es el departamento que presenta la mayor cantidad de distritos en riesgo muy alto, con 16 jurisdicciones, seguido de Amazonas (5), Ayacucho (5), Pasco (3), Cajamarca (2), Junín (2), Puno (2) y Loreto (1).
 En tanto , 124 distritos de estas mismas regiones, además de Cusco, Huánuco y Ucayali se encuentran en riesgo alto.
@@ -561,27 +586,27 @@
 La ANA interviene 2 km de la margen derecha en Malingas para proteger a 30 familias y unas 80 hectáreas de cultivos.?? https://t.co/pHt1feyULt pic.twitter.com/dNAQiiBqHZ — Agencia Andina (@Agencia_Andina) September 10, 2026</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>https://andina.pe/agencia/noticia-lluvias-ligeras-a-moderadas-prevista-la-selva-ponen-riesgo-a-160-distritos-1091335.aspx</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
+    <row r="7">
+      <c r="A7" t="inlineStr">
         <is>
           <t>Andina</t>
         </is>
       </c>
-      <c r="B6" s="2" t="n">
+      <c r="B7" s="2" t="n">
         <v>46276</v>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>Café: más de 46,000 familias cafetaleras se benefician de la Ruta Productiva Exportadora</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>La viceministra de Comercio Exterior, Sayuri Bayona , destacó este resultado durante su participación en el festival “Yo Tomo Café Peruano 2026”, que se desarrolla en el parque Kennedy, en Miraflores.
 Señaló que, a la fecha, 245 beneficiarios de la RPE forman parte de la cadena del café, con un impacto que alcanza a distintas regiones del país.
@@ -600,27 +625,27 @@
 ?? https://t.co/BDNcgRSUVA pic.twitter.com/rCZUAWWd6Z — Agencia Andina (@Agencia_Andina) September 11, 2026</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>https://andina.pe/agencia/noticia-cafe-mas-46000-familias-cafetaleras-se-benefician-de-ruta-productiva-exportadora-1091362.aspx</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
+    <row r="8">
+      <c r="A8" t="inlineStr">
         <is>
           <t>Andina</t>
         </is>
       </c>
-      <c r="B7" s="2" t="n">
+      <c r="B8" s="2" t="n">
         <v>46275</v>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>Piura: Vivienda inspecciona infraestructura estratégica ante posibles impactos de El Niño</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>Como parte de estas acciones, el equipo del OTASS efectuó una jornada de inspección técnica en diversas instalaciones de la EPS Grau, entre ellas la planta de tratamiento de agua potable (PTAP) Curumuy, que representa aproximadamente el 44% del abastecimiento de agua potable de la provincia de Piura.
 También se inspeccionaron la PTAR San Martín y la estación de bombeo de aguas residuales (EBAR) Cortijo, en el distrito de Castilla, donde se verificó la operatividad de tres electrobombas recientemente instaladas, de 250 litros por segundo cada una, financiadas mediante una IOARR de emergencia, y las condiciones de sus demás componentes.
@@ -633,27 +658,27 @@
 ?? https://t.co/Rk9ilfkyym pic.twitter.com/nFvVi2wW2B — Agencia Andina (@Agencia_Andina) September 11, 2026</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>https://andina.pe/agencia/noticia-piura-vivienda-inspecciona-infraestructura-estrategica-ante-posibles-impactos-de-nino-1091321.aspx</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
+    <row r="9">
+      <c r="A9" t="inlineStr">
         <is>
           <t>Andina</t>
         </is>
       </c>
-      <c r="B8" s="2" t="n">
+      <c r="B9" s="2" t="n">
         <v>46275</v>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>El Niño: aprueban patrullaje integrado y respuesta logística con OxI ante emergencias</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>La Resolución Ministerial 1334-2026-IN, que lleva la firma del ministro del Interior, César Astudillo Salcedo, y publicada en la edición extraordinaria del boletín de Normas Legales del Diario Oficial El Peruano , tiene por finalidad acelerar y financiar de manera prioritaria el despliegue logístico y de seguridad ciudadana frente a situaciones críticas en el país como el FEN.
 De esta forma se reducirá la exposición de la población y la infraestructura pública, además de asegurar la continuidad de los servicios públicos esenciales y evitar que los daños que pudieran producirse deriven en perjuicios de difícil o imposible reparación y en mayores costos fiscales de rehabilitación y reconstrucción.
@@ -667,27 +692,27 @@
 ?? https://t.co/ypNmV34u4N pic.twitter.com/kvK3SeA6Qh — Agencia Andina (@Agencia_Andina) September 11, 2026</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>https://andina.pe/agencia/noticia-el-nino-aprueban-patrullaje-integrado-y-respuesta-logistica-oxi-ante-emergencias-1091329.aspx</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
+    <row r="10">
+      <c r="A10" t="inlineStr">
         <is>
           <t>Andina</t>
         </is>
       </c>
-      <c r="B9" s="2" t="n">
+      <c r="B10" s="2" t="n">
         <v>46275</v>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>Conoce las 125 agencias donde el Reniec brindará atención especial este fin de semana</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>La atención del sábado se realizará en agencias de Piura, La Libertad, Lambayeque, Tumbes, Cajamarca, San Martín, Loreto, Áncash, Junín, Ayacucho, Arequipa, Cusco, Lima, Puno, Ica, Ucayali, Huancavelica, Madre de Dios y Amazonas.
 En tanto, el domingo, el Reniec continuará atendiendo en Piura, Lambayeque, Tumbes, Lima y Puno, de 8:15 a.
@@ -710,41 +735,16 @@
 Más en Andina: La Autoridad Nacional de Infraestructura (ANIN) amplió su cartera de intervención integral para el control de riesgos por movimientos de masa e inundaciones en la cuenca del río Rímac con la incorporación de las quebradas Vizcachera, Ñaña y La Laguna ?? https://t.co/T25qFB3xn7 pic.twitter.com/vrqvZ2YCgN — Agencia Andina (@Agencia_Andina) September 10, 2026</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>https://andina.pe/agencia/noticia-conoce-las-125-agencias-donde-reniec-brindara-atencion-especial-este-fin-semana-1091330.aspx</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>El Comercio</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="n">
-        <v>46275</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>¿Masificación de gas en el norte? Gasoducto entre Piura y Chiclayo es posible, señala Gas Energy</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>El norte del Perú tiene la oportunidad de abastecerse de gas natural y lograr una verdadera masificación sin la obligatoriedad de recurrir a Camisea. Esto, a través de la construcción de gasoductos que aprovechen el potencial de los lotes de hidrocarburos piuranos. Y es que la única manera de lograr un proceso de masificación económico y eficiente es “construyendo tubos”, alternativa que elimina la necesidad de transportar el gas en camiones, apunta Luis Fernández, socio director de Gas Energy Perú. En esa línea, la consultora lanzó en la XV Conferencia Gas Natural Perú 2026 una propuesta para crear un corredor energético de gas natural entre Piura y Chimbote utilizando las reservas y recursos de los campos piuranos, hoy desaprovechados. “El norte del Perú tiene suficientes reservas y recursos para crear un polo de desarrollo energético e industrial descentralizado e independiente del gas de Camisea”, manifiesta el especialista. Así, la consultora propone construir un gasoducto de 250 kilómetros de longitud que conecte Piura con la localidad lambayecana de Eten, en una primera etapa, sacando partido de la existencia de dos plantas térmicas en esa jurisdicción, las cuales servirán de ‘ancla’ para el proyecto. Es el caso de las centrales duales Eten (180 MW) y Recka (190 MW) las cuales están en capacidad de producir electricidad tanto con gas como con diésel. Se trata, explica Fernández, de dos infraestructuras que hoy en día no pueden ser abastecidas con gas pues el transporte en camiones cisternas no permite el abastecimiento de grandes volúmenes. De allí la solución de un gasoducto capaz de proveer los 80 millones de pies cúbicos diarios (mmpcd) de gas que necesitarían continuamente. “Si tenemos 80 mmpcd de demanda en Éten ya existiría un ancla para incentivar la producción de los lotes piuranos. Y a ello se agregaría la demanda de GNV en Chiclayo y las azucareras que tienen un alto consumo de energía”, precisa el especialista. Piura produce y consume alrededor de 60 mmpcd de gas natural. La apertura de nuevos mercados en Lambayeque incentivaría la búsqueda y producción de mayores volúmenes, lo cual no representaría un problema pues la región tiene un potencial de 5,5 trillones de pies cúbicos (TFC) de gas, es decir, 91.666 veces su producción diaria hoy. “Conceptualmente, el proyecto es posible porque existe el gas y existen las centrales térmicas que servirían de ancla. Por lo tanto, se puede construir la infraestructura”, manifiesta Fernández. Dicho ducto recorrería Paita, Sechura y Bayóvar hasta llegar a Éten, siguiendo un recorrido paralelo al que Gasnorp opera en Piura. Así, se conectaría la ciudad de Chiclayo, en primer lugar, y luego las de Trujillo, Paramonga y Chimbote, andando el tiempo. Lo único que faltaría para concretar el proyecto es plasmar las condiciones para que sea comercial y regulatoriamente posible, anota Fernández. Y es que la regulación no contempla una tarifa especial para el sector de generación eléctrica en el norte del país, a diferencia de lo que ocurre en las concesiones de Lima (Cálidda) e Ica (Contugas). “Para que el proyecto tenga éxito hace falta armar una nueva regulación que permita que esas centrales entren en base y para ello se necesita políticas adecuadas que partan desde el Minem”, anota Fernández.</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>https://elcomercio.pe/economia/peru/masificacion-de-gas-en-el-norte-gasoducto-entre-piura-y-chiclayo-es-posible-senala-gas-energy-noticia/</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>El Tiempo</t>
+          <t>El Comercio</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
@@ -752,17 +752,17 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Ministro de Defensa promete mayor velocidad en la descolmatación del río Piura</t>
+          <t>¿Masificación de gas en el norte? Gasoducto entre Piura y Chiclayo es posible, señala Gas Energy</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>El ministro de Defensa, Rafael Belaunde , aseguró que el Ejército incrementará la velocidad de los trabajos de descolmatación del río Piura , como parte de las acciones preventivas frente al eventual impacto del fenómeno El Niño en la región. El titular del sector supervisó el despliegue de personal y maquinaria pesada en dos de los puntos considerados críticos. Durante su visita al puente Bolognesi, en Piura, Belaunde verificó las labores destinadas a retirar los sedimentos acumulados en el cauce. Según explicó, existe confianza en que los trabajos avanzarán al ritmo requerido para cumplir con las metas establecidas. “Estoy confiado en que el Ejército avanzará en la velocidad que se le ha requerido”, afirmó el ministro durante la inspección. ¿Dónde se realizan los trabajos en el río Piura? Las labores de limpieza y recuperación del cauce se ejecutan en siete puntos críticos del río Piura , en un tramo de aproximadamente 15.5 kilómetros comprendido entre los puentes Independencia y Bolognesi. Para esta operación se ha desplegado personal especializado del Ejército y maquinaria pesada destinada principalmente a retirar el material acumulado en diferentes sectores del afluente. La intervención busca mejorar las condiciones del cauce ante la posibilidad de lluvias intensas y un incremento del caudal. En el sector del puente Bolognesi trabaja el Batallón de Ingeniería de Construcción N.° 1 “Jazán”, unidad trasladada desde la región Amazonas. Para cumplir con su misión, cuenta con 13 camiones volquetes, dos excavadoras, dos tractores oruga y un cargador frontal . La meta establecida para este punto es intervenir aproximadamente dos kilómetros del cauce del río Piura . El retiro de los sedimentos permitirá recuperar parte de la capacidad hidráulica del río en una zona considerada estratégica para la prevención de inundaciones. Ejército trabaja en el puente Independencia El ministro de Defensa también llegó hasta el puente Independencia para inspeccionar los trabajos que se desarrollan en este sector. Las acciones están a cargo del Batallón de Ingeniería de Combate N.° 211, proveniente de Tumbes. Esta unidad dispone de dos tractores oruga, una excavadora, un cargador frontal y un volquete . De acuerdo con la planificación presentada durante la supervisión, sus trabajos tienen como objetivo intervenir aproximadamente 1.8 kilómetros del cauce. La presencia de maquinaria en ambos sectores forma parte de una operación de ingeniería de mayor escala. Para el Gobierno, la recuperación del cauce constituye una de las medidas preventivas frente a un eventual escenario de lluvias asociadas al fenómeno El Niño. Piura recibirá 600 toneladas de ayuda no alimentaria Durante su visita, el ministro de Defensa también informó sobre las acciones de preparación ante una eventual emergencia por lluvias. Según indicó, alrededor de 200 toneladas de ayuda no alimentaria ya han llegado a Piura como parte de un envío mayor. La ayuda es gestionada mediante el Instituto Nacional de Defensa Civil (Indeci) y forma parte de un total de 600 toneladas que serán trasladadas y almacenadas en un hangar ubicado en territorio piurano. Según declaraciones brindadas a TVPerú, el objetivo es contar con recursos suficientes para atender a unas 100,000 familias , lo que representa cerca de medio millón de personas ante un escenario de emergencia. “La idea es tener capacidad para atender a 100,000 familias. Eso es algo cercano al medio millón de personas”, explicó Belaunde, quien añadió que progresivamente también se incorporará ayuda alimentaria. ¿Por qué es importante la descolmatación del río Piura? La descolmatación consiste en retirar sedimentos, tierra y otros materiales acumulados en el cauce de un río. En el caso del río Piura , estas labores tienen especial importancia durante la temporada de lluvias, debido al riesgo de incremento del caudal y posibles desbordes. La recuperación de la capacidad del cauce forma parte de las medidas de prevención frente a inundaciones. En Piura, una región que históricamente ha enfrentado episodios de lluvias intensas, mantener libres los sectores críticos permite mejorar las condiciones para el desplazamiento del agua. De acuerdo con el Instituto Nacional de Defensa Civil (Indeci) , las acciones de preparación y prevención son fundamentales para reducir los riesgos y mejorar la capacidad de respuesta ante emergencias. Una operación que abarca 15.5 kilómetros La intervención del Ejército contempla un tramo total de 15.5 kilómetros del río Piura , distribuido en siete puntos críticos ubicados entre los puentes Independencia y Bolognesi. La operación requiere el desplazamiento de unidades de ingeniería, operadores y maquinaria especializada. Para las autoridades, el avance de estos trabajos será especialmente importante conforme se acerquen los periodos de mayor riesgo de lluvias. La incorporación de nuevos equipos, anunciada por el Ministerio de Defensa, busca acelerar el retiro de los sedimentos y cumplir con las metas establecidas para cada sector. La información sobre las acciones de prevención y respuesta ante emergencias puede consultarse en los canales oficiales del Ministerio de Defensa y del Indeci .</t>
+          <t>El norte del Perú tiene la oportunidad de abastecerse de gas natural y lograr una verdadera masificación sin la obligatoriedad de recurrir a Camisea. Esto, a través de la construcción de gasoductos que aprovechen el potencial de los lotes de hidrocarburos piuranos. Y es que la única manera de lograr un proceso de masificación económico y eficiente es “construyendo tubos”, alternativa que elimina la necesidad de transportar el gas en camiones, apunta Luis Fernández, socio director de Gas Energy Perú. En esa línea, la consultora lanzó en la XV Conferencia Gas Natural Perú 2026 una propuesta para crear un corredor energético de gas natural entre Piura y Chimbote utilizando las reservas y recursos de los campos piuranos, hoy desaprovechados. “El norte del Perú tiene suficientes reservas y recursos para crear un polo de desarrollo energético e industrial descentralizado e independiente del gas de Camisea”, manifiesta el especialista. Así, la consultora propone construir un gasoducto de 250 kilómetros de longitud que conecte Piura con la localidad lambayecana de Eten, en una primera etapa, sacando partido de la existencia de dos plantas térmicas en esa jurisdicción, las cuales servirán de ‘ancla’ para el proyecto. Es el caso de las centrales duales Eten (180 MW) y Recka (190 MW) las cuales están en capacidad de producir electricidad tanto con gas como con diésel. Se trata, explica Fernández, de dos infraestructuras que hoy en día no pueden ser abastecidas con gas pues el transporte en camiones cisternas no permite el abastecimiento de grandes volúmenes. De allí la solución de un gasoducto capaz de proveer los 80 millones de pies cúbicos diarios (mmpcd) de gas que necesitarían continuamente. “Si tenemos 80 mmpcd de demanda en Éten ya existiría un ancla para incentivar la producción de los lotes piuranos. Y a ello se agregaría la demanda de GNV en Chiclayo y las azucareras que tienen un alto consumo de energía”, precisa el especialista. Piura produce y consume alrededor de 60 mmpcd de gas natural. La apertura de nuevos mercados en Lambayeque incentivaría la búsqueda y producción de mayores volúmenes, lo cual no representaría un problema pues la región tiene un potencial de 5,5 trillones de pies cúbicos (TFC) de gas, es decir, 91.666 veces su producción diaria hoy. “Conceptualmente, el proyecto es posible porque existe el gas y existen las centrales térmicas que servirían de ancla. Por lo tanto, se puede construir la infraestructura”, manifiesta Fernández. Dicho ducto recorrería Paita, Sechura y Bayóvar hasta llegar a Éten, siguiendo un recorrido paralelo al que Gasnorp opera en Piura. Así, se conectaría la ciudad de Chiclayo, en primer lugar, y luego las de Trujillo, Paramonga y Chimbote, andando el tiempo. Lo único que faltaría para concretar el proyecto es plasmar las condiciones para que sea comercial y regulatoriamente posible, anota Fernández. Y es que la regulación no contempla una tarifa especial para el sector de generación eléctrica en el norte del país, a diferencia de lo que ocurre en las concesiones de Lima (Cálidda) e Ica (Contugas). “Para que el proyecto tenga éxito hace falta armar una nueva regulación que permita que esas centrales entren en base y para ello se necesita políticas adecuadas que partan desde el Minem”, anota Fernández.</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>https://eltiempo.pe/local/ministro-de-defensa-promete-mayor-velocidad-en-la-descolmatacion-del-rio-piura/</t>
+          <t>https://elcomercio.pe/economia/peru/masificacion-de-gas-en-el-norte-gasoducto-entre-piura-y-chiclayo-es-posible-senala-gas-energy-noticia/</t>
         </is>
       </c>
     </row>
@@ -777,17 +777,17 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>¿Quién responde por los 106 muertos en la región Piura? Nuevo asesinato se consuma en Castilla</t>
+          <t>Ministro de Defensa promete mayor velocidad en la descolmatación del río Piura</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>La racha criminal sigue en aumento en la región, luego que un joven técnico de celulares fuera asesinado de tres balazos en la cabeza y rostro por un gatillero, que disparó con una pasmosa frialdad, delante de dos amigos, para luego huir en un auto blanco. El asesinato de José Fernando Castillo Quevedo, de 24 años, ocurrió cerca de las nueve de la noche del pasado martes frente al bar “Pikaflor”, ubicado en la Asociación Villa Universitaria, sector norteste de Castilla. Hasta ese lugar llegó la Policía para iniciar las investigaciones. ESCALOFRIANTE DATA Con este episodio escaló a 106 los asesinatos ocurridos en lo que va del año en la región, siendo la mayoría de casos por la modalidad de sicariato (o crimenes por encargo). Cabe resaltar que en 2025 se registraron 107 homicidios en el lapso de enero a setiembre. Cabe precisar que en menos de 72 horas han ocurrido siete homicidios: dos mujeres, un varón y un menor de 13 años en Sullana, otro caso en Talara. De igual manera uno en Paita Alta y el último registrado en Castilla, contra José Fernando Castillo. IMÁGENES CLAVES El asesinato del joven técnico de equipos móviles muestra el alto grado de peligrosidad que existe en las calles. Precisamente una cámara de seguridad muestra que ya no se puede confian en nadie, luego que en escena se observa a José Fernando Castillo platicando con dos personas, que serían amigos. Según las imágenes de las cámaras de seguridad, Castillo Quevedo y dos sujetos, en la vía públlica, observan un celular. De pronto, se aprecia la salida de un individuo desconocido para subir apuradamente a un automóvil blanco y dar arranque. TODOS SE CONOCÍAN En ese momento, se oberva la llegada de un gatillero que vestía polo verde y bermuda blu jeans, quien se acerca a los tres amigos y dispara tres veces contra José Fernando Castillo, luego con pistola en mano camina y sube al mencionado vehículo blanco. Del mismo modo se distingue que uno de los dos individuos, que estaba conversando con la víctima mortal abordó el mismo vehículo en el que huyó el atacante. La Policía continúa con las investigaciones para esclarecer el crimen, identificar a los involucrados y determinar las circunstancias del asesinato.</t>
+          <t>El ministro de Defensa, Rafael Belaunde , aseguró que el Ejército incrementará la velocidad de los trabajos de descolmatación del río Piura , como parte de las acciones preventivas frente al eventual impacto del fenómeno El Niño en la región. El titular del sector supervisó el despliegue de personal y maquinaria pesada en dos de los puntos considerados críticos. Durante su visita al puente Bolognesi, en Piura, Belaunde verificó las labores destinadas a retirar los sedimentos acumulados en el cauce. Según explicó, existe confianza en que los trabajos avanzarán al ritmo requerido para cumplir con las metas establecidas. “Estoy confiado en que el Ejército avanzará en la velocidad que se le ha requerido”, afirmó el ministro durante la inspección. ¿Dónde se realizan los trabajos en el río Piura? Las labores de limpieza y recuperación del cauce se ejecutan en siete puntos críticos del río Piura , en un tramo de aproximadamente 15.5 kilómetros comprendido entre los puentes Independencia y Bolognesi. Para esta operación se ha desplegado personal especializado del Ejército y maquinaria pesada destinada principalmente a retirar el material acumulado en diferentes sectores del afluente. La intervención busca mejorar las condiciones del cauce ante la posibilidad de lluvias intensas y un incremento del caudal. En el sector del puente Bolognesi trabaja el Batallón de Ingeniería de Construcción N.° 1 “Jazán”, unidad trasladada desde la región Amazonas. Para cumplir con su misión, cuenta con 13 camiones volquetes, dos excavadoras, dos tractores oruga y un cargador frontal . La meta establecida para este punto es intervenir aproximadamente dos kilómetros del cauce del río Piura . El retiro de los sedimentos permitirá recuperar parte de la capacidad hidráulica del río en una zona considerada estratégica para la prevención de inundaciones. Ejército trabaja en el puente Independencia El ministro de Defensa también llegó hasta el puente Independencia para inspeccionar los trabajos que se desarrollan en este sector. Las acciones están a cargo del Batallón de Ingeniería de Combate N.° 211, proveniente de Tumbes. Esta unidad dispone de dos tractores oruga, una excavadora, un cargador frontal y un volquete . De acuerdo con la planificación presentada durante la supervisión, sus trabajos tienen como objetivo intervenir aproximadamente 1.8 kilómetros del cauce. La presencia de maquinaria en ambos sectores forma parte de una operación de ingeniería de mayor escala. Para el Gobierno, la recuperación del cauce constituye una de las medidas preventivas frente a un eventual escenario de lluvias asociadas al fenómeno El Niño. Piura recibirá 600 toneladas de ayuda no alimentaria Durante su visita, el ministro de Defensa también informó sobre las acciones de preparación ante una eventual emergencia por lluvias. Según indicó, alrededor de 200 toneladas de ayuda no alimentaria ya han llegado a Piura como parte de un envío mayor. La ayuda es gestionada mediante el Instituto Nacional de Defensa Civil (Indeci) y forma parte de un total de 600 toneladas que serán trasladadas y almacenadas en un hangar ubicado en territorio piurano. Según declaraciones brindadas a TVPerú, el objetivo es contar con recursos suficientes para atender a unas 100,000 familias , lo que representa cerca de medio millón de personas ante un escenario de emergencia. “La idea es tener capacidad para atender a 100,000 familias. Eso es algo cercano al medio millón de personas”, explicó Belaunde, quien añadió que progresivamente también se incorporará ayuda alimentaria. ¿Por qué es importante la descolmatación del río Piura? La descolmatación consiste en retirar sedimentos, tierra y otros materiales acumulados en el cauce de un río. En el caso del río Piura , estas labores tienen especial importancia durante la temporada de lluvias, debido al riesgo de incremento del caudal y posibles desbordes. La recuperación de la capacidad del cauce forma parte de las medidas de prevención frente a inundaciones. En Piura, una región que históricamente ha enfrentado episodios de lluvias intensas, mantener libres los sectores críticos permite mejorar las condiciones para el desplazamiento del agua. De acuerdo con el Instituto Nacional de Defensa Civil (Indeci) , las acciones de preparación y prevención son fundamentales para reducir los riesgos y mejorar la capacidad de respuesta ante emergencias. Una operación que abarca 15.5 kilómetros La intervención del Ejército contempla un tramo total de 15.5 kilómetros del río Piura , distribuido en siete puntos críticos ubicados entre los puentes Independencia y Bolognesi. La operación requiere el desplazamiento de unidades de ingeniería, operadores y maquinaria especializada. Para las autoridades, el avance de estos trabajos será especialmente importante conforme se acerquen los periodos de mayor riesgo de lluvias. La incorporación de nuevos equipos, anunciada por el Ministerio de Defensa, busca acelerar el retiro de los sedimentos y cumplir con las metas establecidas para cada sector. La información sobre las acciones de prevención y respuesta ante emergencias puede consultarse en los canales oficiales del Ministerio de Defensa y del Indeci .</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>https://eltiempo.pe/local/quien-responde-por-los-106-muertos-en-la-region-piura-nuevo-asesinato-se-consuma-en-castilla/</t>
+          <t>https://eltiempo.pe/local/ministro-de-defensa-promete-mayor-velocidad-en-la-descolmatacion-del-rio-piura/</t>
         </is>
       </c>
     </row>
@@ -802,17 +802,17 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Comerciantes del Complejo de Mercados de Piura solicitan administración de parqueos</t>
+          <t>¿Quién responde por los 106 muertos en la región Piura? Nuevo asesinato se consuma en Castilla</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>A través de Resolución de Alcaldía N° 0592-2026, la Municipalidad Provincial de Piura ha dispuesto la conformación de una Comisión técnica multidisciplinaria para que evalué la viabilidad jurídica, técnica, económica, financiera, patrimonial y administrativa sobre la propuesta presentada por la Asociación regional de mercados de Piura (AREMEPI) referente a la administración de los estacionamientos del Complejo de Mercados. La asociación, que representa a los mercados formales, plantea implementar un modelo de gestión conjunta con la comuna piurana orientado a mejorar la administración del servicio, reducir los costos operativos y generar recursos económicos destinados a financiar proyectos estratégicos para el ordenamiento urbano del propio centro de abastos de la ciudad. La gerente de Desarrollo Económico, Ruth Oliva, señaló que hay voluntad política para evaluar el pedido de los comerciantes, por lo que se tendrá que esperar los informes técnicos para la toma de decisiones. REVERSIÓN La funcionaria también dio a conocer que realizaron una inspección en el Mercado San Miguel y constataron una vez más que varios puestos se encuentran cerrados. Indicó que este tipo de acciones que vienen realizando permitirán identificar los puestos que no cumplen con las disposiciones establecidas y, posteriormente, iniciar el proceso de reversión de aquellos espacios que correspondan, con el objetivo de brindar la oportunidad a otros comerciantes que sí tengan la voluntad de trabajar en dicho local comercial.</t>
+          <t>La racha criminal sigue en aumento en la región, luego que un joven técnico de celulares fuera asesinado de tres balazos en la cabeza y rostro por un gatillero, que disparó con una pasmosa frialdad, delante de dos amigos, para luego huir en un auto blanco. El asesinato de José Fernando Castillo Quevedo, de 24 años, ocurrió cerca de las nueve de la noche del pasado martes frente al bar “Pikaflor”, ubicado en la Asociación Villa Universitaria, sector norteste de Castilla. Hasta ese lugar llegó la Policía para iniciar las investigaciones. ESCALOFRIANTE DATA Con este episodio escaló a 106 los asesinatos ocurridos en lo que va del año en la región, siendo la mayoría de casos por la modalidad de sicariato (o crimenes por encargo). Cabe resaltar que en 2025 se registraron 107 homicidios en el lapso de enero a setiembre. Cabe precisar que en menos de 72 horas han ocurrido siete homicidios: dos mujeres, un varón y un menor de 13 años en Sullana, otro caso en Talara. De igual manera uno en Paita Alta y el último registrado en Castilla, contra José Fernando Castillo. IMÁGENES CLAVES El asesinato del joven técnico de equipos móviles muestra el alto grado de peligrosidad que existe en las calles. Precisamente una cámara de seguridad muestra que ya no se puede confian en nadie, luego que en escena se observa a José Fernando Castillo platicando con dos personas, que serían amigos. Según las imágenes de las cámaras de seguridad, Castillo Quevedo y dos sujetos, en la vía públlica, observan un celular. De pronto, se aprecia la salida de un individuo desconocido para subir apuradamente a un automóvil blanco y dar arranque. TODOS SE CONOCÍAN En ese momento, se oberva la llegada de un gatillero que vestía polo verde y bermuda blu jeans, quien se acerca a los tres amigos y dispara tres veces contra José Fernando Castillo, luego con pistola en mano camina y sube al mencionado vehículo blanco. Del mismo modo se distingue que uno de los dos individuos, que estaba conversando con la víctima mortal abordó el mismo vehículo en el que huyó el atacante. La Policía continúa con las investigaciones para esclarecer el crimen, identificar a los involucrados y determinar las circunstancias del asesinato.</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>https://eltiempo.pe/local/comerciantes-del-complejo-de-mercados-de-piura-solicitan-administracion-de-parqueos/</t>
+          <t>https://eltiempo.pe/local/quien-responde-por-los-106-muertos-en-la-region-piura-nuevo-asesinato-se-consuma-en-castilla/</t>
         </is>
       </c>
     </row>
@@ -827,17 +827,17 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Burocracia retrasa obras de emergencia por el Fenómeno El Niño</t>
+          <t>Comerciantes del Complejo de Mercados de Piura solicitan administración de parqueos</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Mientras que entidades oficiales como Enfen y Senamhi advierten de un Fenómeno El Niño de “magnitud fuerte” o “extraordinario”; el empresariado piurano aún sigue a la espera que Proinversión defina los proyectos que se van ejecutar a través de la modalidad de “servicios por impuestos”. Se trata de 18 propuestas que han hecho llegar a Proinversión, según lo informó la gerente general de la Cámara de Comercio y Producción de Piura, Susana Seminario, quien ayer aprovechó la presencia de los ministros de Desarrollo Agrario y Riego, Marco Vinelli; del ministro de Defensa, Rafael Belaúnde Llosa y de otras autoridades que participaron de la reunión de trabajo de la Plataforma de Defensa Civil para pedir celeridad en los trámites y los proyectos se pueden iniciar cuanto antes en aras de mitigar el impacto del FEN. S/ 130 millones La empresaria también dio a conocer que disponen de 130 millones de soles en impuestos para ser ejecutados en los proyectos de emergencia. Chutuque La ampliación del canal de Chutuque es una de las prioridades de los empresarios para evitar una posible inundación. Mientras días atrás el presidente de la Camco, Javier Bereche, señalaba que se trata de “un canal de 6.7 kilómetros de roca y eso hay que volarlo”, ayer el titular del Midagri remarcó que dentro de dos o tres días se iniciarán los trabajos, pero solo limpiarán 5 kilómetros que iniciarán en el distrito de Cristo Nos Valga y terminarán en Sechura. “Es lo que se puede garantizar y cumplir”, subrayó. Bajo Piura Sobre el reclamo del Bajo Piura que demanda más maquinaria para los trabajos de descolmatación, el ministro Vinelli aseguró que en los próximos días llegará más maquinaria aguas abajo del puente Grau. Para 3,900 m3/s Vinelli también dio a conocer que los trabajos de descolmatación tienen un avance del 42% en el tramo entre la represa Los Ejidos y el puente Bolognesi y el objetivo es ampliar la capacidad de la caja hidráulica a 3.900 metros cúbicos por segundo (m3/s); sin embargo, el supervisor de los trabajos indicó un día antes que la proyección es para 3.000 m3/s. Ayuda humanitaria Finalmente se dio a conocer que actualmente se cuenta con 725 toneladas de ayuda humanitaria en el almacén central y 113 toneladas distribuidas en 17 almacenes adelantados, además de 51 motobombas en mantenimiento y la planificación para incorporar otras 70. Solo priorizan 69 establecimientos de salud Durante la reunión realizada en el Gobierno Regional, también se dio a conocer sobre la intervención de establecimientos de salud para mitigar el impacto del FEN. Sin embargo, se informó que de los 438 establecimientos de salud existentes en la región, 269 requieren algún tipo de intervención y se han priorizado 69. Asimismo, se informó sobre la coordinación para implementar un hospital temporal de 104 camas en la Universidad de Piura, además del fortalecimiento de brigadas, equipos de fumigación, ambulancias y acciones de prevención frente al dengue. Sobre las vacunas, el titular del Midagri aseguró que llegará otro lote de 50 mil vacunas contra el dengue.</t>
+          <t>A través de Resolución de Alcaldía N° 0592-2026, la Municipalidad Provincial de Piura ha dispuesto la conformación de una Comisión técnica multidisciplinaria para que evalué la viabilidad jurídica, técnica, económica, financiera, patrimonial y administrativa sobre la propuesta presentada por la Asociación regional de mercados de Piura (AREMEPI) referente a la administración de los estacionamientos del Complejo de Mercados. La asociación, que representa a los mercados formales, plantea implementar un modelo de gestión conjunta con la comuna piurana orientado a mejorar la administración del servicio, reducir los costos operativos y generar recursos económicos destinados a financiar proyectos estratégicos para el ordenamiento urbano del propio centro de abastos de la ciudad. La gerente de Desarrollo Económico, Ruth Oliva, señaló que hay voluntad política para evaluar el pedido de los comerciantes, por lo que se tendrá que esperar los informes técnicos para la toma de decisiones. REVERSIÓN La funcionaria también dio a conocer que realizaron una inspección en el Mercado San Miguel y constataron una vez más que varios puestos se encuentran cerrados. Indicó que este tipo de acciones que vienen realizando permitirán identificar los puestos que no cumplen con las disposiciones establecidas y, posteriormente, iniciar el proceso de reversión de aquellos espacios que correspondan, con el objetivo de brindar la oportunidad a otros comerciantes que sí tengan la voluntad de trabajar en dicho local comercial.</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>https://eltiempo.pe/local/burocracia-retrasa-obras-de-emergencia-por-el-fenomeno-el-nino/</t>
+          <t>https://eltiempo.pe/local/comerciantes-del-complejo-de-mercados-de-piura-solicitan-administracion-de-parqueos/</t>
         </is>
       </c>
     </row>
@@ -848,21 +848,21 @@
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Piura: en menos de 72 horas, delincuentes asesinan a ocho personas en la región</t>
+          <t>Burocracia retrasa obras de emergencia por el Fenómeno El Niño</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>La violencia criminal golpeó nuevamente a la región Piura . En menos de 72 horas, ocho personas fueron asesinadas en distintos hechos registrados en Sullana, Castilla, Paita y Talara. Entre las víctimas se encuentra un menor de 13 años y tres personas que murieron durante un ataque armado ocurrido en el asentamiento humano Manuel Seoane, en Sullana. Los homicidios se registraron entre la noche del domingo 6 y el lunes 7 de setiembre, en una seguidilla de hechos violentos que también dejó personas heridas y motivó operativos policiales en diferentes puntos de la región. Los casos presentan características similares, como el uso de armas de fuego y, en algunos ataques, la participación de sujetos que se movilizaban en motocicletas. Sin embargo, hasta el momento no existe información oficial que permita establecer que todos los crímenes estén relacionados. ¿Quiénes son las ocho víctimas asesinadas en Piura? El balance de los hechos registrados en este periodo incluye a Alexis Arellano Gómez , asesinado en el sector Salaverry de Sullana; Fernando Castillo , víctima de un ataque en Castilla; y Giancarlo Jiménez Hernández , asesinado en Paita Alta. A ellos se suma un adolescente de 13 años , asesinado la noche del domingo en Sullana. También figuran las tres víctimas mortales del ataque ocurrido la noche del lunes en Manuel Seoane: Sheyla Viera Elías, Lady Lore Valdiviezo Nole y Daniel Alfonso Páucar Manchay . El octavo caso corresponde a un hombre conocido como “Van Dan” , quien había trabajado como sereno y fue asesinado en el distrito de La Brea-Negritos, en la provincia de Talara. Sullana: asesinan a menor de 13 años en un mototaxi Uno de los casos que más conmoción provocó ocurrió la noche del domingo en Sullana. Un adolescente de 13 años fue asesinado cuando viajaba como pasajero en un mototaxi por la intersección de la calle Túpac Amaru con la avenida Par Vial, en el asentamiento humano 17 de Enero. El ataque ocurrió aproximadamente a las 10:40 de la noche. Según las primeras diligencias, el vehículo habría quedado detenido debido a un desperfecto mecánico. En ese momento, sujetos que se desplazaban en una motocicleta llegaron hasta el mototaxi y dispararon contra el menor. Uno de los proyectiles impactó en su cabeza y le provocó la muerte en el lugar. Sus acompañantes huyeron de la zona, mientras la víctima quedó junto al vehículo. Un tatuaje permitió identificar al adolescente La identificación del menor se realizó posteriormente en la morgue legal. Una familiar acudió ante las autoridades y logró reconocerlo por un tatuaje que llevaba en el brazo derecho con el nombre “Alexander”. La Policía continúa con las diligencias para establecer las circunstancias exactas del crimen. Entre las hipótesis preliminares figura un posible ajuste de cuentas, aunque esta versión todavía debe ser corroborada por los investigadores. Alexis Arellano Gómez fue asesinado en Sullana Otro de los homicidios registrados durante este periodo ocurrió en el sector Salaverry, en Sullana. La víctima fue identificada como Alexis Arellano Gómez . El asesinato forma parte de los hechos violentos registrados durante estas horas en la provincia. La Policía inició las diligencias correspondientes para recoger evidencias, identificar a los responsables y establecer el móvil del ataque. Fernando Castillo fue asesinado en Castilla La ola de violencia también alcanzó Castilla, en la provincia de Piura. Fernando Castillo fue asesinado en circunstancias que son investigadas por las autoridades. El caso se suma a los demás homicidios registrados en la región durante el mismo periodo. Los agentes buscan reconstruir los momentos previos al crimen y determinar quiénes participaron en el ataque. Paita: asesinan a Giancarlo Jiménez Hernández En Paita Alta, Giancarlo Jiménez Hernández, de 33 años , fue asesinado la noche del lunes durante un ataque perpetrado por sujetos que se movilizaban en una motocicleta. El joven caminaba junto a William Daniel Aldana Prado , de 24 años, por la parte posterior de las empresas de transporte Andrea y Santangel cuando fueron interceptados. Según la información preliminar, el pasajero de la motocicleta sacó un arma de fuego y disparó contra ambos. Los heridos fueron trasladados de emergencia al Hospital Nuestra Señora de las Mercedes. Sin embargo, el médico de turno certificó la muerte de Giancarlo Jiménez debido a una hemorragia intracraneal provocada por un proyectil de arma de fuego. William Aldana quedó gravemente herido y permanecía con pronóstico reservado. Dos sospechosos fueron capturados Tras el ataque, agentes de la Comisaría Ciudad del Pescador iniciaron la búsqueda de los responsables. La motocicleta fue ubicada en inmediaciones del colegio Lunitas de Paita y los policías iniciaron una persecución. El conductor, identificado con las iniciales C. A. T. D., de 20 años, fue intervenido. De acuerdo con la información proporcionada, durante el operativo se le encontró un cartucho de dinamita. El pasajero huyó a pie y, según la versión policial, realizó disparos contra los agentes antes de refugiarse en una vivienda. Finalmente fue detenido e identificado con las iniciales L. J. Ch. N., de 25 años. Los agentes le habrían encontrado un arma de fuego. Talara: exsereno es asesinado dentro de un restaurante Otro de los crímenes ocurrió en la provincia de Talara. Un hombre conocido como “Van Dan” , quien había trabajado como sereno y era propietario de un gimnasio en el distrito de La Brea-Negritos, fue asesinado dentro del restaurante La Caleta 10, ubicado en el asentamiento Mario Aguirre. Según la información preliminar, un sujeto irrumpió en el segundo piso del establecimiento y disparó varias veces contra la víctima. El hombre murió pocos segundos después del ataque. La Policía investiga las circunstancias del homicidio y busca establecer si existieron amenazas previas, conflictos personales u otros elementos que permitan determinar el móvil. Sullana: tres personas mueren en ataque armado en Manuel Seoane La noche del lunes 7 de setiembre, un ataque armado registrado en un puesto de venta de comida ubicado en el pasaje Municipal del asentamiento humano Manuel Seoane, en Sullana, dejó tres personas fallecidas y una herida de gravedad . De acuerdo con la información preliminar, varios sujetos armados llegaron hasta el establecimiento y dispararon contra un grupo de personas que se encontraba reunido alrededor de una mesa. Como consecuencia del atentado perdieron la vida Sheyla Viera Elías, Lady Lore Valdiviezo Nole y Daniel Alfonso Páucar Manchay . Asimismo, Carlos Daniel Cornejo Lupú resultó gravemente herido y fue trasladado a un establecimiento de salud para recibir atención médica. Criminalística recogió evidencias en la escena Tras el ataque, agentes de la División de Investigación Criminal (Divincri) y personal de Criminalística acudieron al lugar para realizar las diligencias correspondientes. Los especialistas recogieron evidencias e indicios balísticos que podrían ayudar a reconstruir el ataque e identificar a los responsables. Las autoridades también iniciaron las investigaciones para determinar el móvil del triple homicidio. Una de las víctimas estaba embarazada Entre las víctimas se encontraba Lady Lore Valdiviezo Nole, de 28 años , quien tenía aproximadamente seis meses de gestación. De acuerdo con la información proporcionada por sus familiares, la joven se dedicaba a la venta de parrilladas y hamburguesas durante fiestas, aniversarios y actividades patronales. Su hermana Greysi relató que ambas venían preparando actividades comerciales relacionadas con el aniversario del distrito de Ignacio Escudero. Según su versión, Loren había salido inicialmente de la vivienda donde ocurrió el ataque, pero decidió regresar. Poco después se escucharon los disparos. La familia pidió a las autoridades esclarecer el crimen y determinar quiénes estuvieron detrás del ataque. ¿Qué investiga la Policía tras los ocho asesinatos? Los ocho homicidios registrados en este periodo ocurrieron en diferentes puntos de Piura. Por ello, las autoridades deberán determinar si existe alguna relación entre los casos o si se trata de hechos independientes. El uso de armas de fuego y la participación de motocicletas en algunos de los ataques son elementos que forman parte de las diligencias. No obstante, establecer una conexión entre los crímenes requiere evidencias que todavía están siendo recopiladas. Piura permanece bajo medidas contra la criminalidad Los nuevos asesinatos se producen mientras diferentes sectores de la región permanecen bajo medidas especiales frente al incremento de la inseguridad. El Gobierno declaró el estado de emergencia en Piura, Castilla, Veintiséis de Octubre y Catacaos mediante el Decreto Supremo N.° 126-2026. Para el exjefe de la Región Policial de Piura, coronel en retiro Máximo Vargas Hugo, este tipo de medidas no ha generado los resultados que reclama la población. El exmando policial consideró necesario fortalecer la labor policial con recursos, logística e inteligencia. “La población quiere seguridad y están repitiendo lo mismo que han hecho gestiones anteriores”, señaló Vargas Hugo al referirse a las declaratorias de emergencia aplicadas en la región. Sobre el cambio en el comando de la Policía, sostuvo que una modificación en el alto mando no garantiza por sí sola mejores resultados y remarcó la necesidad de proporcionar herramientas adecuadas a los agentes para enfrentar a las organizaciones criminales. Por su parte, el general Daniel Jares, jefe de la Región Policial Piura, informó que durante los primeros días de setiembre se habían contabilizado 12 personas asesinadas . Esta cifra corresponde a un periodo más amplio y no debe confundirse con los ocho homicidios registrados en menos de 72 horas detallados en este reporte.</t>
+          <t>Mientras que entidades oficiales como Enfen y Senamhi advierten de un Fenómeno El Niño de “magnitud fuerte” o “extraordinario”; el empresariado piurano aún sigue a la espera que Proinversión defina los proyectos que se van ejecutar a través de la modalidad de “servicios por impuestos”. Se trata de 18 propuestas que han hecho llegar a Proinversión, según lo informó la gerente general de la Cámara de Comercio y Producción de Piura, Susana Seminario, quien ayer aprovechó la presencia de los ministros de Desarrollo Agrario y Riego, Marco Vinelli; del ministro de Defensa, Rafael Belaúnde Llosa y de otras autoridades que participaron de la reunión de trabajo de la Plataforma de Defensa Civil para pedir celeridad en los trámites y los proyectos se pueden iniciar cuanto antes en aras de mitigar el impacto del FEN. S/ 130 millones La empresaria también dio a conocer que disponen de 130 millones de soles en impuestos para ser ejecutados en los proyectos de emergencia. Chutuque La ampliación del canal de Chutuque es una de las prioridades de los empresarios para evitar una posible inundación. Mientras días atrás el presidente de la Camco, Javier Bereche, señalaba que se trata de “un canal de 6.7 kilómetros de roca y eso hay que volarlo”, ayer el titular del Midagri remarcó que dentro de dos o tres días se iniciarán los trabajos, pero solo limpiarán 5 kilómetros que iniciarán en el distrito de Cristo Nos Valga y terminarán en Sechura. “Es lo que se puede garantizar y cumplir”, subrayó. Bajo Piura Sobre el reclamo del Bajo Piura que demanda más maquinaria para los trabajos de descolmatación, el ministro Vinelli aseguró que en los próximos días llegará más maquinaria aguas abajo del puente Grau. Para 3,900 m3/s Vinelli también dio a conocer que los trabajos de descolmatación tienen un avance del 42% en el tramo entre la represa Los Ejidos y el puente Bolognesi y el objetivo es ampliar la capacidad de la caja hidráulica a 3.900 metros cúbicos por segundo (m3/s); sin embargo, el supervisor de los trabajos indicó un día antes que la proyección es para 3.000 m3/s. Ayuda humanitaria Finalmente se dio a conocer que actualmente se cuenta con 725 toneladas de ayuda humanitaria en el almacén central y 113 toneladas distribuidas en 17 almacenes adelantados, además de 51 motobombas en mantenimiento y la planificación para incorporar otras 70. Solo priorizan 69 establecimientos de salud Durante la reunión realizada en el Gobierno Regional, también se dio a conocer sobre la intervención de establecimientos de salud para mitigar el impacto del FEN. Sin embargo, se informó que de los 438 establecimientos de salud existentes en la región, 269 requieren algún tipo de intervención y se han priorizado 69. Asimismo, se informó sobre la coordinación para implementar un hospital temporal de 104 camas en la Universidad de Piura, además del fortalecimiento de brigadas, equipos de fumigación, ambulancias y acciones de prevención frente al dengue. Sobre las vacunas, el titular del Midagri aseguró que llegará otro lote de 50 mil vacunas contra el dengue.</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>https://eltiempo.pe/local/piura-en-menos-de-72-horas-delincuentes-asesinan-a-ocho-personas-en-la-region/</t>
+          <t>https://eltiempo.pe/local/burocracia-retrasa-obras-de-emergencia-por-el-fenomeno-el-nino/</t>
         </is>
       </c>
     </row>
@@ -877,17 +877,17 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>ODPE Piura recibe material para capacitar a actores electorales</t>
+          <t>Piura: en menos de 72 horas, delincuentes asesinan a ocho personas en la región</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>En el marco de las Elecciones Regionales y Municipales (ERM) 2026, la Oficina Descentralizada de Procesos Electorales (ODPE) Piura recibió el material de capacitación que será empleado en la preparación de los diversos actores electorales que participarán en los comicios del próximo 4 de octubre. Puedes Leer | Bajo Piura se levanta y exige obras para evitar inundación El cargamento, remitido desde el almacén central de la Gerencia de Gestión Electoral de la ONPE en Lurín, arribó a la sede de la ODPE Piura bajo protocolos de seguridad y resguardo para su inmediata verificación, almacenamiento y posterior distribución en los distritos y centros poblados bajo su jurisdicción. Entre los instrumentos recibidos se encuentran materiales pedagógicos que replican con exactitud las condiciones de una mesa de sufragio, los cuales serán utilizados en los talleres que se desarrollarán en las oficinas distritales de la circunscripción electoral, así como en las jornadas masivas de capacitación a miembros de mesa programadas para los días 20 y 27 de setiembre. Asimismo, arribó insumos didácticos dirigidos a los talleres de formación de capacitadores electorales, coordinadores distritales, coordinadores de local de votación y personal de campo que desplegará acciones informativas en los distritos. Mira También | Advierten incremento de casos de cáncer infantil en Piura El jefe de la ODPE Piura, Juan Roel Godofredo Valdivia, señaló que la preparación de los actores electorales constituye una etapa fundamental para garantizar el adecuado desarrollo de los comicios y destacó la importancia de que quienes participarán en la jornada conozcan oportunamente las tareas y responsabilidades que deberán cumplir. Para estos comicios, el organismo electoral instalará en los distritos Piura y Veintiséis de Octubre un total de 884 mesas de sufragio en 67 locales de votación, donde están llamados a sufragar aproximadamente 264 809 electores hábiles. Más información https://erm2026.onpe.gob.pe</t>
+          <t>La violencia criminal golpeó nuevamente a la región Piura . En menos de 72 horas, ocho personas fueron asesinadas en distintos hechos registrados en Sullana, Castilla, Paita y Talara. Entre las víctimas se encuentra un menor de 13 años y tres personas que murieron durante un ataque armado ocurrido en el asentamiento humano Manuel Seoane, en Sullana. Los homicidios se registraron entre la noche del domingo 6 y el lunes 7 de setiembre, en una seguidilla de hechos violentos que también dejó personas heridas y motivó operativos policiales en diferentes puntos de la región. Los casos presentan características similares, como el uso de armas de fuego y, en algunos ataques, la participación de sujetos que se movilizaban en motocicletas. Sin embargo, hasta el momento no existe información oficial que permita establecer que todos los crímenes estén relacionados. ¿Quiénes son las ocho víctimas asesinadas en Piura? El balance de los hechos registrados en este periodo incluye a Alexis Arellano Gómez , asesinado en el sector Salaverry de Sullana; Fernando Castillo , víctima de un ataque en Castilla; y Giancarlo Jiménez Hernández , asesinado en Paita Alta. A ellos se suma un adolescente de 13 años , asesinado la noche del domingo en Sullana. También figuran las tres víctimas mortales del ataque ocurrido la noche del lunes en Manuel Seoane: Sheyla Viera Elías, Lady Lore Valdiviezo Nole y Daniel Alfonso Páucar Manchay . El octavo caso corresponde a un hombre conocido como “Van Dan” , quien había trabajado como sereno y fue asesinado en el distrito de La Brea-Negritos, en la provincia de Talara. Sullana: asesinan a menor de 13 años en un mototaxi Uno de los casos que más conmoción provocó ocurrió la noche del domingo en Sullana. Un adolescente de 13 años fue asesinado cuando viajaba como pasajero en un mototaxi por la intersección de la calle Túpac Amaru con la avenida Par Vial, en el asentamiento humano 17 de Enero. El ataque ocurrió aproximadamente a las 10:40 de la noche. Según las primeras diligencias, el vehículo habría quedado detenido debido a un desperfecto mecánico. En ese momento, sujetos que se desplazaban en una motocicleta llegaron hasta el mototaxi y dispararon contra el menor. Uno de los proyectiles impactó en su cabeza y le provocó la muerte en el lugar. Sus acompañantes huyeron de la zona, mientras la víctima quedó junto al vehículo. Un tatuaje permitió identificar al adolescente La identificación del menor se realizó posteriormente en la morgue legal. Una familiar acudió ante las autoridades y logró reconocerlo por un tatuaje que llevaba en el brazo derecho con el nombre “Alexander”. La Policía continúa con las diligencias para establecer las circunstancias exactas del crimen. Entre las hipótesis preliminares figura un posible ajuste de cuentas, aunque esta versión todavía debe ser corroborada por los investigadores. Alexis Arellano Gómez fue asesinado en Sullana Otro de los homicidios registrados durante este periodo ocurrió en el sector Salaverry, en Sullana. La víctima fue identificada como Alexis Arellano Gómez . El asesinato forma parte de los hechos violentos registrados durante estas horas en la provincia. La Policía inició las diligencias correspondientes para recoger evidencias, identificar a los responsables y establecer el móvil del ataque. Fernando Castillo fue asesinado en Castilla La ola de violencia también alcanzó Castilla, en la provincia de Piura. Fernando Castillo fue asesinado en circunstancias que son investigadas por las autoridades. El caso se suma a los demás homicidios registrados en la región durante el mismo periodo. Los agentes buscan reconstruir los momentos previos al crimen y determinar quiénes participaron en el ataque. Paita: asesinan a Giancarlo Jiménez Hernández En Paita Alta, Giancarlo Jiménez Hernández, de 33 años , fue asesinado la noche del lunes durante un ataque perpetrado por sujetos que se movilizaban en una motocicleta. El joven caminaba junto a William Daniel Aldana Prado , de 24 años, por la parte posterior de las empresas de transporte Andrea y Santangel cuando fueron interceptados. Según la información preliminar, el pasajero de la motocicleta sacó un arma de fuego y disparó contra ambos. Los heridos fueron trasladados de emergencia al Hospital Nuestra Señora de las Mercedes. Sin embargo, el médico de turno certificó la muerte de Giancarlo Jiménez debido a una hemorragia intracraneal provocada por un proyectil de arma de fuego. William Aldana quedó gravemente herido y permanecía con pronóstico reservado. Dos sospechosos fueron capturados Tras el ataque, agentes de la Comisaría Ciudad del Pescador iniciaron la búsqueda de los responsables. La motocicleta fue ubicada en inmediaciones del colegio Lunitas de Paita y los policías iniciaron una persecución. El conductor, identificado con las iniciales C. A. T. D., de 20 años, fue intervenido. De acuerdo con la información proporcionada, durante el operativo se le encontró un cartucho de dinamita. El pasajero huyó a pie y, según la versión policial, realizó disparos contra los agentes antes de refugiarse en una vivienda. Finalmente fue detenido e identificado con las iniciales L. J. Ch. N., de 25 años. Los agentes le habrían encontrado un arma de fuego. Talara: exsereno es asesinado dentro de un restaurante Otro de los crímenes ocurrió en la provincia de Talara. Un hombre conocido como “Van Dan” , quien había trabajado como sereno y era propietario de un gimnasio en el distrito de La Brea-Negritos, fue asesinado dentro del restaurante La Caleta 10, ubicado en el asentamiento Mario Aguirre. Según la información preliminar, un sujeto irrumpió en el segundo piso del establecimiento y disparó varias veces contra la víctima. El hombre murió pocos segundos después del ataque. La Policía investiga las circunstancias del homicidio y busca establecer si existieron amenazas previas, conflictos personales u otros elementos que permitan determinar el móvil. Sullana: tres personas mueren en ataque armado en Manuel Seoane La noche del lunes 7 de setiembre, un ataque armado registrado en un puesto de venta de comida ubicado en el pasaje Municipal del asentamiento humano Manuel Seoane, en Sullana, dejó tres personas fallecidas y una herida de gravedad . De acuerdo con la información preliminar, varios sujetos armados llegaron hasta el establecimiento y dispararon contra un grupo de personas que se encontraba reunido alrededor de una mesa. Como consecuencia del atentado perdieron la vida Sheyla Viera Elías, Lady Lore Valdiviezo Nole y Daniel Alfonso Páucar Manchay . Asimismo, Carlos Daniel Cornejo Lupú resultó gravemente herido y fue trasladado a un establecimiento de salud para recibir atención médica. Criminalística recogió evidencias en la escena Tras el ataque, agentes de la División de Investigación Criminal (Divincri) y personal de Criminalística acudieron al lugar para realizar las diligencias correspondientes. Los especialistas recogieron evidencias e indicios balísticos que podrían ayudar a reconstruir el ataque e identificar a los responsables. Las autoridades también iniciaron las investigaciones para determinar el móvil del triple homicidio. Una de las víctimas estaba embarazada Entre las víctimas se encontraba Lady Lore Valdiviezo Nole, de 28 años , quien tenía aproximadamente seis meses de gestación. De acuerdo con la información proporcionada por sus familiares, la joven se dedicaba a la venta de parrilladas y hamburguesas durante fiestas, aniversarios y actividades patronales. Su hermana Greysi relató que ambas venían preparando actividades comerciales relacionadas con el aniversario del distrito de Ignacio Escudero. Según su versión, Loren había salido inicialmente de la vivienda donde ocurrió el ataque, pero decidió regresar. Poco después se escucharon los disparos. La familia pidió a las autoridades esclarecer el crimen y determinar quiénes estuvieron detrás del ataque. ¿Qué investiga la Policía tras los ocho asesinatos? Los ocho homicidios registrados en este periodo ocurrieron en diferentes puntos de Piura. Por ello, las autoridades deberán determinar si existe alguna relación entre los casos o si se trata de hechos independientes. El uso de armas de fuego y la participación de motocicletas en algunos de los ataques son elementos que forman parte de las diligencias. No obstante, establecer una conexión entre los crímenes requiere evidencias que todavía están siendo recopiladas. Piura permanece bajo medidas contra la criminalidad Los nuevos asesinatos se producen mientras diferentes sectores de la región permanecen bajo medidas especiales frente al incremento de la inseguridad. El Gobierno declaró el estado de emergencia en Piura, Castilla, Veintiséis de Octubre y Catacaos mediante el Decreto Supremo N.° 126-2026. Para el exjefe de la Región Policial de Piura, coronel en retiro Máximo Vargas Hugo, este tipo de medidas no ha generado los resultados que reclama la población. El exmando policial consideró necesario fortalecer la labor policial con recursos, logística e inteligencia. “La población quiere seguridad y están repitiendo lo mismo que han hecho gestiones anteriores”, señaló Vargas Hugo al referirse a las declaratorias de emergencia aplicadas en la región. Sobre el cambio en el comando de la Policía, sostuvo que una modificación en el alto mando no garantiza por sí sola mejores resultados y remarcó la necesidad de proporcionar herramientas adecuadas a los agentes para enfrentar a las organizaciones criminales. Por su parte, el general Daniel Jares, jefe de la Región Policial Piura, informó que durante los primeros días de setiembre se habían contabilizado 12 personas asesinadas . Esta cifra corresponde a un periodo más amplio y no debe confundirse con los ocho homicidios registrados en menos de 72 horas detallados en este reporte.</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>https://eltiempo.pe/local/odpe-piura-recibe-material-para-capacitar-a-actores-electorales/</t>
+          <t>https://eltiempo.pe/local/piura-en-menos-de-72-horas-delincuentes-asesinan-a-ocho-personas-en-la-region/</t>
         </is>
       </c>
     </row>
@@ -902,17 +902,17 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Dos gatilleros matan a sujeto y hieren a otro en Paita, pero Policía los captura</t>
+          <t>ODPE Piura recibe material para capacitar a actores electorales</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>A cinco se incrementaron los asesinatos del pasado lunes en la región, luego que gatilleros motorizados asesinaran a tiros a joven en Paita alta y dejarán gravemente herido a su amigo. Esta vez, la Policía Nacional en rápida repuesta capturó a balazos dos sospechosos, incautando una motocicleta y un arma de fuego. Transcurría las 9:50 de la noche del lunes, cuando los amigos Giancarlo Jiménez Hernández, de 33 años, y William Daniel Aldana Prado, de 24 años, caminaban por la parte posterior de las empresas de transporte Andrea y Santangel, fueron interceptados por una motocicleta. Disparó a matar El sujeto que iba como pasajero sacó un arma de fuego y disparó a matar contra los dos amigos. Los ocupantes de la motocicleta al ver caer a sus blancos se dieron a la fuga por las calles de Paita Alta. Los dos amigos gravemenre heridos fueron socorridos y trasladados de emergencia al Hospital Nuestra Señora de las Mercedes.Lamentablemente, el médico de turno, Ricardo Pereira certificó la muerte de Giancarlo Jiménez por hemorragia intercraneal por disparo de arma de fuego. En tanto, dio el diagnóstico oara Willian Aldaba de traumatismo abdominal abierto por proyectil con arma de fuego. Su estado de salud es de pronostico reservado. Persecución y captura Un grupo de agentes de la Comisaría Ciudad del Pescador con las características de la moto y los sujetos a inmediaciones del colegio “Lunitas de Paita” localizó la motocicleta, modelo Triax, de placa de rodaje 1764-GP. Luego de una tenaz persecución capturó al conductor C. A. T. D. (20), el mismo que portaba un cartucho de dinamita. El pasajero de la moto huyó a pie realizando disparos contra la policía, bajo fuego cruzado se refugió en una vivienda donde finalmente fue detenido siendo identificado con las iniciales L. J. Ch. N. (25). Los custodios le hallaron un arma de fuego.</t>
+          <t>En el marco de las Elecciones Regionales y Municipales (ERM) 2026, la Oficina Descentralizada de Procesos Electorales (ODPE) Piura recibió el material de capacitación que será empleado en la preparación de los diversos actores electorales que participarán en los comicios del próximo 4 de octubre. Puedes Leer | Bajo Piura se levanta y exige obras para evitar inundación El cargamento, remitido desde el almacén central de la Gerencia de Gestión Electoral de la ONPE en Lurín, arribó a la sede de la ODPE Piura bajo protocolos de seguridad y resguardo para su inmediata verificación, almacenamiento y posterior distribución en los distritos y centros poblados bajo su jurisdicción. Entre los instrumentos recibidos se encuentran materiales pedagógicos que replican con exactitud las condiciones de una mesa de sufragio, los cuales serán utilizados en los talleres que se desarrollarán en las oficinas distritales de la circunscripción electoral, así como en las jornadas masivas de capacitación a miembros de mesa programadas para los días 20 y 27 de setiembre. Asimismo, arribó insumos didácticos dirigidos a los talleres de formación de capacitadores electorales, coordinadores distritales, coordinadores de local de votación y personal de campo que desplegará acciones informativas en los distritos. Mira También | Advierten incremento de casos de cáncer infantil en Piura El jefe de la ODPE Piura, Juan Roel Godofredo Valdivia, señaló que la preparación de los actores electorales constituye una etapa fundamental para garantizar el adecuado desarrollo de los comicios y destacó la importancia de que quienes participarán en la jornada conozcan oportunamente las tareas y responsabilidades que deberán cumplir. Para estos comicios, el organismo electoral instalará en los distritos Piura y Veintiséis de Octubre un total de 884 mesas de sufragio en 67 locales de votación, donde están llamados a sufragar aproximadamente 264 809 electores hábiles. Más información https://erm2026.onpe.gob.pe</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>https://eltiempo.pe/local/dos-gatilleros-matan-a-sujeto-y-hieren-a-otro-en-paita-pero-policia-los-captura/</t>
+          <t>https://eltiempo.pe/local/odpe-piura-recibe-material-para-capacitar-a-actores-electorales/</t>
         </is>
       </c>
     </row>
@@ -927,17 +927,17 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Advierten incremento de casos de cáncer infantil en Piura</t>
+          <t>Dos gatilleros matan a sujeto y hieren a otro en Paita, pero Policía los captura</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>El cáncer infantil en Piura registra un incremento progresivo en los últimos años, situación que ha generado preocupación entre las autoridades sanitarias de la región. Jean Martín Galecio, médico oncólogo y coordinador de la estrategia del cáncer de la Dirección Regional de Salud (Diresa) Piura, pidió a los padres de familia prestar atención a los signos y síntomas que puedan presentar sus hijos. El especialista señaló que reconocer las señales de alerta y buscar atención médica de manera oportuna puede marcar una diferencia importante en el tratamiento de niños y adolescentes. Según explicó, en muchos casos las primeras manifestaciones pueden confundirse con enfermedades comunes. “En estos últimos años viene incrementándose progresivamente”, señaló Galecio, quien destacó la importancia de identificar la enfermedad a tiempo debido a que un tratamiento oportuno puede permitir la curación de los menores. ¿Cuántos casos de cáncer infantil se reportaron en Piura? De acuerdo con la información proporcionada por el especialista de la Diresa, durante el 2025 se reportaron 200 casos de cáncer infantil en Piura . La cifra forma parte del panorama que preocupa a las autoridades sanitarias y refuerza el llamado a mejorar la detección temprana. La Diresa Piura también viene trabajando en el fortalecimiento del registro de casos de cáncer en la región. En mayo de 2026, la institución informó que inició una asistencia técnica junto con el Instituto Nacional de Enfermedades Neoplásicas (INEN) para mejorar el Registro de Cáncer de Base Poblacional y contar con información más precisa y actualizada. Según la Diresa Piura , este trabajo permitirá fortalecer la vigilancia epidemiológica y la atención de los pacientes. ¿Qué tipos de cáncer afectan con mayor frecuencia a los niños? Entre las enfermedades oncológicas más frecuentes en la población infantil se encuentra la leucemia , además de los tumores cerebrales y los linfomas. También pueden presentarse tumores renales y óseos, entre otros tipos de neoplasias. El Ministerio de Salud (Minsa) señala que la leucemia es el tipo de cáncer más frecuente entre niñas, niños y adolescentes en el Perú. La institución explica que el cáncer infantil comprende un conjunto de enfermedades que pueden presentarse antes de los 19 años y que, a diferencia de muchos tipos de cáncer en adultos, no puede prevenirse mediante acciones específicas, por lo que la detección temprana adquiere especial importancia. Para el Minsa, la identificación oportuna de los síntomas permite que los profesionales de salud realicen una evaluación, determinen si existe sospecha de una enfermedad oncológica y, de ser necesario, deriven al menor a un establecimiento especializado. De acuerdo con información oficial del Minsa , el diagnóstico temprano y el tratamiento adecuado aumentan las posibilidades de curación. Cáncer infantil en Piura: ¿cuáles son los principales signos de alerta? El médico Jean Martín Galecio mencionó varios síntomas que deben llamar la atención de los padres. Entre ellos se encuentran el dolor persistente de huesos y la fiebre que no desaparece , además de la aparición de moretones en la piel sin una causa evidente. También pueden presentarse sangrados espontáneos por la nariz o las encías, así como tumoraciones o aumentos de volumen en distintas partes del cuerpo. Los ganglios aumentados en zonas como el cuello o las axilas y el incremento del volumen del abdomen son otras señales que requieren una evaluación médica. El Minsa incluye entre sus principales señales de alerta la fiebre durante más de siete días, ganglios duros de más de dos centímetros en cuello, axilas o ingle, palidez progresiva, moretones espontáneos, sangrado reciente de nariz o encías y dolor persistente en los huesos. Según el Ministerio de Salud , ante uno o más de estos signos se debe acudir a un establecimiento de salud para una evaluación. Fiebre, moretones y dolor de huesos Una fiebre que permanece durante varios días, especialmente cuando no existe una causa clara, merece atención. Lo mismo ocurre con el dolor de huesos que persiste y llega a limitar las actividades habituales del menor. Los moretones o pequeños puntos rojos que aparecen de manera espontánea también forman parte de las señales que los especialistas recomiendan vigilar. En algunos casos pueden acompañarse de palidez, cansancio o sangrado. Bultos, ganglios y aumento del abdomen Otra señal que no debe pasar desapercibida es la aparición de una masa o aumento de volumen en alguna parte del cuerpo. Esto puede ocurrir en el cuello, las axilas, la ingle o el abdomen. El Minsa recomienda prestar especial atención a los ganglios duros de más de dos centímetros y a cualquier aumento de volumen que aparezca sin signos claros de inflamación. Estos síntomas no significan necesariamente que un niño tenga cáncer, pero sí justifican una evaluación médica. Dolor de cabeza, vómitos y cambios en la visión Los dolores de cabeza persistentes acompañados de vómitos también figuran entre las señales de alerta. De igual manera, una mancha blanca en la pupila o la aparición repentina de estrabismo requieren una valoración médica. La información oficial del Minsa advierte que algunos de estos síntomas pueden parecerse a los de enfermedades frecuentes de la infancia. Por ello, la recomendación no es asumir que se trata de una neoplasia, sino consultar con un profesional de salud cuando las manifestaciones sean persistentes o llamen especialmente la atención. ¿Por qué es importante detectar temprano el cáncer infantil? La detección temprana es uno de los principales factores relacionados con las posibilidades de recuperación de los menores. El Minsa sostiene que el diagnóstico oportuno permite iniciar el tratamiento en una etapa en la que existen mayores posibilidades de respuesta. En el caso de la leucemia infantil, por ejemplo, los síntomas pueden aparecer de manera relativamente rápida. Cansancio, palidez, fiebre, pérdida de peso, moretones o sangrados pueden ser algunas de sus manifestaciones. Para el Minsa , la identificación de estas señales y la consulta médica temprana son fundamentales para iniciar el diagnóstico correspondiente. ¿Qué deben hacer los padres ante una señal de alerta? Ante la presencia persistente de alguno de estos síntomas, los padres o cuidadores deben llevar al menor a un establecimiento de salud para que sea evaluado por profesionales. Un síntoma aislado no significa necesariamente que exista cáncer, pero tampoco debe ser ignorado cuando persiste, empeora o afecta las actividades habituales del niño. El Ministerio de Salud dispone además de la Línea 113 Salud para orientación gratuita. Los usuarios pueden llamar desde cualquier operador y seleccionar la opción 3 para recibir información relacionada con salud. El Minsa también publica una guía oficial sobre los signos y síntomas de alerta del cáncer infantil . En Piura, el llamado de la Diresa apunta precisamente a evitar que las señales sean ignoradas y a que los menores puedan acceder a una evaluación médica cuando aparezcan síntomas que se mantienen en el tiempo.</t>
+          <t>A cinco se incrementaron los asesinatos del pasado lunes en la región, luego que gatilleros motorizados asesinaran a tiros a joven en Paita alta y dejarán gravemente herido a su amigo. Esta vez, la Policía Nacional en rápida repuesta capturó a balazos dos sospechosos, incautando una motocicleta y un arma de fuego. Transcurría las 9:50 de la noche del lunes, cuando los amigos Giancarlo Jiménez Hernández, de 33 años, y William Daniel Aldana Prado, de 24 años, caminaban por la parte posterior de las empresas de transporte Andrea y Santangel, fueron interceptados por una motocicleta. Disparó a matar El sujeto que iba como pasajero sacó un arma de fuego y disparó a matar contra los dos amigos. Los ocupantes de la motocicleta al ver caer a sus blancos se dieron a la fuga por las calles de Paita Alta. Los dos amigos gravemenre heridos fueron socorridos y trasladados de emergencia al Hospital Nuestra Señora de las Mercedes.Lamentablemente, el médico de turno, Ricardo Pereira certificó la muerte de Giancarlo Jiménez por hemorragia intercraneal por disparo de arma de fuego. En tanto, dio el diagnóstico oara Willian Aldaba de traumatismo abdominal abierto por proyectil con arma de fuego. Su estado de salud es de pronostico reservado. Persecución y captura Un grupo de agentes de la Comisaría Ciudad del Pescador con las características de la moto y los sujetos a inmediaciones del colegio “Lunitas de Paita” localizó la motocicleta, modelo Triax, de placa de rodaje 1764-GP. Luego de una tenaz persecución capturó al conductor C. A. T. D. (20), el mismo que portaba un cartucho de dinamita. El pasajero de la moto huyó a pie realizando disparos contra la policía, bajo fuego cruzado se refugió en una vivienda donde finalmente fue detenido siendo identificado con las iniciales L. J. Ch. N. (25). Los custodios le hallaron un arma de fuego.</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>https://eltiempo.pe/local/advierten-incremento-de-casos-de-cancer-infantil-en-piura/</t>
+          <t>https://eltiempo.pe/local/dos-gatilleros-matan-a-sujeto-y-hieren-a-otro-en-paita-pero-policia-los-captura/</t>
         </is>
       </c>
     </row>
@@ -952,17 +952,17 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Advierten que la sensación del calor podría llegar a los 39°C en la región Piura</t>
+          <t>Advierten incremento de casos de cáncer infantil en Piura</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>El Senamhi Piura informó que durante el mes, se registraron temperaturas de hasta 37,2°C en Chulucanas, Piura. No descartan que la sensación de calor pueda alcanzar los 39 °C en Piura. Así lo señaló el especialista del Senamhi Piura, Héctor Yauri quien indicó que este panorama se podría dar por diversos factores, con lo cual la población deberá tomar sus precauciones. El Senamhi informó que durante las últimas semanas las temperaturas se han mantenido por encima de sus valores normales, especialmente las temperaturas máximas. MAGNITUD FUERTE Explican que esta situación estaría “asociada principalmente a la persistencia de anomalías positivas de la temperatura superficial del mar frente a la costa de Piura y en la región Niño 1+2”. “Se espera que las temperaturas del aire continúen registrando valores relativamente elevados durante las próximas semanas, debido a la persistencia de temperaturas superficiales del mar por encima de lo normal en la región Niño 1+2. Estas condiciones son consistentes con la evolución del evento Niño Costero, que actualmente presenta magnitud fuerte, favoreciendo la persistencia de temperaturas superiores a los valores climatológicos para la temporada”, indicó el especialista Fabricio Fabián Herrera. Asimismo, de acuerdo al aviso meteorológico 161 del Senamhi, no se descarta lluvias dispersas en la costa norte y la presencia de lluvias localizadas en la sierra norte.</t>
+          <t>El cáncer infantil en Piura registra un incremento progresivo en los últimos años, situación que ha generado preocupación entre las autoridades sanitarias de la región. Jean Martín Galecio, médico oncólogo y coordinador de la estrategia del cáncer de la Dirección Regional de Salud (Diresa) Piura, pidió a los padres de familia prestar atención a los signos y síntomas que puedan presentar sus hijos. El especialista señaló que reconocer las señales de alerta y buscar atención médica de manera oportuna puede marcar una diferencia importante en el tratamiento de niños y adolescentes. Según explicó, en muchos casos las primeras manifestaciones pueden confundirse con enfermedades comunes. “En estos últimos años viene incrementándose progresivamente”, señaló Galecio, quien destacó la importancia de identificar la enfermedad a tiempo debido a que un tratamiento oportuno puede permitir la curación de los menores. ¿Cuántos casos de cáncer infantil se reportaron en Piura? De acuerdo con la información proporcionada por el especialista de la Diresa, durante el 2025 se reportaron 200 casos de cáncer infantil en Piura . La cifra forma parte del panorama que preocupa a las autoridades sanitarias y refuerza el llamado a mejorar la detección temprana. La Diresa Piura también viene trabajando en el fortalecimiento del registro de casos de cáncer en la región. En mayo de 2026, la institución informó que inició una asistencia técnica junto con el Instituto Nacional de Enfermedades Neoplásicas (INEN) para mejorar el Registro de Cáncer de Base Poblacional y contar con información más precisa y actualizada. Según la Diresa Piura , este trabajo permitirá fortalecer la vigilancia epidemiológica y la atención de los pacientes. ¿Qué tipos de cáncer afectan con mayor frecuencia a los niños? Entre las enfermedades oncológicas más frecuentes en la población infantil se encuentra la leucemia , además de los tumores cerebrales y los linfomas. También pueden presentarse tumores renales y óseos, entre otros tipos de neoplasias. El Ministerio de Salud (Minsa) señala que la leucemia es el tipo de cáncer más frecuente entre niñas, niños y adolescentes en el Perú. La institución explica que el cáncer infantil comprende un conjunto de enfermedades que pueden presentarse antes de los 19 años y que, a diferencia de muchos tipos de cáncer en adultos, no puede prevenirse mediante acciones específicas, por lo que la detección temprana adquiere especial importancia. Para el Minsa, la identificación oportuna de los síntomas permite que los profesionales de salud realicen una evaluación, determinen si existe sospecha de una enfermedad oncológica y, de ser necesario, deriven al menor a un establecimiento especializado. De acuerdo con información oficial del Minsa , el diagnóstico temprano y el tratamiento adecuado aumentan las posibilidades de curación. Cáncer infantil en Piura: ¿cuáles son los principales signos de alerta? El médico Jean Martín Galecio mencionó varios síntomas que deben llamar la atención de los padres. Entre ellos se encuentran el dolor persistente de huesos y la fiebre que no desaparece , además de la aparición de moretones en la piel sin una causa evidente. También pueden presentarse sangrados espontáneos por la nariz o las encías, así como tumoraciones o aumentos de volumen en distintas partes del cuerpo. Los ganglios aumentados en zonas como el cuello o las axilas y el incremento del volumen del abdomen son otras señales que requieren una evaluación médica. El Minsa incluye entre sus principales señales de alerta la fiebre durante más de siete días, ganglios duros de más de dos centímetros en cuello, axilas o ingle, palidez progresiva, moretones espontáneos, sangrado reciente de nariz o encías y dolor persistente en los huesos. Según el Ministerio de Salud , ante uno o más de estos signos se debe acudir a un establecimiento de salud para una evaluación. Fiebre, moretones y dolor de huesos Una fiebre que permanece durante varios días, especialmente cuando no existe una causa clara, merece atención. Lo mismo ocurre con el dolor de huesos que persiste y llega a limitar las actividades habituales del menor. Los moretones o pequeños puntos rojos que aparecen de manera espontánea también forman parte de las señales que los especialistas recomiendan vigilar. En algunos casos pueden acompañarse de palidez, cansancio o sangrado. Bultos, ganglios y aumento del abdomen Otra señal que no debe pasar desapercibida es la aparición de una masa o aumento de volumen en alguna parte del cuerpo. Esto puede ocurrir en el cuello, las axilas, la ingle o el abdomen. El Minsa recomienda prestar especial atención a los ganglios duros de más de dos centímetros y a cualquier aumento de volumen que aparezca sin signos claros de inflamación. Estos síntomas no significan necesariamente que un niño tenga cáncer, pero sí justifican una evaluación médica. Dolor de cabeza, vómitos y cambios en la visión Los dolores de cabeza persistentes acompañados de vómitos también figuran entre las señales de alerta. De igual manera, una mancha blanca en la pupila o la aparición repentina de estrabismo requieren una valoración médica. La información oficial del Minsa advierte que algunos de estos síntomas pueden parecerse a los de enfermedades frecuentes de la infancia. Por ello, la recomendación no es asumir que se trata de una neoplasia, sino consultar con un profesional de salud cuando las manifestaciones sean persistentes o llamen especialmente la atención. ¿Por qué es importante detectar temprano el cáncer infantil? La detección temprana es uno de los principales factores relacionados con las posibilidades de recuperación de los menores. El Minsa sostiene que el diagnóstico oportuno permite iniciar el tratamiento en una etapa en la que existen mayores posibilidades de respuesta. En el caso de la leucemia infantil, por ejemplo, los síntomas pueden aparecer de manera relativamente rápida. Cansancio, palidez, fiebre, pérdida de peso, moretones o sangrados pueden ser algunas de sus manifestaciones. Para el Minsa , la identificación de estas señales y la consulta médica temprana son fundamentales para iniciar el diagnóstico correspondiente. ¿Qué deben hacer los padres ante una señal de alerta? Ante la presencia persistente de alguno de estos síntomas, los padres o cuidadores deben llevar al menor a un establecimiento de salud para que sea evaluado por profesionales. Un síntoma aislado no significa necesariamente que exista cáncer, pero tampoco debe ser ignorado cuando persiste, empeora o afecta las actividades habituales del niño. El Ministerio de Salud dispone además de la Línea 113 Salud para orientación gratuita. Los usuarios pueden llamar desde cualquier operador y seleccionar la opción 3 para recibir información relacionada con salud. El Minsa también publica una guía oficial sobre los signos y síntomas de alerta del cáncer infantil . En Piura, el llamado de la Diresa apunta precisamente a evitar que las señales sean ignoradas y a que los menores puedan acceder a una evaluación médica cuando aparezcan síntomas que se mantienen en el tiempo.</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>https://eltiempo.pe/local/advierten-que-la-sensacion-del-calor-podria-llegar-a-los-39c-en-la-region-piura/</t>
+          <t>https://eltiempo.pe/local/advierten-incremento-de-casos-de-cancer-infantil-en-piura/</t>
         </is>
       </c>
     </row>
@@ -977,17 +977,17 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Bajo Piura se levanta y exige obras para evitar inundación</t>
+          <t>Advierten que la sensación del calor podría llegar a los 39°C en la región Piura</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>La población no quiere ser expectante de como apenas siete maquinarias pesadas trabajan en la descolmatación del río Piura, desde el puente Grau hasta el puente Independencia, sin haberse considerado obras adicionales como el reforzamiento de las defensas ribereñas, los diques de contención, entre otras obras que permitan mitigar el impacto del Fenómeno El Niño (FEN) que se avecina. Por ello ayer, y tras una asamblea, dirigentes de los distritos de Catacaos, Cura Mori y El Tallán acordaron realizar una marcha de protesta el 14 de setiembre a partir de las 8:00 a.m. bajo el lema “Inundación nunca más”. La población está dispuesta a bloquear las vías hasta ser escuchados por las autoridades. «Es una burla» Víctor Chunga, presidente del Frente de reconstrucción de pueblos afectados por el Niño Costero 2017, calificó como una “burla” que en su primera visita a Piura la presidenta Keiko Fujimori anunciara una inversión de 140 millones y un pull de maquinaria para los trabajos de descolmatación y no se está cumpliendo. “Anunció 140 millones, luego 129 millones, pero no está desglosado cuánto le toca a Piura y los trabajos no van ni al 30%. Ahora en la descolmatación (hacia el Bajo Piura) solo están retirando 90 centímetros de sedimento, eso es limpieza no descolmatación”, indicó. Para octubre prometen terminar descolmatación Tras la denuncia del diputado Félix Chang Apuy, sobre la paralización de los trabajos de descolmatación del río Piura, el supervisor de estos trabajos, Ítalo Cuba, señaló que ya solucionaron el tema administrativo de los contratos del personal y se ha retomado los trabajos en el tramo entre la represa Los Ejidos y el puente Bolognesi. Informó que 20 maquinarias pesadas del Gobierno Regional se sumarán a los trabajos, con lo cual esperan culminar los mismos antes de las lluvias pronosticadas para noviembre. “A mediados de octubre se quiere terminar todo esto”, indicó el supervisor quien agregó que buscan recuperar un encausamiento del río con capacidad para 3000 m3/s.</t>
+          <t>El Senamhi Piura informó que durante el mes, se registraron temperaturas de hasta 37,2°C en Chulucanas, Piura. No descartan que la sensación de calor pueda alcanzar los 39 °C en Piura. Así lo señaló el especialista del Senamhi Piura, Héctor Yauri quien indicó que este panorama se podría dar por diversos factores, con lo cual la población deberá tomar sus precauciones. El Senamhi informó que durante las últimas semanas las temperaturas se han mantenido por encima de sus valores normales, especialmente las temperaturas máximas. MAGNITUD FUERTE Explican que esta situación estaría “asociada principalmente a la persistencia de anomalías positivas de la temperatura superficial del mar frente a la costa de Piura y en la región Niño 1+2”. “Se espera que las temperaturas del aire continúen registrando valores relativamente elevados durante las próximas semanas, debido a la persistencia de temperaturas superficiales del mar por encima de lo normal en la región Niño 1+2. Estas condiciones son consistentes con la evolución del evento Niño Costero, que actualmente presenta magnitud fuerte, favoreciendo la persistencia de temperaturas superiores a los valores climatológicos para la temporada”, indicó el especialista Fabricio Fabián Herrera. Asimismo, de acuerdo al aviso meteorológico 161 del Senamhi, no se descarta lluvias dispersas en la costa norte y la presencia de lluvias localizadas en la sierra norte.</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>https://eltiempo.pe/local/bajo-piura-se-levanta-y-exige-obras-para-evitar-inundacion/</t>
+          <t>https://eltiempo.pe/local/advierten-que-la-sensacion-del-calor-podria-llegar-a-los-39c-en-la-region-piura/</t>
         </is>
       </c>
     </row>
@@ -1002,17 +1002,17 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>¿Quiénes estuvieron detrás de asesinatos en Sullana?</t>
+          <t>Bajo Piura se levanta y exige obras para evitar inundación</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>La violencia criminal continúa golpeando a la provincia de Sullana. Con los últimos hechos de sangre, ya son 46 las personas asesinadas por sicarios en lo que va del año, mientras que sólo en los primeros días de septiembre se han registrado cuatro homicidios, situación que mantiene preocupada a la población. Sin embargo, se abre la interrogante sobre el último episodio: ¿quienes estuvieron detrás del execrable baño de sangre? Alcohol, bala y tragedia El último ataque ocurrió en el sector Manuel Seoane, donde dos mujeres fueron asesinadas a balazos y otros dos sujetos quedaron heridos cuando se encontraban en una vivienda departiendo bebidas alcohólicas junto a otras personas. Una de las víctimas mortales fue identificada como Loren Valdiviezo Nole, de 28 años, quien se encontraba en estado de gestación. La joven deja en la orfandad a tres menores de edad. Retorno mortal Sus familiares exigieron a la Policía esclarecer el crimen y determinar quiénes estuvieron detrás del ataque. Aseguraron que Loren no tenía problemas con ninguna persona y que nunca había recibido amenazas. Se dedicaba a la venta de parrilladas y hamburguesas durante fiestas de aniversario y celebraciones patronales. Precisamente, junto a su hermana Greysi se encontraba preparando sus actividades comerciales para el aniversario del distrito de Ignacio Escudero. Según relató Greysi, la noche del crimen Loren ya había salido de la vivienda atacada, pero decidió regresar. Minutos después se escucharon los disparos. Estuvo en el lugar equivocado “Mi hermana estuvo en el lugar equivocado, es lo único que podemos decir, solo queremos que se esclarezca lo ocurrido”, manifestó Greysi Valdiviezo al diario La Hora. La segunda dama asesinada, Sheila Anabelen Viera Elías (30), quien también deja en la orfandad a tres niños, sus familiares, evitaron dar declaraciones y mayores detalles de lo ocurrido. La mañana de ayer su padre esperaba que culminara la necropsia en la morgue legal para retirar el cuerpo y trasladarlo a la calle Cusco, cuadra 8, en Bellavista, donde será velado. La Policía, desde la misma noche del lunes, puso en marcha un operativo que ayer dio resultados con la detención de un gatillero.</t>
+          <t>La población no quiere ser expectante de como apenas siete maquinarias pesadas trabajan en la descolmatación del río Piura, desde el puente Grau hasta el puente Independencia, sin haberse considerado obras adicionales como el reforzamiento de las defensas ribereñas, los diques de contención, entre otras obras que permitan mitigar el impacto del Fenómeno El Niño (FEN) que se avecina. Por ello ayer, y tras una asamblea, dirigentes de los distritos de Catacaos, Cura Mori y El Tallán acordaron realizar una marcha de protesta el 14 de setiembre a partir de las 8:00 a.m. bajo el lema “Inundación nunca más”. La población está dispuesta a bloquear las vías hasta ser escuchados por las autoridades. «Es una burla» Víctor Chunga, presidente del Frente de reconstrucción de pueblos afectados por el Niño Costero 2017, calificó como una “burla” que en su primera visita a Piura la presidenta Keiko Fujimori anunciara una inversión de 140 millones y un pull de maquinaria para los trabajos de descolmatación y no se está cumpliendo. “Anunció 140 millones, luego 129 millones, pero no está desglosado cuánto le toca a Piura y los trabajos no van ni al 30%. Ahora en la descolmatación (hacia el Bajo Piura) solo están retirando 90 centímetros de sedimento, eso es limpieza no descolmatación”, indicó. Para octubre prometen terminar descolmatación Tras la denuncia del diputado Félix Chang Apuy, sobre la paralización de los trabajos de descolmatación del río Piura, el supervisor de estos trabajos, Ítalo Cuba, señaló que ya solucionaron el tema administrativo de los contratos del personal y se ha retomado los trabajos en el tramo entre la represa Los Ejidos y el puente Bolognesi. Informó que 20 maquinarias pesadas del Gobierno Regional se sumarán a los trabajos, con lo cual esperan culminar los mismos antes de las lluvias pronosticadas para noviembre. “A mediados de octubre se quiere terminar todo esto”, indicó el supervisor quien agregó que buscan recuperar un encausamiento del río con capacidad para 3000 m3/s.</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>https://eltiempo.pe/local/quienes-estuvieron-detras-de-asesinatos-en-sullana/</t>
+          <t>https://eltiempo.pe/local/bajo-piura-se-levanta-y-exige-obras-para-evitar-inundacion/</t>
         </is>
       </c>
     </row>
@@ -1027,17 +1027,17 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>UPAO Piura lleva el cine universitario a una nueva edición del Festival Ojo Errante</t>
+          <t>¿Quiénes estuvieron detrás de asesinatos en Sullana?</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>La tercera edición del certamen convoca a jóvenes realizadores de todo el país, quienes presentarán sus cortometrajes de ficción, documental y animación hasta el 9 de octubre. El talento audiovisual universitario tiene un nuevo espacio de encuentro en Piura. El Programa de Estudio de Comunicación y Medios Digitales de la Universidad Privada Antenor Orrego (UPAO) filial Piura desarrollará la tercera edición del Festival de Cortometrajes Universitarios Ojo Errante, una iniciativa que promueve la producción audiovisual de jóvenes universitarios y su difusión desde las regiones. El certamen se desarrollará de manera presencial y tendrá ingreso gratuito. La convocatoria está dirigida a los estudiantes universitarios de comunicación y facultades afines de todo el país, quienes podrán postular cortometrajes realizados en el ámbito académico, entre agosto del 2024 y octubre del 2026. Ficción, documental y animación Los participantes podrán competir en tres categorías oficiales. En ficción, se recibirán obras basadas en personajes, situaciones y conflictos narrativos imaginarios, con una duración de 5 a 20 minutos. En documental, podrán participar obras de no ficción construidas a partir de hechos, realidades o espacios interpretados por el realizador, con una duración de 5 a 20 minutos. Por su parte, la categoría animación comprende creaciones realizadas mediante técnicas tradicionales, digitales o mixtas, con una duración de 30 segundos a 20 minutos. Inscripciones hasta el 9 de octubre Para la filial Piura, la convocatoria estará abierta hasta el 9 de octubre del 2026, hasta las 11:59 p. m. La exhibición oficial de los trabajos se realizará el 29 de octubre del presente. La inscripción es gratuita y se realizará exclusivamente de manera virtual. Los participantes deberán presentar el cortometraje en formato MP4 H.264 Full HD o 4K, además del póster, teaser y la evidencia del curso universitario y docente responsable. Un espacio para reconocer el talento emergente Los trabajos serán evaluados por un comité especializado, que considerará criterios como la originalidad, la coherencia narrativa y la resolución técnica. El festival otorgará un reconocimiento al mejor cortometraje y menciones honrosas al segundo mejor trabajo de cada categoría. Además, los equipos seleccionados recibirán constancias de participación. Acerca del Festival Ojo Errante El Festival de Cortometrajes Universitarios Ojo Errante es una plataforma cultural y académica impulsada por el Programa de Estudio de Comunicación y Medios Digitales de la UPAO. De este modo se promueve la visibilidad, circulación y experimentación de la producción audiovisual realizada por jóvenes universitarios. A través de proyecciones presenciales, circuitos itinerantes y espacios formativos en Piura, el festival fomenta el desarrollo de la industria cinematográfica emergente desde las regiones. Para más detalles o información, los interesados pueden comunicarse través del siguiente correo: [email protected]</t>
+          <t>La violencia criminal continúa golpeando a la provincia de Sullana. Con los últimos hechos de sangre, ya son 46 las personas asesinadas por sicarios en lo que va del año, mientras que sólo en los primeros días de septiembre se han registrado cuatro homicidios, situación que mantiene preocupada a la población. Sin embargo, se abre la interrogante sobre el último episodio: ¿quienes estuvieron detrás del execrable baño de sangre? Alcohol, bala y tragedia El último ataque ocurrió en el sector Manuel Seoane, donde dos mujeres fueron asesinadas a balazos y otros dos sujetos quedaron heridos cuando se encontraban en una vivienda departiendo bebidas alcohólicas junto a otras personas. Una de las víctimas mortales fue identificada como Loren Valdiviezo Nole, de 28 años, quien se encontraba en estado de gestación. La joven deja en la orfandad a tres menores de edad. Retorno mortal Sus familiares exigieron a la Policía esclarecer el crimen y determinar quiénes estuvieron detrás del ataque. Aseguraron que Loren no tenía problemas con ninguna persona y que nunca había recibido amenazas. Se dedicaba a la venta de parrilladas y hamburguesas durante fiestas de aniversario y celebraciones patronales. Precisamente, junto a su hermana Greysi se encontraba preparando sus actividades comerciales para el aniversario del distrito de Ignacio Escudero. Según relató Greysi, la noche del crimen Loren ya había salido de la vivienda atacada, pero decidió regresar. Minutos después se escucharon los disparos. Estuvo en el lugar equivocado “Mi hermana estuvo en el lugar equivocado, es lo único que podemos decir, solo queremos que se esclarezca lo ocurrido”, manifestó Greysi Valdiviezo al diario La Hora. La segunda dama asesinada, Sheila Anabelen Viera Elías (30), quien también deja en la orfandad a tres niños, sus familiares, evitaron dar declaraciones y mayores detalles de lo ocurrido. La mañana de ayer su padre esperaba que culminara la necropsia en la morgue legal para retirar el cuerpo y trasladarlo a la calle Cusco, cuadra 8, en Bellavista, donde será velado. La Policía, desde la misma noche del lunes, puso en marcha un operativo que ayer dio resultados con la detención de un gatillero.</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>https://eltiempo.pe/local/upao-piura-lleva-el-cine-universitario-a-una-nueva-edicion-del-festival-ojo-errante/</t>
+          <t>https://eltiempo.pe/local/quienes-estuvieron-detras-de-asesinatos-en-sullana/</t>
         </is>
       </c>
     </row>
@@ -1048,21 +1048,21 @@
         </is>
       </c>
       <c r="B23" s="2" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>El Niño superaría al de 1998 y traería impactos “insospechados” en la región Piura</t>
+          <t>UPAO Piura lleva el cine universitario a una nueva edición del Festival Ojo Errante</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>El fenómeno “El Niño” (FEN) sigue acumulando energía en el mar frente a las costas de la región y los impactos de este calentamiento son hasta el momento insospechados, según informó el especialista en meteorología del Senamhi Piura, Héctor Yauli. PUEDES LEER ► Es hora de rescatar la cultura de Piura De lo que sí se tiene mayor certeza es que los indicadores de este fenómeno en desarrollo ya superaron los valores previos al Mega Niño que castigó la región entre los años 1997 y 1998. “Lo que ha dicho el Organismo Mundial de Meteorología es que los impactos que pueda generar este Niño en el contexto en el cual se presenta, porque el nivel de calentamiento es muy exacerbado y no se tiene comparación con los años 1997 y 1998. Es una gran cantidad de energía y calor no solamente en la zona tropical donde se desarrolla El Niño sino en todos los océanos el nivel de calentamiento es muy mayor. Se esperan impactos insospechados por la alta incertidumbre que hay. [...] Lo que sí tenemos mucha seguridad es en cuanto a que se van a presentar lluvias bastante fuertes e intensas en los meses de verano”, manifestó. Sobre la magnitud, Yauri indicó que existe una incertidumbre sobre los niveles que se alcanzarán las precipitaciones. Cabe indicar que durante el Mega Niño de 1998, se registró la máxima precipitación el 24 de enero con un valor de 173.6 milímetros de acumulado en una sola lluvia. Esto implica que ese día cayeron más de 173 litros de agua sobre un metro cuadrado. Peores En este punto, Yauli informó que el escenario es mucho más complicado porque no solo es un calentamiento del mar frente a la costa norte, sino en diferentes partes del mundo. “Es un nivel de calentamiento exacerbado que no tiene comparación. Si nos situamos en septiembre de 1997, solamente veíamos el calentamiento de El Niño, pero el océano Pacífico en el norte estaba en condiciones normales, en Chile estaba normal y en el Atlántico igual. Sin embargo, ahora está caliente el norte y sur del Pacífico, e incluso en el Atlántico también está caliente y eso trae otras implicancias y diferente tipo de impactos vinculados a que habrá mucha lluvia en la zona norte del Perú y bastante deficiencia de lluvias en la zona noroeste de Brasil”, destacó Yauli.</t>
+          <t>La tercera edición del certamen convoca a jóvenes realizadores de todo el país, quienes presentarán sus cortometrajes de ficción, documental y animación hasta el 9 de octubre. El talento audiovisual universitario tiene un nuevo espacio de encuentro en Piura. El Programa de Estudio de Comunicación y Medios Digitales de la Universidad Privada Antenor Orrego (UPAO) filial Piura desarrollará la tercera edición del Festival de Cortometrajes Universitarios Ojo Errante, una iniciativa que promueve la producción audiovisual de jóvenes universitarios y su difusión desde las regiones. El certamen se desarrollará de manera presencial y tendrá ingreso gratuito. La convocatoria está dirigida a los estudiantes universitarios de comunicación y facultades afines de todo el país, quienes podrán postular cortometrajes realizados en el ámbito académico, entre agosto del 2024 y octubre del 2026. Ficción, documental y animación Los participantes podrán competir en tres categorías oficiales. En ficción, se recibirán obras basadas en personajes, situaciones y conflictos narrativos imaginarios, con una duración de 5 a 20 minutos. En documental, podrán participar obras de no ficción construidas a partir de hechos, realidades o espacios interpretados por el realizador, con una duración de 5 a 20 minutos. Por su parte, la categoría animación comprende creaciones realizadas mediante técnicas tradicionales, digitales o mixtas, con una duración de 30 segundos a 20 minutos. Inscripciones hasta el 9 de octubre Para la filial Piura, la convocatoria estará abierta hasta el 9 de octubre del 2026, hasta las 11:59 p. m. La exhibición oficial de los trabajos se realizará el 29 de octubre del presente. La inscripción es gratuita y se realizará exclusivamente de manera virtual. Los participantes deberán presentar el cortometraje en formato MP4 H.264 Full HD o 4K, además del póster, teaser y la evidencia del curso universitario y docente responsable. Un espacio para reconocer el talento emergente Los trabajos serán evaluados por un comité especializado, que considerará criterios como la originalidad, la coherencia narrativa y la resolución técnica. El festival otorgará un reconocimiento al mejor cortometraje y menciones honrosas al segundo mejor trabajo de cada categoría. Además, los equipos seleccionados recibirán constancias de participación. Acerca del Festival Ojo Errante El Festival de Cortometrajes Universitarios Ojo Errante es una plataforma cultural y académica impulsada por el Programa de Estudio de Comunicación y Medios Digitales de la UPAO. De este modo se promueve la visibilidad, circulación y experimentación de la producción audiovisual realizada por jóvenes universitarios. A través de proyecciones presenciales, circuitos itinerantes y espacios formativos en Piura, el festival fomenta el desarrollo de la industria cinematográfica emergente desde las regiones. Para más detalles o información, los interesados pueden comunicarse través del siguiente correo: [email protected]</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>https://eltiempo.pe/local/el-nino-traera-unos-impactos-insospechados-en-la-region-piura/</t>
+          <t>https://eltiempo.pe/local/upao-piura-lleva-el-cine-universitario-a-una-nueva-edicion-del-festival-ojo-errante/</t>
         </is>
       </c>
     </row>
@@ -1077,17 +1077,17 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Los SARE siguen sin mantenimiento para funcionar durante las lluvias</t>
+          <t>El Niño superaría al de 1998 y traería impactos “insospechados” en la región Piura</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Diferentes informes de las oficinas de control institucional del Programa Nacional de Saneamiento Urbano (PNSU) dan cuenta del estado de abandono en su mantenimiento de los Sistemas Alternativos de Recolección y Evacuación de aguas de lluvia (SARE) que se habilitaron en Piura y que costaron millones de soles. Un ejemplo es lo que ocurre en el SARE Cinco Esquinas que costó más de 28 millones de soles, pero ni siquiera tiene un cerco perimétrico para proteger los costosos equipos instalados a pesar de los años pasados. “El grupo electrógeno y la electrobomba constituyen equipos necesarios para el funcionamiento del sistema de bombeo y la evacuación, por lo que su exposición en un área sin control físico permanente de acceso podría afectar su seguridad, conservación y disponibilidad cuando sean requeridos para la operación del SARE”, se lee en el informe de control. De otro lado, el SARE de Ignacio Merino, valorizado en 15 millones de soles, también tiene problemas de falta de mantenimiento. “La falta de culminación de la transferencia legal integral y la ausencia de un marco procedimental que regule las obligaciones de custodia operativa provisoria han provocado que un sistema pluvial de gran inversión (S/ 17.1 millones) no registre ningún tipo de mantenimiento preventivo sobre sus componentes críticos. Esto neutraliza la capacidad de respuesta instalada para salvaguardar a las urbanizaciones del distrito de Piura”, se indica en el documento de Contraloría. Entre las principales observaciones se tiene la acumulación de sedimentos en canaletas cunetas de las vías.</t>
+          <t>El fenómeno “El Niño” (FEN) sigue acumulando energía en el mar frente a las costas de la región y los impactos de este calentamiento son hasta el momento insospechados, según informó el especialista en meteorología del Senamhi Piura, Héctor Yauli. PUEDES LEER ► Es hora de rescatar la cultura de Piura De lo que sí se tiene mayor certeza es que los indicadores de este fenómeno en desarrollo ya superaron los valores previos al Mega Niño que castigó la región entre los años 1997 y 1998. “Lo que ha dicho el Organismo Mundial de Meteorología es que los impactos que pueda generar este Niño en el contexto en el cual se presenta, porque el nivel de calentamiento es muy exacerbado y no se tiene comparación con los años 1997 y 1998. Es una gran cantidad de energía y calor no solamente en la zona tropical donde se desarrolla El Niño sino en todos los océanos el nivel de calentamiento es muy mayor. Se esperan impactos insospechados por la alta incertidumbre que hay. [...] Lo que sí tenemos mucha seguridad es en cuanto a que se van a presentar lluvias bastante fuertes e intensas en los meses de verano”, manifestó. Sobre la magnitud, Yauri indicó que existe una incertidumbre sobre los niveles que se alcanzarán las precipitaciones. Cabe indicar que durante el Mega Niño de 1998, se registró la máxima precipitación el 24 de enero con un valor de 173.6 milímetros de acumulado en una sola lluvia. Esto implica que ese día cayeron más de 173 litros de agua sobre un metro cuadrado. Peores En este punto, Yauli informó que el escenario es mucho más complicado porque no solo es un calentamiento del mar frente a la costa norte, sino en diferentes partes del mundo. “Es un nivel de calentamiento exacerbado que no tiene comparación. Si nos situamos en septiembre de 1997, solamente veíamos el calentamiento de El Niño, pero el océano Pacífico en el norte estaba en condiciones normales, en Chile estaba normal y en el Atlántico igual. Sin embargo, ahora está caliente el norte y sur del Pacífico, e incluso en el Atlántico también está caliente y eso trae otras implicancias y diferente tipo de impactos vinculados a que habrá mucha lluvia en la zona norte del Perú y bastante deficiencia de lluvias en la zona noroeste de Brasil”, destacó Yauli.</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>https://eltiempo.pe/local/los-sare-siguen-sin-mantenimiento-para-funcionar-durante-las-lluvias/</t>
+          <t>https://eltiempo.pe/local/el-nino-traera-unos-impactos-insospechados-en-la-region-piura/</t>
         </is>
       </c>
     </row>
@@ -1102,17 +1102,17 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Refuerzan la vigilancia de flamencos en humedales de Sechura</t>
+          <t>Los SARE siguen sin mantenimiento para funcionar durante las lluvias</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Unos 4.800 flamencos chilenos ( Phoenicopterus chilensis ) habrían completado este año su etapa de reproducción y desplazamiento en el Estuario de Virrilá y la laguna La Niña , dos importantes humedales ubicados en la provincia de Sechura , en Piura. El registro fue recogido por el Servicio Nacional Forestal y de Fauna Silvestre (Serfor) , organismo adscrito al Ministerio de Desarrollo Agrario y Riego (Midagri), durante las labores de monitoreo de esta especie migratoria. Debido a la importancia de estos ecosistemas para la reproducción de los flamencos, especialistas del Serfor recorrieron los puntos de anidamiento identificados en los humedales de Sechura . Las acciones forman parte de las labores de vigilancia y seguimiento de la fauna silvestre en Piura. ¿Por qué se refuerza la vigilancia en Sechura? El seguimiento de los flamencos representa un desafío debido a la extensión del territorio y a las características de los humedales. A ello se suma que estas aves no necesariamente utilizan los mismos lugares para construir sus nidos cada año. Por esa razón, los especialistas deben realizar recorridos periódicos para localizar las zonas donde las aves se concentran durante su periodo reproductivo y verificar que no existan situaciones que puedan afectar a los ejemplares. El especialista en fauna silvestre del Serfor, Max Guerra, señaló que es necesario fortalecer las acciones de patrullaje y monitoreo en los espacios de anidamiento, tomando en cuenta tanto las condiciones del territorio como las amenazas que pueden afectar a estas aves. En las intervenciones realizadas en la provincia participaron representantes del Serfor sede Piura , la Fiscalía Especializada en Materia Ambiental de Piura y la Unidad Desconcentrada de Protección de Medio Ambiente de la Policía Nacional del Perú. El trabajo conjunto resulta especialmente importante en una zona donde ya se han registrado casos de afectación a estas aves. En julio de 2025, el Serfor constató la caza ilegal de crías de flamencos chilenos en la laguna del sector La Huaquilla, en Sechura, luego de recibir una alerta. Los especialistas encontraron patas y plumas de polluelos en el lugar. El ciclo reproductivo de los flamencos en Sechura La reproducción de los flamencos chilenos sigue un proceso que se desarrolla durante varios meses. En los humedales de Sechura , la temporada comienza aproximadamente a mediados de abril, cuando las aves empiezan a construir sus nidos. Entre mayo y junio ocurre la postura de los huevos, mientras que durante julio aparecen los primeros polluelos. A partir de la primera semana de agosto, las crías comienzan a desplazarse, una etapa que requiere especial atención por parte de quienes realizan el monitoreo. “Es un lugar alejado, hay mucho territorio que recorrer y se necesita prestar atención cuando están los polluelos; los puntos de anidamiento cambian todos los años”, explicó el guardaparque local Pablo Martínez, quien también destacó la coordinación con el Serfor para realizar los recorridos. ¿Dónde se reproducen los flamencos? El Estuario de Virrilá y la laguna La Niña forman parte de los espacios utilizados por estas aves en la costa norte del Perú. El Serfor ya ha documentado en años anteriores procesos reproductivos y trabajos de seguimiento en ambos lugares. En 2022, por ejemplo, la entidad informó sobre el nacimiento de alrededor de 700 pichones de flamenco chileno en el Estuario de Virrilá. El lugar fue reconocido además como Sitio Ramsar en 2021, debido a su importancia como humedal de relevancia internacional. Un año después, en agosto de 2023, el Serfor realizó el anillamiento de 183 polluelos nacidos en la laguna La Niña. Esta práctica permite identificar a los ejemplares y obtener información sobre sus desplazamientos y los lugares que utilizan durante su vida. El flamenco chileno es una especie migratoria El flamenco chileno utiliza diferentes cuerpos de agua a lo largo de su distribución. Según el Serfor, puede encontrarse en lagunas poco profundas de agua dulce y salada, desde la costa hasta zonas ubicadas a unos 4.800 metros de altitud. Su distribución comprende territorios desde Chile hasta Ecuador , por lo que los ejemplares que nacen en los humedales de Sechura pueden desplazarse posteriormente hacia otras zonas del país o incluso hacia territorios de países vecinos. El anillamiento se ha convertido en una herramienta para conocer mejor estos movimientos. Los registros realizados por especialistas y observadores de aves permiten identificar ejemplares en diferentes puntos y reconstruir parte de sus rutas de desplazamiento. De acuerdo con el Serfor, la especie está clasificada como “Casi Amenazada” . Entre las principales amenazas identificadas figuran la caza ilegal y la degradación de sus hábitats. ¿Qué amenazas enfrentan los flamencos de Sechura? La ubicación alejada de los humedales no elimina los riesgos para estas aves. La caza, la captura y el consumo de fauna silvestre son prácticas que pueden afectar directamente a las poblaciones de flamencos, especialmente durante la temporada en la que permanecen concentrados en las zonas de reproducción. La dificultad para acceder a determinados sectores también obliga a reforzar la vigilancia. Los recorridos permiten identificar nuevos puntos de anidamiento y detectar posibles casos de afectación antes de que el impacto sea mayor. El antecedente de 2025 en La Huaquilla muestra la necesidad de mantener una presencia constante en estos espacios. Para el Serfor, la protección de las áreas donde se reproducen y alimentan las aves requiere coordinación entre autoridades, especialistas y comunidades locales. ¿Cómo reportar un flamenco en situación de riesgo? La ciudadanía puede comunicar al Serfor cualquier caso relacionado con fauna silvestre que se encuentre herida, enferma, fuera de su hábitat o que requiera evaluación e intervención. Según el canal oficial Alerta SERFOR , los ciudadanos deben enviar un mensaje escrito al WhatsApp 947 588 269 , explicando qué ocurrió, dónde se produjo el hecho y cuándo fue observado. También se deben adjuntar fotografías, videos o información de ubicación que ayude a los especialistas a identificar el lugar y evaluar la situación. El Serfor precisa que este canal recibe mensajes escritos y no llamadas telefónicas . Los reportes son derivados a las Administraciones Técnicas Forestales y de Fauna Silvestre según el ámbito correspondiente.</t>
+          <t>Diferentes informes de las oficinas de control institucional del Programa Nacional de Saneamiento Urbano (PNSU) dan cuenta del estado de abandono en su mantenimiento de los Sistemas Alternativos de Recolección y Evacuación de aguas de lluvia (SARE) que se habilitaron en Piura y que costaron millones de soles. Un ejemplo es lo que ocurre en el SARE Cinco Esquinas que costó más de 28 millones de soles, pero ni siquiera tiene un cerco perimétrico para proteger los costosos equipos instalados a pesar de los años pasados. “El grupo electrógeno y la electrobomba constituyen equipos necesarios para el funcionamiento del sistema de bombeo y la evacuación, por lo que su exposición en un área sin control físico permanente de acceso podría afectar su seguridad, conservación y disponibilidad cuando sean requeridos para la operación del SARE”, se lee en el informe de control. De otro lado, el SARE de Ignacio Merino, valorizado en 15 millones de soles, también tiene problemas de falta de mantenimiento. “La falta de culminación de la transferencia legal integral y la ausencia de un marco procedimental que regule las obligaciones de custodia operativa provisoria han provocado que un sistema pluvial de gran inversión (S/ 17.1 millones) no registre ningún tipo de mantenimiento preventivo sobre sus componentes críticos. Esto neutraliza la capacidad de respuesta instalada para salvaguardar a las urbanizaciones del distrito de Piura”, se indica en el documento de Contraloría. Entre las principales observaciones se tiene la acumulación de sedimentos en canaletas cunetas de las vías.</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>https://eltiempo.pe/local/refuerzan-la-vigilancia-de-flamencos-en-humedales-de-sechura/</t>
+          <t>https://eltiempo.pe/local/los-sare-siguen-sin-mantenimiento-para-funcionar-durante-las-lluvias/</t>
         </is>
       </c>
     </row>
@@ -1127,17 +1127,17 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Estado de emergencia en Piura es más de lo mismo</t>
+          <t>Refuerzan la vigilancia de flamencos en humedales de Sechura</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>La emisión del decreto supremo N° 126-2026 con la declaratoria de emergencia en Piura, Castilla, Veintiséis de Octubre y Catacaos para luchar contra la criminalidad, no tuvo mayor impacto en la opinión pública agobiada por la ola criminal que castiga a la región. Según el exjefe de la Región Policial de Piura, Coronel (r) Máximo Vargas Hugo, esta medida es más de lo mismo y casi un calco de lo que hicieron los gobiernos anteriores, sin mayores resultados. “Es evidente que el actual gobierno viene utilizando las medidas de gobiernos anteriores para frenar la criminalidad e inseguridad que se vive [...] realmente no se tiene los resultados que la población requiere. Esto es algo repetitivo y creo que el gobierno actual puede entrar en un desgaste político toda vez que la población exige seguridad”, manifestó el exmando policial. Agregó que pese a estas declaratorias de emergencia, siguen creciendo la comisión de delitos como el asesinato, extorsiones y ahora los secuestros. “La población quiere seguridad y están repitiendo lo mismo que han hecho gestiones anteriores. Desde el año pasado, Piura viene en estados de emergencia y quizás tenemos el año en situación de emergencia. Esta es una medida que a todas luces no ha dado resultados. Cambios Sobre el cambio del comandante general de la Policía, Vargas Hugo señaló que los resultados se notarán cuando se fortalezca la labor policial con recursos, logística e inteligencia. “Ese cambio no garantiza una modificación en la lucha contra el crimen. Hay policías que tienen la mejor intención de tener éxito contra el crimen, pero si no le dan las herramientas necesarias, nada pueden hacer”, manifestó.</t>
+          <t>Unos 4.800 flamencos chilenos ( Phoenicopterus chilensis ) habrían completado este año su etapa de reproducción y desplazamiento en el Estuario de Virrilá y la laguna La Niña , dos importantes humedales ubicados en la provincia de Sechura , en Piura. El registro fue recogido por el Servicio Nacional Forestal y de Fauna Silvestre (Serfor) , organismo adscrito al Ministerio de Desarrollo Agrario y Riego (Midagri), durante las labores de monitoreo de esta especie migratoria. Debido a la importancia de estos ecosistemas para la reproducción de los flamencos, especialistas del Serfor recorrieron los puntos de anidamiento identificados en los humedales de Sechura . Las acciones forman parte de las labores de vigilancia y seguimiento de la fauna silvestre en Piura. ¿Por qué se refuerza la vigilancia en Sechura? El seguimiento de los flamencos representa un desafío debido a la extensión del territorio y a las características de los humedales. A ello se suma que estas aves no necesariamente utilizan los mismos lugares para construir sus nidos cada año. Por esa razón, los especialistas deben realizar recorridos periódicos para localizar las zonas donde las aves se concentran durante su periodo reproductivo y verificar que no existan situaciones que puedan afectar a los ejemplares. El especialista en fauna silvestre del Serfor, Max Guerra, señaló que es necesario fortalecer las acciones de patrullaje y monitoreo en los espacios de anidamiento, tomando en cuenta tanto las condiciones del territorio como las amenazas que pueden afectar a estas aves. En las intervenciones realizadas en la provincia participaron representantes del Serfor sede Piura , la Fiscalía Especializada en Materia Ambiental de Piura y la Unidad Desconcentrada de Protección de Medio Ambiente de la Policía Nacional del Perú. El trabajo conjunto resulta especialmente importante en una zona donde ya se han registrado casos de afectación a estas aves. En julio de 2025, el Serfor constató la caza ilegal de crías de flamencos chilenos en la laguna del sector La Huaquilla, en Sechura, luego de recibir una alerta. Los especialistas encontraron patas y plumas de polluelos en el lugar. El ciclo reproductivo de los flamencos en Sechura La reproducción de los flamencos chilenos sigue un proceso que se desarrolla durante varios meses. En los humedales de Sechura , la temporada comienza aproximadamente a mediados de abril, cuando las aves empiezan a construir sus nidos. Entre mayo y junio ocurre la postura de los huevos, mientras que durante julio aparecen los primeros polluelos. A partir de la primera semana de agosto, las crías comienzan a desplazarse, una etapa que requiere especial atención por parte de quienes realizan el monitoreo. “Es un lugar alejado, hay mucho territorio que recorrer y se necesita prestar atención cuando están los polluelos; los puntos de anidamiento cambian todos los años”, explicó el guardaparque local Pablo Martínez, quien también destacó la coordinación con el Serfor para realizar los recorridos. ¿Dónde se reproducen los flamencos? El Estuario de Virrilá y la laguna La Niña forman parte de los espacios utilizados por estas aves en la costa norte del Perú. El Serfor ya ha documentado en años anteriores procesos reproductivos y trabajos de seguimiento en ambos lugares. En 2022, por ejemplo, la entidad informó sobre el nacimiento de alrededor de 700 pichones de flamenco chileno en el Estuario de Virrilá. El lugar fue reconocido además como Sitio Ramsar en 2021, debido a su importancia como humedal de relevancia internacional. Un año después, en agosto de 2023, el Serfor realizó el anillamiento de 183 polluelos nacidos en la laguna La Niña. Esta práctica permite identificar a los ejemplares y obtener información sobre sus desplazamientos y los lugares que utilizan durante su vida. El flamenco chileno es una especie migratoria El flamenco chileno utiliza diferentes cuerpos de agua a lo largo de su distribución. Según el Serfor, puede encontrarse en lagunas poco profundas de agua dulce y salada, desde la costa hasta zonas ubicadas a unos 4.800 metros de altitud. Su distribución comprende territorios desde Chile hasta Ecuador , por lo que los ejemplares que nacen en los humedales de Sechura pueden desplazarse posteriormente hacia otras zonas del país o incluso hacia territorios de países vecinos. El anillamiento se ha convertido en una herramienta para conocer mejor estos movimientos. Los registros realizados por especialistas y observadores de aves permiten identificar ejemplares en diferentes puntos y reconstruir parte de sus rutas de desplazamiento. De acuerdo con el Serfor, la especie está clasificada como “Casi Amenazada” . Entre las principales amenazas identificadas figuran la caza ilegal y la degradación de sus hábitats. ¿Qué amenazas enfrentan los flamencos de Sechura? La ubicación alejada de los humedales no elimina los riesgos para estas aves. La caza, la captura y el consumo de fauna silvestre son prácticas que pueden afectar directamente a las poblaciones de flamencos, especialmente durante la temporada en la que permanecen concentrados en las zonas de reproducción. La dificultad para acceder a determinados sectores también obliga a reforzar la vigilancia. Los recorridos permiten identificar nuevos puntos de anidamiento y detectar posibles casos de afectación antes de que el impacto sea mayor. El antecedente de 2025 en La Huaquilla muestra la necesidad de mantener una presencia constante en estos espacios. Para el Serfor, la protección de las áreas donde se reproducen y alimentan las aves requiere coordinación entre autoridades, especialistas y comunidades locales. ¿Cómo reportar un flamenco en situación de riesgo? La ciudadanía puede comunicar al Serfor cualquier caso relacionado con fauna silvestre que se encuentre herida, enferma, fuera de su hábitat o que requiera evaluación e intervención. Según el canal oficial Alerta SERFOR , los ciudadanos deben enviar un mensaje escrito al WhatsApp 947 588 269 , explicando qué ocurrió, dónde se produjo el hecho y cuándo fue observado. También se deben adjuntar fotografías, videos o información de ubicación que ayude a los especialistas a identificar el lugar y evaluar la situación. El Serfor precisa que este canal recibe mensajes escritos y no llamadas telefónicas . Los reportes son derivados a las Administraciones Técnicas Forestales y de Fauna Silvestre según el ámbito correspondiente.</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>https://eltiempo.pe/local/estado-de-emergencia-en-piura-es-mas-de-lo-mismo/</t>
+          <t>https://eltiempo.pe/local/refuerzan-la-vigilancia-de-flamencos-en-humedales-de-sechura/</t>
         </is>
       </c>
     </row>
@@ -1152,17 +1152,17 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Piura: Sicarios asesinan a menor, dos mujeres y un exsereno</t>
+          <t>Estado de emergencia en Piura es más de lo mismo</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>La violencia volvió a golpear con fuerza a la provincia de Sullana y otros sectores de Piura. En distintos hechos registrados durante las últimas horas, sicarios habrían atacado a varias personas, dejando como saldo la muerte de un adolescente de 13 años, dos mujeres y un exsereno. Además, otras dos personas resultaron heridas por impactos de bala. Los casos son investigados por la Policía Nacional del Perú, que busca determinar quiénes participaron en los ataques y cuáles fueron los móviles. La institución mantiene abiertas distintas líneas de investigación y no descarta que algunos de estos crímenes estén relacionados con ajustes de cuentas. Sicarios asesinan a menor de 13 años en Sullana Uno de los casos que más ha conmocionado a Sullana corresponde a la muerte de un menor de apenas 13 años. El adolescente, identificado con las iniciales M. F. L. Ch., era natural de Trujillo, aunque residía en Piura, y se convirtió, según la información proporcionada, en la víctima número 44 de los asesinatos atribuidos al sicariato en la provincia. El crimen ocurrió la noche del domingo en la intersección de la calle Túpac Amaru con la avenida Par Vial, en el asentamiento 17 de Enero. Eran aproximadamente las 10:40 de la noche cuando el adolescente viajaba como pasajero en un mototaxi rojo de placa 3784-DP. De acuerdo con las primeras investigaciones, el vehículo habría quedado detenido en medio de la vía debido a un desperfecto mecánico. La tapa del tanque de combustible había sido retirada y esa situación habría sido aprovechada por los atacantes. Según los primeros testimonios recogidos en el lugar, sujetos que se desplazaban en una motocicleta llegaron hasta el mototaxi y dispararon directamente contra el menor. Uno de los proyectiles impactó en su cabeza y le ocasionó una herida de entrada y salida que provocó su muerte de manera instantánea. Un tatuaje permitió identificar al adolescente Tras el ataque, sus acompañantes habrían escapado corriendo en dirección al sector La Selva, mientras la víctima y el trimóvil quedaron abandonados en la zona. La identificación del adolescente se pudo realizar gracias a un tatuaje que llevaba en el brazo derecho con el nombre “Alexander”. Una tía acudió a la dependencia policial y posteriormente a la morgue legal, donde reconoció plenamente al menor. La Policía continúa con las diligencias para establecer las circunstancias exactas del asesinato. Entre las hipótesis que se manejan figura un posible ajuste de cuentas, aunque esta versión todavía debe ser corroborada por los investigadores. Para establecer si existían antecedentes que puedan ayudar a explicar el ataque, la Policía coordina con sus unidades de Piura para conocer si el adolescente había sido intervenido durante las últimas semanas. Asesinan a exsereno dentro de restaurante en Talara Otro hecho violento ocurrió en Talara. Un hombre conocido como “Van Dan”, quien había sido sereno y era propietario de un gimnasio en el distrito de La Brea-Negritos, fue asesinado a balazos dentro del restaurante “La Caleta 10”, ubicado en el asentamiento Mario Aguirre. Según la información preliminar, un sicario irrumpió en el segundo piso del establecimiento y disparó en cinco oportunidades contra la víctima. El hombre quedó sentado en una silla y murió pocos segundos después del ataque. La Policía deberá determinar si este crimen guarda relación con alguna amenaza previa, conflicto personal u otra actividad delictiva. Por ahora, el móvil permanece bajo investigación. Dos mujeres mueren tras una balacera en Sullana La noche del lunes, otro ataque armado dejó dos mujeres fallecidas y dos hombres heridos en el sector Manuel Seoane, en Sullana. El hecho ocurrió en la manzana B, lote 13, donde cuatro personas se encontraban dentro de una vivienda consumiendo bebidas alcohólicas y ceviche. Según los testimonios recogidos inicialmente, una motocicleta se estacionó frente al inmueble. Uno de los ocupantes descendió y habría ingresado rápidamente a la vivienda para abrir fuego contra las personas que se encontraban en el interior. Los testigos describieron el ataque como una ráfaga de disparos. Aunque las víctimas intentaron protegerse y lanzarse al suelo, varias de ellas fueron alcanzadas por los proyectiles. Las víctimas fueron identificadas Una de las víctimas fue identificada como Sheila Anabelen Viera Elias, de 30 años. De acuerdo con las primeras versiones, la mujer intentó escapar hacia el baño, pero el atacante la habría perseguido y disparado varias veces. También resultó gravemente herida Lady Loren Valdiviezo Nole, de 28 años. Los disparos le ocasionaron lesiones en el tórax y la cabeza. La mujer fue trasladada a un establecimiento de salud junto con los demás afectados. Además de las dos jóvenes, Daniel Paucar y Carlos Cornejo resultaron heridos por impactos de bala y fueron trasladados a los hospitales antiguo y nuevo de Sullana. Hasta el cierre de la información proporcionada, ambos permanecían con pronóstico reservado. Las dos mujeres fallecieron pese a los esfuerzos realizados por los médicos. En el caso de Loren Valdiviezo, se conoció que tenía seis meses de gestación, lo que añadió una nueva dimensión a la tragedia. ¿Qué investiga la Policía sobre los ataques? Los investigadores buscan establecer si los tres hechos tienen alguna conexión o si se trata de ataques independientes. La presencia de motocicletas, el uso de armas de fuego y la rapidez con la que actuaron los presuntos atacantes son algunos de los elementos que forman parte de las diligencias. De acuerdo con la Policía Nacional del Perú , la investigación criminal permite reunir evidencias para determinar responsabilidades y esclarecer los hechos. La institución mantiene información institucional y canales de atención a través de su portal oficial . Asimismo, el Ministerio Público participa en las investigaciones cuando corresponde y tiene entre sus funciones dirigir la investigación del delito. Para conocer información institucional, denuncias y servicios fiscales, se puede consultar el portal oficial del Ministerio Público . ¿Dónde se puede consultar información sobre el sicariato? Para conocer la incidencia de distintos delitos, el Ministerio del Interior cuenta con el Mapa del Delito Georreferenciado . Esta herramienta permite consultar registros relacionados con homicidios, extorsiones y sicariato , además de ubicar comisarías y otros puntos de interés. El servicio forma parte del Observatorio Nacional de Seguridad Ciudadana y puede ser consultado en el Mapa del Delito Georreferenciado del Ministerio del Interior . En Sullana, la violencia vinculada a ataques con armas de fuego y asesinatos por encargo no es un fenómeno nuevo. El propio Poder Judicial ha informado anteriormente sobre procesos por presunto sicariato en esta provincia, incluyendo investigaciones en las que se analizaron testimonios protegidos y registros audiovisuales como elementos de convicción. Mientras avanzan las diligencias, la Policía deberá determinar quiénes fueron los autores materiales de estos crímenes, quiénes pudieron ordenar los ataques y cuáles fueron las razones detrás de cada asesinato. Por el momento, las investigaciones continúan abiertas.</t>
+          <t>La emisión del decreto supremo N° 126-2026 con la declaratoria de emergencia en Piura, Castilla, Veintiséis de Octubre y Catacaos para luchar contra la criminalidad, no tuvo mayor impacto en la opinión pública agobiada por la ola criminal que castiga a la región. Según el exjefe de la Región Policial de Piura, Coronel (r) Máximo Vargas Hugo, esta medida es más de lo mismo y casi un calco de lo que hicieron los gobiernos anteriores, sin mayores resultados. “Es evidente que el actual gobierno viene utilizando las medidas de gobiernos anteriores para frenar la criminalidad e inseguridad que se vive [...] realmente no se tiene los resultados que la población requiere. Esto es algo repetitivo y creo que el gobierno actual puede entrar en un desgaste político toda vez que la población exige seguridad”, manifestó el exmando policial. Agregó que pese a estas declaratorias de emergencia, siguen creciendo la comisión de delitos como el asesinato, extorsiones y ahora los secuestros. “La población quiere seguridad y están repitiendo lo mismo que han hecho gestiones anteriores. Desde el año pasado, Piura viene en estados de emergencia y quizás tenemos el año en situación de emergencia. Esta es una medida que a todas luces no ha dado resultados. Cambios Sobre el cambio del comandante general de la Policía, Vargas Hugo señaló que los resultados se notarán cuando se fortalezca la labor policial con recursos, logística e inteligencia. “Ese cambio no garantiza una modificación en la lucha contra el crimen. Hay policías que tienen la mejor intención de tener éxito contra el crimen, pero si no le dan las herramientas necesarias, nada pueden hacer”, manifestó.</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>https://eltiempo.pe/local/piura-sicarios-asesinan-a-menor-dos-mujeres-y-un-exsereno/</t>
+          <t>https://eltiempo.pe/local/estado-de-emergencia-en-piura-es-mas-de-lo-mismo/</t>
         </is>
       </c>
     </row>
@@ -1177,17 +1177,17 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>¡Ni los niños se salvan del hampa! Delincuentes saquean colegio y se llevan hasta los juguetes en el Bajo Piura</t>
+          <t>Candidatos a gobernadores y alcaldes obligados a rendir sus gastos</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>La inseguridad vuelve a causar indignación en el corazón del Bajo Piura. Esta vez, los delincuentes pusieron en la mira a la I. E. I. N.° 463 del caserío Santa Cruz, donde, durante la madrugada, ingresaron al plantel y sustrajeron diversos bienes utilizados por más de 40 estudiantes del nivel inicial. Según la información preliminar, los sujetos violentaron dos ambientes de la institución educativa para ingresar y apoderarse de dos parlantes, dos ventiladores y otros bienes. Pero lo que más ha indignado a los padres de familia es que los delincuentes también se llevaron los juguetes utilizados por los niños durante sus actividades de aprendizaje y desarrollo psicomotor. El robo fue descubierto en las primeras horas de la mañana y comunicado al personal de Serenazgo y a la Policía Nacional. La docente Gaby De La Cruz fue quien alertó a las autoridades, quienes llegaron hasta el colegio para constatar los daños y recoger información que permita esclarecer lo ocurrido. BLANCO DE LA DELINCUENCIA Sin embargo, este no sería un hecho aislado. Padres de familia señalaron que la institución educativa ya habría sido víctima anteriormente de la delincuencia. En una ocasión pasada, sujetos desconocidos se llevaron un tanque Rotoplas, dejando nuevamente al plantel expuesto y afectando el normal desarrollo de las actividades educativas. La presidenta Jackeline Silupú expresó su malestar y preocupación ante las autoridades por la situación que viene atravesando la institución. Los padres exigieron mayor seguridad y acciones concretas para evitar que los delincuentes continúen ingresando a los centros educativos. De acuerdo con las primeras versiones, serían dos sujetos los que habrían cometido el robo, para luego escapar rápidamente a bordo de un mototaxi. La Policía Nacional continúa con las diligencias e investigaciones para identificar a los responsables y recuperar los bienes sustraídos.</t>
+          <t>Las organizaciones políticas que participarán en las Elecciones Regionales y Municipales (ERM) 2026 están obligadas a presentar ante la Oficina Nacional de Procesos Electorales (ONPE) dos informes donde registren los gastos, aportes e ingresos de sus campañas. La fecha límite para presentar el primero de dichos informes es el próximo viernes 11 de setiembre. La obligación y el plazo también alcanzan a todos los ciudadanos que hayan logrado inscribir sus candidaturas para una Gobernación, una Vicegobernación o una Alcaldía –provincial o distrital– y se mantienen aun cuando la candidatura no llegue al final del proceso por renuncia, tacha o exclusión. Debido a un cambio en la Ley de Organizaciones Políticas, ya no rinden cuentas quienes aspiran a ser consejeros regionales o regidores municipales. El informe financiero lo puede presentar él mismo o, si tiene, su responsable de campaña.</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>https://eltiempo.pe/local/ni-los-ninos-se-salvan-del-hampa-delincuentes-saquean-colegio-y-se-llevan-hasta-los-juguetes-en-el-bajo-piura/</t>
+          <t>https://eltiempo.pe/local/candidatos-a-gobernadores-y-alcaldes-obligados-a-rendir-sus-gastos/</t>
         </is>
       </c>
     </row>
@@ -1202,17 +1202,17 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Dren Maldonado: MTC enviará puente a Piura tras alerta por riesgo de dejar incomunicadas a 60 mil personas</t>
+          <t>¡Ni los niños se salvan del hampa! Delincuentes saquean colegio y se llevan hasta los juguetes en el Bajo Piura</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>La senadora por Piura, Karla Schaefer, informó que el ministro de Transportes y Comunicaciones, Rafael Rey Rey, dispuso el envío de un puente que será utilizado para garantizar la conexión vial ante una eventual afectación del dren Maldonado. Puedes Leer | El Niño superaría al de 1998 y traería impactos “insospechados” en la región Piura La situación de riesgo en el dren Maldonado, en el distrito de Veintiséis de Octubre, habría encontrado una respuesta desde el Gobierno central. La senadora por Piura, Karla Schaefer , informó que el Ministerio de Transportes y Comunicaciones (MTC) dispuso el envío de un puente para atender una eventual interrupción de la vía en este sector. Según explicó Schaefer, el pedido fue trasladado al MTC debido a la preocupación por la seguridad de la red vial y el riesgo de que una eventual afectación del dren Maldonado pueda comprometer la comunicación de importantes sectores de Piura. “ El ministro de Transportes y Comunicaciones, Rafael Rey, afirmó que él va a poner el puente ”, señaló la senadora. Schaefer explicó que inicialmente se realizaron consultas tanto al MTC como al Ministerio de Defensa (Mindef), a través de la empresa estatal SIMA Perú , para evaluar una alternativa que permita responder ante una emergencia. Sin embargo, de acuerdo con la parlamentaria, el ministro Rey tomó la decisión de disponer directamente la estructura tras conocer la situación. “Se había hecho la consulta al Ministerio de Transportes y Comunicaciones y al Ministerio de Defensa a través de SIMA Perú. Pero el ministro Rafael Rey, gracias a la delegación de facultades, ni bien vio el tema, dijo: ‘ Yo voy a dar ese puente ’”, declaró. Puente será trasladado a Piura La senadora informó además que la estructura ya habría salido de Lima con destino a Piura y será almacenada temporalmente en Piura Futura , desde donde podrá ser trasladada hacia los puntos que requieran atención. “Hoy han salido de Lima y serán almacenados en Piura Futura para que desde ahí se vayan a varios puntos”, indicó Schaefer. La medida busca contar con una alternativa de conexión ante una eventual emergencia relacionada con el dren Maldonado, especialmente considerando el riesgo advertido para la población de Veintiséis de Octubre. En declaraciones difundidas previamente por El Tiempo , Schaefer había advertido que una eventual afectación del dren podría dejar incomunicadas a unas 60 mil personas y había cuestionado las dificultades generadas por la distribución de competencias entre distintas instituciones del Estado. Schaefer agradece respuesta del MTC La senadora destacó la rapidez con la que, según su versión, el ministro de Transportes habría atendido el pedido. “ Agradecerle al ministro esa eficiencia en solucionar ese problema en que se prioriza la vida ”, manifestó. Asimismo, reconoció el trabajo del director de Puentes, Julio Palacios , y de la Municipalidad Distrital de Veintiséis de Octubre , instituciones que, según indicó, tendrán participación en la gestión relacionada con la estructura. Mira También | ¡Ni los niños se salvan del hampa! Delincuentes saquean colegio y se llevan hasta los juguetes en el Bajo Piura El dren Maldonado es uno de los puntos críticos del sistema de drenaje de Veintiséis de Octubre. En febrero de 2026, el INDECI ya había identificado la necesidad de gestionar requerimientos para garantizar su operatividad, debido a su importancia para la evacuación de aguas pluviales durante lluvias intensas. La atención al dren Maldonado forma parte de una problemática mayor de infraestructura y prevención frente a lluvias en Piura, donde distintas autoridades han advertido sobre la necesidad de acelerar las intervenciones antes de que se presenten emergencias.</t>
+          <t>La inseguridad vuelve a causar indignación en el corazón del Bajo Piura. Esta vez, los delincuentes pusieron en la mira a la I. E. I. N.° 463 del caserío Santa Cruz, donde, durante la madrugada, ingresaron al plantel y sustrajeron diversos bienes utilizados por más de 40 estudiantes del nivel inicial. Según la información preliminar, los sujetos violentaron dos ambientes de la institución educativa para ingresar y apoderarse de dos parlantes, dos ventiladores y otros bienes. Pero lo que más ha indignado a los padres de familia es que los delincuentes también se llevaron los juguetes utilizados por los niños durante sus actividades de aprendizaje y desarrollo psicomotor. El robo fue descubierto en las primeras horas de la mañana y comunicado al personal de Serenazgo y a la Policía Nacional. La docente Gaby De La Cruz fue quien alertó a las autoridades, quienes llegaron hasta el colegio para constatar los daños y recoger información que permita esclarecer lo ocurrido. BLANCO DE LA DELINCUENCIA Sin embargo, este no sería un hecho aislado. Padres de familia señalaron que la institución educativa ya habría sido víctima anteriormente de la delincuencia. En una ocasión pasada, sujetos desconocidos se llevaron un tanque Rotoplas, dejando nuevamente al plantel expuesto y afectando el normal desarrollo de las actividades educativas. La presidenta Jackeline Silupú expresó su malestar y preocupación ante las autoridades por la situación que viene atravesando la institución. Los padres exigieron mayor seguridad y acciones concretas para evitar que los delincuentes continúen ingresando a los centros educativos. De acuerdo con las primeras versiones, serían dos sujetos los que habrían cometido el robo, para luego escapar rápidamente a bordo de un mototaxi. La Policía Nacional continúa con las diligencias e investigaciones para identificar a los responsables y recuperar los bienes sustraídos.</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>https://eltiempo.pe/local/dren-maldonado-mtc-enviara-puente-a-piura-tras-alerta-por-riesgo-de-dejar-incomunicadas-a-60-mil-personas/</t>
+          <t>https://eltiempo.pe/local/ni-los-ninos-se-salvan-del-hampa-delincuentes-saquean-colegio-y-se-llevan-hasta-los-juguetes-en-el-bajo-piura/</t>
         </is>
       </c>
     </row>
@@ -1227,17 +1227,17 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Candidatos a gobernadores y alcaldes obligados a rendir sus gastos</t>
+          <t>Dren Maldonado: MTC enviará puente a Piura tras alerta por riesgo de dejar incomunicadas a 60 mil personas</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Las organizaciones políticas que participarán en las Elecciones Regionales y Municipales (ERM) 2026 están obligadas a presentar ante la Oficina Nacional de Procesos Electorales (ONPE) dos informes donde registren los gastos, aportes e ingresos de sus campañas. La fecha límite para presentar el primero de dichos informes es el próximo viernes 11 de setiembre. La obligación y el plazo también alcanzan a todos los ciudadanos que hayan logrado inscribir sus candidaturas para una Gobernación, una Vicegobernación o una Alcaldía –provincial o distrital– y se mantienen aun cuando la candidatura no llegue al final del proceso por renuncia, tacha o exclusión. Debido a un cambio en la Ley de Organizaciones Políticas, ya no rinden cuentas quienes aspiran a ser consejeros regionales o regidores municipales. El informe financiero lo puede presentar él mismo o, si tiene, su responsable de campaña.</t>
+          <t>La senadora por Piura, Karla Schaefer, informó que el ministro de Transportes y Comunicaciones, Rafael Rey Rey, dispuso el envío de un puente que será utilizado para garantizar la conexión vial ante una eventual afectación del dren Maldonado. Puedes Leer | El Niño superaría al de 1998 y traería impactos “insospechados” en la región Piura La situación de riesgo en el dren Maldonado, en el distrito de Veintiséis de Octubre, habría encontrado una respuesta desde el Gobierno central. La senadora por Piura, Karla Schaefer , informó que el Ministerio de Transportes y Comunicaciones (MTC) dispuso el envío de un puente para atender una eventual interrupción de la vía en este sector. Según explicó Schaefer, el pedido fue trasladado al MTC debido a la preocupación por la seguridad de la red vial y el riesgo de que una eventual afectación del dren Maldonado pueda comprometer la comunicación de importantes sectores de Piura. “ El ministro de Transportes y Comunicaciones, Rafael Rey, afirmó que él va a poner el puente ”, señaló la senadora. Schaefer explicó que inicialmente se realizaron consultas tanto al MTC como al Ministerio de Defensa (Mindef), a través de la empresa estatal SIMA Perú , para evaluar una alternativa que permita responder ante una emergencia. Sin embargo, de acuerdo con la parlamentaria, el ministro Rey tomó la decisión de disponer directamente la estructura tras conocer la situación. “Se había hecho la consulta al Ministerio de Transportes y Comunicaciones y al Ministerio de Defensa a través de SIMA Perú. Pero el ministro Rafael Rey, gracias a la delegación de facultades, ni bien vio el tema, dijo: ‘ Yo voy a dar ese puente ’”, declaró. Puente será trasladado a Piura La senadora informó además que la estructura ya habría salido de Lima con destino a Piura y será almacenada temporalmente en Piura Futura , desde donde podrá ser trasladada hacia los puntos que requieran atención. “Hoy han salido de Lima y serán almacenados en Piura Futura para que desde ahí se vayan a varios puntos”, indicó Schaefer. La medida busca contar con una alternativa de conexión ante una eventual emergencia relacionada con el dren Maldonado, especialmente considerando el riesgo advertido para la población de Veintiséis de Octubre. En declaraciones difundidas previamente por El Tiempo , Schaefer había advertido que una eventual afectación del dren podría dejar incomunicadas a unas 60 mil personas y había cuestionado las dificultades generadas por la distribución de competencias entre distintas instituciones del Estado. Schaefer agradece respuesta del MTC La senadora destacó la rapidez con la que, según su versión, el ministro de Transportes habría atendido el pedido. “ Agradecerle al ministro esa eficiencia en solucionar ese problema en que se prioriza la vida ”, manifestó. Asimismo, reconoció el trabajo del director de Puentes, Julio Palacios , y de la Municipalidad Distrital de Veintiséis de Octubre , instituciones que, según indicó, tendrán participación en la gestión relacionada con la estructura. Mira También | ¡Ni los niños se salvan del hampa! Delincuentes saquean colegio y se llevan hasta los juguetes en el Bajo Piura El dren Maldonado es uno de los puntos críticos del sistema de drenaje de Veintiséis de Octubre. En febrero de 2026, el INDECI ya había identificado la necesidad de gestionar requerimientos para garantizar su operatividad, debido a su importancia para la evacuación de aguas pluviales durante lluvias intensas. La atención al dren Maldonado forma parte de una problemática mayor de infraestructura y prevención frente a lluvias en Piura, donde distintas autoridades han advertido sobre la necesidad de acelerar las intervenciones antes de que se presenten emergencias.</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>https://eltiempo.pe/local/candidatos-a-gobernadores-y-alcaldes-obligados-a-rendir-sus-gastos/</t>
+          <t>https://eltiempo.pe/local/dren-maldonado-mtc-enviara-puente-a-piura-tras-alerta-por-riesgo-de-dejar-incomunicadas-a-60-mil-personas/</t>
         </is>
       </c>
     </row>
@@ -1248,21 +1248,21 @@
         </is>
       </c>
       <c r="B31" s="2" t="n">
-        <v>46272</v>
+        <v>46273</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>I.E. San Ramón de Chulucanas se consagra campeona del Regional Singing Festival 2026</t>
+          <t>Piura: Sicarios asesinan a menor, dos mujeres y un exsereno</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>La Institución Educativa San Ramón de Chulucanas, representante de la UGEL Chulucanas , obtuvo el primer lugar en el Regional Singing Festival 2026 “Singing for a Better World”, organizado por la Dirección Regional de Educación de Piura. PUEDES LEER ► Sobrevive tras 10 días sepultada por el lodo y es rescatada cuando su familia ya la había dado por muerta La actividad se desarrolló en el parque Néstor Martos de Piura y reunió a estudiantes representantes de las 12 UGEL de la región, quienes demostraron sus habilidades en la interpretación de canciones en inglés. El festival tiene como finalidad fortalecer las competencias comunicativas en el idioma inglés, además de promover la creatividad, la expresión artística y la participación de los estudiantes. La iniciativa se desarrolla en concordancia con el Currículo Nacional de la Educación Básica. Durante sus presentaciones, los participantes también transmitieron mensajes relacionados con valores y actitudes que contribuyen a una convivencia democrática, respetuosa, inclusiva y solidaria. San Ramón conquistó el primer lugar La IE San Ramón logró imponerse en la competencia con la interpretación de la canción “Hand for Chulucanas”, presentación que le permitió quedarse con el primer puesto del festival regional. El segundo lugar fue para la IE Libertadores de América, representante de la UGEL La Unión, que participó con la canción “The Song of Tomorrow”. Mientras que el tercer puesto correspondió a la IE César Vallejo, de la UGEL Morropón, con la interpretación de “Brighter Than Before”. La competencia comenzó en cada institución educativa y posteriormente continuó en las diferentes etapas de las 12 UGEL de Piura: Ayabaca, Chulucanas, Huancabamba, Huarmaca, La Unión, Morropón, Paita, Piura, Sechura, Sullana, Talara y Tambogrande. Además de impulsar el aprendizaje del inglés, el festival busca fortalecer la sana competencia, el trabajo en equipo y la integración entre estudiantes de diferentes provincias de la región.</t>
+          <t>La violencia volvió a golpear con fuerza a la provincia de Sullana y otros sectores de Piura. En distintos hechos registrados durante las últimas horas, sicarios habrían atacado a varias personas, dejando como saldo la muerte de un adolescente de 13 años, dos mujeres y un exsereno. Además, otras dos personas resultaron heridas por impactos de bala. Los casos son investigados por la Policía Nacional del Perú, que busca determinar quiénes participaron en los ataques y cuáles fueron los móviles. La institución mantiene abiertas distintas líneas de investigación y no descarta que algunos de estos crímenes estén relacionados con ajustes de cuentas. Sicarios asesinan a menor de 13 años en Sullana Uno de los casos que más ha conmocionado a Sullana corresponde a la muerte de un menor de apenas 13 años. El adolescente, identificado con las iniciales M. F. L. Ch., era natural de Trujillo, aunque residía en Piura, y se convirtió, según la información proporcionada, en la víctima número 44 de los asesinatos atribuidos al sicariato en la provincia. El crimen ocurrió la noche del domingo en la intersección de la calle Túpac Amaru con la avenida Par Vial, en el asentamiento 17 de Enero. Eran aproximadamente las 10:40 de la noche cuando el adolescente viajaba como pasajero en un mototaxi rojo de placa 3784-DP. De acuerdo con las primeras investigaciones, el vehículo habría quedado detenido en medio de la vía debido a un desperfecto mecánico. La tapa del tanque de combustible había sido retirada y esa situación habría sido aprovechada por los atacantes. Según los primeros testimonios recogidos en el lugar, sujetos que se desplazaban en una motocicleta llegaron hasta el mototaxi y dispararon directamente contra el menor. Uno de los proyectiles impactó en su cabeza y le ocasionó una herida de entrada y salida que provocó su muerte de manera instantánea. Un tatuaje permitió identificar al adolescente Tras el ataque, sus acompañantes habrían escapado corriendo en dirección al sector La Selva, mientras la víctima y el trimóvil quedaron abandonados en la zona. La identificación del adolescente se pudo realizar gracias a un tatuaje que llevaba en el brazo derecho con el nombre “Alexander”. Una tía acudió a la dependencia policial y posteriormente a la morgue legal, donde reconoció plenamente al menor. La Policía continúa con las diligencias para establecer las circunstancias exactas del asesinato. Entre las hipótesis que se manejan figura un posible ajuste de cuentas, aunque esta versión todavía debe ser corroborada por los investigadores. Para establecer si existían antecedentes que puedan ayudar a explicar el ataque, la Policía coordina con sus unidades de Piura para conocer si el adolescente había sido intervenido durante las últimas semanas. Asesinan a exsereno dentro de restaurante en Talara Otro hecho violento ocurrió en Talara. Un hombre conocido como “Van Dan”, quien había sido sereno y era propietario de un gimnasio en el distrito de La Brea-Negritos, fue asesinado a balazos dentro del restaurante “La Caleta 10”, ubicado en el asentamiento Mario Aguirre. Según la información preliminar, un sicario irrumpió en el segundo piso del establecimiento y disparó en cinco oportunidades contra la víctima. El hombre quedó sentado en una silla y murió pocos segundos después del ataque. La Policía deberá determinar si este crimen guarda relación con alguna amenaza previa, conflicto personal u otra actividad delictiva. Por ahora, el móvil permanece bajo investigación. Dos mujeres mueren tras una balacera en Sullana La noche del lunes, otro ataque armado dejó dos mujeres fallecidas y dos hombres heridos en el sector Manuel Seoane, en Sullana. El hecho ocurrió en la manzana B, lote 13, donde cuatro personas se encontraban dentro de una vivienda consumiendo bebidas alcohólicas y ceviche. Según los testimonios recogidos inicialmente, una motocicleta se estacionó frente al inmueble. Uno de los ocupantes descendió y habría ingresado rápidamente a la vivienda para abrir fuego contra las personas que se encontraban en el interior. Los testigos describieron el ataque como una ráfaga de disparos. Aunque las víctimas intentaron protegerse y lanzarse al suelo, varias de ellas fueron alcanzadas por los proyectiles. Las víctimas fueron identificadas Una de las víctimas fue identificada como Sheila Anabelen Viera Elias, de 30 años. De acuerdo con las primeras versiones, la mujer intentó escapar hacia el baño, pero el atacante la habría perseguido y disparado varias veces. También resultó gravemente herida Lady Loren Valdiviezo Nole, de 28 años. Los disparos le ocasionaron lesiones en el tórax y la cabeza. La mujer fue trasladada a un establecimiento de salud junto con los demás afectados. Además de las dos jóvenes, Daniel Paucar y Carlos Cornejo resultaron heridos por impactos de bala y fueron trasladados a los hospitales antiguo y nuevo de Sullana. Hasta el cierre de la información proporcionada, ambos permanecían con pronóstico reservado. Las dos mujeres fallecieron pese a los esfuerzos realizados por los médicos. En el caso de Loren Valdiviezo, se conoció que tenía seis meses de gestación, lo que añadió una nueva dimensión a la tragedia. ¿Qué investiga la Policía sobre los ataques? Los investigadores buscan establecer si los tres hechos tienen alguna conexión o si se trata de ataques independientes. La presencia de motocicletas, el uso de armas de fuego y la rapidez con la que actuaron los presuntos atacantes son algunos de los elementos que forman parte de las diligencias. De acuerdo con la Policía Nacional del Perú , la investigación criminal permite reunir evidencias para determinar responsabilidades y esclarecer los hechos. La institución mantiene información institucional y canales de atención a través de su portal oficial . Asimismo, el Ministerio Público participa en las investigaciones cuando corresponde y tiene entre sus funciones dirigir la investigación del delito. Para conocer información institucional, denuncias y servicios fiscales, se puede consultar el portal oficial del Ministerio Público . ¿Dónde se puede consultar información sobre el sicariato? Para conocer la incidencia de distintos delitos, el Ministerio del Interior cuenta con el Mapa del Delito Georreferenciado . Esta herramienta permite consultar registros relacionados con homicidios, extorsiones y sicariato , además de ubicar comisarías y otros puntos de interés. El servicio forma parte del Observatorio Nacional de Seguridad Ciudadana y puede ser consultado en el Mapa del Delito Georreferenciado del Ministerio del Interior . En Sullana, la violencia vinculada a ataques con armas de fuego y asesinatos por encargo no es un fenómeno nuevo. El propio Poder Judicial ha informado anteriormente sobre procesos por presunto sicariato en esta provincia, incluyendo investigaciones en las que se analizaron testimonios protegidos y registros audiovisuales como elementos de convicción. Mientras avanzan las diligencias, la Policía deberá determinar quiénes fueron los autores materiales de estos crímenes, quiénes pudieron ordenar los ataques y cuáles fueron las razones detrás de cada asesinato. Por el momento, las investigaciones continúan abiertas.</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>https://eltiempo.pe/local/i-e-san-ramon-de-chulucanas-se-consagra-campeona-del-regional-singing-festival-2026/</t>
+          <t>https://eltiempo.pe/local/piura-sicarios-asesinan-a-menor-dos-mujeres-y-un-exsereno/</t>
         </is>
       </c>
     </row>
@@ -1277,17 +1277,17 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Así van los candidatos a falta de un mes para elecciones</t>
+          <t>I.E. San Ramón de Chulucanas se consagra campeona del Regional Singing Festival 2026</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>ICSI Perú hizo una encuesta y revela cómo van las preferencias de los piuranos sobre su próximo gobernador y alcaldes. PUEDES LEER ► Miniván queda al borde de un abismo en la carretera Canchaque -Huancabamba Las elecciones regionales y municipales están a la vuelta de la esquina y lo único seguro es que sí o sí habrá una segunda vuelta para el cargo de gobernador regional. De acuerdo a ley, si ninguna lista supera el 30% de votos válidos, se convoca a una segunda vuelta entre los dos primeros del escrutinio. De acuerdo a la última encuesta de la empresa ICSI Perú ninguno de los aspirantes a la máxima autoridad regional llega al 30% de las preferencias. Según el estudio de opinión pública, el primer lugar es para el exgobernador Reynaldo Hilbck (Alianza para el Progreso) con 22.5%; seguido por Santiago Paz (Somos Perú) con 13.7% ; Mártires Lizana (Fuerza Popular) con 11.1% y Guillermo La Torre (Podemos Perú) con 10.9%. En el caso de los candidatos provinciales, la disputa parece más reñida y la diferencia de porcentajes es más ajustada entre los aspirantes, con lo cual la campaña de aquí hasta el domingo 4 de octubre será una competencia voto a voto y de convencimiento de los indecisos. Gobierno Regional Sobre el tema, el gerente de ICSI Perú, Mauro Vegas Carmen , consideró que uno de los factores del respaldo a Hilbck son sus candidatos en las provincias con mayor caudal electoral de votos. “En los resultados de los 27 distritos a donde se ha ido, Hilbck alcanza la mayor votación en Piura, Veintiséis de Octubre, Catacaos, Sullana, Morropón, Chulucanas, Talara, Órganos y otros. Todo eso le da ese porcentaje que ahora ha sacado frente al segundo. Por ejemplo, en Piura tiene 19.66% y Somos Perú tiene 15.33%; en Castilla, Hilbck tiene 13.60% y Somos Perú unos 10.90% y en Veintiséis de Octubre, Hilbck tiene 20.35% y Somos Perú, 15.34%. En Sullana que es una plaza fuerte, se tiene 19.59% y Santiago Paz llega a 12.14%, asimismo, en Chulucanas, Hilbck logra 17.4% y Somos Perú 9.87%”, mencionó. Agrega que este respaldo de Hilbck en las provincias y distritos se refleja en sus candidatos para estas jurisdicciones. Un segundo factor, sostiene, es el respaldo de la maquinaria electoral de un partido como Alianza para el Progreso (APP). “Ese porcentaje es coherente porque sus candidatos provinciales y también distritales ganan, además que la maquinaria electoral que se percibe en la región”, agregó. Somos Perú Sobre Santiago Paz de Somos Perú que marcha en segundo lugar con 13.7%, el gerente de ICSI Perú sostuvo que no le va bien con sus candidatos en Piura, Castilla, Veintiséis de Octubre, Tambogrande o Sullana. “En el caso Chulucanas, como distrito capital, el candidato Nelson Mío que hace un mes era fuerte, ha tenido un descenso porque ahí han ingresado candidatos nuevos como Hernán Pasapera de Renovación y Manuel Cueva de Podemos. Eso le ha restado fuerza a Somos Perú”, aseveró. Sobre Mártires Lizana de Fuerza Popular que marcha tercero, Vegas destaca que esto ocurre por la aceptación del candidato a la provincia de Piura, Martín Olivares, que está segundo en la preferencial provincial. Nulos En el estudio también se revela que un 18% de los encuestados no votaría por ninguno de los postulantes o lo haría en blanco. “Esto puede variar producto de la campaña y contracampaña. Aquí quien tiene mejor equipo de contracampaña es el que tiene mayor ventaja de ganar. Es quien reacciona rápido, de forma contundente y demoledora. No siempre la percepción es la verdad, por eso una contracampaña tiene que responderse de manera rápida y contundente. No se trata del mejor indudablemente, sino de quien cometa menos errores y sepa responder a los ataques fundados o infundados”, destacó.n</t>
+          <t>La Institución Educativa San Ramón de Chulucanas, representante de la UGEL Chulucanas , obtuvo el primer lugar en el Regional Singing Festival 2026 “Singing for a Better World”, organizado por la Dirección Regional de Educación de Piura. PUEDES LEER ► Sobrevive tras 10 días sepultada por el lodo y es rescatada cuando su familia ya la había dado por muerta La actividad se desarrolló en el parque Néstor Martos de Piura y reunió a estudiantes representantes de las 12 UGEL de la región, quienes demostraron sus habilidades en la interpretación de canciones en inglés. El festival tiene como finalidad fortalecer las competencias comunicativas en el idioma inglés, además de promover la creatividad, la expresión artística y la participación de los estudiantes. La iniciativa se desarrolla en concordancia con el Currículo Nacional de la Educación Básica. Durante sus presentaciones, los participantes también transmitieron mensajes relacionados con valores y actitudes que contribuyen a una convivencia democrática, respetuosa, inclusiva y solidaria. San Ramón conquistó el primer lugar La IE San Ramón logró imponerse en la competencia con la interpretación de la canción “Hand for Chulucanas”, presentación que le permitió quedarse con el primer puesto del festival regional. El segundo lugar fue para la IE Libertadores de América, representante de la UGEL La Unión, que participó con la canción “The Song of Tomorrow”. Mientras que el tercer puesto correspondió a la IE César Vallejo, de la UGEL Morropón, con la interpretación de “Brighter Than Before”. La competencia comenzó en cada institución educativa y posteriormente continuó en las diferentes etapas de las 12 UGEL de Piura: Ayabaca, Chulucanas, Huancabamba, Huarmaca, La Unión, Morropón, Paita, Piura, Sechura, Sullana, Talara y Tambogrande. Además de impulsar el aprendizaje del inglés, el festival busca fortalecer la sana competencia, el trabajo en equipo y la integración entre estudiantes de diferentes provincias de la región.</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>https://eltiempo.pe/local/asi-van-los-candidatos-a-falta-de-un-mes-para-elecciones/</t>
+          <t>https://eltiempo.pe/local/i-e-san-ramon-de-chulucanas-se-consagra-campeona-del-regional-singing-festival-2026/</t>
         </is>
       </c>
     </row>
@@ -1302,17 +1302,17 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Miniván queda al borde de un abismo en la carretera Canchaque -Huancabamba</t>
+          <t>Así van los candidatos a falta de un mes para elecciones</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Unos 12 pasajeros se salvaron de caer a un abismo de aproximadamente 200 metros luego de que una miniván de una empresa de transporte sufriera un accidente en la carretera Canchaque-Huancabamba, en el sector Las Minas. Según información preliminar, la unidad terminó volcada y quedó peligrosamente cerca del precipicio, generando momentos de angustia entre los pasajeros, entre ellos algunos menores de edad, quienes temieron lo peor. Pese a la violencia del accidente, los ocupantes solo habrían sufrido algunos golpes, además del fuerte susto provocado por el incidente. Hasta el momento no se han reportado oficialmente personas con lesiones de consideración. EL EQUIPAJE El accidente también ocasionó la caída de algunos equipajes que eran transportados en la parte superior de la miniván, los cuales algunos habrían terminado en el fondo del abismo. De acuerdo con versiones preliminares, no se descarta que el vehículo haya sufrido algún desperfecto mecánico antes de producirse el accidente. Sin embargo, esta posibilidad deberá ser determinada mediante las investigaciones correspondientes. Asimismo, las autoridades realizan las diligencias para establecer las causas exactas del siniestro y determinar las condiciones en las que circulaba la unidad. Cabe mencionar que el hecho vuelve a poner en evidencia el peligro de transitar por esta vía, caracterizada por sus pronunciadas pendientes y zonas de profundo precipicio.</t>
+          <t>ICSI Perú hizo una encuesta y revela cómo van las preferencias de los piuranos sobre su próximo gobernador y alcaldes. PUEDES LEER ► Miniván queda al borde de un abismo en la carretera Canchaque -Huancabamba Las elecciones regionales y municipales están a la vuelta de la esquina y lo único seguro es que sí o sí habrá una segunda vuelta para el cargo de gobernador regional. De acuerdo a ley, si ninguna lista supera el 30% de votos válidos, se convoca a una segunda vuelta entre los dos primeros del escrutinio. De acuerdo a la última encuesta de la empresa ICSI Perú ninguno de los aspirantes a la máxima autoridad regional llega al 30% de las preferencias. Según el estudio de opinión pública, el primer lugar es para el exgobernador Reynaldo Hilbck (Alianza para el Progreso) con 22.5%; seguido por Santiago Paz (Somos Perú) con 13.7% ; Mártires Lizana (Fuerza Popular) con 11.1% y Guillermo La Torre (Podemos Perú) con 10.9%. En el caso de los candidatos provinciales, la disputa parece más reñida y la diferencia de porcentajes es más ajustada entre los aspirantes, con lo cual la campaña de aquí hasta el domingo 4 de octubre será una competencia voto a voto y de convencimiento de los indecisos. Gobierno Regional Sobre el tema, el gerente de ICSI Perú, Mauro Vegas Carmen , consideró que uno de los factores del respaldo a Hilbck son sus candidatos en las provincias con mayor caudal electoral de votos. “En los resultados de los 27 distritos a donde se ha ido, Hilbck alcanza la mayor votación en Piura, Veintiséis de Octubre, Catacaos, Sullana, Morropón, Chulucanas, Talara, Órganos y otros. Todo eso le da ese porcentaje que ahora ha sacado frente al segundo. Por ejemplo, en Piura tiene 19.66% y Somos Perú tiene 15.33%; en Castilla, Hilbck tiene 13.60% y Somos Perú unos 10.90% y en Veintiséis de Octubre, Hilbck tiene 20.35% y Somos Perú, 15.34%. En Sullana que es una plaza fuerte, se tiene 19.59% y Santiago Paz llega a 12.14%, asimismo, en Chulucanas, Hilbck logra 17.4% y Somos Perú 9.87%”, mencionó. Agrega que este respaldo de Hilbck en las provincias y distritos se refleja en sus candidatos para estas jurisdicciones. Un segundo factor, sostiene, es el respaldo de la maquinaria electoral de un partido como Alianza para el Progreso (APP). “Ese porcentaje es coherente porque sus candidatos provinciales y también distritales ganan, además que la maquinaria electoral que se percibe en la región”, agregó. Somos Perú Sobre Santiago Paz de Somos Perú que marcha en segundo lugar con 13.7%, el gerente de ICSI Perú sostuvo que no le va bien con sus candidatos en Piura, Castilla, Veintiséis de Octubre, Tambogrande o Sullana. “En el caso Chulucanas, como distrito capital, el candidato Nelson Mío que hace un mes era fuerte, ha tenido un descenso porque ahí han ingresado candidatos nuevos como Hernán Pasapera de Renovación y Manuel Cueva de Podemos. Eso le ha restado fuerza a Somos Perú”, aseveró. Sobre Mártires Lizana de Fuerza Popular que marcha tercero, Vegas destaca que esto ocurre por la aceptación del candidato a la provincia de Piura, Martín Olivares, que está segundo en la preferencial provincial. Nulos En el estudio también se revela que un 18% de los encuestados no votaría por ninguno de los postulantes o lo haría en blanco. “Esto puede variar producto de la campaña y contracampaña. Aquí quien tiene mejor equipo de contracampaña es el que tiene mayor ventaja de ganar. Es quien reacciona rápido, de forma contundente y demoledora. No siempre la percepción es la verdad, por eso una contracampaña tiene que responderse de manera rápida y contundente. No se trata del mejor indudablemente, sino de quien cometa menos errores y sepa responder a los ataques fundados o infundados”, destacó.n</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>https://eltiempo.pe/local/minivan-queda-al-borde-de-un-abismo-en-la-carretera-canchaque-huancabamba/</t>
+          <t>https://eltiempo.pe/local/asi-van-los-candidatos-a-falta-de-un-mes-para-elecciones/</t>
         </is>
       </c>
     </row>
@@ -1327,17 +1327,17 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Fiesta termina con una mujer fallecida</t>
+          <t>Miniván queda al borde de un abismo en la carretera Canchaque -Huancabamba</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Una fiesta terminó en tragedia en la urbanización Las Casuarinas II Etapa, en el distrito Veintiséis de Octubre , luego de que una joven de nacionalidad colombiana perdiera la vida tras caer desde un tragaluz del tercer piso de un inmueble hacia el segundo nivel. La víctima fue identificada como Juliet Alisson Zambrano Fino, de 21 años de edad. PUEDES LEER ► FEN asusta a la banca privada El hecho ocurrió durante una reunión social y las circunstancias de la caída son materia de investigación por parte de la Policía. De acuerdo con información preliminar, una de las hipótesis que manejan las autoridades es que la joven habría sido presuntamente arrojada por un tragaluz, desde donde terminó cayendo hasta el segundo piso del inmueble. Sin embargo, esta versión todavía deberá ser corroborada mediante las diligencias policiales, pericias y demás elementos que permitan determinar qué ocurrió exactamente antes de la caída. SIN SIGNOS VITALES Tras conocerse el hecho, personal de Serenazgo del distrito Veintiséis de Octubre y una ambulancia del SAMU Piura llegaron hasta el lugar de la tragedia para brindar atención a la víctima. No obstante, los equipos de emergencia encontraron a la joven sin signos vitales. En el lugar también se encontraba un ciudadano extranjero, quien, visiblemente afectado y entre lágrimas, solicitaba ayuda para la mujer. RECOPILAN INFORMACIÓN Agentes de la Policía Nacional acudieron posteriormente a la escena para realizar las primeras diligencias, verificar las condiciones del inmueble y recopilar información que permita reconstruir los momentos previos y posteriores al fatal incidente. Las autoridades deberán determinar si la caída se produjo accidentalmente o si existió la intervención de otra persona. Para ello, se vienen recogiendo testimonios de quiénes participaron en la fiesta y de otros posibles testigos, además de realizarse las pericias correspondientes. El cuerpo de Juliet Alisson Zambrano Fino fue trasladado a la morgue de Piura, donde se realizarán los procedimientos establecidos por ley. INVESTIGACIONES Mientras avanzan las investigaciones, el caso ha generado preocupación entre los vecinos de Las Casuarinas. La Policía busca establecer las circunstancias exactas de la muerte y, de corresponder, identificar a los responsables y determinar las responsabilidades que establezca la investigación.</t>
+          <t>Unos 12 pasajeros se salvaron de caer a un abismo de aproximadamente 200 metros luego de que una miniván de una empresa de transporte sufriera un accidente en la carretera Canchaque-Huancabamba, en el sector Las Minas. Según información preliminar, la unidad terminó volcada y quedó peligrosamente cerca del precipicio, generando momentos de angustia entre los pasajeros, entre ellos algunos menores de edad, quienes temieron lo peor. Pese a la violencia del accidente, los ocupantes solo habrían sufrido algunos golpes, además del fuerte susto provocado por el incidente. Hasta el momento no se han reportado oficialmente personas con lesiones de consideración. EL EQUIPAJE El accidente también ocasionó la caída de algunos equipajes que eran transportados en la parte superior de la miniván, los cuales algunos habrían terminado en el fondo del abismo. De acuerdo con versiones preliminares, no se descarta que el vehículo haya sufrido algún desperfecto mecánico antes de producirse el accidente. Sin embargo, esta posibilidad deberá ser determinada mediante las investigaciones correspondientes. Asimismo, las autoridades realizan las diligencias para establecer las causas exactas del siniestro y determinar las condiciones en las que circulaba la unidad. Cabe mencionar que el hecho vuelve a poner en evidencia el peligro de transitar por esta vía, caracterizada por sus pronunciadas pendientes y zonas de profundo precipicio.</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>https://eltiempo.pe/local/fiesta-termina-con-una-mujer-fallecida/</t>
+          <t>https://eltiempo.pe/local/minivan-queda-al-borde-de-un-abismo-en-la-carretera-canchaque-huancabamba/</t>
         </is>
       </c>
     </row>
@@ -1352,17 +1352,17 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Choque de autos derriba poste</t>
+          <t>Fiesta termina con una mujer fallecida</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Un violento accidente de tránsito entre dos automóviles se registró ayer en horas de la mañana en la avenida Universitaria de Piura, a la altura del Fundo Vite. PUEDES LEER ► “Monstruo de las 10 cabezas” Según información preliminar, uno de los vehículos tras el choque habría también impactado contra un poste que no sería de tendido eléctrico, provocando que la estructura se desplomara y terminara cayendo sobre el otro automóvil. Los vehículos permanecieron en la zona del accidente, mientras efectivos de la Policía Nacional acudieron para realizar las diligencias correspondientes y determinar las circunstancias en que ocurrió el hecho. Hasta el cierre de edición, no se informó oficialmente sobre personas heridas como consecuencia del accidente. Cabe mencionar que el accidente generó preocupación entre los conductores que transitaban por este importante tramo de la avenida Universitaria.</t>
+          <t>Una fiesta terminó en tragedia en la urbanización Las Casuarinas II Etapa, en el distrito Veintiséis de Octubre , luego de que una joven de nacionalidad colombiana perdiera la vida tras caer desde un tragaluz del tercer piso de un inmueble hacia el segundo nivel. La víctima fue identificada como Juliet Alisson Zambrano Fino, de 21 años de edad. PUEDES LEER ► FEN asusta a la banca privada El hecho ocurrió durante una reunión social y las circunstancias de la caída son materia de investigación por parte de la Policía. De acuerdo con información preliminar, una de las hipótesis que manejan las autoridades es que la joven habría sido presuntamente arrojada por un tragaluz, desde donde terminó cayendo hasta el segundo piso del inmueble. Sin embargo, esta versión todavía deberá ser corroborada mediante las diligencias policiales, pericias y demás elementos que permitan determinar qué ocurrió exactamente antes de la caída. SIN SIGNOS VITALES Tras conocerse el hecho, personal de Serenazgo del distrito Veintiséis de Octubre y una ambulancia del SAMU Piura llegaron hasta el lugar de la tragedia para brindar atención a la víctima. No obstante, los equipos de emergencia encontraron a la joven sin signos vitales. En el lugar también se encontraba un ciudadano extranjero, quien, visiblemente afectado y entre lágrimas, solicitaba ayuda para la mujer. RECOPILAN INFORMACIÓN Agentes de la Policía Nacional acudieron posteriormente a la escena para realizar las primeras diligencias, verificar las condiciones del inmueble y recopilar información que permita reconstruir los momentos previos y posteriores al fatal incidente. Las autoridades deberán determinar si la caída se produjo accidentalmente o si existió la intervención de otra persona. Para ello, se vienen recogiendo testimonios de quiénes participaron en la fiesta y de otros posibles testigos, además de realizarse las pericias correspondientes. El cuerpo de Juliet Alisson Zambrano Fino fue trasladado a la morgue de Piura, donde se realizarán los procedimientos establecidos por ley. INVESTIGACIONES Mientras avanzan las investigaciones, el caso ha generado preocupación entre los vecinos de Las Casuarinas. La Policía busca establecer las circunstancias exactas de la muerte y, de corresponder, identificar a los responsables y determinar las responsabilidades que establezca la investigación.</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>https://eltiempo.pe/local/choque-de-autos-derriba-poste/</t>
+          <t>https://eltiempo.pe/local/fiesta-termina-con-una-mujer-fallecida/</t>
         </is>
       </c>
     </row>
@@ -1377,17 +1377,17 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>FEN asusta a la banca privada</t>
+          <t>Choque de autos derriba poste</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>El impacto del Fenómeno El Niño (FEN) en el terreno económico también se sentirá en los créditos a las pequeñas y medianas empresas relacionadas a los sectores primarios de la economía como son la pesca y agricultura. PUEDES LEER ► ProInversión y Marina de Guerra evaluarán proyectos de inversión privada sobre terrenos y bienes navales De acuerdo a los especialistas consultados, algunas empresas financieras podrían reforzar sus criterios para el otorgamiento de préstamos a los pequeños empresarios, con la finalidad de prevenir problemas de morosidad. “Los créditos asociados a personas que se desempeñan en esos sectores van a tener probablemente dificultades para afrontar sus deudas. Eso es algo que ya vimos en períodos pasados del FEN como en el 2023 y 2017” , comentó Stephani Maita, economista senior del Instituto Peruano de Economía (IPE). Explica que el impacto del FEN en el agro y pesca se relaciona en un primer momento con la pérdida del empleo. “Un tercio del empleo total en la región está vinculado al sector agrícola entonces las familias que tengan actividades vinculadas a este sector y tengan préstamos probablemente van a tener dificultades para afrontar sus deudas. Lo mismo con las empresas. A esto también se va el efecto por los precios al alza. Potencialmente podría terminar afectando la calidad de las carteras de créditos ”, enfatizó. Expectativas De otro lado, Maita señala que pese a la amenaza del fenómeno natural que se avecina, todavía hay expectativas positivas en la economía nacional. “El Banco Central de Reserva publicó una encuesta de perspectivas sobre el mercado de créditos tanto desde el lado de la oferta, es decir la perspectiva de los bancos y entidades financieras, como desde la demanda que es más desde los usuarios que solicitan los créditos. Por el lado de la demanda se encontraba que la perspectiva era favorable en la medida que la actividad económica en general, mas allá de los sectores primarios, goza de salud y está creciendo de forma importante”, aseveró Maita. Sin embargo, por el lado de las empresas existe un mayo grado de cautela sobre a quién le otorgan los préstamos con la finalidad de evitar el aumento de la morosidad. “Las empresas ya están previendo reforzar algunos criterios para otorgar créditos considerando los eventos climáticos que van a afectar, probablemente, en mayor medida los segmentos de las carteras más pequeñas, hablamos de microempresas, medianas y pequeñas empresas, las cuales son las que han registrado las mayores dificultades para afrontar sus créditos en el pasado”, manifestó Maita. Criterios Desde su punto de vista los nuevos requisitos implica un examen más exhaustivo del cliente que llega a solicitar el financiamiento. “Se refiere a otorgar créditos de menor tamaño, con plazos más extensos para que las cuotas sean un poco más pequeñas o quizás hacer una evaluación más minuciosa respecto de los ingresos de las empresas o que tanta exposición tienen a este tipo de fenómenos dependiendo de las actividades en las que se desempeñan. Por ejemplo, una empresa dedicada a la agroexportación probablemente será mucho más golpeada por el fenómeno climático frente a una empresa de transporte. Igual esta última va a sufrir algunos estragos por las lluvias, pero ese impacto es considerablemente menor frente a una empresa que se desempeña en agricultura. Agrega que en este punto los bancos tienden a elegir un poco mejor o cambiar un poco sus decisiones de dación de créditos para evitar exponerse a potenciales impagos.</t>
+          <t>Un violento accidente de tránsito entre dos automóviles se registró ayer en horas de la mañana en la avenida Universitaria de Piura, a la altura del Fundo Vite. PUEDES LEER ► “Monstruo de las 10 cabezas” Según información preliminar, uno de los vehículos tras el choque habría también impactado contra un poste que no sería de tendido eléctrico, provocando que la estructura se desplomara y terminara cayendo sobre el otro automóvil. Los vehículos permanecieron en la zona del accidente, mientras efectivos de la Policía Nacional acudieron para realizar las diligencias correspondientes y determinar las circunstancias en que ocurrió el hecho. Hasta el cierre de edición, no se informó oficialmente sobre personas heridas como consecuencia del accidente. Cabe mencionar que el accidente generó preocupación entre los conductores que transitaban por este importante tramo de la avenida Universitaria.</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>https://eltiempo.pe/local/fen-asusta-a-la-banca-privada/</t>
+          <t>https://eltiempo.pe/local/choque-de-autos-derriba-poste/</t>
         </is>
       </c>
     </row>
@@ -1402,17 +1402,17 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>“Monstruo de las 10 cabezas”</t>
+          <t>FEN asusta a la banca privada</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>En la carrera contra el tiempo para ejecutar las actividades que aminoren el impacto del Fenómeno El Niño (FEN) , la región se enfrenta a otro enemigo. Se trata del propio Estado y la complejidad de sus instituciones, procesos y competencias que hacen mucho más lenta la respuesta a la emergencia. PUEDES LEER ► Callao: joven de 20 años es asesinado a balazos en el distrito de Mi Perú “La situación de desorden que tenemos en el Estado es como decir que tenemos un monstruo de 10 cabezas. Está lo que maneja Veintiséis de Octubre, lo que maneja la Municipalidad de Piura o el Ministerio de Vivienda, cuando debería haber una sola cabeza en el control de inundaciones y de nuestras cuencas [Luego] tenemos el proyecto Alto Piura y el proyecto Chira Piura que manejan la jurisdicción de estas dos cuencas con el ANA (Autoridad Nacional del Agua) como ente rector. [También] tuvimos la Autoridad para la Reconstrucción con Cambios (ARCC) que evaluaba un plan maestro”, aseveró la senadora de Piura, Karla Schaefer. Otra muestra del problema de esta gran burocracia, señala, es que luego se creó la Autoridad Nacional de Infraestructura (ANIN) que también tiene fichas de intervención de diferentes puntos críticos. “Y esas benditas competencias que no te dejan [trabajar] y todos se mueren de miedo de firmar un documento por la Contraloría [...] Por ejemplo, el alcalde de Veintiséis de Octubre tiene una situación compleja con el dren Maldonado y que podría dejar incomunicado a 60 mil personas de un lado a otro. Se pidió el apoyo a Transportes, como una de las alternativas, que tiene puentes Baileys, aún esperamos respuesta. [...] Este es un tema que el decreto de urgencia nos debería dejar actuar y que no permitan que los empresarios, que hace dos semanas están esperando este documento, luego se vean entrampados” , consideró. Reunión Schaefer brindó estas declaraciones este martes en la primera sesión descentralizada del Consejo Directivo Descentralizado Macro Región Norte que agrupa a las empresas asociadas a la Confiep (Confederación Nacional de Instituciones Empresariales Privadas), que desean apoyar a las actividades de mitigación contra El Niño. Parte de este problema también fue expuesto por el presidente de la Confiep, Jorge Zapata , quien destacó que las empresas privadas podrían invertir unos 4 mil millones de sus impuestos en Piura bajo una modalidad abreviada de obras por impuestos Se trata de servicios por impuestos que todavía no existe porque debe aprobarse el decreto supremo para que las empresas privadas tengan marco legal para intervenir en Chutuque, cuencas ciegas u otros puntos críticos. “Pi ura cuenta con 4 mil 352 millones de soles bajo la modalidad de obras o servicios por impuestos. Tenemos la plata y no somos capaces de solucionar los temas. No es un tema de dinero y hace mucho tiempo lo venimos diciendo. Los privados ya están haciendo el esfuerzo necesario; ya hemos visto donaciones de varias empresas; la Sociedad Nacional de Minería está evaluando la apertura del canal de Chutuque, pero hay un detalle mínimo y que parece absurdo, sobre a quién se va a contratar para la información de la ficha técnica [de Chutuque]. Tenemos que ponernos de acuerdo en un detalle mínimo cuando tenemos 18 mil millones de soles por ejecutar”, destacó. Zapata mencionó esto en relación a la ficha técnica que hace falta para intervenir en los 6 kilómetros del canal Chutuque mediante explosivos. La ANA señala que no hay información, mientras que desde la Cámara de Comercio se indica que esta información la posee el ingeniero César Alvarado. Alvarado es el especialista y autor de la primera versión del Plan Integral de Manejo del Río Piura que contrató la desaparecida Autoridad para la Reconstrucción con Cambios (ARCC), la cual nació luego de la inundación del 2017.</t>
+          <t>El impacto del Fenómeno El Niño (FEN) en el terreno económico también se sentirá en los créditos a las pequeñas y medianas empresas relacionadas a los sectores primarios de la economía como son la pesca y agricultura. PUEDES LEER ► ProInversión y Marina de Guerra evaluarán proyectos de inversión privada sobre terrenos y bienes navales De acuerdo a los especialistas consultados, algunas empresas financieras podrían reforzar sus criterios para el otorgamiento de préstamos a los pequeños empresarios, con la finalidad de prevenir problemas de morosidad. “Los créditos asociados a personas que se desempeñan en esos sectores van a tener probablemente dificultades para afrontar sus deudas. Eso es algo que ya vimos en períodos pasados del FEN como en el 2023 y 2017” , comentó Stephani Maita, economista senior del Instituto Peruano de Economía (IPE). Explica que el impacto del FEN en el agro y pesca se relaciona en un primer momento con la pérdida del empleo. “Un tercio del empleo total en la región está vinculado al sector agrícola entonces las familias que tengan actividades vinculadas a este sector y tengan préstamos probablemente van a tener dificultades para afrontar sus deudas. Lo mismo con las empresas. A esto también se va el efecto por los precios al alza. Potencialmente podría terminar afectando la calidad de las carteras de créditos ”, enfatizó. Expectativas De otro lado, Maita señala que pese a la amenaza del fenómeno natural que se avecina, todavía hay expectativas positivas en la economía nacional. “El Banco Central de Reserva publicó una encuesta de perspectivas sobre el mercado de créditos tanto desde el lado de la oferta, es decir la perspectiva de los bancos y entidades financieras, como desde la demanda que es más desde los usuarios que solicitan los créditos. Por el lado de la demanda se encontraba que la perspectiva era favorable en la medida que la actividad económica en general, mas allá de los sectores primarios, goza de salud y está creciendo de forma importante”, aseveró Maita. Sin embargo, por el lado de las empresas existe un mayo grado de cautela sobre a quién le otorgan los préstamos con la finalidad de evitar el aumento de la morosidad. “Las empresas ya están previendo reforzar algunos criterios para otorgar créditos considerando los eventos climáticos que van a afectar, probablemente, en mayor medida los segmentos de las carteras más pequeñas, hablamos de microempresas, medianas y pequeñas empresas, las cuales son las que han registrado las mayores dificultades para afrontar sus créditos en el pasado”, manifestó Maita. Criterios Desde su punto de vista los nuevos requisitos implica un examen más exhaustivo del cliente que llega a solicitar el financiamiento. “Se refiere a otorgar créditos de menor tamaño, con plazos más extensos para que las cuotas sean un poco más pequeñas o quizás hacer una evaluación más minuciosa respecto de los ingresos de las empresas o que tanta exposición tienen a este tipo de fenómenos dependiendo de las actividades en las que se desempeñan. Por ejemplo, una empresa dedicada a la agroexportación probablemente será mucho más golpeada por el fenómeno climático frente a una empresa de transporte. Igual esta última va a sufrir algunos estragos por las lluvias, pero ese impacto es considerablemente menor frente a una empresa que se desempeña en agricultura. Agrega que en este punto los bancos tienden a elegir un poco mejor o cambiar un poco sus decisiones de dación de créditos para evitar exponerse a potenciales impagos.</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>https://eltiempo.pe/local/monstruo-de-las-10-cabezas/</t>
+          <t>https://eltiempo.pe/local/fen-asusta-a-la-banca-privada/</t>
         </is>
       </c>
     </row>

--- a/Data/Piura/noticias_piura_20260904_20260911.xlsx
+++ b/Data/Piura/noticias_piura_20260904_20260911.xlsx
@@ -470,17 +470,17 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Piura ya registra temperaturas máximas: Niño Costero entra en fase extraordinaria</t>
+          <t>Reportan 68 escolares intoxicados tras fumigación en colegio de Sullana</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>El Servicio Nacional de Meteorología e Hidrología del Perú (Senamhi) informó que El Niño Costero ingresó a una fase extraordinaria debido al incremento de la temperatura superficial del mar frente al litoral peruano y por la cual urge la ejecución de los proyectos para mitigar el impacto del fenómeno natural. El especialista del Senamhi, Nelson Quispe, informó que Tumbes, Piura, Lambayeque y La Libertad ya registran temperaturas máximas de hasta 37 °C, valores superiores a los habituales para esta época. El especialista explicó que el calentamiento del mar y la proximidad de la primavera, que comenzará el 22 de setiembre, serán otros de los factores que contribuirán al incremento del calor. Advierten que el escenario podría intensificarse durante los próximos meses. El Senamhi estima que las temperaturas en la costa norte continuarán aumentando y podrían bordear los 40 °C en febrero y marzo de 2027. LLUVIAS Y VIENTOS Respecto a las lluvias, el Senamhi precisó que todavía no se presentan precipitaciones intensas asociadas a esta fase del fenómeno. Asimismo informaron que entre el sábado y domingo se registrará un incremento de la velocidad del viento a lo largo de la costa, de moderada intensidad. “Este fenómeno podría generar levantamiento de polvo y arena, así como la reducción de la visibilidad horizontal”, refiere parte del aviso meteorológico regional N° 162, con lo cual se deberán tomar las precauciones del caso.</t>
+          <t>Una masiva intoxicación se registró en la institución educativa “Rosa Cardó de Guarderas”, ubicada en el centro poblado de Mallares, distrito de Marcavelica, luego de que 68 escolares presentaran síntomas como vómitos, dificultad para respirar, náuseas. El día anterior, el plantel había sido fumigado en su totalidad para prevenir el dengue, sin embargo, las autoridades de salud indicaron que esperarán los reportes para conocer la causa. La mañana de ayer, al ingresar a las aulas, principalmente a los ambientes prefabricados donde reciben clases alumnos de primero y segundo grado de secundaria, varios escolares comenzaron a presentar mareos, náuseas, vómitos y escozor en diferentes partes del cuerpo. Ante la aparición de los primeros casos, los estudiantes fueron evacuados hacia la posta de salud de Mallares. Sin embargo, conforme transcurrían las horas, el número de afectados fue aumentando e incluso algunos alumnos del nivel primario comenzaron a presentar síntomas similares. El personal del establecimiento de salud activó la atención de emergencia y coordinó con la Subregión de Salud Luciano Castillo Colonna y la Microred de Marcavelica para reforzar la atención. Hasta Mallares fueron enviadas brigadas y carpas y una ambulancia más para atender a los escolares y afrontar la contingencia. La emergencia pudo ser controlada después de la 1 de la tarde. Según la información proporcionada, no se registraron casos de gravedad. Un estudiante fue trasladado al hospital de EsSalud a pedido de sus padres.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>https://eltiempo.pe/local/piura-ya-registra-temperaturas-maximas-nino-costero-entra-en-fase-extraordinaria/</t>
+          <t>https://eltiempo.pe/local/reportan-68-escolares-intoxicados-tras-fumigacion-en-colegio-de-sullana/</t>
         </is>
       </c>
     </row>
@@ -495,17 +495,17 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Contraloría: Obra recién culminada presenta signos de deterioro prematuro en Universidad Nacional de Frontera</t>
+          <t>Piura ya registra temperaturas máximas: Niño Costero entra en fase extraordinaria</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>La Contraloría General de la República (CGR) evidenció que la obra de ampliación del servicio de aulas de la facultad de Ingeniería Económica de la Universidad Nacional de Frontera, en la provincia de Sullana, presenta signos de deterioro prematuro pese a que los trabajos fueron recibidos en enero de este año. Esta situación genera el riesgo de afectar la calidad, operatividad y vida útil de este proyecto que tiene una inversión superior a los S/ 14 millones. En el Informe de Hito de Control n.° 11384-2026-CG/GRPI-SCC (periodo de evaluación del 12 al 18 de agosto de 2026), se identificaron diversas deficiencias en la infraestructura de los bloques I-A, I-B y II, entre ellas, puertas de madera desniveladas, falta de agua en inodoros y lavatorios, y tapajuntas de acero inoxidable con fijación deficiente en juntas de dilatación. En los servicios higiénicos del cuarto piso se constató que algunos inodoros permanecen inoperativos por falla en el sistema de abastecimiento de agua, mientras que el lavamanos destinado a personas con discapacidad presenta insuficiente presión. Además, se observaron aberturas en los tapajuntas que podrían facilitar el ingreso de humedad, residuos y agentes contaminantes. También se detectaron problemas en ambientes administrativos y académicos: una de las cuatro unidades evaporadoras del sistema de aire acondicionado de la sala de cómputo se encuentra inoperativa y varios lavatorios no cuentan con flujo de agua. En la sala de impresiones se verificó el desprendimiento de una baldosa del techo que dejó un sensor de humo suspendido por sus cables, además de evidencias de humedad y moho. En la actual área de grados y títulos y responsabilidad social se constató la ausencia de una puerta de vidrio, situación que deja expuestos equipos, mobiliario y documentación. A ello se suman el desprendimiento y agrietamiento del sellador de una escalera de madera, deformaciones en elementos de la pérgola en una plazoleta y tapas de concreto de canaletas pluviales deterioradas y desalineadas, generando riesgos para los usuarios. Asimismo, se constató que el ascensor del pabellón permanece fuera de servicio, pese a que la Unidad Ejecutora de Inversiones había requerido al contratista la subsanación de la falla en el marco de la garantía de obra y posteriormente realizó gestiones para evaluar técnicamente el problema. La inoperatividad del equipo obliga a estudiantes, docentes y personal a utilizar exclusivamente las escaleras y constituye una barrera crítica para las personas con movilidad reducida o discapacidad. Durante la inspección se verificó una diferencia entre los equipos adquiridos para el proyecto y los encontrados físicamente en el pabellón de la Facultad de Ingeniería Económica. De los 26 monitores con procesador integrado previstos para el proyecto, solo 12 fueron ubicados, uno en cada una de las aulas. Del mismo modo, se constató que únicamente ocho equipos cuentan con actas de entrega al área usuaria, pese a que la documentación de la entidad acredita la adquisición de los 26 monitores. Esta situación genera el riesgo de que 14 equipos no estén siendo utilizados para el fin para el cual fueron adquiridos, se encuentren en desuso o incluso se haya producido su pérdida. La obra se inició en noviembre de 2023 y debió culminar al siguiente año. Recién en enero de este año se suscribió el acta de recepción. El informe fue notificado al titular de la entidad para que adopte las acciones que correspondan, en el marco de sus competencias y obligaciones en la gestión institucional.</t>
+          <t>El Servicio Nacional de Meteorología e Hidrología del Perú (Senamhi) informó que El Niño Costero ingresó a una fase extraordinaria debido al incremento de la temperatura superficial del mar frente al litoral peruano y por la cual urge la ejecución de los proyectos para mitigar el impacto del fenómeno natural. El especialista del Senamhi, Nelson Quispe, informó que Tumbes, Piura, Lambayeque y La Libertad ya registran temperaturas máximas de hasta 37 °C, valores superiores a los habituales para esta época. El especialista explicó que el calentamiento del mar y la proximidad de la primavera, que comenzará el 22 de setiembre, serán otros de los factores que contribuirán al incremento del calor. Advierten que el escenario podría intensificarse durante los próximos meses. El Senamhi estima que las temperaturas en la costa norte continuarán aumentando y podrían bordear los 40 °C en febrero y marzo de 2027. LLUVIAS Y VIENTOS Respecto a las lluvias, el Senamhi precisó que todavía no se presentan precipitaciones intensas asociadas a esta fase del fenómeno. Asimismo informaron que entre el sábado y domingo se registrará un incremento de la velocidad del viento a lo largo de la costa, de moderada intensidad. “Este fenómeno podría generar levantamiento de polvo y arena, así como la reducción de la visibilidad horizontal”, refiere parte del aviso meteorológico regional N° 162, con lo cual se deberán tomar las precauciones del caso.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>https://eltiempo.pe/local/contraloria-obra-recien-culminada-presenta-signos-de-deterioro-prematuro-en-universidad-nacional-de-frontera/</t>
+          <t>https://eltiempo.pe/local/piura-ya-registra-temperaturas-maximas-nino-costero-entra-en-fase-extraordinaria/</t>
         </is>
       </c>
     </row>
@@ -520,17 +520,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Más de 4 mil casos de violencia contra mujeres y familiares genera preocupación en Piura</t>
+          <t>Contraloría: Obra recién culminada presenta signos de deterioro prematuro en Universidad Nacional de Frontera</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>La violencia contra las mujeres y los integrantes del grupo familiar mantiene cifras preocupantes en Piura . Entre enero y julio de 2026, los Centros Emergencia Mujer (CEM) de la región atendieron 4,578 casos de violencia , de acuerdo con el último reporte del Programa Nacional Warmi Ñan del Ministerio de la Mujer y Poblaciones Vulnerables (MIMP). La cifra representa un incremento considerable respecto al reporte acumulado hasta junio, cuando se registraban 3,272 casos. En solo un mes se sumaron 1,306 nuevas atenciones, lo que evidencia la magnitud del problema que enfrentan mujeres, niñas, niños, adolescentes y otros integrantes de las familias en diferentes provincias de la región. Según el Programa Nacional Warmi Ñan , los CEM son servicios públicos especializados y gratuitos que brindan atención psicológica, social y legal a personas afectadas por hechos de violencia. Consulta aquí la información oficial de Warmi Ñan sobre los Centros Emergencia Mujer . Piura concentra la mayor cantidad de casos de violencia La provincia de Piura concentra la mayor cantidad de atenciones reportadas en la región, con 2,580 casos entre enero y julio. La distribución muestra que las situaciones de violencia llegan a diferentes puntos de atención y no se concentran únicamente en una institución. La comisaría de Piura atendió 735 víctimas, mientras que el centro de salud Santa Julia registró 547 casos. A estos se suman 435 atenciones en la comisaría de familia, 236 en la comisaría rural de Tambogrande, 231 en Catacaos, 208 en La Unión y 188 correspondientes al distrito de Piura. Después de la provincia de Piura aparecen Sullana, con 436 casos; Paita, con 420; Ayabaca, con 359; Talara, con 256; Morropón, con 252; Sechura, con 163; y Huancabamba, con 112 casos . ¿Quiénes son los principales afectados por la violencia en Piura? Del total de 4,578 casos atendidos en los primeros siete meses del año, 4,015 corresponden a mujeres , equivalente al 87.7 %. Los hombres representan 563 casos, es decir, el 12.3 % del total. El grupo de edad con mayor número de atenciones corresponde a personas de entre 18 y 59 años, con 3,067 casos , que representan el 67 % del registro regional. También preocupa la cantidad de menores afectados. Entre niñas, niños y adolescentes de 0 a 17 años se contabilizaron 1,294 casos , equivalentes al 28.3 %. En tanto, las personas adultas mayores de 60 años registraron 217 atenciones, que representan el 4.7 %. Estos datos muestran que la violencia no afecta únicamente a las parejas o a mujeres adultas. También alcanza a menores de edad y adultos mayores dentro del entorno familiar, lo que amplía el impacto social de este problema. Violencia psicológica encabeza los casos registrados La violencia psicológica es la modalidad que concentra la mayor cantidad de atenciones en la región Piura. De acuerdo con el reporte, se registraron 2,091 casos, equivalentes al 45.7 % del total. En segundo lugar aparece la violencia física , con 1,833 casos y una participación del 40 %. Le sigue la violencia sexual, que alcanzó 650 casos, equivalente al 14.2 %. Finalmente, se reportaron cuatro casos de violencia económica, que representan el 0.1 %. La distribución permite observar que las agresiones no siempre dejan lesiones visibles. La violencia psicológica representa casi la mitad de las atenciones registradas y puede manifestarse mediante amenazas, humillaciones, control, intimidación u otras conductas que afectan a la víctima. Piura registra un feminicidio y dos tentativas El reporte del Programa Nacional Warmi Ñan también registra hechos de mayor gravedad. Durante el periodo analizado se confirmó un caso de feminicidio en la provincia de Huancabamba . Asimismo, fueron reportadas dos tentativas de feminicidio , ocurridas en las provincias de Piura y Morropón. Estos casos reflejan situaciones de violencia extrema que requieren una intervención rápida de las instituciones responsables de proteger a las víctimas. De acuerdo con el MIMP, el Programa Nacional Warmi Ñan desarrolla servicios de atención, protección y prevención frente a la violencia contra las mujeres y los integrantes del grupo familiar en todo el país. Conoce los servicios oficiales del Programa Nacional Warmi Ñan . Adolescentes y embarazo también forman parte del panorama El informe incorpora además un indicador relacionado con las adolescentes de la región. El 10.6 % de las mujeres de 15 a 19 años en Piura ha tenido un hijo o ha estado embarazada por primera vez . Del total, el 9.9 % ya son madres, mientras que el 0.7 % estuvo embarazada por primera vez. Este indicador forma parte del contexto social que acompaña las cifras de violencia y permite observar la situación de adolescentes y jóvenes en la región. Warmi Ñan cuenta con 20 Centros Emergencia Mujer en Piura Para atender esta problemática, la región cuenta con 20 Centros Emergencia Mujer . De ellos, 10 funcionan en comisarías y brindan atención durante las 24 horas del día. El despliegue también incluye el Servicio de Atención Rural (SAR) , que atendió 117 casos en comunidades de Sechura y Huancabamba. Este servicio busca acercar la atención especializada a poblaciones ubicadas en zonas rurales y con mayores dificultades para acceder a los servicios institucionales. Asimismo, el Hogar de Refugio Temporal recibió a 61 personas en situación de riesgo severo: 32 mujeres y 29 hijos o acompañantes. Estos espacios permiten brindar protección y atención integral a personas que necesitan salir de un entorno considerado peligroso. Línea 100 recibió más de 3 mil consultas en Piura La atención frente a la violencia también se realiza mediante servicios remotos. Entre enero y julio de 2026, la Línea 100 registró 3,375 consultas telefónicas en la región. Del total de consultas, el 36.4 % estuvo relacionado con violencia física, el 32.8 % con violencia psicológica y el 7.3 % con violencia sexual. El servicio permite orientar a las personas afectadas o a quienes conocen un caso de violencia. Por su parte, el Chat 100 atendió 153 consultas relacionadas principalmente con la identificación de situaciones de riesgo en relaciones de pareja o noviazgo. Según el Ministerio de la Mujer y Poblaciones Vulnerables, la Línea 100 brinda orientación y consejería de manera gratuita las 24 horas del día. Revisa la información oficial del MIMP sobre la Línea 100 y los servicios de atención . ¿Dónde buscar ayuda ante un caso de violencia? Las personas que atraviesen una situación de violencia o conozcan un caso pueden acudir a un Centro Emergencia Mujer para recibir orientación especializada. También pueden comunicarse con la Línea 100 para solicitar información y apoyo. Los CEM brindan atención integral y gratuita, incluyendo orientación legal, atención psicológica y acompañamiento social, de acuerdo con las características de cada caso. Consulta los servicios y datos oficiales de Warmi Ñan .</t>
+          <t>La Contraloría General de la República (CGR) evidenció que la obra de ampliación del servicio de aulas de la facultad de Ingeniería Económica de la Universidad Nacional de Frontera, en la provincia de Sullana, presenta signos de deterioro prematuro pese a que los trabajos fueron recibidos en enero de este año. Esta situación genera el riesgo de afectar la calidad, operatividad y vida útil de este proyecto que tiene una inversión superior a los S/ 14 millones. En el Informe de Hito de Control n.° 11384-2026-CG/GRPI-SCC (periodo de evaluación del 12 al 18 de agosto de 2026), se identificaron diversas deficiencias en la infraestructura de los bloques I-A, I-B y II, entre ellas, puertas de madera desniveladas, falta de agua en inodoros y lavatorios, y tapajuntas de acero inoxidable con fijación deficiente en juntas de dilatación. En los servicios higiénicos del cuarto piso se constató que algunos inodoros permanecen inoperativos por falla en el sistema de abastecimiento de agua, mientras que el lavamanos destinado a personas con discapacidad presenta insuficiente presión. Además, se observaron aberturas en los tapajuntas que podrían facilitar el ingreso de humedad, residuos y agentes contaminantes. También se detectaron problemas en ambientes administrativos y académicos: una de las cuatro unidades evaporadoras del sistema de aire acondicionado de la sala de cómputo se encuentra inoperativa y varios lavatorios no cuentan con flujo de agua. En la sala de impresiones se verificó el desprendimiento de una baldosa del techo que dejó un sensor de humo suspendido por sus cables, además de evidencias de humedad y moho. En la actual área de grados y títulos y responsabilidad social se constató la ausencia de una puerta de vidrio, situación que deja expuestos equipos, mobiliario y documentación. A ello se suman el desprendimiento y agrietamiento del sellador de una escalera de madera, deformaciones en elementos de la pérgola en una plazoleta y tapas de concreto de canaletas pluviales deterioradas y desalineadas, generando riesgos para los usuarios. Asimismo, se constató que el ascensor del pabellón permanece fuera de servicio, pese a que la Unidad Ejecutora de Inversiones había requerido al contratista la subsanación de la falla en el marco de la garantía de obra y posteriormente realizó gestiones para evaluar técnicamente el problema. La inoperatividad del equipo obliga a estudiantes, docentes y personal a utilizar exclusivamente las escaleras y constituye una barrera crítica para las personas con movilidad reducida o discapacidad. Durante la inspección se verificó una diferencia entre los equipos adquiridos para el proyecto y los encontrados físicamente en el pabellón de la Facultad de Ingeniería Económica. De los 26 monitores con procesador integrado previstos para el proyecto, solo 12 fueron ubicados, uno en cada una de las aulas. Del mismo modo, se constató que únicamente ocho equipos cuentan con actas de entrega al área usuaria, pese a que la documentación de la entidad acredita la adquisición de los 26 monitores. Esta situación genera el riesgo de que 14 equipos no estén siendo utilizados para el fin para el cual fueron adquiridos, se encuentren en desuso o incluso se haya producido su pérdida. La obra se inició en noviembre de 2023 y debió culminar al siguiente año. Recién en enero de este año se suscribió el acta de recepción. El informe fue notificado al titular de la entidad para que adopte las acciones que correspondan, en el marco de sus competencias y obligaciones en la gestión institucional.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>https://eltiempo.pe/local/mas-de-4-mil-casos-de-violencia-contra-mujeres-y-familiares-genera-preocupacion-en-piura/</t>
+          <t>https://eltiempo.pe/local/contraloria-obra-recien-culminada-presenta-signos-de-deterioro-prematuro-en-universidad-nacional-de-frontera/</t>
         </is>
       </c>
     </row>
@@ -545,24 +545,24 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Sí habrá mango, pero en menor cantidad: La anomalía en las temperaturas no permitieron una adecuada floración de las plantaciones</t>
+          <t>Más de 4 mil casos de violencia contra mujeres y familiares genera preocupación en Piura</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>El invierno cálido que se vivió en Piura dejó secuelas importantes en la agricultura piurana. Las altas temperaturas afectaron el proceso de floración de algunos cultivos como es el caso del mango, lo cual traerá consecuencias en la producción nacional que tiene destino Estados Unidos o Europa. De acuerdo a los especialistas, en la variedad de exportación del mango Kent la floración alcanzó un 30% en promedio entre las más de 33 mil hectáreas del valle de San Lorenzo en Tambogrande. De esta manera se podría tener un disminución de la producción con fines de exportación de más del 60%. Sin embargo, otras variedades como el mango criollo, Ataulfo o Edwards han tenido mejores resultados en la floración. “El año pasado la producción se contrajo un 20%. Ahora la situación se ha agudizado porque las anomalías de 4 y 5 grados en la temperatura impiden la producción de fitohormonas en el nivel adecuado para la floración. No hay una respuesta floral adecuada”, informó la doctora en agrometeorología, Ninell Dediós. De continuar las condiciones térmicas, lo siguiente serían problemas con el cuajado de la fruta que ha logrado generar. Asimismo, una lluvia en plena etapa de cosecha dañaría este proceso final antes de la exportación. Un similar impacto se tiene en cultivos como el limón (floración del 30%), arroz (plantas débiles por acelerado crecimiento ante el calor) y algodón (menor calidad de la fibra). En el campo Desde el lado de los productores aún existe una ligera esperanza de que este panorama pueda mejorar en las siguientes semanas. “Algunos productores dicen que la floración está en 20% y otros en 30%. Todavía no está todo culminado, ni vencido; hay una pequeña ventana de oportunidad. En un año relativamente bueno en el norte se producen 500 mil toneladas de mango, pero ahora que está en 30% [de la floración], nos quedarían unas 120 mil toneladas aproximadamente. Se estima una disminución del 70% de la producción en todas las variedades”, manifestó el expresidente de la Junta de Usuarios del valle de San Lorenzo, Darío Castillo. Seguro Para los agricultores, la expectativa es que se pueda aplicar el seguro agrario catastrófico frente a las pérdidas que sufrirán por efecto del impacto del clima. “El ministro ha sido claro, habló de que existe un seguro agrario catastrófico por cambio climático o un bono, pero es relativamente poco que no soluciona el problema. por una hectárea te dan 800 soles. Por una hectárea de mango se invierte arriba de 10 mil soles”, informó Castillo. Producción para mercado local ayudaría En declaraciones a un medio nacional, Milton Calle, productor de mango en Piura y Casma y propietario de la exportadora Boom Fruit, informó que la baja floración de las plantas de mango no significa necesariamente una caída significativa. “Pienso que vamos a tener una caída de alrededor de 60% en la producción, básicamente por El Niño”, señaló. En ese contexto, el país cerraría la campaña con entre 80.000 y 100.000 toneladas exportables, frente a las 240.000 toneladas registradas en la temporada anterior. Agregó que es posible que parte de la fruta que se destina al mercado local o a la industria de congelados podría irse hacia a la exportación para compensar parcialmente el menor volumen que se obtenga de los campos. De otro lado, Calle también mencionó que Brasil se vería beneficiado con mayores ventas en el mercado europeo por la caída de la producción en Ecuador y Perú.</t>
+          <t>La violencia contra las mujeres y los integrantes del grupo familiar mantiene cifras preocupantes en Piura . Entre enero y julio de 2026, los Centros Emergencia Mujer (CEM) de la región atendieron 4,578 casos de violencia , de acuerdo con el último reporte del Programa Nacional Warmi Ñan del Ministerio de la Mujer y Poblaciones Vulnerables (MIMP). La cifra representa un incremento considerable respecto al reporte acumulado hasta junio, cuando se registraban 3,272 casos. En solo un mes se sumaron 1,306 nuevas atenciones, lo que evidencia la magnitud del problema que enfrentan mujeres, niñas, niños, adolescentes y otros integrantes de las familias en diferentes provincias de la región. Según el Programa Nacional Warmi Ñan , los CEM son servicios públicos especializados y gratuitos que brindan atención psicológica, social y legal a personas afectadas por hechos de violencia. Consulta aquí la información oficial de Warmi Ñan sobre los Centros Emergencia Mujer . Piura concentra la mayor cantidad de casos de violencia La provincia de Piura concentra la mayor cantidad de atenciones reportadas en la región, con 2,580 casos entre enero y julio. La distribución muestra que las situaciones de violencia llegan a diferentes puntos de atención y no se concentran únicamente en una institución. La comisaría de Piura atendió 735 víctimas, mientras que el centro de salud Santa Julia registró 547 casos. A estos se suman 435 atenciones en la comisaría de familia, 236 en la comisaría rural de Tambogrande, 231 en Catacaos, 208 en La Unión y 188 correspondientes al distrito de Piura. Después de la provincia de Piura aparecen Sullana, con 436 casos; Paita, con 420; Ayabaca, con 359; Talara, con 256; Morropón, con 252; Sechura, con 163; y Huancabamba, con 112 casos . ¿Quiénes son los principales afectados por la violencia en Piura? Del total de 4,578 casos atendidos en los primeros siete meses del año, 4,015 corresponden a mujeres , equivalente al 87.7 %. Los hombres representan 563 casos, es decir, el 12.3 % del total. El grupo de edad con mayor número de atenciones corresponde a personas de entre 18 y 59 años, con 3,067 casos , que representan el 67 % del registro regional. También preocupa la cantidad de menores afectados. Entre niñas, niños y adolescentes de 0 a 17 años se contabilizaron 1,294 casos , equivalentes al 28.3 %. En tanto, las personas adultas mayores de 60 años registraron 217 atenciones, que representan el 4.7 %. Estos datos muestran que la violencia no afecta únicamente a las parejas o a mujeres adultas. También alcanza a menores de edad y adultos mayores dentro del entorno familiar, lo que amplía el impacto social de este problema. Violencia psicológica encabeza los casos registrados La violencia psicológica es la modalidad que concentra la mayor cantidad de atenciones en la región Piura. De acuerdo con el reporte, se registraron 2,091 casos, equivalentes al 45.7 % del total. En segundo lugar aparece la violencia física , con 1,833 casos y una participación del 40 %. Le sigue la violencia sexual, que alcanzó 650 casos, equivalente al 14.2 %. Finalmente, se reportaron cuatro casos de violencia económica, que representan el 0.1 %. La distribución permite observar que las agresiones no siempre dejan lesiones visibles. La violencia psicológica representa casi la mitad de las atenciones registradas y puede manifestarse mediante amenazas, humillaciones, control, intimidación u otras conductas que afectan a la víctima. Piura registra un feminicidio y dos tentativas El reporte del Programa Nacional Warmi Ñan también registra hechos de mayor gravedad. Durante el periodo analizado se confirmó un caso de feminicidio en la provincia de Huancabamba . Asimismo, fueron reportadas dos tentativas de feminicidio , ocurridas en las provincias de Piura y Morropón. Estos casos reflejan situaciones de violencia extrema que requieren una intervención rápida de las instituciones responsables de proteger a las víctimas. De acuerdo con el MIMP, el Programa Nacional Warmi Ñan desarrolla servicios de atención, protección y prevención frente a la violencia contra las mujeres y los integrantes del grupo familiar en todo el país. Conoce los servicios oficiales del Programa Nacional Warmi Ñan . Adolescentes y embarazo también forman parte del panorama El informe incorpora además un indicador relacionado con las adolescentes de la región. El 10.6 % de las mujeres de 15 a 19 años en Piura ha tenido un hijo o ha estado embarazada por primera vez . Del total, el 9.9 % ya son madres, mientras que el 0.7 % estuvo embarazada por primera vez. Este indicador forma parte del contexto social que acompaña las cifras de violencia y permite observar la situación de adolescentes y jóvenes en la región. Warmi Ñan cuenta con 20 Centros Emergencia Mujer en Piura Para atender esta problemática, la región cuenta con 20 Centros Emergencia Mujer . De ellos, 10 funcionan en comisarías y brindan atención durante las 24 horas del día. El despliegue también incluye el Servicio de Atención Rural (SAR) , que atendió 117 casos en comunidades de Sechura y Huancabamba. Este servicio busca acercar la atención especializada a poblaciones ubicadas en zonas rurales y con mayores dificultades para acceder a los servicios institucionales. Asimismo, el Hogar de Refugio Temporal recibió a 61 personas en situación de riesgo severo: 32 mujeres y 29 hijos o acompañantes. Estos espacios permiten brindar protección y atención integral a personas que necesitan salir de un entorno considerado peligroso. Línea 100 recibió más de 3 mil consultas en Piura La atención frente a la violencia también se realiza mediante servicios remotos. Entre enero y julio de 2026, la Línea 100 registró 3,375 consultas telefónicas en la región. Del total de consultas, el 36.4 % estuvo relacionado con violencia física, el 32.8 % con violencia psicológica y el 7.3 % con violencia sexual. El servicio permite orientar a las personas afectadas o a quienes conocen un caso de violencia. Por su parte, el Chat 100 atendió 153 consultas relacionadas principalmente con la identificación de situaciones de riesgo en relaciones de pareja o noviazgo. Según el Ministerio de la Mujer y Poblaciones Vulnerables, la Línea 100 brinda orientación y consejería de manera gratuita las 24 horas del día. Revisa la información oficial del MIMP sobre la Línea 100 y los servicios de atención . ¿Dónde buscar ayuda ante un caso de violencia? Las personas que atraviesen una situación de violencia o conozcan un caso pueden acudir a un Centro Emergencia Mujer para recibir orientación especializada. También pueden comunicarse con la Línea 100 para solicitar información y apoyo. Los CEM brindan atención integral y gratuita, incluyendo orientación legal, atención psicológica y acompañamiento social, de acuerdo con las características de cada caso. Consulta los servicios y datos oficiales de Warmi Ñan .</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>https://eltiempo.pe/local/si-habra-mango-pero-en-menor-cantidad-la-anomalia-en-las-temperaturas-no-permitieron-una-adecuada-floracion-de-las-plantaciones/</t>
+          <t>https://eltiempo.pe/local/mas-de-4-mil-casos-de-violencia-contra-mujeres-y-familiares-genera-preocupacion-en-piura/</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Andina</t>
+          <t>El Tiempo</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -570,10 +570,35 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
+          <t>Sí habrá mango, pero en menor cantidad: La anomalía en las temperaturas no permitieron una adecuada floración de las plantaciones</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>El invierno cálido que se vivió en Piura dejó secuelas importantes en la agricultura piurana. Las altas temperaturas afectaron el proceso de floración de algunos cultivos como es el caso del mango, lo cual traerá consecuencias en la producción nacional que tiene destino Estados Unidos o Europa. De acuerdo a los especialistas, en la variedad de exportación del mango Kent la floración alcanzó un 30% en promedio entre las más de 33 mil hectáreas del valle de San Lorenzo en Tambogrande. De esta manera se podría tener un disminución de la producción con fines de exportación de más del 60%. Sin embargo, otras variedades como el mango criollo, Ataulfo o Edwards han tenido mejores resultados en la floración. “El año pasado la producción se contrajo un 20%. Ahora la situación se ha agudizado porque las anomalías de 4 y 5 grados en la temperatura impiden la producción de fitohormonas en el nivel adecuado para la floración. No hay una respuesta floral adecuada”, informó la doctora en agrometeorología, Ninell Dediós. De continuar las condiciones térmicas, lo siguiente serían problemas con el cuajado de la fruta que ha logrado generar. Asimismo, una lluvia en plena etapa de cosecha dañaría este proceso final antes de la exportación. Un similar impacto se tiene en cultivos como el limón (floración del 30%), arroz (plantas débiles por acelerado crecimiento ante el calor) y algodón (menor calidad de la fibra). En el campo Desde el lado de los productores aún existe una ligera esperanza de que este panorama pueda mejorar en las siguientes semanas. “Algunos productores dicen que la floración está en 20% y otros en 30%. Todavía no está todo culminado, ni vencido; hay una pequeña ventana de oportunidad. En un año relativamente bueno en el norte se producen 500 mil toneladas de mango, pero ahora que está en 30% [de la floración], nos quedarían unas 120 mil toneladas aproximadamente. Se estima una disminución del 70% de la producción en todas las variedades”, manifestó el expresidente de la Junta de Usuarios del valle de San Lorenzo, Darío Castillo. Seguro Para los agricultores, la expectativa es que se pueda aplicar el seguro agrario catastrófico frente a las pérdidas que sufrirán por efecto del impacto del clima. “El ministro ha sido claro, habló de que existe un seguro agrario catastrófico por cambio climático o un bono, pero es relativamente poco que no soluciona el problema. por una hectárea te dan 800 soles. Por una hectárea de mango se invierte arriba de 10 mil soles”, informó Castillo. Producción para mercado local ayudaría En declaraciones a un medio nacional, Milton Calle, productor de mango en Piura y Casma y propietario de la exportadora Boom Fruit, informó que la baja floración de las plantas de mango no significa necesariamente una caída significativa. “Pienso que vamos a tener una caída de alrededor de 60% en la producción, básicamente por El Niño”, señaló. En ese contexto, el país cerraría la campaña con entre 80.000 y 100.000 toneladas exportables, frente a las 240.000 toneladas registradas en la temporada anterior. Agregó que es posible que parte de la fruta que se destina al mercado local o a la industria de congelados podría irse hacia a la exportación para compensar parcialmente el menor volumen que se obtenga de los campos. De otro lado, Calle también mencionó que Brasil se vería beneficiado con mayores ventas en el mercado europeo por la caída de la producción en Ecuador y Perú.</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>https://eltiempo.pe/local/si-habra-mango-pero-en-menor-cantidad-la-anomalia-en-las-temperaturas-no-permitieron-una-adecuada-floracion-de-las-plantaciones/</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Andina</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>46276</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
           <t>Lluvias ligeras a moderadas prevista en la selva ponen en riesgo a 160 distritos</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>Según dicho documento, San Martín es el departamento que presenta la mayor cantidad de distritos en riesgo muy alto, con 16 jurisdicciones, seguido de Amazonas (5), Ayacucho (5), Pasco (3), Cajamarca (2), Junín (2), Puno (2) y Loreto (1).
 En tanto , 124 distritos de estas mismas regiones, además de Cusco, Huánuco y Ucayali se encuentran en riesgo alto.
@@ -586,27 +611,27 @@
 La ANA interviene 2 km de la margen derecha en Malingas para proteger a 30 familias y unas 80 hectáreas de cultivos.?? https://t.co/pHt1feyULt pic.twitter.com/dNAQiiBqHZ — Agencia Andina (@Agencia_Andina) September 10, 2026</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>https://andina.pe/agencia/noticia-lluvias-ligeras-a-moderadas-prevista-la-selva-ponen-riesgo-a-160-distritos-1091335.aspx</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
+    <row r="8">
+      <c r="A8" t="inlineStr">
         <is>
           <t>Andina</t>
         </is>
       </c>
-      <c r="B7" s="2" t="n">
+      <c r="B8" s="2" t="n">
         <v>46276</v>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>Café: más de 46,000 familias cafetaleras se benefician de la Ruta Productiva Exportadora</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>La viceministra de Comercio Exterior, Sayuri Bayona , destacó este resultado durante su participación en el festival “Yo Tomo Café Peruano 2026”, que se desarrolla en el parque Kennedy, en Miraflores.
 Señaló que, a la fecha, 245 beneficiarios de la RPE forman parte de la cadena del café, con un impacto que alcanza a distintas regiones del país.
@@ -625,27 +650,27 @@
 ?? https://t.co/BDNcgRSUVA pic.twitter.com/rCZUAWWd6Z — Agencia Andina (@Agencia_Andina) September 11, 2026</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>https://andina.pe/agencia/noticia-cafe-mas-46000-familias-cafetaleras-se-benefician-de-ruta-productiva-exportadora-1091362.aspx</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
+    <row r="9">
+      <c r="A9" t="inlineStr">
         <is>
           <t>Andina</t>
         </is>
       </c>
-      <c r="B8" s="2" t="n">
+      <c r="B9" s="2" t="n">
         <v>46275</v>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>Piura: Vivienda inspecciona infraestructura estratégica ante posibles impactos de El Niño</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>Como parte de estas acciones, el equipo del OTASS efectuó una jornada de inspección técnica en diversas instalaciones de la EPS Grau, entre ellas la planta de tratamiento de agua potable (PTAP) Curumuy, que representa aproximadamente el 44% del abastecimiento de agua potable de la provincia de Piura.
 También se inspeccionaron la PTAR San Martín y la estación de bombeo de aguas residuales (EBAR) Cortijo, en el distrito de Castilla, donde se verificó la operatividad de tres electrobombas recientemente instaladas, de 250 litros por segundo cada una, financiadas mediante una IOARR de emergencia, y las condiciones de sus demás componentes.
@@ -658,27 +683,27 @@
 ?? https://t.co/Rk9ilfkyym pic.twitter.com/nFvVi2wW2B — Agencia Andina (@Agencia_Andina) September 11, 2026</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>https://andina.pe/agencia/noticia-piura-vivienda-inspecciona-infraestructura-estrategica-ante-posibles-impactos-de-nino-1091321.aspx</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
+    <row r="10">
+      <c r="A10" t="inlineStr">
         <is>
           <t>Andina</t>
         </is>
       </c>
-      <c r="B9" s="2" t="n">
+      <c r="B10" s="2" t="n">
         <v>46275</v>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>El Niño: aprueban patrullaje integrado y respuesta logística con OxI ante emergencias</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>La Resolución Ministerial 1334-2026-IN, que lleva la firma del ministro del Interior, César Astudillo Salcedo, y publicada en la edición extraordinaria del boletín de Normas Legales del Diario Oficial El Peruano , tiene por finalidad acelerar y financiar de manera prioritaria el despliegue logístico y de seguridad ciudadana frente a situaciones críticas en el país como el FEN.
 De esta forma se reducirá la exposición de la población y la infraestructura pública, además de asegurar la continuidad de los servicios públicos esenciales y evitar que los daños que pudieran producirse deriven en perjuicios de difícil o imposible reparación y en mayores costos fiscales de rehabilitación y reconstrucción.
@@ -692,27 +717,27 @@
 ?? https://t.co/ypNmV34u4N pic.twitter.com/kvK3SeA6Qh — Agencia Andina (@Agencia_Andina) September 11, 2026</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>https://andina.pe/agencia/noticia-el-nino-aprueban-patrullaje-integrado-y-respuesta-logistica-oxi-ante-emergencias-1091329.aspx</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
+    <row r="11">
+      <c r="A11" t="inlineStr">
         <is>
           <t>Andina</t>
         </is>
       </c>
-      <c r="B10" s="2" t="n">
+      <c r="B11" s="2" t="n">
         <v>46275</v>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>Conoce las 125 agencias donde el Reniec brindará atención especial este fin de semana</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>La atención del sábado se realizará en agencias de Piura, La Libertad, Lambayeque, Tumbes, Cajamarca, San Martín, Loreto, Áncash, Junín, Ayacucho, Arequipa, Cusco, Lima, Puno, Ica, Ucayali, Huancavelica, Madre de Dios y Amazonas.
 En tanto, el domingo, el Reniec continuará atendiendo en Piura, Lambayeque, Tumbes, Lima y Puno, de 8:15 a.
@@ -735,41 +760,16 @@
 Más en Andina: La Autoridad Nacional de Infraestructura (ANIN) amplió su cartera de intervención integral para el control de riesgos por movimientos de masa e inundaciones en la cuenca del río Rímac con la incorporación de las quebradas Vizcachera, Ñaña y La Laguna ?? https://t.co/T25qFB3xn7 pic.twitter.com/vrqvZ2YCgN — Agencia Andina (@Agencia_Andina) September 10, 2026</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>https://andina.pe/agencia/noticia-conoce-las-125-agencias-donde-reniec-brindara-atencion-especial-este-fin-semana-1091330.aspx</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>El Comercio</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="n">
-        <v>46275</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>¿Masificación de gas en el norte? Gasoducto entre Piura y Chiclayo es posible, señala Gas Energy</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>El norte del Perú tiene la oportunidad de abastecerse de gas natural y lograr una verdadera masificación sin la obligatoriedad de recurrir a Camisea. Esto, a través de la construcción de gasoductos que aprovechen el potencial de los lotes de hidrocarburos piuranos. Y es que la única manera de lograr un proceso de masificación económico y eficiente es “construyendo tubos”, alternativa que elimina la necesidad de transportar el gas en camiones, apunta Luis Fernández, socio director de Gas Energy Perú. En esa línea, la consultora lanzó en la XV Conferencia Gas Natural Perú 2026 una propuesta para crear un corredor energético de gas natural entre Piura y Chimbote utilizando las reservas y recursos de los campos piuranos, hoy desaprovechados. “El norte del Perú tiene suficientes reservas y recursos para crear un polo de desarrollo energético e industrial descentralizado e independiente del gas de Camisea”, manifiesta el especialista. Así, la consultora propone construir un gasoducto de 250 kilómetros de longitud que conecte Piura con la localidad lambayecana de Eten, en una primera etapa, sacando partido de la existencia de dos plantas térmicas en esa jurisdicción, las cuales servirán de ‘ancla’ para el proyecto. Es el caso de las centrales duales Eten (180 MW) y Recka (190 MW) las cuales están en capacidad de producir electricidad tanto con gas como con diésel. Se trata, explica Fernández, de dos infraestructuras que hoy en día no pueden ser abastecidas con gas pues el transporte en camiones cisternas no permite el abastecimiento de grandes volúmenes. De allí la solución de un gasoducto capaz de proveer los 80 millones de pies cúbicos diarios (mmpcd) de gas que necesitarían continuamente. “Si tenemos 80 mmpcd de demanda en Éten ya existiría un ancla para incentivar la producción de los lotes piuranos. Y a ello se agregaría la demanda de GNV en Chiclayo y las azucareras que tienen un alto consumo de energía”, precisa el especialista. Piura produce y consume alrededor de 60 mmpcd de gas natural. La apertura de nuevos mercados en Lambayeque incentivaría la búsqueda y producción de mayores volúmenes, lo cual no representaría un problema pues la región tiene un potencial de 5,5 trillones de pies cúbicos (TFC) de gas, es decir, 91.666 veces su producción diaria hoy. “Conceptualmente, el proyecto es posible porque existe el gas y existen las centrales térmicas que servirían de ancla. Por lo tanto, se puede construir la infraestructura”, manifiesta Fernández. Dicho ducto recorrería Paita, Sechura y Bayóvar hasta llegar a Éten, siguiendo un recorrido paralelo al que Gasnorp opera en Piura. Así, se conectaría la ciudad de Chiclayo, en primer lugar, y luego las de Trujillo, Paramonga y Chimbote, andando el tiempo. Lo único que faltaría para concretar el proyecto es plasmar las condiciones para que sea comercial y regulatoriamente posible, anota Fernández. Y es que la regulación no contempla una tarifa especial para el sector de generación eléctrica en el norte del país, a diferencia de lo que ocurre en las concesiones de Lima (Cálidda) e Ica (Contugas). “Para que el proyecto tenga éxito hace falta armar una nueva regulación que permita que esas centrales entren en base y para ello se necesita políticas adecuadas que partan desde el Minem”, anota Fernández.</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>https://elcomercio.pe/economia/peru/masificacion-de-gas-en-el-norte-gasoducto-entre-piura-y-chiclayo-es-posible-senala-gas-energy-noticia/</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>El Tiempo</t>
+          <t>El Comercio</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -777,17 +777,17 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Ministro de Defensa promete mayor velocidad en la descolmatación del río Piura</t>
+          <t>¿Masificación de gas en el norte? Gasoducto entre Piura y Chiclayo es posible, señala Gas Energy</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>El ministro de Defensa, Rafael Belaunde , aseguró que el Ejército incrementará la velocidad de los trabajos de descolmatación del río Piura , como parte de las acciones preventivas frente al eventual impacto del fenómeno El Niño en la región. El titular del sector supervisó el despliegue de personal y maquinaria pesada en dos de los puntos considerados críticos. Durante su visita al puente Bolognesi, en Piura, Belaunde verificó las labores destinadas a retirar los sedimentos acumulados en el cauce. Según explicó, existe confianza en que los trabajos avanzarán al ritmo requerido para cumplir con las metas establecidas. “Estoy confiado en que el Ejército avanzará en la velocidad que se le ha requerido”, afirmó el ministro durante la inspección. ¿Dónde se realizan los trabajos en el río Piura? Las labores de limpieza y recuperación del cauce se ejecutan en siete puntos críticos del río Piura , en un tramo de aproximadamente 15.5 kilómetros comprendido entre los puentes Independencia y Bolognesi. Para esta operación se ha desplegado personal especializado del Ejército y maquinaria pesada destinada principalmente a retirar el material acumulado en diferentes sectores del afluente. La intervención busca mejorar las condiciones del cauce ante la posibilidad de lluvias intensas y un incremento del caudal. En el sector del puente Bolognesi trabaja el Batallón de Ingeniería de Construcción N.° 1 “Jazán”, unidad trasladada desde la región Amazonas. Para cumplir con su misión, cuenta con 13 camiones volquetes, dos excavadoras, dos tractores oruga y un cargador frontal . La meta establecida para este punto es intervenir aproximadamente dos kilómetros del cauce del río Piura . El retiro de los sedimentos permitirá recuperar parte de la capacidad hidráulica del río en una zona considerada estratégica para la prevención de inundaciones. Ejército trabaja en el puente Independencia El ministro de Defensa también llegó hasta el puente Independencia para inspeccionar los trabajos que se desarrollan en este sector. Las acciones están a cargo del Batallón de Ingeniería de Combate N.° 211, proveniente de Tumbes. Esta unidad dispone de dos tractores oruga, una excavadora, un cargador frontal y un volquete . De acuerdo con la planificación presentada durante la supervisión, sus trabajos tienen como objetivo intervenir aproximadamente 1.8 kilómetros del cauce. La presencia de maquinaria en ambos sectores forma parte de una operación de ingeniería de mayor escala. Para el Gobierno, la recuperación del cauce constituye una de las medidas preventivas frente a un eventual escenario de lluvias asociadas al fenómeno El Niño. Piura recibirá 600 toneladas de ayuda no alimentaria Durante su visita, el ministro de Defensa también informó sobre las acciones de preparación ante una eventual emergencia por lluvias. Según indicó, alrededor de 200 toneladas de ayuda no alimentaria ya han llegado a Piura como parte de un envío mayor. La ayuda es gestionada mediante el Instituto Nacional de Defensa Civil (Indeci) y forma parte de un total de 600 toneladas que serán trasladadas y almacenadas en un hangar ubicado en territorio piurano. Según declaraciones brindadas a TVPerú, el objetivo es contar con recursos suficientes para atender a unas 100,000 familias , lo que representa cerca de medio millón de personas ante un escenario de emergencia. “La idea es tener capacidad para atender a 100,000 familias. Eso es algo cercano al medio millón de personas”, explicó Belaunde, quien añadió que progresivamente también se incorporará ayuda alimentaria. ¿Por qué es importante la descolmatación del río Piura? La descolmatación consiste en retirar sedimentos, tierra y otros materiales acumulados en el cauce de un río. En el caso del río Piura , estas labores tienen especial importancia durante la temporada de lluvias, debido al riesgo de incremento del caudal y posibles desbordes. La recuperación de la capacidad del cauce forma parte de las medidas de prevención frente a inundaciones. En Piura, una región que históricamente ha enfrentado episodios de lluvias intensas, mantener libres los sectores críticos permite mejorar las condiciones para el desplazamiento del agua. De acuerdo con el Instituto Nacional de Defensa Civil (Indeci) , las acciones de preparación y prevención son fundamentales para reducir los riesgos y mejorar la capacidad de respuesta ante emergencias. Una operación que abarca 15.5 kilómetros La intervención del Ejército contempla un tramo total de 15.5 kilómetros del río Piura , distribuido en siete puntos críticos ubicados entre los puentes Independencia y Bolognesi. La operación requiere el desplazamiento de unidades de ingeniería, operadores y maquinaria especializada. Para las autoridades, el avance de estos trabajos será especialmente importante conforme se acerquen los periodos de mayor riesgo de lluvias. La incorporación de nuevos equipos, anunciada por el Ministerio de Defensa, busca acelerar el retiro de los sedimentos y cumplir con las metas establecidas para cada sector. La información sobre las acciones de prevención y respuesta ante emergencias puede consultarse en los canales oficiales del Ministerio de Defensa y del Indeci .</t>
+          <t>El norte del Perú tiene la oportunidad de abastecerse de gas natural y lograr una verdadera masificación sin la obligatoriedad de recurrir a Camisea. Esto, a través de la construcción de gasoductos que aprovechen el potencial de los lotes de hidrocarburos piuranos. Y es que la única manera de lograr un proceso de masificación económico y eficiente es “construyendo tubos”, alternativa que elimina la necesidad de transportar el gas en camiones, apunta Luis Fernández, socio director de Gas Energy Perú. En esa línea, la consultora lanzó en la XV Conferencia Gas Natural Perú 2026 una propuesta para crear un corredor energético de gas natural entre Piura y Chimbote utilizando las reservas y recursos de los campos piuranos, hoy desaprovechados. “El norte del Perú tiene suficientes reservas y recursos para crear un polo de desarrollo energético e industrial descentralizado e independiente del gas de Camisea”, manifiesta el especialista. Así, la consultora propone construir un gasoducto de 250 kilómetros de longitud que conecte Piura con la localidad lambayecana de Eten, en una primera etapa, sacando partido de la existencia de dos plantas térmicas en esa jurisdicción, las cuales servirán de ‘ancla’ para el proyecto. Es el caso de las centrales duales Eten (180 MW) y Recka (190 MW) las cuales están en capacidad de producir electricidad tanto con gas como con diésel. Se trata, explica Fernández, de dos infraestructuras que hoy en día no pueden ser abastecidas con gas pues el transporte en camiones cisternas no permite el abastecimiento de grandes volúmenes. De allí la solución de un gasoducto capaz de proveer los 80 millones de pies cúbicos diarios (mmpcd) de gas que necesitarían continuamente. “Si tenemos 80 mmpcd de demanda en Éten ya existiría un ancla para incentivar la producción de los lotes piuranos. Y a ello se agregaría la demanda de GNV en Chiclayo y las azucareras que tienen un alto consumo de energía”, precisa el especialista. Piura produce y consume alrededor de 60 mmpcd de gas natural. La apertura de nuevos mercados en Lambayeque incentivaría la búsqueda y producción de mayores volúmenes, lo cual no representaría un problema pues la región tiene un potencial de 5,5 trillones de pies cúbicos (TFC) de gas, es decir, 91.666 veces su producción diaria hoy. “Conceptualmente, el proyecto es posible porque existe el gas y existen las centrales térmicas que servirían de ancla. Por lo tanto, se puede construir la infraestructura”, manifiesta Fernández. Dicho ducto recorrería Paita, Sechura y Bayóvar hasta llegar a Éten, siguiendo un recorrido paralelo al que Gasnorp opera en Piura. Así, se conectaría la ciudad de Chiclayo, en primer lugar, y luego las de Trujillo, Paramonga y Chimbote, andando el tiempo. Lo único que faltaría para concretar el proyecto es plasmar las condiciones para que sea comercial y regulatoriamente posible, anota Fernández. Y es que la regulación no contempla una tarifa especial para el sector de generación eléctrica en el norte del país, a diferencia de lo que ocurre en las concesiones de Lima (Cálidda) e Ica (Contugas). “Para que el proyecto tenga éxito hace falta armar una nueva regulación que permita que esas centrales entren en base y para ello se necesita políticas adecuadas que partan desde el Minem”, anota Fernández.</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>https://eltiempo.pe/local/ministro-de-defensa-promete-mayor-velocidad-en-la-descolmatacion-del-rio-piura/</t>
+          <t>https://elcomercio.pe/economia/peru/masificacion-de-gas-en-el-norte-gasoducto-entre-piura-y-chiclayo-es-posible-senala-gas-energy-noticia/</t>
         </is>
       </c>
     </row>
@@ -802,17 +802,17 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>¿Quién responde por los 106 muertos en la región Piura? Nuevo asesinato se consuma en Castilla</t>
+          <t>Ministro de Defensa promete mayor velocidad en la descolmatación del río Piura</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>La racha criminal sigue en aumento en la región, luego que un joven técnico de celulares fuera asesinado de tres balazos en la cabeza y rostro por un gatillero, que disparó con una pasmosa frialdad, delante de dos amigos, para luego huir en un auto blanco. El asesinato de José Fernando Castillo Quevedo, de 24 años, ocurrió cerca de las nueve de la noche del pasado martes frente al bar “Pikaflor”, ubicado en la Asociación Villa Universitaria, sector norteste de Castilla. Hasta ese lugar llegó la Policía para iniciar las investigaciones. ESCALOFRIANTE DATA Con este episodio escaló a 106 los asesinatos ocurridos en lo que va del año en la región, siendo la mayoría de casos por la modalidad de sicariato (o crimenes por encargo). Cabe resaltar que en 2025 se registraron 107 homicidios en el lapso de enero a setiembre. Cabe precisar que en menos de 72 horas han ocurrido siete homicidios: dos mujeres, un varón y un menor de 13 años en Sullana, otro caso en Talara. De igual manera uno en Paita Alta y el último registrado en Castilla, contra José Fernando Castillo. IMÁGENES CLAVES El asesinato del joven técnico de equipos móviles muestra el alto grado de peligrosidad que existe en las calles. Precisamente una cámara de seguridad muestra que ya no se puede confian en nadie, luego que en escena se observa a José Fernando Castillo platicando con dos personas, que serían amigos. Según las imágenes de las cámaras de seguridad, Castillo Quevedo y dos sujetos, en la vía públlica, observan un celular. De pronto, se aprecia la salida de un individuo desconocido para subir apuradamente a un automóvil blanco y dar arranque. TODOS SE CONOCÍAN En ese momento, se oberva la llegada de un gatillero que vestía polo verde y bermuda blu jeans, quien se acerca a los tres amigos y dispara tres veces contra José Fernando Castillo, luego con pistola en mano camina y sube al mencionado vehículo blanco. Del mismo modo se distingue que uno de los dos individuos, que estaba conversando con la víctima mortal abordó el mismo vehículo en el que huyó el atacante. La Policía continúa con las investigaciones para esclarecer el crimen, identificar a los involucrados y determinar las circunstancias del asesinato.</t>
+          <t>El ministro de Defensa, Rafael Belaunde , aseguró que el Ejército incrementará la velocidad de los trabajos de descolmatación del río Piura , como parte de las acciones preventivas frente al eventual impacto del fenómeno El Niño en la región. El titular del sector supervisó el despliegue de personal y maquinaria pesada en dos de los puntos considerados críticos. Durante su visita al puente Bolognesi, en Piura, Belaunde verificó las labores destinadas a retirar los sedimentos acumulados en el cauce. Según explicó, existe confianza en que los trabajos avanzarán al ritmo requerido para cumplir con las metas establecidas. “Estoy confiado en que el Ejército avanzará en la velocidad que se le ha requerido”, afirmó el ministro durante la inspección. ¿Dónde se realizan los trabajos en el río Piura? Las labores de limpieza y recuperación del cauce se ejecutan en siete puntos críticos del río Piura , en un tramo de aproximadamente 15.5 kilómetros comprendido entre los puentes Independencia y Bolognesi. Para esta operación se ha desplegado personal especializado del Ejército y maquinaria pesada destinada principalmente a retirar el material acumulado en diferentes sectores del afluente. La intervención busca mejorar las condiciones del cauce ante la posibilidad de lluvias intensas y un incremento del caudal. En el sector del puente Bolognesi trabaja el Batallón de Ingeniería de Construcción N.° 1 “Jazán”, unidad trasladada desde la región Amazonas. Para cumplir con su misión, cuenta con 13 camiones volquetes, dos excavadoras, dos tractores oruga y un cargador frontal . La meta establecida para este punto es intervenir aproximadamente dos kilómetros del cauce del río Piura . El retiro de los sedimentos permitirá recuperar parte de la capacidad hidráulica del río en una zona considerada estratégica para la prevención de inundaciones. Ejército trabaja en el puente Independencia El ministro de Defensa también llegó hasta el puente Independencia para inspeccionar los trabajos que se desarrollan en este sector. Las acciones están a cargo del Batallón de Ingeniería de Combate N.° 211, proveniente de Tumbes. Esta unidad dispone de dos tractores oruga, una excavadora, un cargador frontal y un volquete . De acuerdo con la planificación presentada durante la supervisión, sus trabajos tienen como objetivo intervenir aproximadamente 1.8 kilómetros del cauce. La presencia de maquinaria en ambos sectores forma parte de una operación de ingeniería de mayor escala. Para el Gobierno, la recuperación del cauce constituye una de las medidas preventivas frente a un eventual escenario de lluvias asociadas al fenómeno El Niño. Piura recibirá 600 toneladas de ayuda no alimentaria Durante su visita, el ministro de Defensa también informó sobre las acciones de preparación ante una eventual emergencia por lluvias. Según indicó, alrededor de 200 toneladas de ayuda no alimentaria ya han llegado a Piura como parte de un envío mayor. La ayuda es gestionada mediante el Instituto Nacional de Defensa Civil (Indeci) y forma parte de un total de 600 toneladas que serán trasladadas y almacenadas en un hangar ubicado en territorio piurano. Según declaraciones brindadas a TVPerú, el objetivo es contar con recursos suficientes para atender a unas 100,000 familias , lo que representa cerca de medio millón de personas ante un escenario de emergencia. “La idea es tener capacidad para atender a 100,000 familias. Eso es algo cercano al medio millón de personas”, explicó Belaunde, quien añadió que progresivamente también se incorporará ayuda alimentaria. ¿Por qué es importante la descolmatación del río Piura? La descolmatación consiste en retirar sedimentos, tierra y otros materiales acumulados en el cauce de un río. En el caso del río Piura , estas labores tienen especial importancia durante la temporada de lluvias, debido al riesgo de incremento del caudal y posibles desbordes. La recuperación de la capacidad del cauce forma parte de las medidas de prevención frente a inundaciones. En Piura, una región que históricamente ha enfrentado episodios de lluvias intensas, mantener libres los sectores críticos permite mejorar las condiciones para el desplazamiento del agua. De acuerdo con el Instituto Nacional de Defensa Civil (Indeci) , las acciones de preparación y prevención son fundamentales para reducir los riesgos y mejorar la capacidad de respuesta ante emergencias. Una operación que abarca 15.5 kilómetros La intervención del Ejército contempla un tramo total de 15.5 kilómetros del río Piura , distribuido en siete puntos críticos ubicados entre los puentes Independencia y Bolognesi. La operación requiere el desplazamiento de unidades de ingeniería, operadores y maquinaria especializada. Para las autoridades, el avance de estos trabajos será especialmente importante conforme se acerquen los periodos de mayor riesgo de lluvias. La incorporación de nuevos equipos, anunciada por el Ministerio de Defensa, busca acelerar el retiro de los sedimentos y cumplir con las metas establecidas para cada sector. La información sobre las acciones de prevención y respuesta ante emergencias puede consultarse en los canales oficiales del Ministerio de Defensa y del Indeci .</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>https://eltiempo.pe/local/quien-responde-por-los-106-muertos-en-la-region-piura-nuevo-asesinato-se-consuma-en-castilla/</t>
+          <t>https://eltiempo.pe/local/ministro-de-defensa-promete-mayor-velocidad-en-la-descolmatacion-del-rio-piura/</t>
         </is>
       </c>
     </row>
@@ -827,17 +827,17 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Comerciantes del Complejo de Mercados de Piura solicitan administración de parqueos</t>
+          <t>¿Quién responde por los 106 muertos en la región Piura? Nuevo asesinato se consuma en Castilla</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>A través de Resolución de Alcaldía N° 0592-2026, la Municipalidad Provincial de Piura ha dispuesto la conformación de una Comisión técnica multidisciplinaria para que evalué la viabilidad jurídica, técnica, económica, financiera, patrimonial y administrativa sobre la propuesta presentada por la Asociación regional de mercados de Piura (AREMEPI) referente a la administración de los estacionamientos del Complejo de Mercados. La asociación, que representa a los mercados formales, plantea implementar un modelo de gestión conjunta con la comuna piurana orientado a mejorar la administración del servicio, reducir los costos operativos y generar recursos económicos destinados a financiar proyectos estratégicos para el ordenamiento urbano del propio centro de abastos de la ciudad. La gerente de Desarrollo Económico, Ruth Oliva, señaló que hay voluntad política para evaluar el pedido de los comerciantes, por lo que se tendrá que esperar los informes técnicos para la toma de decisiones. REVERSIÓN La funcionaria también dio a conocer que realizaron una inspección en el Mercado San Miguel y constataron una vez más que varios puestos se encuentran cerrados. Indicó que este tipo de acciones que vienen realizando permitirán identificar los puestos que no cumplen con las disposiciones establecidas y, posteriormente, iniciar el proceso de reversión de aquellos espacios que correspondan, con el objetivo de brindar la oportunidad a otros comerciantes que sí tengan la voluntad de trabajar en dicho local comercial.</t>
+          <t>La racha criminal sigue en aumento en la región, luego que un joven técnico de celulares fuera asesinado de tres balazos en la cabeza y rostro por un gatillero, que disparó con una pasmosa frialdad, delante de dos amigos, para luego huir en un auto blanco. El asesinato de José Fernando Castillo Quevedo, de 24 años, ocurrió cerca de las nueve de la noche del pasado martes frente al bar “Pikaflor”, ubicado en la Asociación Villa Universitaria, sector norteste de Castilla. Hasta ese lugar llegó la Policía para iniciar las investigaciones. ESCALOFRIANTE DATA Con este episodio escaló a 106 los asesinatos ocurridos en lo que va del año en la región, siendo la mayoría de casos por la modalidad de sicariato (o crimenes por encargo). Cabe resaltar que en 2025 se registraron 107 homicidios en el lapso de enero a setiembre. Cabe precisar que en menos de 72 horas han ocurrido siete homicidios: dos mujeres, un varón y un menor de 13 años en Sullana, otro caso en Talara. De igual manera uno en Paita Alta y el último registrado en Castilla, contra José Fernando Castillo. IMÁGENES CLAVES El asesinato del joven técnico de equipos móviles muestra el alto grado de peligrosidad que existe en las calles. Precisamente una cámara de seguridad muestra que ya no se puede confian en nadie, luego que en escena se observa a José Fernando Castillo platicando con dos personas, que serían amigos. Según las imágenes de las cámaras de seguridad, Castillo Quevedo y dos sujetos, en la vía públlica, observan un celular. De pronto, se aprecia la salida de un individuo desconocido para subir apuradamente a un automóvil blanco y dar arranque. TODOS SE CONOCÍAN En ese momento, se oberva la llegada de un gatillero que vestía polo verde y bermuda blu jeans, quien se acerca a los tres amigos y dispara tres veces contra José Fernando Castillo, luego con pistola en mano camina y sube al mencionado vehículo blanco. Del mismo modo se distingue que uno de los dos individuos, que estaba conversando con la víctima mortal abordó el mismo vehículo en el que huyó el atacante. La Policía continúa con las investigaciones para esclarecer el crimen, identificar a los involucrados y determinar las circunstancias del asesinato.</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>https://eltiempo.pe/local/comerciantes-del-complejo-de-mercados-de-piura-solicitan-administracion-de-parqueos/</t>
+          <t>https://eltiempo.pe/local/quien-responde-por-los-106-muertos-en-la-region-piura-nuevo-asesinato-se-consuma-en-castilla/</t>
         </is>
       </c>
     </row>
@@ -852,17 +852,17 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Burocracia retrasa obras de emergencia por el Fenómeno El Niño</t>
+          <t>Comerciantes del Complejo de Mercados de Piura solicitan administración de parqueos</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Mientras que entidades oficiales como Enfen y Senamhi advierten de un Fenómeno El Niño de “magnitud fuerte” o “extraordinario”; el empresariado piurano aún sigue a la espera que Proinversión defina los proyectos que se van ejecutar a través de la modalidad de “servicios por impuestos”. Se trata de 18 propuestas que han hecho llegar a Proinversión, según lo informó la gerente general de la Cámara de Comercio y Producción de Piura, Susana Seminario, quien ayer aprovechó la presencia de los ministros de Desarrollo Agrario y Riego, Marco Vinelli; del ministro de Defensa, Rafael Belaúnde Llosa y de otras autoridades que participaron de la reunión de trabajo de la Plataforma de Defensa Civil para pedir celeridad en los trámites y los proyectos se pueden iniciar cuanto antes en aras de mitigar el impacto del FEN. S/ 130 millones La empresaria también dio a conocer que disponen de 130 millones de soles en impuestos para ser ejecutados en los proyectos de emergencia. Chutuque La ampliación del canal de Chutuque es una de las prioridades de los empresarios para evitar una posible inundación. Mientras días atrás el presidente de la Camco, Javier Bereche, señalaba que se trata de “un canal de 6.7 kilómetros de roca y eso hay que volarlo”, ayer el titular del Midagri remarcó que dentro de dos o tres días se iniciarán los trabajos, pero solo limpiarán 5 kilómetros que iniciarán en el distrito de Cristo Nos Valga y terminarán en Sechura. “Es lo que se puede garantizar y cumplir”, subrayó. Bajo Piura Sobre el reclamo del Bajo Piura que demanda más maquinaria para los trabajos de descolmatación, el ministro Vinelli aseguró que en los próximos días llegará más maquinaria aguas abajo del puente Grau. Para 3,900 m3/s Vinelli también dio a conocer que los trabajos de descolmatación tienen un avance del 42% en el tramo entre la represa Los Ejidos y el puente Bolognesi y el objetivo es ampliar la capacidad de la caja hidráulica a 3.900 metros cúbicos por segundo (m3/s); sin embargo, el supervisor de los trabajos indicó un día antes que la proyección es para 3.000 m3/s. Ayuda humanitaria Finalmente se dio a conocer que actualmente se cuenta con 725 toneladas de ayuda humanitaria en el almacén central y 113 toneladas distribuidas en 17 almacenes adelantados, además de 51 motobombas en mantenimiento y la planificación para incorporar otras 70. Solo priorizan 69 establecimientos de salud Durante la reunión realizada en el Gobierno Regional, también se dio a conocer sobre la intervención de establecimientos de salud para mitigar el impacto del FEN. Sin embargo, se informó que de los 438 establecimientos de salud existentes en la región, 269 requieren algún tipo de intervención y se han priorizado 69. Asimismo, se informó sobre la coordinación para implementar un hospital temporal de 104 camas en la Universidad de Piura, además del fortalecimiento de brigadas, equipos de fumigación, ambulancias y acciones de prevención frente al dengue. Sobre las vacunas, el titular del Midagri aseguró que llegará otro lote de 50 mil vacunas contra el dengue.</t>
+          <t>A través de Resolución de Alcaldía N° 0592-2026, la Municipalidad Provincial de Piura ha dispuesto la conformación de una Comisión técnica multidisciplinaria para que evalué la viabilidad jurídica, técnica, económica, financiera, patrimonial y administrativa sobre la propuesta presentada por la Asociación regional de mercados de Piura (AREMEPI) referente a la administración de los estacionamientos del Complejo de Mercados. La asociación, que representa a los mercados formales, plantea implementar un modelo de gestión conjunta con la comuna piurana orientado a mejorar la administración del servicio, reducir los costos operativos y generar recursos económicos destinados a financiar proyectos estratégicos para el ordenamiento urbano del propio centro de abastos de la ciudad. La gerente de Desarrollo Económico, Ruth Oliva, señaló que hay voluntad política para evaluar el pedido de los comerciantes, por lo que se tendrá que esperar los informes técnicos para la toma de decisiones. REVERSIÓN La funcionaria también dio a conocer que realizaron una inspección en el Mercado San Miguel y constataron una vez más que varios puestos se encuentran cerrados. Indicó que este tipo de acciones que vienen realizando permitirán identificar los puestos que no cumplen con las disposiciones establecidas y, posteriormente, iniciar el proceso de reversión de aquellos espacios que correspondan, con el objetivo de brindar la oportunidad a otros comerciantes que sí tengan la voluntad de trabajar en dicho local comercial.</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>https://eltiempo.pe/local/burocracia-retrasa-obras-de-emergencia-por-el-fenomeno-el-nino/</t>
+          <t>https://eltiempo.pe/local/comerciantes-del-complejo-de-mercados-de-piura-solicitan-administracion-de-parqueos/</t>
         </is>
       </c>
     </row>
@@ -873,21 +873,21 @@
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Piura: en menos de 72 horas, delincuentes asesinan a ocho personas en la región</t>
+          <t>Burocracia retrasa obras de emergencia por el Fenómeno El Niño</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>La violencia criminal golpeó nuevamente a la región Piura . En menos de 72 horas, ocho personas fueron asesinadas en distintos hechos registrados en Sullana, Castilla, Paita y Talara. Entre las víctimas se encuentra un menor de 13 años y tres personas que murieron durante un ataque armado ocurrido en el asentamiento humano Manuel Seoane, en Sullana. Los homicidios se registraron entre la noche del domingo 6 y el lunes 7 de setiembre, en una seguidilla de hechos violentos que también dejó personas heridas y motivó operativos policiales en diferentes puntos de la región. Los casos presentan características similares, como el uso de armas de fuego y, en algunos ataques, la participación de sujetos que se movilizaban en motocicletas. Sin embargo, hasta el momento no existe información oficial que permita establecer que todos los crímenes estén relacionados. ¿Quiénes son las ocho víctimas asesinadas en Piura? El balance de los hechos registrados en este periodo incluye a Alexis Arellano Gómez , asesinado en el sector Salaverry de Sullana; Fernando Castillo , víctima de un ataque en Castilla; y Giancarlo Jiménez Hernández , asesinado en Paita Alta. A ellos se suma un adolescente de 13 años , asesinado la noche del domingo en Sullana. También figuran las tres víctimas mortales del ataque ocurrido la noche del lunes en Manuel Seoane: Sheyla Viera Elías, Lady Lore Valdiviezo Nole y Daniel Alfonso Páucar Manchay . El octavo caso corresponde a un hombre conocido como “Van Dan” , quien había trabajado como sereno y fue asesinado en el distrito de La Brea-Negritos, en la provincia de Talara. Sullana: asesinan a menor de 13 años en un mototaxi Uno de los casos que más conmoción provocó ocurrió la noche del domingo en Sullana. Un adolescente de 13 años fue asesinado cuando viajaba como pasajero en un mototaxi por la intersección de la calle Túpac Amaru con la avenida Par Vial, en el asentamiento humano 17 de Enero. El ataque ocurrió aproximadamente a las 10:40 de la noche. Según las primeras diligencias, el vehículo habría quedado detenido debido a un desperfecto mecánico. En ese momento, sujetos que se desplazaban en una motocicleta llegaron hasta el mototaxi y dispararon contra el menor. Uno de los proyectiles impactó en su cabeza y le provocó la muerte en el lugar. Sus acompañantes huyeron de la zona, mientras la víctima quedó junto al vehículo. Un tatuaje permitió identificar al adolescente La identificación del menor se realizó posteriormente en la morgue legal. Una familiar acudió ante las autoridades y logró reconocerlo por un tatuaje que llevaba en el brazo derecho con el nombre “Alexander”. La Policía continúa con las diligencias para establecer las circunstancias exactas del crimen. Entre las hipótesis preliminares figura un posible ajuste de cuentas, aunque esta versión todavía debe ser corroborada por los investigadores. Alexis Arellano Gómez fue asesinado en Sullana Otro de los homicidios registrados durante este periodo ocurrió en el sector Salaverry, en Sullana. La víctima fue identificada como Alexis Arellano Gómez . El asesinato forma parte de los hechos violentos registrados durante estas horas en la provincia. La Policía inició las diligencias correspondientes para recoger evidencias, identificar a los responsables y establecer el móvil del ataque. Fernando Castillo fue asesinado en Castilla La ola de violencia también alcanzó Castilla, en la provincia de Piura. Fernando Castillo fue asesinado en circunstancias que son investigadas por las autoridades. El caso se suma a los demás homicidios registrados en la región durante el mismo periodo. Los agentes buscan reconstruir los momentos previos al crimen y determinar quiénes participaron en el ataque. Paita: asesinan a Giancarlo Jiménez Hernández En Paita Alta, Giancarlo Jiménez Hernández, de 33 años , fue asesinado la noche del lunes durante un ataque perpetrado por sujetos que se movilizaban en una motocicleta. El joven caminaba junto a William Daniel Aldana Prado , de 24 años, por la parte posterior de las empresas de transporte Andrea y Santangel cuando fueron interceptados. Según la información preliminar, el pasajero de la motocicleta sacó un arma de fuego y disparó contra ambos. Los heridos fueron trasladados de emergencia al Hospital Nuestra Señora de las Mercedes. Sin embargo, el médico de turno certificó la muerte de Giancarlo Jiménez debido a una hemorragia intracraneal provocada por un proyectil de arma de fuego. William Aldana quedó gravemente herido y permanecía con pronóstico reservado. Dos sospechosos fueron capturados Tras el ataque, agentes de la Comisaría Ciudad del Pescador iniciaron la búsqueda de los responsables. La motocicleta fue ubicada en inmediaciones del colegio Lunitas de Paita y los policías iniciaron una persecución. El conductor, identificado con las iniciales C. A. T. D., de 20 años, fue intervenido. De acuerdo con la información proporcionada, durante el operativo se le encontró un cartucho de dinamita. El pasajero huyó a pie y, según la versión policial, realizó disparos contra los agentes antes de refugiarse en una vivienda. Finalmente fue detenido e identificado con las iniciales L. J. Ch. N., de 25 años. Los agentes le habrían encontrado un arma de fuego. Talara: exsereno es asesinado dentro de un restaurante Otro de los crímenes ocurrió en la provincia de Talara. Un hombre conocido como “Van Dan” , quien había trabajado como sereno y era propietario de un gimnasio en el distrito de La Brea-Negritos, fue asesinado dentro del restaurante La Caleta 10, ubicado en el asentamiento Mario Aguirre. Según la información preliminar, un sujeto irrumpió en el segundo piso del establecimiento y disparó varias veces contra la víctima. El hombre murió pocos segundos después del ataque. La Policía investiga las circunstancias del homicidio y busca establecer si existieron amenazas previas, conflictos personales u otros elementos que permitan determinar el móvil. Sullana: tres personas mueren en ataque armado en Manuel Seoane La noche del lunes 7 de setiembre, un ataque armado registrado en un puesto de venta de comida ubicado en el pasaje Municipal del asentamiento humano Manuel Seoane, en Sullana, dejó tres personas fallecidas y una herida de gravedad . De acuerdo con la información preliminar, varios sujetos armados llegaron hasta el establecimiento y dispararon contra un grupo de personas que se encontraba reunido alrededor de una mesa. Como consecuencia del atentado perdieron la vida Sheyla Viera Elías, Lady Lore Valdiviezo Nole y Daniel Alfonso Páucar Manchay . Asimismo, Carlos Daniel Cornejo Lupú resultó gravemente herido y fue trasladado a un establecimiento de salud para recibir atención médica. Criminalística recogió evidencias en la escena Tras el ataque, agentes de la División de Investigación Criminal (Divincri) y personal de Criminalística acudieron al lugar para realizar las diligencias correspondientes. Los especialistas recogieron evidencias e indicios balísticos que podrían ayudar a reconstruir el ataque e identificar a los responsables. Las autoridades también iniciaron las investigaciones para determinar el móvil del triple homicidio. Una de las víctimas estaba embarazada Entre las víctimas se encontraba Lady Lore Valdiviezo Nole, de 28 años , quien tenía aproximadamente seis meses de gestación. De acuerdo con la información proporcionada por sus familiares, la joven se dedicaba a la venta de parrilladas y hamburguesas durante fiestas, aniversarios y actividades patronales. Su hermana Greysi relató que ambas venían preparando actividades comerciales relacionadas con el aniversario del distrito de Ignacio Escudero. Según su versión, Loren había salido inicialmente de la vivienda donde ocurrió el ataque, pero decidió regresar. Poco después se escucharon los disparos. La familia pidió a las autoridades esclarecer el crimen y determinar quiénes estuvieron detrás del ataque. ¿Qué investiga la Policía tras los ocho asesinatos? Los ocho homicidios registrados en este periodo ocurrieron en diferentes puntos de Piura. Por ello, las autoridades deberán determinar si existe alguna relación entre los casos o si se trata de hechos independientes. El uso de armas de fuego y la participación de motocicletas en algunos de los ataques son elementos que forman parte de las diligencias. No obstante, establecer una conexión entre los crímenes requiere evidencias que todavía están siendo recopiladas. Piura permanece bajo medidas contra la criminalidad Los nuevos asesinatos se producen mientras diferentes sectores de la región permanecen bajo medidas especiales frente al incremento de la inseguridad. El Gobierno declaró el estado de emergencia en Piura, Castilla, Veintiséis de Octubre y Catacaos mediante el Decreto Supremo N.° 126-2026. Para el exjefe de la Región Policial de Piura, coronel en retiro Máximo Vargas Hugo, este tipo de medidas no ha generado los resultados que reclama la población. El exmando policial consideró necesario fortalecer la labor policial con recursos, logística e inteligencia. “La población quiere seguridad y están repitiendo lo mismo que han hecho gestiones anteriores”, señaló Vargas Hugo al referirse a las declaratorias de emergencia aplicadas en la región. Sobre el cambio en el comando de la Policía, sostuvo que una modificación en el alto mando no garantiza por sí sola mejores resultados y remarcó la necesidad de proporcionar herramientas adecuadas a los agentes para enfrentar a las organizaciones criminales. Por su parte, el general Daniel Jares, jefe de la Región Policial Piura, informó que durante los primeros días de setiembre se habían contabilizado 12 personas asesinadas . Esta cifra corresponde a un periodo más amplio y no debe confundirse con los ocho homicidios registrados en menos de 72 horas detallados en este reporte.</t>
+          <t>Mientras que entidades oficiales como Enfen y Senamhi advierten de un Fenómeno El Niño de “magnitud fuerte” o “extraordinario”; el empresariado piurano aún sigue a la espera que Proinversión defina los proyectos que se van ejecutar a través de la modalidad de “servicios por impuestos”. Se trata de 18 propuestas que han hecho llegar a Proinversión, según lo informó la gerente general de la Cámara de Comercio y Producción de Piura, Susana Seminario, quien ayer aprovechó la presencia de los ministros de Desarrollo Agrario y Riego, Marco Vinelli; del ministro de Defensa, Rafael Belaúnde Llosa y de otras autoridades que participaron de la reunión de trabajo de la Plataforma de Defensa Civil para pedir celeridad en los trámites y los proyectos se pueden iniciar cuanto antes en aras de mitigar el impacto del FEN. S/ 130 millones La empresaria también dio a conocer que disponen de 130 millones de soles en impuestos para ser ejecutados en los proyectos de emergencia. Chutuque La ampliación del canal de Chutuque es una de las prioridades de los empresarios para evitar una posible inundación. Mientras días atrás el presidente de la Camco, Javier Bereche, señalaba que se trata de “un canal de 6.7 kilómetros de roca y eso hay que volarlo”, ayer el titular del Midagri remarcó que dentro de dos o tres días se iniciarán los trabajos, pero solo limpiarán 5 kilómetros que iniciarán en el distrito de Cristo Nos Valga y terminarán en Sechura. “Es lo que se puede garantizar y cumplir”, subrayó. Bajo Piura Sobre el reclamo del Bajo Piura que demanda más maquinaria para los trabajos de descolmatación, el ministro Vinelli aseguró que en los próximos días llegará más maquinaria aguas abajo del puente Grau. Para 3,900 m3/s Vinelli también dio a conocer que los trabajos de descolmatación tienen un avance del 42% en el tramo entre la represa Los Ejidos y el puente Bolognesi y el objetivo es ampliar la capacidad de la caja hidráulica a 3.900 metros cúbicos por segundo (m3/s); sin embargo, el supervisor de los trabajos indicó un día antes que la proyección es para 3.000 m3/s. Ayuda humanitaria Finalmente se dio a conocer que actualmente se cuenta con 725 toneladas de ayuda humanitaria en el almacén central y 113 toneladas distribuidas en 17 almacenes adelantados, además de 51 motobombas en mantenimiento y la planificación para incorporar otras 70. Solo priorizan 69 establecimientos de salud Durante la reunión realizada en el Gobierno Regional, también se dio a conocer sobre la intervención de establecimientos de salud para mitigar el impacto del FEN. Sin embargo, se informó que de los 438 establecimientos de salud existentes en la región, 269 requieren algún tipo de intervención y se han priorizado 69. Asimismo, se informó sobre la coordinación para implementar un hospital temporal de 104 camas en la Universidad de Piura, además del fortalecimiento de brigadas, equipos de fumigación, ambulancias y acciones de prevención frente al dengue. Sobre las vacunas, el titular del Midagri aseguró que llegará otro lote de 50 mil vacunas contra el dengue.</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>https://eltiempo.pe/local/piura-en-menos-de-72-horas-delincuentes-asesinan-a-ocho-personas-en-la-region/</t>
+          <t>https://eltiempo.pe/local/burocracia-retrasa-obras-de-emergencia-por-el-fenomeno-el-nino/</t>
         </is>
       </c>
     </row>
@@ -902,17 +902,17 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>ODPE Piura recibe material para capacitar a actores electorales</t>
+          <t>Piura: en menos de 72 horas, delincuentes asesinan a ocho personas en la región</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>En el marco de las Elecciones Regionales y Municipales (ERM) 2026, la Oficina Descentralizada de Procesos Electorales (ODPE) Piura recibió el material de capacitación que será empleado en la preparación de los diversos actores electorales que participarán en los comicios del próximo 4 de octubre. Puedes Leer | Bajo Piura se levanta y exige obras para evitar inundación El cargamento, remitido desde el almacén central de la Gerencia de Gestión Electoral de la ONPE en Lurín, arribó a la sede de la ODPE Piura bajo protocolos de seguridad y resguardo para su inmediata verificación, almacenamiento y posterior distribución en los distritos y centros poblados bajo su jurisdicción. Entre los instrumentos recibidos se encuentran materiales pedagógicos que replican con exactitud las condiciones de una mesa de sufragio, los cuales serán utilizados en los talleres que se desarrollarán en las oficinas distritales de la circunscripción electoral, así como en las jornadas masivas de capacitación a miembros de mesa programadas para los días 20 y 27 de setiembre. Asimismo, arribó insumos didácticos dirigidos a los talleres de formación de capacitadores electorales, coordinadores distritales, coordinadores de local de votación y personal de campo que desplegará acciones informativas en los distritos. Mira También | Advierten incremento de casos de cáncer infantil en Piura El jefe de la ODPE Piura, Juan Roel Godofredo Valdivia, señaló que la preparación de los actores electorales constituye una etapa fundamental para garantizar el adecuado desarrollo de los comicios y destacó la importancia de que quienes participarán en la jornada conozcan oportunamente las tareas y responsabilidades que deberán cumplir. Para estos comicios, el organismo electoral instalará en los distritos Piura y Veintiséis de Octubre un total de 884 mesas de sufragio en 67 locales de votación, donde están llamados a sufragar aproximadamente 264 809 electores hábiles. Más información https://erm2026.onpe.gob.pe</t>
+          <t>La violencia criminal golpeó nuevamente a la región Piura . En menos de 72 horas, ocho personas fueron asesinadas en distintos hechos registrados en Sullana, Castilla, Paita y Talara. Entre las víctimas se encuentra un menor de 13 años y tres personas que murieron durante un ataque armado ocurrido en el asentamiento humano Manuel Seoane, en Sullana. Los homicidios se registraron entre la noche del domingo 6 y el lunes 7 de setiembre, en una seguidilla de hechos violentos que también dejó personas heridas y motivó operativos policiales en diferentes puntos de la región. Los casos presentan características similares, como el uso de armas de fuego y, en algunos ataques, la participación de sujetos que se movilizaban en motocicletas. Sin embargo, hasta el momento no existe información oficial que permita establecer que todos los crímenes estén relacionados. ¿Quiénes son las ocho víctimas asesinadas en Piura? El balance de los hechos registrados en este periodo incluye a Alexis Arellano Gómez , asesinado en el sector Salaverry de Sullana; Fernando Castillo , víctima de un ataque en Castilla; y Giancarlo Jiménez Hernández , asesinado en Paita Alta. A ellos se suma un adolescente de 13 años , asesinado la noche del domingo en Sullana. También figuran las tres víctimas mortales del ataque ocurrido la noche del lunes en Manuel Seoane: Sheyla Viera Elías, Lady Lore Valdiviezo Nole y Daniel Alfonso Páucar Manchay . El octavo caso corresponde a un hombre conocido como “Van Dan” , quien había trabajado como sereno y fue asesinado en el distrito de La Brea-Negritos, en la provincia de Talara. Sullana: asesinan a menor de 13 años en un mototaxi Uno de los casos que más conmoción provocó ocurrió la noche del domingo en Sullana. Un adolescente de 13 años fue asesinado cuando viajaba como pasajero en un mototaxi por la intersección de la calle Túpac Amaru con la avenida Par Vial, en el asentamiento humano 17 de Enero. El ataque ocurrió aproximadamente a las 10:40 de la noche. Según las primeras diligencias, el vehículo habría quedado detenido debido a un desperfecto mecánico. En ese momento, sujetos que se desplazaban en una motocicleta llegaron hasta el mototaxi y dispararon contra el menor. Uno de los proyectiles impactó en su cabeza y le provocó la muerte en el lugar. Sus acompañantes huyeron de la zona, mientras la víctima quedó junto al vehículo. Un tatuaje permitió identificar al adolescente La identificación del menor se realizó posteriormente en la morgue legal. Una familiar acudió ante las autoridades y logró reconocerlo por un tatuaje que llevaba en el brazo derecho con el nombre “Alexander”. La Policía continúa con las diligencias para establecer las circunstancias exactas del crimen. Entre las hipótesis preliminares figura un posible ajuste de cuentas, aunque esta versión todavía debe ser corroborada por los investigadores. Alexis Arellano Gómez fue asesinado en Sullana Otro de los homicidios registrados durante este periodo ocurrió en el sector Salaverry, en Sullana. La víctima fue identificada como Alexis Arellano Gómez . El asesinato forma parte de los hechos violentos registrados durante estas horas en la provincia. La Policía inició las diligencias correspondientes para recoger evidencias, identificar a los responsables y establecer el móvil del ataque. Fernando Castillo fue asesinado en Castilla La ola de violencia también alcanzó Castilla, en la provincia de Piura. Fernando Castillo fue asesinado en circunstancias que son investigadas por las autoridades. El caso se suma a los demás homicidios registrados en la región durante el mismo periodo. Los agentes buscan reconstruir los momentos previos al crimen y determinar quiénes participaron en el ataque. Paita: asesinan a Giancarlo Jiménez Hernández En Paita Alta, Giancarlo Jiménez Hernández, de 33 años , fue asesinado la noche del lunes durante un ataque perpetrado por sujetos que se movilizaban en una motocicleta. El joven caminaba junto a William Daniel Aldana Prado , de 24 años, por la parte posterior de las empresas de transporte Andrea y Santangel cuando fueron interceptados. Según la información preliminar, el pasajero de la motocicleta sacó un arma de fuego y disparó contra ambos. Los heridos fueron trasladados de emergencia al Hospital Nuestra Señora de las Mercedes. Sin embargo, el médico de turno certificó la muerte de Giancarlo Jiménez debido a una hemorragia intracraneal provocada por un proyectil de arma de fuego. William Aldana quedó gravemente herido y permanecía con pronóstico reservado. Dos sospechosos fueron capturados Tras el ataque, agentes de la Comisaría Ciudad del Pescador iniciaron la búsqueda de los responsables. La motocicleta fue ubicada en inmediaciones del colegio Lunitas de Paita y los policías iniciaron una persecución. El conductor, identificado con las iniciales C. A. T. D., de 20 años, fue intervenido. De acuerdo con la información proporcionada, durante el operativo se le encontró un cartucho de dinamita. El pasajero huyó a pie y, según la versión policial, realizó disparos contra los agentes antes de refugiarse en una vivienda. Finalmente fue detenido e identificado con las iniciales L. J. Ch. N., de 25 años. Los agentes le habrían encontrado un arma de fuego. Talara: exsereno es asesinado dentro de un restaurante Otro de los crímenes ocurrió en la provincia de Talara. Un hombre conocido como “Van Dan” , quien había trabajado como sereno y era propietario de un gimnasio en el distrito de La Brea-Negritos, fue asesinado dentro del restaurante La Caleta 10, ubicado en el asentamiento Mario Aguirre. Según la información preliminar, un sujeto irrumpió en el segundo piso del establecimiento y disparó varias veces contra la víctima. El hombre murió pocos segundos después del ataque. La Policía investiga las circunstancias del homicidio y busca establecer si existieron amenazas previas, conflictos personales u otros elementos que permitan determinar el móvil. Sullana: tres personas mueren en ataque armado en Manuel Seoane La noche del lunes 7 de setiembre, un ataque armado registrado en un puesto de venta de comida ubicado en el pasaje Municipal del asentamiento humano Manuel Seoane, en Sullana, dejó tres personas fallecidas y una herida de gravedad . De acuerdo con la información preliminar, varios sujetos armados llegaron hasta el establecimiento y dispararon contra un grupo de personas que se encontraba reunido alrededor de una mesa. Como consecuencia del atentado perdieron la vida Sheyla Viera Elías, Lady Lore Valdiviezo Nole y Daniel Alfonso Páucar Manchay . Asimismo, Carlos Daniel Cornejo Lupú resultó gravemente herido y fue trasladado a un establecimiento de salud para recibir atención médica. Criminalística recogió evidencias en la escena Tras el ataque, agentes de la División de Investigación Criminal (Divincri) y personal de Criminalística acudieron al lugar para realizar las diligencias correspondientes. Los especialistas recogieron evidencias e indicios balísticos que podrían ayudar a reconstruir el ataque e identificar a los responsables. Las autoridades también iniciaron las investigaciones para determinar el móvil del triple homicidio. Una de las víctimas estaba embarazada Entre las víctimas se encontraba Lady Lore Valdiviezo Nole, de 28 años , quien tenía aproximadamente seis meses de gestación. De acuerdo con la información proporcionada por sus familiares, la joven se dedicaba a la venta de parrilladas y hamburguesas durante fiestas, aniversarios y actividades patronales. Su hermana Greysi relató que ambas venían preparando actividades comerciales relacionadas con el aniversario del distrito de Ignacio Escudero. Según su versión, Loren había salido inicialmente de la vivienda donde ocurrió el ataque, pero decidió regresar. Poco después se escucharon los disparos. La familia pidió a las autoridades esclarecer el crimen y determinar quiénes estuvieron detrás del ataque. ¿Qué investiga la Policía tras los ocho asesinatos? Los ocho homicidios registrados en este periodo ocurrieron en diferentes puntos de Piura. Por ello, las autoridades deberán determinar si existe alguna relación entre los casos o si se trata de hechos independientes. El uso de armas de fuego y la participación de motocicletas en algunos de los ataques son elementos que forman parte de las diligencias. No obstante, establecer una conexión entre los crímenes requiere evidencias que todavía están siendo recopiladas. Piura permanece bajo medidas contra la criminalidad Los nuevos asesinatos se producen mientras diferentes sectores de la región permanecen bajo medidas especiales frente al incremento de la inseguridad. El Gobierno declaró el estado de emergencia en Piura, Castilla, Veintiséis de Octubre y Catacaos mediante el Decreto Supremo N.° 126-2026. Para el exjefe de la Región Policial de Piura, coronel en retiro Máximo Vargas Hugo, este tipo de medidas no ha generado los resultados que reclama la población. El exmando policial consideró necesario fortalecer la labor policial con recursos, logística e inteligencia. “La población quiere seguridad y están repitiendo lo mismo que han hecho gestiones anteriores”, señaló Vargas Hugo al referirse a las declaratorias de emergencia aplicadas en la región. Sobre el cambio en el comando de la Policía, sostuvo que una modificación en el alto mando no garantiza por sí sola mejores resultados y remarcó la necesidad de proporcionar herramientas adecuadas a los agentes para enfrentar a las organizaciones criminales. Por su parte, el general Daniel Jares, jefe de la Región Policial Piura, informó que durante los primeros días de setiembre se habían contabilizado 12 personas asesinadas . Esta cifra corresponde a un periodo más amplio y no debe confundirse con los ocho homicidios registrados en menos de 72 horas detallados en este reporte.</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>https://eltiempo.pe/local/odpe-piura-recibe-material-para-capacitar-a-actores-electorales/</t>
+          <t>https://eltiempo.pe/local/piura-en-menos-de-72-horas-delincuentes-asesinan-a-ocho-personas-en-la-region/</t>
         </is>
       </c>
     </row>
@@ -1073,21 +1073,21 @@
         </is>
       </c>
       <c r="B24" s="2" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>El Niño superaría al de 1998 y traería impactos “insospechados” en la región Piura</t>
+          <t>ODPE Piura recibe material para capacitar a actores electorales</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>El fenómeno “El Niño” (FEN) sigue acumulando energía en el mar frente a las costas de la región y los impactos de este calentamiento son hasta el momento insospechados, según informó el especialista en meteorología del Senamhi Piura, Héctor Yauli. PUEDES LEER ► Es hora de rescatar la cultura de Piura De lo que sí se tiene mayor certeza es que los indicadores de este fenómeno en desarrollo ya superaron los valores previos al Mega Niño que castigó la región entre los años 1997 y 1998. “Lo que ha dicho el Organismo Mundial de Meteorología es que los impactos que pueda generar este Niño en el contexto en el cual se presenta, porque el nivel de calentamiento es muy exacerbado y no se tiene comparación con los años 1997 y 1998. Es una gran cantidad de energía y calor no solamente en la zona tropical donde se desarrolla El Niño sino en todos los océanos el nivel de calentamiento es muy mayor. Se esperan impactos insospechados por la alta incertidumbre que hay. [...] Lo que sí tenemos mucha seguridad es en cuanto a que se van a presentar lluvias bastante fuertes e intensas en los meses de verano”, manifestó. Sobre la magnitud, Yauri indicó que existe una incertidumbre sobre los niveles que se alcanzarán las precipitaciones. Cabe indicar que durante el Mega Niño de 1998, se registró la máxima precipitación el 24 de enero con un valor de 173.6 milímetros de acumulado en una sola lluvia. Esto implica que ese día cayeron más de 173 litros de agua sobre un metro cuadrado. Peores En este punto, Yauli informó que el escenario es mucho más complicado porque no solo es un calentamiento del mar frente a la costa norte, sino en diferentes partes del mundo. “Es un nivel de calentamiento exacerbado que no tiene comparación. Si nos situamos en septiembre de 1997, solamente veíamos el calentamiento de El Niño, pero el océano Pacífico en el norte estaba en condiciones normales, en Chile estaba normal y en el Atlántico igual. Sin embargo, ahora está caliente el norte y sur del Pacífico, e incluso en el Atlántico también está caliente y eso trae otras implicancias y diferente tipo de impactos vinculados a que habrá mucha lluvia en la zona norte del Perú y bastante deficiencia de lluvias en la zona noroeste de Brasil”, destacó Yauli.</t>
+          <t>En el marco de las Elecciones Regionales y Municipales (ERM) 2026, la Oficina Descentralizada de Procesos Electorales (ODPE) Piura recibió el material de capacitación que será empleado en la preparación de los diversos actores electorales que participarán en los comicios del próximo 4 de octubre. Puedes Leer | Bajo Piura se levanta y exige obras para evitar inundación El cargamento, remitido desde el almacén central de la Gerencia de Gestión Electoral de la ONPE en Lurín, arribó a la sede de la ODPE Piura bajo protocolos de seguridad y resguardo para su inmediata verificación, almacenamiento y posterior distribución en los distritos y centros poblados bajo su jurisdicción. Entre los instrumentos recibidos se encuentran materiales pedagógicos que replican con exactitud las condiciones de una mesa de sufragio, los cuales serán utilizados en los talleres que se desarrollarán en las oficinas distritales de la circunscripción electoral, así como en las jornadas masivas de capacitación a miembros de mesa programadas para los días 20 y 27 de setiembre. Asimismo, arribó insumos didácticos dirigidos a los talleres de formación de capacitadores electorales, coordinadores distritales, coordinadores de local de votación y personal de campo que desplegará acciones informativas en los distritos. Mira También | Advierten incremento de casos de cáncer infantil en Piura El jefe de la ODPE Piura, Juan Roel Godofredo Valdivia, señaló que la preparación de los actores electorales constituye una etapa fundamental para garantizar el adecuado desarrollo de los comicios y destacó la importancia de que quienes participarán en la jornada conozcan oportunamente las tareas y responsabilidades que deberán cumplir. Para estos comicios, el organismo electoral instalará en los distritos Piura y Veintiséis de Octubre un total de 884 mesas de sufragio en 67 locales de votación, donde están llamados a sufragar aproximadamente 264 809 electores hábiles. Más información https://erm2026.onpe.gob.pe</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>https://eltiempo.pe/local/el-nino-traera-unos-impactos-insospechados-en-la-region-piura/</t>
+          <t>https://eltiempo.pe/local/odpe-piura-recibe-material-para-capacitar-a-actores-electorales/</t>
         </is>
       </c>
     </row>
@@ -1102,17 +1102,17 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Los SARE siguen sin mantenimiento para funcionar durante las lluvias</t>
+          <t>El Niño superaría al de 1998 y traería impactos “insospechados” en la región Piura</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Diferentes informes de las oficinas de control institucional del Programa Nacional de Saneamiento Urbano (PNSU) dan cuenta del estado de abandono en su mantenimiento de los Sistemas Alternativos de Recolección y Evacuación de aguas de lluvia (SARE) que se habilitaron en Piura y que costaron millones de soles. Un ejemplo es lo que ocurre en el SARE Cinco Esquinas que costó más de 28 millones de soles, pero ni siquiera tiene un cerco perimétrico para proteger los costosos equipos instalados a pesar de los años pasados. “El grupo electrógeno y la electrobomba constituyen equipos necesarios para el funcionamiento del sistema de bombeo y la evacuación, por lo que su exposición en un área sin control físico permanente de acceso podría afectar su seguridad, conservación y disponibilidad cuando sean requeridos para la operación del SARE”, se lee en el informe de control. De otro lado, el SARE de Ignacio Merino, valorizado en 15 millones de soles, también tiene problemas de falta de mantenimiento. “La falta de culminación de la transferencia legal integral y la ausencia de un marco procedimental que regule las obligaciones de custodia operativa provisoria han provocado que un sistema pluvial de gran inversión (S/ 17.1 millones) no registre ningún tipo de mantenimiento preventivo sobre sus componentes críticos. Esto neutraliza la capacidad de respuesta instalada para salvaguardar a las urbanizaciones del distrito de Piura”, se indica en el documento de Contraloría. Entre las principales observaciones se tiene la acumulación de sedimentos en canaletas cunetas de las vías.</t>
+          <t>El fenómeno “El Niño” (FEN) sigue acumulando energía en el mar frente a las costas de la región y los impactos de este calentamiento son hasta el momento insospechados, según informó el especialista en meteorología del Senamhi Piura, Héctor Yauli. PUEDES LEER ► Es hora de rescatar la cultura de Piura De lo que sí se tiene mayor certeza es que los indicadores de este fenómeno en desarrollo ya superaron los valores previos al Mega Niño que castigó la región entre los años 1997 y 1998. “Lo que ha dicho el Organismo Mundial de Meteorología es que los impactos que pueda generar este Niño en el contexto en el cual se presenta, porque el nivel de calentamiento es muy exacerbado y no se tiene comparación con los años 1997 y 1998. Es una gran cantidad de energía y calor no solamente en la zona tropical donde se desarrolla El Niño sino en todos los océanos el nivel de calentamiento es muy mayor. Se esperan impactos insospechados por la alta incertidumbre que hay. [...] Lo que sí tenemos mucha seguridad es en cuanto a que se van a presentar lluvias bastante fuertes e intensas en los meses de verano”, manifestó. Sobre la magnitud, Yauri indicó que existe una incertidumbre sobre los niveles que se alcanzarán las precipitaciones. Cabe indicar que durante el Mega Niño de 1998, se registró la máxima precipitación el 24 de enero con un valor de 173.6 milímetros de acumulado en una sola lluvia. Esto implica que ese día cayeron más de 173 litros de agua sobre un metro cuadrado. Peores En este punto, Yauli informó que el escenario es mucho más complicado porque no solo es un calentamiento del mar frente a la costa norte, sino en diferentes partes del mundo. “Es un nivel de calentamiento exacerbado que no tiene comparación. Si nos situamos en septiembre de 1997, solamente veíamos el calentamiento de El Niño, pero el océano Pacífico en el norte estaba en condiciones normales, en Chile estaba normal y en el Atlántico igual. Sin embargo, ahora está caliente el norte y sur del Pacífico, e incluso en el Atlántico también está caliente y eso trae otras implicancias y diferente tipo de impactos vinculados a que habrá mucha lluvia en la zona norte del Perú y bastante deficiencia de lluvias en la zona noroeste de Brasil”, destacó Yauli.</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>https://eltiempo.pe/local/los-sare-siguen-sin-mantenimiento-para-funcionar-durante-las-lluvias/</t>
+          <t>https://eltiempo.pe/local/el-nino-traera-unos-impactos-insospechados-en-la-region-piura/</t>
         </is>
       </c>
     </row>
@@ -1127,17 +1127,17 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Refuerzan la vigilancia de flamencos en humedales de Sechura</t>
+          <t>Los SARE siguen sin mantenimiento para funcionar durante las lluvias</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Unos 4.800 flamencos chilenos ( Phoenicopterus chilensis ) habrían completado este año su etapa de reproducción y desplazamiento en el Estuario de Virrilá y la laguna La Niña , dos importantes humedales ubicados en la provincia de Sechura , en Piura. El registro fue recogido por el Servicio Nacional Forestal y de Fauna Silvestre (Serfor) , organismo adscrito al Ministerio de Desarrollo Agrario y Riego (Midagri), durante las labores de monitoreo de esta especie migratoria. Debido a la importancia de estos ecosistemas para la reproducción de los flamencos, especialistas del Serfor recorrieron los puntos de anidamiento identificados en los humedales de Sechura . Las acciones forman parte de las labores de vigilancia y seguimiento de la fauna silvestre en Piura. ¿Por qué se refuerza la vigilancia en Sechura? El seguimiento de los flamencos representa un desafío debido a la extensión del territorio y a las características de los humedales. A ello se suma que estas aves no necesariamente utilizan los mismos lugares para construir sus nidos cada año. Por esa razón, los especialistas deben realizar recorridos periódicos para localizar las zonas donde las aves se concentran durante su periodo reproductivo y verificar que no existan situaciones que puedan afectar a los ejemplares. El especialista en fauna silvestre del Serfor, Max Guerra, señaló que es necesario fortalecer las acciones de patrullaje y monitoreo en los espacios de anidamiento, tomando en cuenta tanto las condiciones del territorio como las amenazas que pueden afectar a estas aves. En las intervenciones realizadas en la provincia participaron representantes del Serfor sede Piura , la Fiscalía Especializada en Materia Ambiental de Piura y la Unidad Desconcentrada de Protección de Medio Ambiente de la Policía Nacional del Perú. El trabajo conjunto resulta especialmente importante en una zona donde ya se han registrado casos de afectación a estas aves. En julio de 2025, el Serfor constató la caza ilegal de crías de flamencos chilenos en la laguna del sector La Huaquilla, en Sechura, luego de recibir una alerta. Los especialistas encontraron patas y plumas de polluelos en el lugar. El ciclo reproductivo de los flamencos en Sechura La reproducción de los flamencos chilenos sigue un proceso que se desarrolla durante varios meses. En los humedales de Sechura , la temporada comienza aproximadamente a mediados de abril, cuando las aves empiezan a construir sus nidos. Entre mayo y junio ocurre la postura de los huevos, mientras que durante julio aparecen los primeros polluelos. A partir de la primera semana de agosto, las crías comienzan a desplazarse, una etapa que requiere especial atención por parte de quienes realizan el monitoreo. “Es un lugar alejado, hay mucho territorio que recorrer y se necesita prestar atención cuando están los polluelos; los puntos de anidamiento cambian todos los años”, explicó el guardaparque local Pablo Martínez, quien también destacó la coordinación con el Serfor para realizar los recorridos. ¿Dónde se reproducen los flamencos? El Estuario de Virrilá y la laguna La Niña forman parte de los espacios utilizados por estas aves en la costa norte del Perú. El Serfor ya ha documentado en años anteriores procesos reproductivos y trabajos de seguimiento en ambos lugares. En 2022, por ejemplo, la entidad informó sobre el nacimiento de alrededor de 700 pichones de flamenco chileno en el Estuario de Virrilá. El lugar fue reconocido además como Sitio Ramsar en 2021, debido a su importancia como humedal de relevancia internacional. Un año después, en agosto de 2023, el Serfor realizó el anillamiento de 183 polluelos nacidos en la laguna La Niña. Esta práctica permite identificar a los ejemplares y obtener información sobre sus desplazamientos y los lugares que utilizan durante su vida. El flamenco chileno es una especie migratoria El flamenco chileno utiliza diferentes cuerpos de agua a lo largo de su distribución. Según el Serfor, puede encontrarse en lagunas poco profundas de agua dulce y salada, desde la costa hasta zonas ubicadas a unos 4.800 metros de altitud. Su distribución comprende territorios desde Chile hasta Ecuador , por lo que los ejemplares que nacen en los humedales de Sechura pueden desplazarse posteriormente hacia otras zonas del país o incluso hacia territorios de países vecinos. El anillamiento se ha convertido en una herramienta para conocer mejor estos movimientos. Los registros realizados por especialistas y observadores de aves permiten identificar ejemplares en diferentes puntos y reconstruir parte de sus rutas de desplazamiento. De acuerdo con el Serfor, la especie está clasificada como “Casi Amenazada” . Entre las principales amenazas identificadas figuran la caza ilegal y la degradación de sus hábitats. ¿Qué amenazas enfrentan los flamencos de Sechura? La ubicación alejada de los humedales no elimina los riesgos para estas aves. La caza, la captura y el consumo de fauna silvestre son prácticas que pueden afectar directamente a las poblaciones de flamencos, especialmente durante la temporada en la que permanecen concentrados en las zonas de reproducción. La dificultad para acceder a determinados sectores también obliga a reforzar la vigilancia. Los recorridos permiten identificar nuevos puntos de anidamiento y detectar posibles casos de afectación antes de que el impacto sea mayor. El antecedente de 2025 en La Huaquilla muestra la necesidad de mantener una presencia constante en estos espacios. Para el Serfor, la protección de las áreas donde se reproducen y alimentan las aves requiere coordinación entre autoridades, especialistas y comunidades locales. ¿Cómo reportar un flamenco en situación de riesgo? La ciudadanía puede comunicar al Serfor cualquier caso relacionado con fauna silvestre que se encuentre herida, enferma, fuera de su hábitat o que requiera evaluación e intervención. Según el canal oficial Alerta SERFOR , los ciudadanos deben enviar un mensaje escrito al WhatsApp 947 588 269 , explicando qué ocurrió, dónde se produjo el hecho y cuándo fue observado. También se deben adjuntar fotografías, videos o información de ubicación que ayude a los especialistas a identificar el lugar y evaluar la situación. El Serfor precisa que este canal recibe mensajes escritos y no llamadas telefónicas . Los reportes son derivados a las Administraciones Técnicas Forestales y de Fauna Silvestre según el ámbito correspondiente.</t>
+          <t>Diferentes informes de las oficinas de control institucional del Programa Nacional de Saneamiento Urbano (PNSU) dan cuenta del estado de abandono en su mantenimiento de los Sistemas Alternativos de Recolección y Evacuación de aguas de lluvia (SARE) que se habilitaron en Piura y que costaron millones de soles. Un ejemplo es lo que ocurre en el SARE Cinco Esquinas que costó más de 28 millones de soles, pero ni siquiera tiene un cerco perimétrico para proteger los costosos equipos instalados a pesar de los años pasados. “El grupo electrógeno y la electrobomba constituyen equipos necesarios para el funcionamiento del sistema de bombeo y la evacuación, por lo que su exposición en un área sin control físico permanente de acceso podría afectar su seguridad, conservación y disponibilidad cuando sean requeridos para la operación del SARE”, se lee en el informe de control. De otro lado, el SARE de Ignacio Merino, valorizado en 15 millones de soles, también tiene problemas de falta de mantenimiento. “La falta de culminación de la transferencia legal integral y la ausencia de un marco procedimental que regule las obligaciones de custodia operativa provisoria han provocado que un sistema pluvial de gran inversión (S/ 17.1 millones) no registre ningún tipo de mantenimiento preventivo sobre sus componentes críticos. Esto neutraliza la capacidad de respuesta instalada para salvaguardar a las urbanizaciones del distrito de Piura”, se indica en el documento de Contraloría. Entre las principales observaciones se tiene la acumulación de sedimentos en canaletas cunetas de las vías.</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>https://eltiempo.pe/local/refuerzan-la-vigilancia-de-flamencos-en-humedales-de-sechura/</t>
+          <t>https://eltiempo.pe/local/los-sare-siguen-sin-mantenimiento-para-funcionar-durante-las-lluvias/</t>
         </is>
       </c>
     </row>
@@ -1152,17 +1152,17 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Estado de emergencia en Piura es más de lo mismo</t>
+          <t>Refuerzan la vigilancia de flamencos en humedales de Sechura</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>La emisión del decreto supremo N° 126-2026 con la declaratoria de emergencia en Piura, Castilla, Veintiséis de Octubre y Catacaos para luchar contra la criminalidad, no tuvo mayor impacto en la opinión pública agobiada por la ola criminal que castiga a la región. Según el exjefe de la Región Policial de Piura, Coronel (r) Máximo Vargas Hugo, esta medida es más de lo mismo y casi un calco de lo que hicieron los gobiernos anteriores, sin mayores resultados. “Es evidente que el actual gobierno viene utilizando las medidas de gobiernos anteriores para frenar la criminalidad e inseguridad que se vive [...] realmente no se tiene los resultados que la población requiere. Esto es algo repetitivo y creo que el gobierno actual puede entrar en un desgaste político toda vez que la población exige seguridad”, manifestó el exmando policial. Agregó que pese a estas declaratorias de emergencia, siguen creciendo la comisión de delitos como el asesinato, extorsiones y ahora los secuestros. “La población quiere seguridad y están repitiendo lo mismo que han hecho gestiones anteriores. Desde el año pasado, Piura viene en estados de emergencia y quizás tenemos el año en situación de emergencia. Esta es una medida que a todas luces no ha dado resultados. Cambios Sobre el cambio del comandante general de la Policía, Vargas Hugo señaló que los resultados se notarán cuando se fortalezca la labor policial con recursos, logística e inteligencia. “Ese cambio no garantiza una modificación en la lucha contra el crimen. Hay policías que tienen la mejor intención de tener éxito contra el crimen, pero si no le dan las herramientas necesarias, nada pueden hacer”, manifestó.</t>
+          <t>Unos 4.800 flamencos chilenos ( Phoenicopterus chilensis ) habrían completado este año su etapa de reproducción y desplazamiento en el Estuario de Virrilá y la laguna La Niña , dos importantes humedales ubicados en la provincia de Sechura , en Piura. El registro fue recogido por el Servicio Nacional Forestal y de Fauna Silvestre (Serfor) , organismo adscrito al Ministerio de Desarrollo Agrario y Riego (Midagri), durante las labores de monitoreo de esta especie migratoria. Debido a la importancia de estos ecosistemas para la reproducción de los flamencos, especialistas del Serfor recorrieron los puntos de anidamiento identificados en los humedales de Sechura . Las acciones forman parte de las labores de vigilancia y seguimiento de la fauna silvestre en Piura. ¿Por qué se refuerza la vigilancia en Sechura? El seguimiento de los flamencos representa un desafío debido a la extensión del territorio y a las características de los humedales. A ello se suma que estas aves no necesariamente utilizan los mismos lugares para construir sus nidos cada año. Por esa razón, los especialistas deben realizar recorridos periódicos para localizar las zonas donde las aves se concentran durante su periodo reproductivo y verificar que no existan situaciones que puedan afectar a los ejemplares. El especialista en fauna silvestre del Serfor, Max Guerra, señaló que es necesario fortalecer las acciones de patrullaje y monitoreo en los espacios de anidamiento, tomando en cuenta tanto las condiciones del territorio como las amenazas que pueden afectar a estas aves. En las intervenciones realizadas en la provincia participaron representantes del Serfor sede Piura , la Fiscalía Especializada en Materia Ambiental de Piura y la Unidad Desconcentrada de Protección de Medio Ambiente de la Policía Nacional del Perú. El trabajo conjunto resulta especialmente importante en una zona donde ya se han registrado casos de afectación a estas aves. En julio de 2025, el Serfor constató la caza ilegal de crías de flamencos chilenos en la laguna del sector La Huaquilla, en Sechura, luego de recibir una alerta. Los especialistas encontraron patas y plumas de polluelos en el lugar. El ciclo reproductivo de los flamencos en Sechura La reproducción de los flamencos chilenos sigue un proceso que se desarrolla durante varios meses. En los humedales de Sechura , la temporada comienza aproximadamente a mediados de abril, cuando las aves empiezan a construir sus nidos. Entre mayo y junio ocurre la postura de los huevos, mientras que durante julio aparecen los primeros polluelos. A partir de la primera semana de agosto, las crías comienzan a desplazarse, una etapa que requiere especial atención por parte de quienes realizan el monitoreo. “Es un lugar alejado, hay mucho territorio que recorrer y se necesita prestar atención cuando están los polluelos; los puntos de anidamiento cambian todos los años”, explicó el guardaparque local Pablo Martínez, quien también destacó la coordinación con el Serfor para realizar los recorridos. ¿Dónde se reproducen los flamencos? El Estuario de Virrilá y la laguna La Niña forman parte de los espacios utilizados por estas aves en la costa norte del Perú. El Serfor ya ha documentado en años anteriores procesos reproductivos y trabajos de seguimiento en ambos lugares. En 2022, por ejemplo, la entidad informó sobre el nacimiento de alrededor de 700 pichones de flamenco chileno en el Estuario de Virrilá. El lugar fue reconocido además como Sitio Ramsar en 2021, debido a su importancia como humedal de relevancia internacional. Un año después, en agosto de 2023, el Serfor realizó el anillamiento de 183 polluelos nacidos en la laguna La Niña. Esta práctica permite identificar a los ejemplares y obtener información sobre sus desplazamientos y los lugares que utilizan durante su vida. El flamenco chileno es una especie migratoria El flamenco chileno utiliza diferentes cuerpos de agua a lo largo de su distribución. Según el Serfor, puede encontrarse en lagunas poco profundas de agua dulce y salada, desde la costa hasta zonas ubicadas a unos 4.800 metros de altitud. Su distribución comprende territorios desde Chile hasta Ecuador , por lo que los ejemplares que nacen en los humedales de Sechura pueden desplazarse posteriormente hacia otras zonas del país o incluso hacia territorios de países vecinos. El anillamiento se ha convertido en una herramienta para conocer mejor estos movimientos. Los registros realizados por especialistas y observadores de aves permiten identificar ejemplares en diferentes puntos y reconstruir parte de sus rutas de desplazamiento. De acuerdo con el Serfor, la especie está clasificada como “Casi Amenazada” . Entre las principales amenazas identificadas figuran la caza ilegal y la degradación de sus hábitats. ¿Qué amenazas enfrentan los flamencos de Sechura? La ubicación alejada de los humedales no elimina los riesgos para estas aves. La caza, la captura y el consumo de fauna silvestre son prácticas que pueden afectar directamente a las poblaciones de flamencos, especialmente durante la temporada en la que permanecen concentrados en las zonas de reproducción. La dificultad para acceder a determinados sectores también obliga a reforzar la vigilancia. Los recorridos permiten identificar nuevos puntos de anidamiento y detectar posibles casos de afectación antes de que el impacto sea mayor. El antecedente de 2025 en La Huaquilla muestra la necesidad de mantener una presencia constante en estos espacios. Para el Serfor, la protección de las áreas donde se reproducen y alimentan las aves requiere coordinación entre autoridades, especialistas y comunidades locales. ¿Cómo reportar un flamenco en situación de riesgo? La ciudadanía puede comunicar al Serfor cualquier caso relacionado con fauna silvestre que se encuentre herida, enferma, fuera de su hábitat o que requiera evaluación e intervención. Según el canal oficial Alerta SERFOR , los ciudadanos deben enviar un mensaje escrito al WhatsApp 947 588 269 , explicando qué ocurrió, dónde se produjo el hecho y cuándo fue observado. También se deben adjuntar fotografías, videos o información de ubicación que ayude a los especialistas a identificar el lugar y evaluar la situación. El Serfor precisa que este canal recibe mensajes escritos y no llamadas telefónicas . Los reportes son derivados a las Administraciones Técnicas Forestales y de Fauna Silvestre según el ámbito correspondiente.</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>https://eltiempo.pe/local/estado-de-emergencia-en-piura-es-mas-de-lo-mismo/</t>
+          <t>https://eltiempo.pe/local/refuerzan-la-vigilancia-de-flamencos-en-humedales-de-sechura/</t>
         </is>
       </c>
     </row>
@@ -1177,17 +1177,17 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Candidatos a gobernadores y alcaldes obligados a rendir sus gastos</t>
+          <t>Estado de emergencia en Piura es más de lo mismo</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Las organizaciones políticas que participarán en las Elecciones Regionales y Municipales (ERM) 2026 están obligadas a presentar ante la Oficina Nacional de Procesos Electorales (ONPE) dos informes donde registren los gastos, aportes e ingresos de sus campañas. La fecha límite para presentar el primero de dichos informes es el próximo viernes 11 de setiembre. La obligación y el plazo también alcanzan a todos los ciudadanos que hayan logrado inscribir sus candidaturas para una Gobernación, una Vicegobernación o una Alcaldía –provincial o distrital– y se mantienen aun cuando la candidatura no llegue al final del proceso por renuncia, tacha o exclusión. Debido a un cambio en la Ley de Organizaciones Políticas, ya no rinden cuentas quienes aspiran a ser consejeros regionales o regidores municipales. El informe financiero lo puede presentar él mismo o, si tiene, su responsable de campaña.</t>
+          <t>La emisión del decreto supremo N° 126-2026 con la declaratoria de emergencia en Piura, Castilla, Veintiséis de Octubre y Catacaos para luchar contra la criminalidad, no tuvo mayor impacto en la opinión pública agobiada por la ola criminal que castiga a la región. Según el exjefe de la Región Policial de Piura, Coronel (r) Máximo Vargas Hugo, esta medida es más de lo mismo y casi un calco de lo que hicieron los gobiernos anteriores, sin mayores resultados. “Es evidente que el actual gobierno viene utilizando las medidas de gobiernos anteriores para frenar la criminalidad e inseguridad que se vive [...] realmente no se tiene los resultados que la población requiere. Esto es algo repetitivo y creo que el gobierno actual puede entrar en un desgaste político toda vez que la población exige seguridad”, manifestó el exmando policial. Agregó que pese a estas declaratorias de emergencia, siguen creciendo la comisión de delitos como el asesinato, extorsiones y ahora los secuestros. “La población quiere seguridad y están repitiendo lo mismo que han hecho gestiones anteriores. Desde el año pasado, Piura viene en estados de emergencia y quizás tenemos el año en situación de emergencia. Esta es una medida que a todas luces no ha dado resultados. Cambios Sobre el cambio del comandante general de la Policía, Vargas Hugo señaló que los resultados se notarán cuando se fortalezca la labor policial con recursos, logística e inteligencia. “Ese cambio no garantiza una modificación en la lucha contra el crimen. Hay policías que tienen la mejor intención de tener éxito contra el crimen, pero si no le dan las herramientas necesarias, nada pueden hacer”, manifestó.</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>https://eltiempo.pe/local/candidatos-a-gobernadores-y-alcaldes-obligados-a-rendir-sus-gastos/</t>
+          <t>https://eltiempo.pe/local/estado-de-emergencia-en-piura-es-mas-de-lo-mismo/</t>
         </is>
       </c>
     </row>
@@ -1202,17 +1202,17 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>¡Ni los niños se salvan del hampa! Delincuentes saquean colegio y se llevan hasta los juguetes en el Bajo Piura</t>
+          <t>Candidatos a gobernadores y alcaldes obligados a rendir sus gastos</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>La inseguridad vuelve a causar indignación en el corazón del Bajo Piura. Esta vez, los delincuentes pusieron en la mira a la I. E. I. N.° 463 del caserío Santa Cruz, donde, durante la madrugada, ingresaron al plantel y sustrajeron diversos bienes utilizados por más de 40 estudiantes del nivel inicial. Según la información preliminar, los sujetos violentaron dos ambientes de la institución educativa para ingresar y apoderarse de dos parlantes, dos ventiladores y otros bienes. Pero lo que más ha indignado a los padres de familia es que los delincuentes también se llevaron los juguetes utilizados por los niños durante sus actividades de aprendizaje y desarrollo psicomotor. El robo fue descubierto en las primeras horas de la mañana y comunicado al personal de Serenazgo y a la Policía Nacional. La docente Gaby De La Cruz fue quien alertó a las autoridades, quienes llegaron hasta el colegio para constatar los daños y recoger información que permita esclarecer lo ocurrido. BLANCO DE LA DELINCUENCIA Sin embargo, este no sería un hecho aislado. Padres de familia señalaron que la institución educativa ya habría sido víctima anteriormente de la delincuencia. En una ocasión pasada, sujetos desconocidos se llevaron un tanque Rotoplas, dejando nuevamente al plantel expuesto y afectando el normal desarrollo de las actividades educativas. La presidenta Jackeline Silupú expresó su malestar y preocupación ante las autoridades por la situación que viene atravesando la institución. Los padres exigieron mayor seguridad y acciones concretas para evitar que los delincuentes continúen ingresando a los centros educativos. De acuerdo con las primeras versiones, serían dos sujetos los que habrían cometido el robo, para luego escapar rápidamente a bordo de un mototaxi. La Policía Nacional continúa con las diligencias e investigaciones para identificar a los responsables y recuperar los bienes sustraídos.</t>
+          <t>Las organizaciones políticas que participarán en las Elecciones Regionales y Municipales (ERM) 2026 están obligadas a presentar ante la Oficina Nacional de Procesos Electorales (ONPE) dos informes donde registren los gastos, aportes e ingresos de sus campañas. La fecha límite para presentar el primero de dichos informes es el próximo viernes 11 de setiembre. La obligación y el plazo también alcanzan a todos los ciudadanos que hayan logrado inscribir sus candidaturas para una Gobernación, una Vicegobernación o una Alcaldía –provincial o distrital– y se mantienen aun cuando la candidatura no llegue al final del proceso por renuncia, tacha o exclusión. Debido a un cambio en la Ley de Organizaciones Políticas, ya no rinden cuentas quienes aspiran a ser consejeros regionales o regidores municipales. El informe financiero lo puede presentar él mismo o, si tiene, su responsable de campaña.</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>https://eltiempo.pe/local/ni-los-ninos-se-salvan-del-hampa-delincuentes-saquean-colegio-y-se-llevan-hasta-los-juguetes-en-el-bajo-piura/</t>
+          <t>https://eltiempo.pe/local/candidatos-a-gobernadores-y-alcaldes-obligados-a-rendir-sus-gastos/</t>
         </is>
       </c>
     </row>
@@ -1227,17 +1227,17 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Dren Maldonado: MTC enviará puente a Piura tras alerta por riesgo de dejar incomunicadas a 60 mil personas</t>
+          <t>Piura: Sicarios asesinan a menor, dos mujeres y un exsereno</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>La senadora por Piura, Karla Schaefer, informó que el ministro de Transportes y Comunicaciones, Rafael Rey Rey, dispuso el envío de un puente que será utilizado para garantizar la conexión vial ante una eventual afectación del dren Maldonado. Puedes Leer | El Niño superaría al de 1998 y traería impactos “insospechados” en la región Piura La situación de riesgo en el dren Maldonado, en el distrito de Veintiséis de Octubre, habría encontrado una respuesta desde el Gobierno central. La senadora por Piura, Karla Schaefer , informó que el Ministerio de Transportes y Comunicaciones (MTC) dispuso el envío de un puente para atender una eventual interrupción de la vía en este sector. Según explicó Schaefer, el pedido fue trasladado al MTC debido a la preocupación por la seguridad de la red vial y el riesgo de que una eventual afectación del dren Maldonado pueda comprometer la comunicación de importantes sectores de Piura. “ El ministro de Transportes y Comunicaciones, Rafael Rey, afirmó que él va a poner el puente ”, señaló la senadora. Schaefer explicó que inicialmente se realizaron consultas tanto al MTC como al Ministerio de Defensa (Mindef), a través de la empresa estatal SIMA Perú , para evaluar una alternativa que permita responder ante una emergencia. Sin embargo, de acuerdo con la parlamentaria, el ministro Rey tomó la decisión de disponer directamente la estructura tras conocer la situación. “Se había hecho la consulta al Ministerio de Transportes y Comunicaciones y al Ministerio de Defensa a través de SIMA Perú. Pero el ministro Rafael Rey, gracias a la delegación de facultades, ni bien vio el tema, dijo: ‘ Yo voy a dar ese puente ’”, declaró. Puente será trasladado a Piura La senadora informó además que la estructura ya habría salido de Lima con destino a Piura y será almacenada temporalmente en Piura Futura , desde donde podrá ser trasladada hacia los puntos que requieran atención. “Hoy han salido de Lima y serán almacenados en Piura Futura para que desde ahí se vayan a varios puntos”, indicó Schaefer. La medida busca contar con una alternativa de conexión ante una eventual emergencia relacionada con el dren Maldonado, especialmente considerando el riesgo advertido para la población de Veintiséis de Octubre. En declaraciones difundidas previamente por El Tiempo , Schaefer había advertido que una eventual afectación del dren podría dejar incomunicadas a unas 60 mil personas y había cuestionado las dificultades generadas por la distribución de competencias entre distintas instituciones del Estado. Schaefer agradece respuesta del MTC La senadora destacó la rapidez con la que, según su versión, el ministro de Transportes habría atendido el pedido. “ Agradecerle al ministro esa eficiencia en solucionar ese problema en que se prioriza la vida ”, manifestó. Asimismo, reconoció el trabajo del director de Puentes, Julio Palacios , y de la Municipalidad Distrital de Veintiséis de Octubre , instituciones que, según indicó, tendrán participación en la gestión relacionada con la estructura. Mira También | ¡Ni los niños se salvan del hampa! Delincuentes saquean colegio y se llevan hasta los juguetes en el Bajo Piura El dren Maldonado es uno de los puntos críticos del sistema de drenaje de Veintiséis de Octubre. En febrero de 2026, el INDECI ya había identificado la necesidad de gestionar requerimientos para garantizar su operatividad, debido a su importancia para la evacuación de aguas pluviales durante lluvias intensas. La atención al dren Maldonado forma parte de una problemática mayor de infraestructura y prevención frente a lluvias en Piura, donde distintas autoridades han advertido sobre la necesidad de acelerar las intervenciones antes de que se presenten emergencias.</t>
+          <t>La violencia volvió a golpear con fuerza a la provincia de Sullana y otros sectores de Piura. En distintos hechos registrados durante las últimas horas, sicarios habrían atacado a varias personas, dejando como saldo la muerte de un adolescente de 13 años, dos mujeres y un exsereno. Además, otras dos personas resultaron heridas por impactos de bala. Los casos son investigados por la Policía Nacional del Perú, que busca determinar quiénes participaron en los ataques y cuáles fueron los móviles. La institución mantiene abiertas distintas líneas de investigación y no descarta que algunos de estos crímenes estén relacionados con ajustes de cuentas. Sicarios asesinan a menor de 13 años en Sullana Uno de los casos que más ha conmocionado a Sullana corresponde a la muerte de un menor de apenas 13 años. El adolescente, identificado con las iniciales M. F. L. Ch., era natural de Trujillo, aunque residía en Piura, y se convirtió, según la información proporcionada, en la víctima número 44 de los asesinatos atribuidos al sicariato en la provincia. El crimen ocurrió la noche del domingo en la intersección de la calle Túpac Amaru con la avenida Par Vial, en el asentamiento 17 de Enero. Eran aproximadamente las 10:40 de la noche cuando el adolescente viajaba como pasajero en un mototaxi rojo de placa 3784-DP. De acuerdo con las primeras investigaciones, el vehículo habría quedado detenido en medio de la vía debido a un desperfecto mecánico. La tapa del tanque de combustible había sido retirada y esa situación habría sido aprovechada por los atacantes. Según los primeros testimonios recogidos en el lugar, sujetos que se desplazaban en una motocicleta llegaron hasta el mototaxi y dispararon directamente contra el menor. Uno de los proyectiles impactó en su cabeza y le ocasionó una herida de entrada y salida que provocó su muerte de manera instantánea. Un tatuaje permitió identificar al adolescente Tras el ataque, sus acompañantes habrían escapado corriendo en dirección al sector La Selva, mientras la víctima y el trimóvil quedaron abandonados en la zona. La identificación del adolescente se pudo realizar gracias a un tatuaje que llevaba en el brazo derecho con el nombre “Alexander”. Una tía acudió a la dependencia policial y posteriormente a la morgue legal, donde reconoció plenamente al menor. La Policía continúa con las diligencias para establecer las circunstancias exactas del asesinato. Entre las hipótesis que se manejan figura un posible ajuste de cuentas, aunque esta versión todavía debe ser corroborada por los investigadores. Para establecer si existían antecedentes que puedan ayudar a explicar el ataque, la Policía coordina con sus unidades de Piura para conocer si el adolescente había sido intervenido durante las últimas semanas. Asesinan a exsereno dentro de restaurante en Talara Otro hecho violento ocurrió en Talara. Un hombre conocido como “Van Dan”, quien había sido sereno y era propietario de un gimnasio en el distrito de La Brea-Negritos, fue asesinado a balazos dentro del restaurante “La Caleta 10”, ubicado en el asentamiento Mario Aguirre. Según la información preliminar, un sicario irrumpió en el segundo piso del establecimiento y disparó en cinco oportunidades contra la víctima. El hombre quedó sentado en una silla y murió pocos segundos después del ataque. La Policía deberá determinar si este crimen guarda relación con alguna amenaza previa, conflicto personal u otra actividad delictiva. Por ahora, el móvil permanece bajo investigación. Dos mujeres mueren tras una balacera en Sullana La noche del lunes, otro ataque armado dejó dos mujeres fallecidas y dos hombres heridos en el sector Manuel Seoane, en Sullana. El hecho ocurrió en la manzana B, lote 13, donde cuatro personas se encontraban dentro de una vivienda consumiendo bebidas alcohólicas y ceviche. Según los testimonios recogidos inicialmente, una motocicleta se estacionó frente al inmueble. Uno de los ocupantes descendió y habría ingresado rápidamente a la vivienda para abrir fuego contra las personas que se encontraban en el interior. Los testigos describieron el ataque como una ráfaga de disparos. Aunque las víctimas intentaron protegerse y lanzarse al suelo, varias de ellas fueron alcanzadas por los proyectiles. Las víctimas fueron identificadas Una de las víctimas fue identificada como Sheila Anabelen Viera Elias, de 30 años. De acuerdo con las primeras versiones, la mujer intentó escapar hacia el baño, pero el atacante la habría perseguido y disparado varias veces. También resultó gravemente herida Lady Loren Valdiviezo Nole, de 28 años. Los disparos le ocasionaron lesiones en el tórax y la cabeza. La mujer fue trasladada a un establecimiento de salud junto con los demás afectados. Además de las dos jóvenes, Daniel Paucar y Carlos Cornejo resultaron heridos por impactos de bala y fueron trasladados a los hospitales antiguo y nuevo de Sullana. Hasta el cierre de la información proporcionada, ambos permanecían con pronóstico reservado. Las dos mujeres fallecieron pese a los esfuerzos realizados por los médicos. En el caso de Loren Valdiviezo, se conoció que tenía seis meses de gestación, lo que añadió una nueva dimensión a la tragedia. ¿Qué investiga la Policía sobre los ataques? Los investigadores buscan establecer si los tres hechos tienen alguna conexión o si se trata de ataques independientes. La presencia de motocicletas, el uso de armas de fuego y la rapidez con la que actuaron los presuntos atacantes son algunos de los elementos que forman parte de las diligencias. De acuerdo con la Policía Nacional del Perú , la investigación criminal permite reunir evidencias para determinar responsabilidades y esclarecer los hechos. La institución mantiene información institucional y canales de atención a través de su portal oficial . Asimismo, el Ministerio Público participa en las investigaciones cuando corresponde y tiene entre sus funciones dirigir la investigación del delito. Para conocer información institucional, denuncias y servicios fiscales, se puede consultar el portal oficial del Ministerio Público . ¿Dónde se puede consultar información sobre el sicariato? Para conocer la incidencia de distintos delitos, el Ministerio del Interior cuenta con el Mapa del Delito Georreferenciado . Esta herramienta permite consultar registros relacionados con homicidios, extorsiones y sicariato , además de ubicar comisarías y otros puntos de interés. El servicio forma parte del Observatorio Nacional de Seguridad Ciudadana y puede ser consultado en el Mapa del Delito Georreferenciado del Ministerio del Interior . En Sullana, la violencia vinculada a ataques con armas de fuego y asesinatos por encargo no es un fenómeno nuevo. El propio Poder Judicial ha informado anteriormente sobre procesos por presunto sicariato en esta provincia, incluyendo investigaciones en las que se analizaron testimonios protegidos y registros audiovisuales como elementos de convicción. Mientras avanzan las diligencias, la Policía deberá determinar quiénes fueron los autores materiales de estos crímenes, quiénes pudieron ordenar los ataques y cuáles fueron las razones detrás de cada asesinato. Por el momento, las investigaciones continúan abiertas.</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>https://eltiempo.pe/local/dren-maldonado-mtc-enviara-puente-a-piura-tras-alerta-por-riesgo-de-dejar-incomunicadas-a-60-mil-personas/</t>
+          <t>https://eltiempo.pe/local/piura-sicarios-asesinan-a-menor-dos-mujeres-y-un-exsereno/</t>
         </is>
       </c>
     </row>
@@ -1252,17 +1252,17 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Piura: Sicarios asesinan a menor, dos mujeres y un exsereno</t>
+          <t>Dren Maldonado: MTC enviará puente a Piura tras alerta por riesgo de dejar incomunicadas a 60 mil personas</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>La violencia volvió a golpear con fuerza a la provincia de Sullana y otros sectores de Piura. En distintos hechos registrados durante las últimas horas, sicarios habrían atacado a varias personas, dejando como saldo la muerte de un adolescente de 13 años, dos mujeres y un exsereno. Además, otras dos personas resultaron heridas por impactos de bala. Los casos son investigados por la Policía Nacional del Perú, que busca determinar quiénes participaron en los ataques y cuáles fueron los móviles. La institución mantiene abiertas distintas líneas de investigación y no descarta que algunos de estos crímenes estén relacionados con ajustes de cuentas. Sicarios asesinan a menor de 13 años en Sullana Uno de los casos que más ha conmocionado a Sullana corresponde a la muerte de un menor de apenas 13 años. El adolescente, identificado con las iniciales M. F. L. Ch., era natural de Trujillo, aunque residía en Piura, y se convirtió, según la información proporcionada, en la víctima número 44 de los asesinatos atribuidos al sicariato en la provincia. El crimen ocurrió la noche del domingo en la intersección de la calle Túpac Amaru con la avenida Par Vial, en el asentamiento 17 de Enero. Eran aproximadamente las 10:40 de la noche cuando el adolescente viajaba como pasajero en un mototaxi rojo de placa 3784-DP. De acuerdo con las primeras investigaciones, el vehículo habría quedado detenido en medio de la vía debido a un desperfecto mecánico. La tapa del tanque de combustible había sido retirada y esa situación habría sido aprovechada por los atacantes. Según los primeros testimonios recogidos en el lugar, sujetos que se desplazaban en una motocicleta llegaron hasta el mototaxi y dispararon directamente contra el menor. Uno de los proyectiles impactó en su cabeza y le ocasionó una herida de entrada y salida que provocó su muerte de manera instantánea. Un tatuaje permitió identificar al adolescente Tras el ataque, sus acompañantes habrían escapado corriendo en dirección al sector La Selva, mientras la víctima y el trimóvil quedaron abandonados en la zona. La identificación del adolescente se pudo realizar gracias a un tatuaje que llevaba en el brazo derecho con el nombre “Alexander”. Una tía acudió a la dependencia policial y posteriormente a la morgue legal, donde reconoció plenamente al menor. La Policía continúa con las diligencias para establecer las circunstancias exactas del asesinato. Entre las hipótesis que se manejan figura un posible ajuste de cuentas, aunque esta versión todavía debe ser corroborada por los investigadores. Para establecer si existían antecedentes que puedan ayudar a explicar el ataque, la Policía coordina con sus unidades de Piura para conocer si el adolescente había sido intervenido durante las últimas semanas. Asesinan a exsereno dentro de restaurante en Talara Otro hecho violento ocurrió en Talara. Un hombre conocido como “Van Dan”, quien había sido sereno y era propietario de un gimnasio en el distrito de La Brea-Negritos, fue asesinado a balazos dentro del restaurante “La Caleta 10”, ubicado en el asentamiento Mario Aguirre. Según la información preliminar, un sicario irrumpió en el segundo piso del establecimiento y disparó en cinco oportunidades contra la víctima. El hombre quedó sentado en una silla y murió pocos segundos después del ataque. La Policía deberá determinar si este crimen guarda relación con alguna amenaza previa, conflicto personal u otra actividad delictiva. Por ahora, el móvil permanece bajo investigación. Dos mujeres mueren tras una balacera en Sullana La noche del lunes, otro ataque armado dejó dos mujeres fallecidas y dos hombres heridos en el sector Manuel Seoane, en Sullana. El hecho ocurrió en la manzana B, lote 13, donde cuatro personas se encontraban dentro de una vivienda consumiendo bebidas alcohólicas y ceviche. Según los testimonios recogidos inicialmente, una motocicleta se estacionó frente al inmueble. Uno de los ocupantes descendió y habría ingresado rápidamente a la vivienda para abrir fuego contra las personas que se encontraban en el interior. Los testigos describieron el ataque como una ráfaga de disparos. Aunque las víctimas intentaron protegerse y lanzarse al suelo, varias de ellas fueron alcanzadas por los proyectiles. Las víctimas fueron identificadas Una de las víctimas fue identificada como Sheila Anabelen Viera Elias, de 30 años. De acuerdo con las primeras versiones, la mujer intentó escapar hacia el baño, pero el atacante la habría perseguido y disparado varias veces. También resultó gravemente herida Lady Loren Valdiviezo Nole, de 28 años. Los disparos le ocasionaron lesiones en el tórax y la cabeza. La mujer fue trasladada a un establecimiento de salud junto con los demás afectados. Además de las dos jóvenes, Daniel Paucar y Carlos Cornejo resultaron heridos por impactos de bala y fueron trasladados a los hospitales antiguo y nuevo de Sullana. Hasta el cierre de la información proporcionada, ambos permanecían con pronóstico reservado. Las dos mujeres fallecieron pese a los esfuerzos realizados por los médicos. En el caso de Loren Valdiviezo, se conoció que tenía seis meses de gestación, lo que añadió una nueva dimensión a la tragedia. ¿Qué investiga la Policía sobre los ataques? Los investigadores buscan establecer si los tres hechos tienen alguna conexión o si se trata de ataques independientes. La presencia de motocicletas, el uso de armas de fuego y la rapidez con la que actuaron los presuntos atacantes son algunos de los elementos que forman parte de las diligencias. De acuerdo con la Policía Nacional del Perú , la investigación criminal permite reunir evidencias para determinar responsabilidades y esclarecer los hechos. La institución mantiene información institucional y canales de atención a través de su portal oficial . Asimismo, el Ministerio Público participa en las investigaciones cuando corresponde y tiene entre sus funciones dirigir la investigación del delito. Para conocer información institucional, denuncias y servicios fiscales, se puede consultar el portal oficial del Ministerio Público . ¿Dónde se puede consultar información sobre el sicariato? Para conocer la incidencia de distintos delitos, el Ministerio del Interior cuenta con el Mapa del Delito Georreferenciado . Esta herramienta permite consultar registros relacionados con homicidios, extorsiones y sicariato , además de ubicar comisarías y otros puntos de interés. El servicio forma parte del Observatorio Nacional de Seguridad Ciudadana y puede ser consultado en el Mapa del Delito Georreferenciado del Ministerio del Interior . En Sullana, la violencia vinculada a ataques con armas de fuego y asesinatos por encargo no es un fenómeno nuevo. El propio Poder Judicial ha informado anteriormente sobre procesos por presunto sicariato en esta provincia, incluyendo investigaciones en las que se analizaron testimonios protegidos y registros audiovisuales como elementos de convicción. Mientras avanzan las diligencias, la Policía deberá determinar quiénes fueron los autores materiales de estos crímenes, quiénes pudieron ordenar los ataques y cuáles fueron las razones detrás de cada asesinato. Por el momento, las investigaciones continúan abiertas.</t>
+          <t>La senadora por Piura, Karla Schaefer, informó que el ministro de Transportes y Comunicaciones, Rafael Rey Rey, dispuso el envío de un puente que será utilizado para garantizar la conexión vial ante una eventual afectación del dren Maldonado. Puedes Leer | El Niño superaría al de 1998 y traería impactos “insospechados” en la región Piura La situación de riesgo en el dren Maldonado, en el distrito de Veintiséis de Octubre, habría encontrado una respuesta desde el Gobierno central. La senadora por Piura, Karla Schaefer , informó que el Ministerio de Transportes y Comunicaciones (MTC) dispuso el envío de un puente para atender una eventual interrupción de la vía en este sector. Según explicó Schaefer, el pedido fue trasladado al MTC debido a la preocupación por la seguridad de la red vial y el riesgo de que una eventual afectación del dren Maldonado pueda comprometer la comunicación de importantes sectores de Piura. “ El ministro de Transportes y Comunicaciones, Rafael Rey, afirmó que él va a poner el puente ”, señaló la senadora. Schaefer explicó que inicialmente se realizaron consultas tanto al MTC como al Ministerio de Defensa (Mindef), a través de la empresa estatal SIMA Perú , para evaluar una alternativa que permita responder ante una emergencia. Sin embargo, de acuerdo con la parlamentaria, el ministro Rey tomó la decisión de disponer directamente la estructura tras conocer la situación. “Se había hecho la consulta al Ministerio de Transportes y Comunicaciones y al Ministerio de Defensa a través de SIMA Perú. Pero el ministro Rafael Rey, gracias a la delegación de facultades, ni bien vio el tema, dijo: ‘ Yo voy a dar ese puente ’”, declaró. Puente será trasladado a Piura La senadora informó además que la estructura ya habría salido de Lima con destino a Piura y será almacenada temporalmente en Piura Futura , desde donde podrá ser trasladada hacia los puntos que requieran atención. “Hoy han salido de Lima y serán almacenados en Piura Futura para que desde ahí se vayan a varios puntos”, indicó Schaefer. La medida busca contar con una alternativa de conexión ante una eventual emergencia relacionada con el dren Maldonado, especialmente considerando el riesgo advertido para la población de Veintiséis de Octubre. En declaraciones difundidas previamente por El Tiempo , Schaefer había advertido que una eventual afectación del dren podría dejar incomunicadas a unas 60 mil personas y había cuestionado las dificultades generadas por la distribución de competencias entre distintas instituciones del Estado. Schaefer agradece respuesta del MTC La senadora destacó la rapidez con la que, según su versión, el ministro de Transportes habría atendido el pedido. “ Agradecerle al ministro esa eficiencia en solucionar ese problema en que se prioriza la vida ”, manifestó. Asimismo, reconoció el trabajo del director de Puentes, Julio Palacios , y de la Municipalidad Distrital de Veintiséis de Octubre , instituciones que, según indicó, tendrán participación en la gestión relacionada con la estructura. Mira También | ¡Ni los niños se salvan del hampa! Delincuentes saquean colegio y se llevan hasta los juguetes en el Bajo Piura El dren Maldonado es uno de los puntos críticos del sistema de drenaje de Veintiséis de Octubre. En febrero de 2026, el INDECI ya había identificado la necesidad de gestionar requerimientos para garantizar su operatividad, debido a su importancia para la evacuación de aguas pluviales durante lluvias intensas. La atención al dren Maldonado forma parte de una problemática mayor de infraestructura y prevención frente a lluvias en Piura, donde distintas autoridades han advertido sobre la necesidad de acelerar las intervenciones antes de que se presenten emergencias.</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>https://eltiempo.pe/local/piura-sicarios-asesinan-a-menor-dos-mujeres-y-un-exsereno/</t>
+          <t>https://eltiempo.pe/local/dren-maldonado-mtc-enviara-puente-a-piura-tras-alerta-por-riesgo-de-dejar-incomunicadas-a-60-mil-personas/</t>
         </is>
       </c>
     </row>
@@ -1273,21 +1273,21 @@
         </is>
       </c>
       <c r="B32" s="2" t="n">
-        <v>46272</v>
+        <v>46273</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>I.E. San Ramón de Chulucanas se consagra campeona del Regional Singing Festival 2026</t>
+          <t>¡Ni los niños se salvan del hampa! Delincuentes saquean colegio y se llevan hasta los juguetes en el Bajo Piura</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>La Institución Educativa San Ramón de Chulucanas, representante de la UGEL Chulucanas , obtuvo el primer lugar en el Regional Singing Festival 2026 “Singing for a Better World”, organizado por la Dirección Regional de Educación de Piura. PUEDES LEER ► Sobrevive tras 10 días sepultada por el lodo y es rescatada cuando su familia ya la había dado por muerta La actividad se desarrolló en el parque Néstor Martos de Piura y reunió a estudiantes representantes de las 12 UGEL de la región, quienes demostraron sus habilidades en la interpretación de canciones en inglés. El festival tiene como finalidad fortalecer las competencias comunicativas en el idioma inglés, además de promover la creatividad, la expresión artística y la participación de los estudiantes. La iniciativa se desarrolla en concordancia con el Currículo Nacional de la Educación Básica. Durante sus presentaciones, los participantes también transmitieron mensajes relacionados con valores y actitudes que contribuyen a una convivencia democrática, respetuosa, inclusiva y solidaria. San Ramón conquistó el primer lugar La IE San Ramón logró imponerse en la competencia con la interpretación de la canción “Hand for Chulucanas”, presentación que le permitió quedarse con el primer puesto del festival regional. El segundo lugar fue para la IE Libertadores de América, representante de la UGEL La Unión, que participó con la canción “The Song of Tomorrow”. Mientras que el tercer puesto correspondió a la IE César Vallejo, de la UGEL Morropón, con la interpretación de “Brighter Than Before”. La competencia comenzó en cada institución educativa y posteriormente continuó en las diferentes etapas de las 12 UGEL de Piura: Ayabaca, Chulucanas, Huancabamba, Huarmaca, La Unión, Morropón, Paita, Piura, Sechura, Sullana, Talara y Tambogrande. Además de impulsar el aprendizaje del inglés, el festival busca fortalecer la sana competencia, el trabajo en equipo y la integración entre estudiantes de diferentes provincias de la región.</t>
+          <t>La inseguridad vuelve a causar indignación en el corazón del Bajo Piura. Esta vez, los delincuentes pusieron en la mira a la I. E. I. N.° 463 del caserío Santa Cruz, donde, durante la madrugada, ingresaron al plantel y sustrajeron diversos bienes utilizados por más de 40 estudiantes del nivel inicial. Según la información preliminar, los sujetos violentaron dos ambientes de la institución educativa para ingresar y apoderarse de dos parlantes, dos ventiladores y otros bienes. Pero lo que más ha indignado a los padres de familia es que los delincuentes también se llevaron los juguetes utilizados por los niños durante sus actividades de aprendizaje y desarrollo psicomotor. El robo fue descubierto en las primeras horas de la mañana y comunicado al personal de Serenazgo y a la Policía Nacional. La docente Gaby De La Cruz fue quien alertó a las autoridades, quienes llegaron hasta el colegio para constatar los daños y recoger información que permita esclarecer lo ocurrido. BLANCO DE LA DELINCUENCIA Sin embargo, este no sería un hecho aislado. Padres de familia señalaron que la institución educativa ya habría sido víctima anteriormente de la delincuencia. En una ocasión pasada, sujetos desconocidos se llevaron un tanque Rotoplas, dejando nuevamente al plantel expuesto y afectando el normal desarrollo de las actividades educativas. La presidenta Jackeline Silupú expresó su malestar y preocupación ante las autoridades por la situación que viene atravesando la institución. Los padres exigieron mayor seguridad y acciones concretas para evitar que los delincuentes continúen ingresando a los centros educativos. De acuerdo con las primeras versiones, serían dos sujetos los que habrían cometido el robo, para luego escapar rápidamente a bordo de un mototaxi. La Policía Nacional continúa con las diligencias e investigaciones para identificar a los responsables y recuperar los bienes sustraídos.</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>https://eltiempo.pe/local/i-e-san-ramon-de-chulucanas-se-consagra-campeona-del-regional-singing-festival-2026/</t>
+          <t>https://eltiempo.pe/local/ni-los-ninos-se-salvan-del-hampa-delincuentes-saquean-colegio-y-se-llevan-hasta-los-juguetes-en-el-bajo-piura/</t>
         </is>
       </c>
     </row>
@@ -1302,17 +1302,17 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Así van los candidatos a falta de un mes para elecciones</t>
+          <t>I.E. San Ramón de Chulucanas se consagra campeona del Regional Singing Festival 2026</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>ICSI Perú hizo una encuesta y revela cómo van las preferencias de los piuranos sobre su próximo gobernador y alcaldes. PUEDES LEER ► Miniván queda al borde de un abismo en la carretera Canchaque -Huancabamba Las elecciones regionales y municipales están a la vuelta de la esquina y lo único seguro es que sí o sí habrá una segunda vuelta para el cargo de gobernador regional. De acuerdo a ley, si ninguna lista supera el 30% de votos válidos, se convoca a una segunda vuelta entre los dos primeros del escrutinio. De acuerdo a la última encuesta de la empresa ICSI Perú ninguno de los aspirantes a la máxima autoridad regional llega al 30% de las preferencias. Según el estudio de opinión pública, el primer lugar es para el exgobernador Reynaldo Hilbck (Alianza para el Progreso) con 22.5%; seguido por Santiago Paz (Somos Perú) con 13.7% ; Mártires Lizana (Fuerza Popular) con 11.1% y Guillermo La Torre (Podemos Perú) con 10.9%. En el caso de los candidatos provinciales, la disputa parece más reñida y la diferencia de porcentajes es más ajustada entre los aspirantes, con lo cual la campaña de aquí hasta el domingo 4 de octubre será una competencia voto a voto y de convencimiento de los indecisos. Gobierno Regional Sobre el tema, el gerente de ICSI Perú, Mauro Vegas Carmen , consideró que uno de los factores del respaldo a Hilbck son sus candidatos en las provincias con mayor caudal electoral de votos. “En los resultados de los 27 distritos a donde se ha ido, Hilbck alcanza la mayor votación en Piura, Veintiséis de Octubre, Catacaos, Sullana, Morropón, Chulucanas, Talara, Órganos y otros. Todo eso le da ese porcentaje que ahora ha sacado frente al segundo. Por ejemplo, en Piura tiene 19.66% y Somos Perú tiene 15.33%; en Castilla, Hilbck tiene 13.60% y Somos Perú unos 10.90% y en Veintiséis de Octubre, Hilbck tiene 20.35% y Somos Perú, 15.34%. En Sullana que es una plaza fuerte, se tiene 19.59% y Santiago Paz llega a 12.14%, asimismo, en Chulucanas, Hilbck logra 17.4% y Somos Perú 9.87%”, mencionó. Agrega que este respaldo de Hilbck en las provincias y distritos se refleja en sus candidatos para estas jurisdicciones. Un segundo factor, sostiene, es el respaldo de la maquinaria electoral de un partido como Alianza para el Progreso (APP). “Ese porcentaje es coherente porque sus candidatos provinciales y también distritales ganan, además que la maquinaria electoral que se percibe en la región”, agregó. Somos Perú Sobre Santiago Paz de Somos Perú que marcha en segundo lugar con 13.7%, el gerente de ICSI Perú sostuvo que no le va bien con sus candidatos en Piura, Castilla, Veintiséis de Octubre, Tambogrande o Sullana. “En el caso Chulucanas, como distrito capital, el candidato Nelson Mío que hace un mes era fuerte, ha tenido un descenso porque ahí han ingresado candidatos nuevos como Hernán Pasapera de Renovación y Manuel Cueva de Podemos. Eso le ha restado fuerza a Somos Perú”, aseveró. Sobre Mártires Lizana de Fuerza Popular que marcha tercero, Vegas destaca que esto ocurre por la aceptación del candidato a la provincia de Piura, Martín Olivares, que está segundo en la preferencial provincial. Nulos En el estudio también se revela que un 18% de los encuestados no votaría por ninguno de los postulantes o lo haría en blanco. “Esto puede variar producto de la campaña y contracampaña. Aquí quien tiene mejor equipo de contracampaña es el que tiene mayor ventaja de ganar. Es quien reacciona rápido, de forma contundente y demoledora. No siempre la percepción es la verdad, por eso una contracampaña tiene que responderse de manera rápida y contundente. No se trata del mejor indudablemente, sino de quien cometa menos errores y sepa responder a los ataques fundados o infundados”, destacó.n</t>
+          <t>La Institución Educativa San Ramón de Chulucanas, representante de la UGEL Chulucanas , obtuvo el primer lugar en el Regional Singing Festival 2026 “Singing for a Better World”, organizado por la Dirección Regional de Educación de Piura. PUEDES LEER ► Sobrevive tras 10 días sepultada por el lodo y es rescatada cuando su familia ya la había dado por muerta La actividad se desarrolló en el parque Néstor Martos de Piura y reunió a estudiantes representantes de las 12 UGEL de la región, quienes demostraron sus habilidades en la interpretación de canciones en inglés. El festival tiene como finalidad fortalecer las competencias comunicativas en el idioma inglés, además de promover la creatividad, la expresión artística y la participación de los estudiantes. La iniciativa se desarrolla en concordancia con el Currículo Nacional de la Educación Básica. Durante sus presentaciones, los participantes también transmitieron mensajes relacionados con valores y actitudes que contribuyen a una convivencia democrática, respetuosa, inclusiva y solidaria. San Ramón conquistó el primer lugar La IE San Ramón logró imponerse en la competencia con la interpretación de la canción “Hand for Chulucanas”, presentación que le permitió quedarse con el primer puesto del festival regional. El segundo lugar fue para la IE Libertadores de América, representante de la UGEL La Unión, que participó con la canción “The Song of Tomorrow”. Mientras que el tercer puesto correspondió a la IE César Vallejo, de la UGEL Morropón, con la interpretación de “Brighter Than Before”. La competencia comenzó en cada institución educativa y posteriormente continuó en las diferentes etapas de las 12 UGEL de Piura: Ayabaca, Chulucanas, Huancabamba, Huarmaca, La Unión, Morropón, Paita, Piura, Sechura, Sullana, Talara y Tambogrande. Además de impulsar el aprendizaje del inglés, el festival busca fortalecer la sana competencia, el trabajo en equipo y la integración entre estudiantes de diferentes provincias de la región.</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>https://eltiempo.pe/local/asi-van-los-candidatos-a-falta-de-un-mes-para-elecciones/</t>
+          <t>https://eltiempo.pe/local/i-e-san-ramon-de-chulucanas-se-consagra-campeona-del-regional-singing-festival-2026/</t>
         </is>
       </c>
     </row>
@@ -1327,17 +1327,17 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Miniván queda al borde de un abismo en la carretera Canchaque -Huancabamba</t>
+          <t>Así van los candidatos a falta de un mes para elecciones</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Unos 12 pasajeros se salvaron de caer a un abismo de aproximadamente 200 metros luego de que una miniván de una empresa de transporte sufriera un accidente en la carretera Canchaque-Huancabamba, en el sector Las Minas. Según información preliminar, la unidad terminó volcada y quedó peligrosamente cerca del precipicio, generando momentos de angustia entre los pasajeros, entre ellos algunos menores de edad, quienes temieron lo peor. Pese a la violencia del accidente, los ocupantes solo habrían sufrido algunos golpes, además del fuerte susto provocado por el incidente. Hasta el momento no se han reportado oficialmente personas con lesiones de consideración. EL EQUIPAJE El accidente también ocasionó la caída de algunos equipajes que eran transportados en la parte superior de la miniván, los cuales algunos habrían terminado en el fondo del abismo. De acuerdo con versiones preliminares, no se descarta que el vehículo haya sufrido algún desperfecto mecánico antes de producirse el accidente. Sin embargo, esta posibilidad deberá ser determinada mediante las investigaciones correspondientes. Asimismo, las autoridades realizan las diligencias para establecer las causas exactas del siniestro y determinar las condiciones en las que circulaba la unidad. Cabe mencionar que el hecho vuelve a poner en evidencia el peligro de transitar por esta vía, caracterizada por sus pronunciadas pendientes y zonas de profundo precipicio.</t>
+          <t>ICSI Perú hizo una encuesta y revela cómo van las preferencias de los piuranos sobre su próximo gobernador y alcaldes. PUEDES LEER ► Miniván queda al borde de un abismo en la carretera Canchaque -Huancabamba Las elecciones regionales y municipales están a la vuelta de la esquina y lo único seguro es que sí o sí habrá una segunda vuelta para el cargo de gobernador regional. De acuerdo a ley, si ninguna lista supera el 30% de votos válidos, se convoca a una segunda vuelta entre los dos primeros del escrutinio. De acuerdo a la última encuesta de la empresa ICSI Perú ninguno de los aspirantes a la máxima autoridad regional llega al 30% de las preferencias. Según el estudio de opinión pública, el primer lugar es para el exgobernador Reynaldo Hilbck (Alianza para el Progreso) con 22.5%; seguido por Santiago Paz (Somos Perú) con 13.7% ; Mártires Lizana (Fuerza Popular) con 11.1% y Guillermo La Torre (Podemos Perú) con 10.9%. En el caso de los candidatos provinciales, la disputa parece más reñida y la diferencia de porcentajes es más ajustada entre los aspirantes, con lo cual la campaña de aquí hasta el domingo 4 de octubre será una competencia voto a voto y de convencimiento de los indecisos. Gobierno Regional Sobre el tema, el gerente de ICSI Perú, Mauro Vegas Carmen , consideró que uno de los factores del respaldo a Hilbck son sus candidatos en las provincias con mayor caudal electoral de votos. “En los resultados de los 27 distritos a donde se ha ido, Hilbck alcanza la mayor votación en Piura, Veintiséis de Octubre, Catacaos, Sullana, Morropón, Chulucanas, Talara, Órganos y otros. Todo eso le da ese porcentaje que ahora ha sacado frente al segundo. Por ejemplo, en Piura tiene 19.66% y Somos Perú tiene 15.33%; en Castilla, Hilbck tiene 13.60% y Somos Perú unos 10.90% y en Veintiséis de Octubre, Hilbck tiene 20.35% y Somos Perú, 15.34%. En Sullana que es una plaza fuerte, se tiene 19.59% y Santiago Paz llega a 12.14%, asimismo, en Chulucanas, Hilbck logra 17.4% y Somos Perú 9.87%”, mencionó. Agrega que este respaldo de Hilbck en las provincias y distritos se refleja en sus candidatos para estas jurisdicciones. Un segundo factor, sostiene, es el respaldo de la maquinaria electoral de un partido como Alianza para el Progreso (APP). “Ese porcentaje es coherente porque sus candidatos provinciales y también distritales ganan, además que la maquinaria electoral que se percibe en la región”, agregó. Somos Perú Sobre Santiago Paz de Somos Perú que marcha en segundo lugar con 13.7%, el gerente de ICSI Perú sostuvo que no le va bien con sus candidatos en Piura, Castilla, Veintiséis de Octubre, Tambogrande o Sullana. “En el caso Chulucanas, como distrito capital, el candidato Nelson Mío que hace un mes era fuerte, ha tenido un descenso porque ahí han ingresado candidatos nuevos como Hernán Pasapera de Renovación y Manuel Cueva de Podemos. Eso le ha restado fuerza a Somos Perú”, aseveró. Sobre Mártires Lizana de Fuerza Popular que marcha tercero, Vegas destaca que esto ocurre por la aceptación del candidato a la provincia de Piura, Martín Olivares, que está segundo en la preferencial provincial. Nulos En el estudio también se revela que un 18% de los encuestados no votaría por ninguno de los postulantes o lo haría en blanco. “Esto puede variar producto de la campaña y contracampaña. Aquí quien tiene mejor equipo de contracampaña es el que tiene mayor ventaja de ganar. Es quien reacciona rápido, de forma contundente y demoledora. No siempre la percepción es la verdad, por eso una contracampaña tiene que responderse de manera rápida y contundente. No se trata del mejor indudablemente, sino de quien cometa menos errores y sepa responder a los ataques fundados o infundados”, destacó.n</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>https://eltiempo.pe/local/minivan-queda-al-borde-de-un-abismo-en-la-carretera-canchaque-huancabamba/</t>
+          <t>https://eltiempo.pe/local/asi-van-los-candidatos-a-falta-de-un-mes-para-elecciones/</t>
         </is>
       </c>
     </row>
@@ -1352,17 +1352,17 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Fiesta termina con una mujer fallecida</t>
+          <t>Miniván queda al borde de un abismo en la carretera Canchaque -Huancabamba</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Una fiesta terminó en tragedia en la urbanización Las Casuarinas II Etapa, en el distrito Veintiséis de Octubre , luego de que una joven de nacionalidad colombiana perdiera la vida tras caer desde un tragaluz del tercer piso de un inmueble hacia el segundo nivel. La víctima fue identificada como Juliet Alisson Zambrano Fino, de 21 años de edad. PUEDES LEER ► FEN asusta a la banca privada El hecho ocurrió durante una reunión social y las circunstancias de la caída son materia de investigación por parte de la Policía. De acuerdo con información preliminar, una de las hipótesis que manejan las autoridades es que la joven habría sido presuntamente arrojada por un tragaluz, desde donde terminó cayendo hasta el segundo piso del inmueble. Sin embargo, esta versión todavía deberá ser corroborada mediante las diligencias policiales, pericias y demás elementos que permitan determinar qué ocurrió exactamente antes de la caída. SIN SIGNOS VITALES Tras conocerse el hecho, personal de Serenazgo del distrito Veintiséis de Octubre y una ambulancia del SAMU Piura llegaron hasta el lugar de la tragedia para brindar atención a la víctima. No obstante, los equipos de emergencia encontraron a la joven sin signos vitales. En el lugar también se encontraba un ciudadano extranjero, quien, visiblemente afectado y entre lágrimas, solicitaba ayuda para la mujer. RECOPILAN INFORMACIÓN Agentes de la Policía Nacional acudieron posteriormente a la escena para realizar las primeras diligencias, verificar las condiciones del inmueble y recopilar información que permita reconstruir los momentos previos y posteriores al fatal incidente. Las autoridades deberán determinar si la caída se produjo accidentalmente o si existió la intervención de otra persona. Para ello, se vienen recogiendo testimonios de quiénes participaron en la fiesta y de otros posibles testigos, además de realizarse las pericias correspondientes. El cuerpo de Juliet Alisson Zambrano Fino fue trasladado a la morgue de Piura, donde se realizarán los procedimientos establecidos por ley. INVESTIGACIONES Mientras avanzan las investigaciones, el caso ha generado preocupación entre los vecinos de Las Casuarinas. La Policía busca establecer las circunstancias exactas de la muerte y, de corresponder, identificar a los responsables y determinar las responsabilidades que establezca la investigación.</t>
+          <t>Unos 12 pasajeros se salvaron de caer a un abismo de aproximadamente 200 metros luego de que una miniván de una empresa de transporte sufriera un accidente en la carretera Canchaque-Huancabamba, en el sector Las Minas. Según información preliminar, la unidad terminó volcada y quedó peligrosamente cerca del precipicio, generando momentos de angustia entre los pasajeros, entre ellos algunos menores de edad, quienes temieron lo peor. Pese a la violencia del accidente, los ocupantes solo habrían sufrido algunos golpes, además del fuerte susto provocado por el incidente. Hasta el momento no se han reportado oficialmente personas con lesiones de consideración. EL EQUIPAJE El accidente también ocasionó la caída de algunos equipajes que eran transportados en la parte superior de la miniván, los cuales algunos habrían terminado en el fondo del abismo. De acuerdo con versiones preliminares, no se descarta que el vehículo haya sufrido algún desperfecto mecánico antes de producirse el accidente. Sin embargo, esta posibilidad deberá ser determinada mediante las investigaciones correspondientes. Asimismo, las autoridades realizan las diligencias para establecer las causas exactas del siniestro y determinar las condiciones en las que circulaba la unidad. Cabe mencionar que el hecho vuelve a poner en evidencia el peligro de transitar por esta vía, caracterizada por sus pronunciadas pendientes y zonas de profundo precipicio.</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>https://eltiempo.pe/local/fiesta-termina-con-una-mujer-fallecida/</t>
+          <t>https://eltiempo.pe/local/minivan-queda-al-borde-de-un-abismo-en-la-carretera-canchaque-huancabamba/</t>
         </is>
       </c>
     </row>
@@ -1377,17 +1377,17 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Choque de autos derriba poste</t>
+          <t>Fiesta termina con una mujer fallecida</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Un violento accidente de tránsito entre dos automóviles se registró ayer en horas de la mañana en la avenida Universitaria de Piura, a la altura del Fundo Vite. PUEDES LEER ► “Monstruo de las 10 cabezas” Según información preliminar, uno de los vehículos tras el choque habría también impactado contra un poste que no sería de tendido eléctrico, provocando que la estructura se desplomara y terminara cayendo sobre el otro automóvil. Los vehículos permanecieron en la zona del accidente, mientras efectivos de la Policía Nacional acudieron para realizar las diligencias correspondientes y determinar las circunstancias en que ocurrió el hecho. Hasta el cierre de edición, no se informó oficialmente sobre personas heridas como consecuencia del accidente. Cabe mencionar que el accidente generó preocupación entre los conductores que transitaban por este importante tramo de la avenida Universitaria.</t>
+          <t>Una fiesta terminó en tragedia en la urbanización Las Casuarinas II Etapa, en el distrito Veintiséis de Octubre , luego de que una joven de nacionalidad colombiana perdiera la vida tras caer desde un tragaluz del tercer piso de un inmueble hacia el segundo nivel. La víctima fue identificada como Juliet Alisson Zambrano Fino, de 21 años de edad. PUEDES LEER ► FEN asusta a la banca privada El hecho ocurrió durante una reunión social y las circunstancias de la caída son materia de investigación por parte de la Policía. De acuerdo con información preliminar, una de las hipótesis que manejan las autoridades es que la joven habría sido presuntamente arrojada por un tragaluz, desde donde terminó cayendo hasta el segundo piso del inmueble. Sin embargo, esta versión todavía deberá ser corroborada mediante las diligencias policiales, pericias y demás elementos que permitan determinar qué ocurrió exactamente antes de la caída. SIN SIGNOS VITALES Tras conocerse el hecho, personal de Serenazgo del distrito Veintiséis de Octubre y una ambulancia del SAMU Piura llegaron hasta el lugar de la tragedia para brindar atención a la víctima. No obstante, los equipos de emergencia encontraron a la joven sin signos vitales. En el lugar también se encontraba un ciudadano extranjero, quien, visiblemente afectado y entre lágrimas, solicitaba ayuda para la mujer. RECOPILAN INFORMACIÓN Agentes de la Policía Nacional acudieron posteriormente a la escena para realizar las primeras diligencias, verificar las condiciones del inmueble y recopilar información que permita reconstruir los momentos previos y posteriores al fatal incidente. Las autoridades deberán determinar si la caída se produjo accidentalmente o si existió la intervención de otra persona. Para ello, se vienen recogiendo testimonios de quiénes participaron en la fiesta y de otros posibles testigos, además de realizarse las pericias correspondientes. El cuerpo de Juliet Alisson Zambrano Fino fue trasladado a la morgue de Piura, donde se realizarán los procedimientos establecidos por ley. INVESTIGACIONES Mientras avanzan las investigaciones, el caso ha generado preocupación entre los vecinos de Las Casuarinas. La Policía busca establecer las circunstancias exactas de la muerte y, de corresponder, identificar a los responsables y determinar las responsabilidades que establezca la investigación.</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>https://eltiempo.pe/local/choque-de-autos-derriba-poste/</t>
+          <t>https://eltiempo.pe/local/fiesta-termina-con-una-mujer-fallecida/</t>
         </is>
       </c>
     </row>
@@ -1402,17 +1402,17 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>FEN asusta a la banca privada</t>
+          <t>Choque de autos derriba poste</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>El impacto del Fenómeno El Niño (FEN) en el terreno económico también se sentirá en los créditos a las pequeñas y medianas empresas relacionadas a los sectores primarios de la economía como son la pesca y agricultura. PUEDES LEER ► ProInversión y Marina de Guerra evaluarán proyectos de inversión privada sobre terrenos y bienes navales De acuerdo a los especialistas consultados, algunas empresas financieras podrían reforzar sus criterios para el otorgamiento de préstamos a los pequeños empresarios, con la finalidad de prevenir problemas de morosidad. “Los créditos asociados a personas que se desempeñan en esos sectores van a tener probablemente dificultades para afrontar sus deudas. Eso es algo que ya vimos en períodos pasados del FEN como en el 2023 y 2017” , comentó Stephani Maita, economista senior del Instituto Peruano de Economía (IPE). Explica que el impacto del FEN en el agro y pesca se relaciona en un primer momento con la pérdida del empleo. “Un tercio del empleo total en la región está vinculado al sector agrícola entonces las familias que tengan actividades vinculadas a este sector y tengan préstamos probablemente van a tener dificultades para afrontar sus deudas. Lo mismo con las empresas. A esto también se va el efecto por los precios al alza. Potencialmente podría terminar afectando la calidad de las carteras de créditos ”, enfatizó. Expectativas De otro lado, Maita señala que pese a la amenaza del fenómeno natural que se avecina, todavía hay expectativas positivas en la economía nacional. “El Banco Central de Reserva publicó una encuesta de perspectivas sobre el mercado de créditos tanto desde el lado de la oferta, es decir la perspectiva de los bancos y entidades financieras, como desde la demanda que es más desde los usuarios que solicitan los créditos. Por el lado de la demanda se encontraba que la perspectiva era favorable en la medida que la actividad económica en general, mas allá de los sectores primarios, goza de salud y está creciendo de forma importante”, aseveró Maita. Sin embargo, por el lado de las empresas existe un mayo grado de cautela sobre a quién le otorgan los préstamos con la finalidad de evitar el aumento de la morosidad. “Las empresas ya están previendo reforzar algunos criterios para otorgar créditos considerando los eventos climáticos que van a afectar, probablemente, en mayor medida los segmentos de las carteras más pequeñas, hablamos de microempresas, medianas y pequeñas empresas, las cuales son las que han registrado las mayores dificultades para afrontar sus créditos en el pasado”, manifestó Maita. Criterios Desde su punto de vista los nuevos requisitos implica un examen más exhaustivo del cliente que llega a solicitar el financiamiento. “Se refiere a otorgar créditos de menor tamaño, con plazos más extensos para que las cuotas sean un poco más pequeñas o quizás hacer una evaluación más minuciosa respecto de los ingresos de las empresas o que tanta exposición tienen a este tipo de fenómenos dependiendo de las actividades en las que se desempeñan. Por ejemplo, una empresa dedicada a la agroexportación probablemente será mucho más golpeada por el fenómeno climático frente a una empresa de transporte. Igual esta última va a sufrir algunos estragos por las lluvias, pero ese impacto es considerablemente menor frente a una empresa que se desempeña en agricultura. Agrega que en este punto los bancos tienden a elegir un poco mejor o cambiar un poco sus decisiones de dación de créditos para evitar exponerse a potenciales impagos.</t>
+          <t>Un violento accidente de tránsito entre dos automóviles se registró ayer en horas de la mañana en la avenida Universitaria de Piura, a la altura del Fundo Vite. PUEDES LEER ► “Monstruo de las 10 cabezas” Según información preliminar, uno de los vehículos tras el choque habría también impactado contra un poste que no sería de tendido eléctrico, provocando que la estructura se desplomara y terminara cayendo sobre el otro automóvil. Los vehículos permanecieron en la zona del accidente, mientras efectivos de la Policía Nacional acudieron para realizar las diligencias correspondientes y determinar las circunstancias en que ocurrió el hecho. Hasta el cierre de edición, no se informó oficialmente sobre personas heridas como consecuencia del accidente. Cabe mencionar que el accidente generó preocupación entre los conductores que transitaban por este importante tramo de la avenida Universitaria.</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>https://eltiempo.pe/local/fen-asusta-a-la-banca-privada/</t>
+          <t>https://eltiempo.pe/local/choque-de-autos-derriba-poste/</t>
         </is>
       </c>
     </row>
